--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -488,7 +488,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar.</t>
+          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar.</t>
         </is>
       </c>
     </row>
@@ -786,6 +786,87 @@
       <c r="E13" s="2" t="inlineStr">
         <is>
           <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Clinia (Reservo)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Otro: Salud (PHR paciente)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zoomtecnologico.com/2026/09/16/clinia-historia-medico/</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>MiRedSalud (RedSalud)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Otro: Salud (portal de red de clínicas)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.redsalud.cl/noticias/miredsalud-lanza-su-nueva-app-movil-tu-salud-ahora-mas-cerca-que-nunca</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Otro: Salud (asistente IA / orientación médica)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>https://mediko.cl</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc.</t>
         </is>
       </c>
     </row>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar.</t>
+          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar. [Iter. 3] Reservo (fundada 2015; opera en Chile, México y Argentina) reporta &gt;36.500 profesionales y centros y ~14 millones de reservas al año (chocale.cl, sep-2026): base de distribución potencial enorme. No se pudo confirmar Clinia en una segunda búsqueda; sigue pendiente su sitio oficial.</t>
         </is>
       </c>
     </row>
@@ -867,6 +867,33 @@
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Mi Bupa (Bupa / Integramédica / Cruz Blanca)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Otro: Salud (portal de red de clínicas y aseguradora)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>https://chocale.cl/2020/10/app-mi-bupa-integramedica-cruz-blanca/</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>[SUSTITUTO PARCIAL · Chile] App lanzada oct-2020 para pacientes de Integramédica y Clínica Bupa y afiliados de Isapre Cruz Blanca. Incluye 'Carpeta Personal de Salud' que consolida exámenes (Integramédica), cirugías (Clínica Bupa) y licencias (Cruz Blanca). Limitación: solo datos del grupo Bupa; no es portable ni consolida otras instituciones. Relevante porque une prestador + aseguradora, el caso que Anamnesis quiere evitar o controlar (etapa B con aseguradoras).</t>
         </is>
       </c>
     </row>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -8,6 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competidores" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funcionalidades" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="func_norm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tabla_frecuencia" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Competidores'!$A$1:$E$13</definedName>
@@ -57,11 +61,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -428,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -436,6 +443,9 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="100" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,6 +474,21 @@
           <t>Información relevante</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Revisado (vuelta actual)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Contador de loops</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Última revisión</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -491,6 +516,19 @@
           <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar.</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -518,6 +556,19 @@
           <t>[DIRECTO · Chile · etapa A] Fundada 2019 por Diego Ibarra, Andrés Fantuzzi y Gabriel Zamora. Lanzada mar-2021 en App Store y Play Store con 1.200 usuarios; planeaba nueva versión jul-2021 y ronda de US$500 mil. Objetivo: llevar el historial en el celular, acceso en emergencias, médico puede ingresar datos con consentimiento. Estado actual NO verificado (posible app inactiva). URL es la nota de prensa; sitio oficial por confirmar.</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -545,6 +596,19 @@
           <t>[REGIONAL · México] Historial por perfil familiar, alergias, vacunas, recetas digitales, gráficas de evolución, agendamiento, compartir con profesionales. Gratis en App Store MX. Sin evidencia de uso en Chile. Cubre parte de la etapa C (familia).</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -572,6 +636,19 @@
           <t>[REGIONAL · Argentina · débil] App para cargar antecedentes médicos propios. Única referencia: nota de opinión en grupoanimal.mx sin fecha verificada. Estado y sitio por confirmar.</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -599,6 +676,19 @@
           <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B.</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -626,6 +716,19 @@
           <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain.</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -653,6 +756,19 @@
           <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain.</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -680,6 +796,19 @@
           <t>[BLOCKCHAIN · Reino Unido · INACTIVO] Londres, 2017, Ethereum, con telemedicina. Piloto según registro de la UE (2020). Tracxn/PitchBook lo marcan fuera de operación (ago-2025). Solo caso de aprendizaje: no cuenta como competidor activo.</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -707,6 +836,19 @@
           <t>[ADYACENTE · global] Agrega registros clínicos vía FHIR; &gt;500 instituciones conectadas en EE.UU. (2018). Sin evidencia de disponibilidad en Chile. Incluida en el dispositivo. Amenaza si FHIR/IPS-CL se adopta en Chile.</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -734,6 +876,19 @@
           <t>[ADYACENTE · global] Lanzado 7-ene-2026. Conecta registros médicos; conectores solo en EE.UU. Dentro de suscripción del asistente. Fija la expectativa de consultar y resumir el historial.</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -761,6 +916,19 @@
           <t>[ADYACENTE · global] Lanzado 11-ene-2026. Conectores solo en EE.UU., planes Pro/Max. Nota: producto de Anthropic, conflicto de interés al evaluarlo.</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -788,6 +956,19 @@
           <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones.</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -815,6 +996,19 @@
           <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar.</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -842,6 +1036,19 @@
           <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis).</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -867,6 +1074,19 @@
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -874,4 +1094,5680 @@
   <autoFilter ref="A1:E13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Competidor</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Categoría/Capacidad</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Funcionalidades</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Detalle</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Mercados</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Fuente / confianza</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Meedika</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Gestión de documentos médicos</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Almacena documentos clínicos del usuario en la app.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nota de prensa (Diario Estrategia, sep-2024); sitio no verificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Meedika</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Importar solicitudes</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Importa solicitudes (órdenes) médicas a la app.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nota de prensa (Diario Estrategia, sep-2024); sitio no verificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Meedika</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Emergencia</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SOS con alergias y medicación</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ficha de emergencia con alergias y medicación accesible rápidamente.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nota de prensa (Diario Estrategia, sep-2024); sitio no verificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Meedika</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Citas y agenda</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Calendario de citas</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Calendario para organizar citas médicas.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nota de prensa (Diario Estrategia, sep-2024); sitio no verificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Meedika</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Medicación y recordatorios</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Recordatorios</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Recordatorios de citas/medicación.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nota de prensa (Diario Estrategia, sep-2024); sitio no verificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Meedika</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Compartir con profesionales elegidos</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>El usuario decide con qué profesionales comparte su información.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nota de prensa (Diario Estrategia, sep-2024); sitio no verificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Infomed</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Historial médico en el celular</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Centraliza el historial médico personal en el móvil.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nota de prensa (DF, 2021); estado actual no verificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Infomed</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Emergencia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Acceso en emergencias</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Acceso a datos clave del paciente en emergencias.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nota de prensa (DF, 2021); estado actual no verificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Infomed</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ingreso de datos por el médico con consentimiento</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>El médico puede ingresar datos al historial con autorización del paciente.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nota de prensa (DF, 2021); estado actual no verificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Familia y dependientes</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Perfiles familiares</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Historial por perfil para cada miembro de la familia.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ficha App Store México (desde ficha en base); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Alergias y vacunas</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Registro de alergias y vacunas.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ficha App Store México (desde ficha en base); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Recetas digitales</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Guarda recetas digitales.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ficha App Store México (desde ficha en base); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Gráficas de evolución</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Gráficas de evolución de indicadores de salud.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ficha App Store México (desde ficha en base); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Citas y agenda</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Agendamiento</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Agenda de citas.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ficha App Store México (desde ficha en base); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Compartir con profesionales</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Compartir información con profesionales de salud.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ficha App Store México (desde ficha en base); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Clingot</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Carga de antecedentes médicos propios</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>El usuario registra sus antecedentes médicos en la app.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nota de opinión grupoanimal.mx; confianza baja</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Clingot</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Emergencia</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Acceso a historial ante urgencias (según nota de opinión)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Disponibilidad del historial en situaciones de atención.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nota de opinión grupoanimal.mx; confianza baja</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Healfies</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Carpetas y etiquetas</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Organiza registros con carpetas y etiquetas.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fuentes 2015-2016; estado actual no verificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Healfies</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Línea de tiempo de salud</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Línea de tiempo con medicación, exámenes, citas y dieta.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fuentes 2015-2016; estado actual no verificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Healfies</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Compartir con familia o profesionales</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Comparte registros con familiares o profesionales.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fuentes 2015-2016; estado actual no verificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Healfies</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Multiplataforma</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Disponible en web, iOS y Android.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fuentes 2015-2016; estado actual no verificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Agregación de registros de hospitales</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Reúne registros de hospitales, resultados de laboratorio y datos genómicos.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Búsqueda web (MIT Solve, HIT Consultant, Blockonomi); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Integración con wearables y apps</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Búsqueda web (MIT Solve, HIT Consultant, Blockonomi); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Herramientas de seguimiento y progreso</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Búsqueda web (MIT Solve, HIT Consultant, Blockonomi); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Coaching de salud con IA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Coaching personalizado con IA.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Búsqueda web (MIT Solve, HIT Consultant, Blockonomi); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Blockchain para datos de salud</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Búsqueda web (MIT Solve, HIT Consultant, Blockonomi); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Incentivos y monetización de datos</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Recompensas y monetización de datos</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>El usuario puede agregar y monetizar sus datos; recompensas en cripto.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Búsqueda web (MIT Solve, HIT Consultant, Blockonomi); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Neith (panel empresarial)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Analítica poblacional on-chain; integrada con Epic, Cerner, Meditech y Allscripts (B2B).</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Búsqueda web (MIT Solve, HIT Consultant, Blockonomi); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Blockchain Panacea</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Búsqueda web (KED Global, MDPI); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Medipass (PHR)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Permite compilar datos de vida/salud, gestionarlos y pasarlos a instituciones médicas.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Búsqueda web (KED Global, MDPI); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Medipass seguros</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Búsqueda web (KED Global, MDPI); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Control de uso de datos</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>El usuario decide si sus registros se usan para análisis de big data.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Búsqueda web (KED Global, MDPI); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Transferencia a instituciones médicas</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Traspaso de registros a hospitales.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Búsqueda web (KED Global, MDPI); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Health Passport</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Versión digital de los registros con acceso por móvil o web.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Digital Health, HTN); INACTIVO, solo aprendizaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Registro de accesos en blockchain</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Digital Health, HTN); INACTIVO, solo aprendizaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Acceso temporal otorgado por el paciente</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Acceso de clínicos limitado en el tiempo.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Digital Health, HTN); INACTIVO, solo aprendizaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Telemedicina y atención remota</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MyClinic: videoconsulta con médico general</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Teleconsultas con GP.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Digital Health, HTN); INACTIVO, solo aprendizaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Pago con criptomoneda (MedTokens)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pago de consultas con token.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Digital Health, HTN); INACTIVO, solo aprendizaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Registros clínicos de varias instituciones</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Vista central de alergias, condiciones, vacunas, laboratorio, medicación, procedimientos y signos vitales.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Búsqueda web (iMore, CultOfMac); registros clínicos solo EE.UU., Reino Unido y Canadá, no Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Alergias, vacunas, laboratorio y medicación</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Información clínica unificada.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Búsqueda web (iMore, CultOfMac); registros clínicos solo EE.UU., Reino Unido y Canadá, no Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Medicación y recordatorios</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Recordatorios de medicación</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Recordatorios desde el app.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Búsqueda web (iMore, CultOfMac); registros clínicos solo EE.UU., Reino Unido y Canadá, no Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Compartir con médicos y cercanos</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Permite compartir información con médicos, familia y amistades.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Búsqueda web (iMore, CultOfMac); registros clínicos solo EE.UU., Reino Unido y Canadá, no Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Cifrado y bloqueo biométrico</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Búsqueda web (iMore, CultOfMac); registros clínicos solo EE.UU., Reino Unido y Canadá, no Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Integración con datos del dispositivo</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Datos de pasos, sueño, peso junto a registros.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Búsqueda web (iMore, CultOfMac); registros clínicos solo EE.UU., Reino Unido y Canadá, no Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Interpretación de resultados de laboratorio</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Explica resultados complejos en lenguaje simple.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Tom's Guide, AlternativeTo); conexión de registros solo EE.UU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Resumen de indicaciones de cuidado</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Resume instrucciones de atención.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Tom's Guide, AlternativeTo); conexión de registros solo EE.UU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Preparación de preguntas para la cita</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Prepara preguntas para el médico.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Tom's Guide, AlternativeTo); conexión de registros solo EE.UU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Conexión de registros médicos (b.well) y Apple Health</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Conexión de historiales electrónicos y apps como Apple Health, MyFitnessPal, Peloton.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Tom's Guide, AlternativeTo); conexión de registros solo EE.UU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Conversaciones de salud aisladas</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Tom's Guide, AlternativeTo); conexión de registros solo EE.UU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Conectores HealthEx y Function</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Acceso a resultados y registros de salud (beta, Pro/Max, EE.UU.).</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Búsqueda web (ERP Today, TechTarget). Conflicto de interés: producto de Anthropic</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Integración Apple Health / Health Connect</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Integración beta en apps iOS/Android.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Búsqueda web (ERP Today, TechTarget). Conflicto de interés: producto de Anthropic</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Resumen de historia médica</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Resume el historial del usuario.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Búsqueda web (ERP Today, TechTarget). Conflicto de interés: producto de Anthropic</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Explicación de resultados</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Explica exámenes en lenguaje simple.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Búsqueda web (ERP Today, TechTarget). Conflicto de interés: producto de Anthropic</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Preparación de preguntas para citas</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Prepara preguntas para el médico.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Búsqueda web (ERP Today, TechTarget). Conflicto de interés: producto de Anthropic</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Detección de patrones</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Detecta patrones entre métricas de salud y fitness.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Búsqueda web (ERP Today, TechTarget). Conflicto de interés: producto de Anthropic</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Citas y agenda</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Reserva de horas</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Reserva de horas en la institución.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ficha App Store; ya registrado en el listado</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Historial de la institución</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Ve historial de esa institución.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Ficha App Store; ya registrado en el listado</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Familia y dependientes</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Vincular familiar</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Vincula familiares a la cuenta.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ficha App Store; ya registrado en el listado</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Clinia (Reservo)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Centralización de recetas, diagnósticos y laboratorios</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Reúne recetas, diagnósticos y laboratorios en un solo lugar.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Zoomtecnológico, Chocale); app anunciada sep-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Clinia (Reservo)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Alimentación desde la red Reservo</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Datos desde profesionales/centros que usan Reservo (fichas clínicas, agenda, telemedicina).</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Zoomtecnológico, Chocale); app anunciada sep-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MiRedSalud (RedSalud)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Información clínica y servicios</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Acceso a información clínica de la red.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Nota de prensa RedSalud (dic-2025); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MiRedSalud (RedSalud)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Familia y dependientes</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Historial propio y familiar</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Guardar y administrar historial propio y familiar.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Nota de prensa RedSalud (dic-2025); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Orientación médica inmediata con IA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Orientación médica instantánea mediante IA.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Descubre.vc, Salud Digital); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Interpretación de exámenes</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Interpreta exámenes de laboratorio.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Descubre.vc, Salud Digital); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Órdenes médicas digitales</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Descarga/genera órdenes médicas digitales.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Descubre.vc, Salud Digital); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Centralización de registros y monitoreo</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Centralizar registros y monitoreo desde el móvil.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Descubre.vc, Salud Digital); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Modelo freemium, suscripción y pago por servicio</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Planes para personas y empresas.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Descubre.vc, Salud Digital); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Competidor</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Categoría/Capacidad</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Funcionalidad (Normalizada)</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Detalle</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Mercados</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Citas y agenda</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Calendario de citas médicas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Agenda de citas.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Meedika</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Citas y agenda</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Calendario de citas médicas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Calendario para organizar citas médicas.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Citas y agenda</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Reserva de citas médicas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Reserva de horas en la institución.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Permite compartir información con médicos, familia y amistades.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Healfies</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Comparte registros con familiares o profesionales.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Traspaso de registros a hospitales.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Compartir información con profesionales de salud.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Acceso de clínicos limitado en el tiempo.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Meedika</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>El usuario decide con qué profesionales comparte su información.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gestión de consentimiento sobre uso de datos</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>El usuario decide si sus registros se usan para análisis de big data.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Infomed</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ingreso de datos por profesional con consentimiento</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>El médico puede ingresar datos al historial con autorización del paciente.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Clingot</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Emergencia</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ficha de emergencia (alergias y medicación)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Disponibilidad del historial en situaciones de atención.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Infomed</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Emergencia</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ficha de emergencia (alergias y medicación)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Acceso a datos clave del paciente en emergencias.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Meedika</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Emergencia</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ficha de emergencia (alergias y medicación)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ficha de emergencia con alergias y medicación accesible rápidamente.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Familia y dependientes</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Perfiles familiares / dependientes</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Vincula familiares a la cuenta.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Familia y dependientes</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Perfiles familiares / dependientes</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Historial por perfil para cada miembro de la familia.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MiRedSalud (RedSalud)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Familia y dependientes</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Perfiles familiares / dependientes</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Guardar y administrar historial propio y familiar.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Clinia (Reservo)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Almacenamiento de documentos médicos</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Reúne recetas, diagnósticos y laboratorios en un solo lugar.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Healfies</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Almacenamiento de documentos médicos</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Organiza registros con carpetas y etiquetas.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Meedika</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Almacenamiento de documentos médicos</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Almacena documentos clínicos del usuario en la app.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Almacenamiento de recetas</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Guarda recetas digitales.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Importación de órdenes/solicitudes médicas</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Descarga/genera órdenes médicas digitales.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Meedika</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Importación de órdenes/solicitudes médicas</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Importa solicitudes (órdenes) médicas a la app.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Historial institucional (solo datos de la propia red)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ve historial de esa institución.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MiRedSalud (RedSalud)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Historial institucional (solo datos de la propia red)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Acceso a información clínica de la red.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Información clínica unificada.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Clingot</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>El usuario registra sus antecedentes médicos en la app.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Infomed</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Centraliza el historial médico personal en el móvil.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Permite compilar datos de vida/salud, gestionarlos y pasarlos a instituciones médicas.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Centralizar registros y monitoreo desde el móvil.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Healfies</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Línea de tiempo de salud</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Línea de tiempo con medicación, exámenes, citas y dieta.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Registro de alergias y vacunas</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Registro de alergias y vacunas.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Incentivos y monetización de datos</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Recompensas / monetización de datos del usuario</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>El usuario puede agregar y monetizar sus datos; recompensas en cripto.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Coaching de salud con IA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Coaching personalizado con IA.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Detección de patrones en métricas de salud con IA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Detecta patrones entre métricas de salud y fitness.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Interpretación de exámenes con IA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Explica resultados complejos en lenguaje simple.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Interpretación de exámenes con IA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Explica exámenes en lenguaje simple.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Interpretación de exámenes con IA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Interpreta exámenes de laboratorio.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Orientación médica con IA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Orientación médica instantánea mediante IA.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Preparación de consultas médicas con IA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Prepara preguntas para el médico.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Preparación de consultas médicas con IA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Prepara preguntas para el médico.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Resumen de historial con IA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Resume instrucciones de atención.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Resumen de historial con IA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Resume el historial del usuario.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Agregación de registros de múltiples instituciones</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Vista central de alergias, condiciones, vacunas, laboratorio, medicación, procedimientos y signos vitales.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Agregación de registros de múltiples instituciones</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Conexión de historiales electrónicos y apps como Apple Health, MyFitnessPal, Peloton.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Agregación de registros de múltiples instituciones</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Acceso a resultados y registros de salud (beta, Pro/Max, EE.UU.).</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Clinia (Reservo)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Agregación de registros de múltiples instituciones</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Datos desde profesionales/centros que usan Reservo (fichas clínicas, agenda, telemedicina).</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Agregación de registros de múltiples instituciones</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Reúne registros de hospitales, resultados de laboratorio y datos genómicos.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Analítica poblacional B2B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Analítica poblacional on-chain; integrada con Epic, Cerner, Meditech y Allscripts (B2B).</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Healfies</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Disponible en web, iOS y Android.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Versión digital de los registros con acceso por móvil o web.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Integración beta en apps iOS/Android.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Medicación y recordatorios</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Recordatorios de medicación y citas</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Recordatorios desde el app.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Meedika</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Medicación y recordatorios</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Recordatorios de medicación y citas</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Recordatorios de citas/medicación.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Gráficas de evolución de indicadores</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Gráficas de evolución de indicadores de salud.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Datos de pasos, sueño, peso junto a registros.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Panel de seguimiento de salud y bienestar</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Cifrado y control de acceso biométrico</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Privacidad reforzada para datos de salud</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Modelo freemium y suscripción</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Planes para personas y empresas.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Pagos con criptomoneda</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Pago de consultas con token.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Telemedicina y atención remota</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Teleconsulta con profesionales</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Teleconsultas con GP.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Categoría/Capacidad</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Funcionalidad (Normalizada)</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Meedika</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Infomed</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Clingot</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Healfies</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Clinia (Reservo)</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>MiRedSalud (RedSalud)</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Total repeticiones</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Citas y agenda</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Calendario de citas médicas</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2">
+        <f>COUNTIF(C2:Q2,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Citas y agenda</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reserva de citas médicas</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3">
+        <f>COUNTIF(C3:Q3,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4">
+        <f>COUNTIF(C4:Q4,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Gestión de consentimiento sobre uso de datos</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5">
+        <f>COUNTIF(C5:Q5,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ingreso de datos por profesional con consentimiento</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6">
+        <f>COUNTIF(C6:Q6,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Emergencia</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ficha de emergencia (alergias y medicación)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7">
+        <f>COUNTIF(C7:Q7,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Familia y dependientes</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Perfiles familiares / dependientes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8">
+        <f>COUNTIF(C8:Q8,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Almacenamiento de documentos médicos</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9">
+        <f>COUNTIF(C9:Q9,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Almacenamiento de recetas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10">
+        <f>COUNTIF(C10:Q10,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Importación de órdenes/solicitudes médicas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11">
+        <f>COUNTIF(C11:Q11,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Historial institucional (solo datos de la propia red)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12">
+        <f>COUNTIF(C12:Q12,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13">
+        <f>COUNTIF(C13:Q13,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Línea de tiempo de salud</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14">
+        <f>COUNTIF(C14:Q14,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Registro de alergias y vacunas</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15">
+        <f>COUNTIF(C15:Q15,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Incentivos y monetización de datos</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Recompensas / monetización de datos del usuario</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16">
+        <f>COUNTIF(C16:Q16,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Coaching de salud con IA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17">
+        <f>COUNTIF(C17:Q17,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Detección de patrones en métricas de salud con IA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18">
+        <f>COUNTIF(C18:Q18,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Interpretación de exámenes con IA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19">
+        <f>COUNTIF(C19:Q19,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Orientación médica con IA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20">
+        <f>COUNTIF(C20:Q20,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Preparación de consultas médicas con IA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21">
+        <f>COUNTIF(C21:Q21,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Resumen de historial con IA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22">
+        <f>COUNTIF(C22:Q22,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Agregación de registros de múltiples instituciones</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23">
+        <f>COUNTIF(C23:Q23,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Analítica poblacional B2B</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24">
+        <f>COUNTIF(C24:Q24,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25">
+        <f>COUNTIF(C25:Q25,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26">
+        <f>COUNTIF(C26:Q26,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27">
+        <f>COUNTIF(C27:Q27,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Medicación y recordatorios</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Recordatorios de medicación y citas</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28">
+        <f>COUNTIF(C28:Q28,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Gráficas de evolución de indicadores</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29">
+        <f>COUNTIF(C29:Q29,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30">
+        <f>COUNTIF(C30:Q30,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Panel de seguimiento de salud y bienestar</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31">
+        <f>COUNTIF(C31:Q31,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32">
+        <f>COUNTIF(C32:Q32,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cifrado y control de acceso biométrico</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33">
+        <f>COUNTIF(C33:Q33,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Privacidad reforzada para datos de salud</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34">
+        <f>COUNTIF(C34:Q34,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Modelo freemium y suscripción</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R35">
+        <f>COUNTIF(C35:Q35,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pagos con criptomoneda</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36">
+        <f>COUNTIF(C36:Q36,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37">
+        <f>COUNTIF(C37:Q37,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Telemedicina y atención remota</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Teleconsulta con profesionales</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38">
+        <f>COUNTIF(C38:Q38,"✓")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="140" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Reglas del loop de revisión (cada 2 h, ~4 competidores por iteración)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1. Elegir competidores con Revisado="No" ordenados por Contador de loops ascendente; los nuevos (celdas F/G vacías) van primero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2. Tras revisar: Revisado="Sí", actualizar Última revisión y añadir/actualizar filas en pestaña Funcionalidades (sin duplicar).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3. Si todos tienen Revisado="Sí": vuelta completa → Contador +1 a todos, Revisado="No" a todos, regenerar func_norm y tabla_frecuencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4. Competidor nuevo: revisarlo de inmediato; luego Contador = máximo de la lista (y Revisado="Sí") para no repetirlo hasta alcanzar al resto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5. Si una vuelta no encuentra funcionalidades nuevas, la siguiente iteración verifica y actualiza lo ya registrado (precio, estado, mercados).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6. Pestaña Funcionalidades = datos crudos con nombre del competidor; func_norm = nombre normalizado; tabla_frecuencia = cruce con ✓.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Vuelta 1 completada: 2026-10-07 (15 competidores). Varios sitios oficiales bloqueados por el proxy; ver columna Fuente/confianza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pendiente de verificar: fecha de lanzamiento de ChatGPT Health (ficha dice 7-ene-2026; búsqueda indica despliegue de registros médicos en EE.UU. jul-2026).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -558,7 +558,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -598,7 +598,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3286,6 +3286,422 @@
       <c r="F68" t="inlineStr">
         <is>
           <t>Búsqueda web (Descubre.vc, Salud Digital); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Infomed</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Seguridad y confianza tipo banca</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Almacenamiento seguro del historial con criterios de seguridad estrictos, comparable a apps bancarias.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>DF (2021); estado actual no verificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Infomed</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Revisión del historial por el médico</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>El médico puede revisar el historial e ingresar datos automáticamente.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>DF (2021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Infomed</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Educación del paciente sobre su enfermedad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Busca que el paciente aprenda sobre sus enfermedades y sea más autónomo.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>DF (2021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Medicación y recordatorios</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Bitácora de medicamentos y adherencia</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Registro de cada toma y control de adherencia; gestiona medicamentos propios y de familiares.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Búsqueda web (ficha App Store MX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Citas y agenda</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Búsqueda y agenda de médicos</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Busca profesionales y agenda citas desde la app.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Búsqueda web (ficha App Store MX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Documentos con buscador y filtros</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Guarda resultados de laboratorio, imágenes y PDFs; búsqueda y filtros.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Búsqueda web (ficha App Store MX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Compartir con cuidadores, maestros y profesionales</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Comparte información con cuidadores, maestros o profesionales de confianza.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Búsqueda web (ficha App Store MX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Clingot</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Carga de estudios, imágenes, indicaciones y notas</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Sube estudios, imágenes, indicaciones médicas y notas personales; accesible en consulta o por terceros en emergencias.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Búsqueda web (La Nación, grupoanimal.mx); confianza media</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Clingot</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Citas y agenda</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Directorio médico filtrable</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Directorio filtrable por obra social, especialidad, subespecialidad y cercanía.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Búsqueda web (La Nación)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Clingot</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Citas y agenda</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ubicación de centros médicos y farmacias</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Localiza centros médicos y farmacias.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Búsqueda web (La Nación)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Clingot</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Familia y dependientes</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Seguimiento de salud de hijos</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Los padres pueden monitorear la salud de hijos pequeños.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Búsqueda web (La Nación)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Clingot</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Valoración de profesionales</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Calificación de la atención de profesionales con autorización previa, compartible con otros usuarios.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Búsqueda web (La Nación)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Clingot</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Acceso móvil y de escritorio; funciones para médicos</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Android, iOS y escritorio; médicos acceden a historias digitalizadas, envían estudios e indicaciones y organizan agenda.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Búsqueda web (La Nación)</t>
         </is>
       </c>
     </row>
@@ -5288,24 +5704,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2">
         <f>COUNTIF(C2:Q2,"✓")</f>
         <v/>
@@ -5322,25 +5725,11 @@
           <t>Reserva de citas médicas</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3">
         <f>COUNTIF(C3:Q3,"✓")</f>
         <v/>
@@ -5362,19 +5751,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5390,12 +5776,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4">
         <f>COUNTIF(C4:Q4,"✓")</f>
         <v/>
@@ -5412,25 +5792,11 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5">
         <f>COUNTIF(C5:Q5,"✓")</f>
         <v/>
@@ -5447,25 +5813,11 @@
           <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6">
         <f>COUNTIF(C6:Q6,"✓")</f>
         <v/>
@@ -5492,23 +5844,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7">
         <f>COUNTIF(C7:Q7,"✓")</f>
         <v/>
@@ -5525,33 +5865,21 @@
           <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8">
         <f>COUNTIF(C8:Q8,"✓")</f>
         <v/>
@@ -5573,28 +5901,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9">
         <f>COUNTIF(C9:Q9,"✓")</f>
         <v/>
@@ -5611,25 +5927,11 @@
           <t>Almacenamiento de recetas</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10">
         <f>COUNTIF(C10:Q10,"✓")</f>
         <v/>
@@ -5651,19 +5953,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5685,29 +5974,16 @@
           <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12">
         <f>COUNTIF(C12:Q12,"✓")</f>
         <v/>
@@ -5724,36 +6000,26 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5775,25 +6041,11 @@
           <t>Línea de tiempo de salud</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14">
         <f>COUNTIF(C14:Q14,"✓")</f>
         <v/>
@@ -5810,25 +6062,11 @@
           <t>Registro de alergias y vacunas</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15">
         <f>COUNTIF(C15:Q15,"✓")</f>
         <v/>
@@ -5845,25 +6083,11 @@
           <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16">
         <f>COUNTIF(C16:Q16,"✓")</f>
         <v/>
@@ -5880,25 +6104,11 @@
           <t>Coaching de salud con IA</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17">
         <f>COUNTIF(C17:Q17,"✓")</f>
         <v/>
@@ -5915,25 +6125,11 @@
           <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18">
         <f>COUNTIF(C18:Q18,"✓")</f>
         <v/>
@@ -5950,15 +6146,6 @@
           <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5969,9 +6156,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5993,20 +6177,6 @@
           <t>Orientación médica con IA</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6028,15 +6198,6 @@
           <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6047,10 +6208,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21">
         <f>COUNTIF(C21:Q21,"✓")</f>
         <v/>
@@ -6067,15 +6224,6 @@
           <t>Resumen de historial con IA</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6086,10 +6234,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22">
         <f>COUNTIF(C22:Q22,"✓")</f>
         <v/>
@@ -6106,18 +6250,11 @@
           <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6133,14 +6270,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23">
         <f>COUNTIF(C23:Q23,"✓")</f>
         <v/>
@@ -6157,25 +6291,11 @@
           <t>Analítica poblacional B2B</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24">
         <f>COUNTIF(C24:Q24,"✓")</f>
         <v/>
@@ -6192,25 +6312,11 @@
           <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25">
         <f>COUNTIF(C25:Q25,"✓")</f>
         <v/>
@@ -6227,25 +6333,11 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26">
         <f>COUNTIF(C26:Q26,"✓")</f>
         <v/>
@@ -6262,29 +6354,16 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27">
         <f>COUNTIF(C27:Q27,"✓")</f>
         <v/>
@@ -6306,24 +6385,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28">
         <f>COUNTIF(C28:Q28,"✓")</f>
         <v/>
@@ -6340,25 +6406,11 @@
           <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29">
         <f>COUNTIF(C29:Q29,"✓")</f>
         <v/>
@@ -6375,25 +6427,11 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30">
         <f>COUNTIF(C30:Q30,"✓")</f>
         <v/>
@@ -6410,25 +6448,11 @@
           <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31">
         <f>COUNTIF(C31:Q31,"✓")</f>
         <v/>
@@ -6445,11 +6469,6 @@
           <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6465,13 +6484,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32">
         <f>COUNTIF(C32:Q32,"✓")</f>
         <v/>
@@ -6488,25 +6500,11 @@
           <t>Cifrado y control de acceso biométrico</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33">
         <f>COUNTIF(C33:Q33,"✓")</f>
         <v/>
@@ -6523,25 +6521,11 @@
           <t>Privacidad reforzada para datos de salud</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34">
         <f>COUNTIF(C34:Q34,"✓")</f>
         <v/>
@@ -6558,20 +6542,6 @@
           <t>Modelo freemium y suscripción</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6593,25 +6563,11 @@
           <t>Pagos con criptomoneda</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36">
         <f>COUNTIF(C36:Q36,"✓")</f>
         <v/>
@@ -6628,25 +6584,11 @@
           <t>Reclamos y trámites con seguros</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37">
         <f>COUNTIF(C37:Q37,"✓")</f>
         <v/>
@@ -6663,25 +6605,11 @@
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38">
         <f>COUNTIF(C38:Q38,"✓")</f>
         <v/>
@@ -6698,7 +6626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -6767,6 +6695,13 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Vuelta 2 (iter. 1): Meedika (sin cambios; sitio oficial y precio siguen sin verificar), Infomed, MediPlanner, Clingot revisados. Pendientes: Healfies, Patientory, MediBloc, Medicalchain, etc.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B.</t>
+          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B. [Vuelta 2] Lanzada simultáneamente en Brasil, Argentina y EE.UU.; permite compartir con no registrados vía clave por email. Sin novedades posteriores a 2016.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -713,12 +713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain.</t>
+          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain. [Vuelta 2] Sin noticias 2026 encontradas en búsqueda; sitio oficial bloqueado.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -753,12 +753,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain.</t>
+          <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain. [Vuelta 2] Panacea incluye DID, Append Only Log, IBC y PNFT; sin anuncios 2026 localizados.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -793,12 +793,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · Reino Unido · INACTIVO] Londres, 2017, Ethereum, con telemedicina. Piloto según registro de la UE (2020). Tracxn/PitchBook lo marcan fuera de operación (ago-2025). Solo caso de aprendizaje: no cuenta como competidor activo.</t>
+          <t>[BLOCKCHAIN · Reino Unido · INACTIVO] Londres, 2017, Ethereum, con telemedicina. Piloto según registro de la UE (2020). Tracxn/PitchBook lo marcan fuera de operación (ago-2025). Solo caso de aprendizaje: no cuenta como competidor activo. [Vuelta 2] Token MTN deslistado de Bitfinex el 26-mar-2021; sin hallazgos de actividad posterior.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3702,6 +3702,230 @@
       <c r="F81" t="inlineStr">
         <is>
           <t>Búsqueda web (La Nación)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Healfies</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Línea de tiempo ampliada: recetas, actividad física y dieta</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Registra notas de medicación, exámenes (laboratorio e imagen), actividad física, recetas, dieta y citas.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Baguete); lanzada en Brasil, Argentina y EE.UU. (2015); estado actual no verificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Healfies</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Red social con profesionales y familiares</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Interacción con médicos, dentistas, kinesiólogos, entrenadores y familiares dentro de la red.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Baguete)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Healfies</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Compartir con no registrados por clave segura</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Datos compartibles con personas sin cuenta mediante clave de acceso segura enviada por email.</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Baguete)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Autorización de acceso a proveedores con consentimiento</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>El usuario autoriza a proveedores a acceder y usar sus datos de salud.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Cryptopolitan); sitio bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Gestión de citas, recetas y archivos</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Administra fechas, prescripciones, archivos y citas desde la app.</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Newswire 2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Identidad descentralizada (DID)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Gestión de identificadores descentralizados en Panacea.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Búsqueda web (pkg.go.dev panacea-core)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Registro de huellas de datos (Append Only Log)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Almacena huellas de datos médicos en un registro de solo escritura, sin guardar datos clínicos en cadena.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Búsqueda web (pkg.go.dev panacea-core)</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -6702,6 +6926,13 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Vuelta 2 (iter. 2, 2026-10-07 16:08 UTC): Healfies, Patientory, MediBloc, Medicalchain revisados (+7 filas). Pendientes: Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas, Clinia, MiRedSalud, Mediko.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -833,12 +833,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Agrega registros clínicos vía FHIR; &gt;500 instituciones conectadas en EE.UU. (2018). Sin evidencia de disponibilidad en Chile. Incluida en el dispositivo. Amenaza si FHIR/IPS-CL se adopta en Chile.</t>
+          <t>[ADYACENTE · global] Agrega registros clínicos vía FHIR; &gt;500 instituciones conectadas en EE.UU. (2018). Sin evidencia de disponibilidad en Chile. Incluida en el dispositivo. Amenaza si FHIR/IPS-CL se adopta en Chile. [Vuelta 2] Sin disponibilidad de registros clínicos en Chile (solo EE.UU., Reino Unido, Canadá).</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -873,12 +873,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Lanzado 7-ene-2026. Conecta registros médicos; conectores solo en EE.UU. Dentro de suscripción del asistente. Fija la expectativa de consultar y resumir el historial.</t>
+          <t>[ADYACENTE · global] Lanzado 7-ene-2026. Conecta registros médicos; conectores solo en EE.UU. Dentro de suscripción del asistente. Fija la expectativa de consultar y resumir el historial. [Vuelta 2] Confirmado: registros solo EE.UU.; sin anuncios para Latinoamérica. Hay inconsistencia de fechas entre fuentes (7-ene-2026 lanzamiento vs. jul-2026 despliegue de registros).</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -913,12 +913,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Lanzado 11-ene-2026. Conectores solo en EE.UU., planes Pro/Max. Nota: producto de Anthropic, conflicto de interés al evaluarlo.</t>
+          <t>[ADYACENTE · global] Lanzado 11-ene-2026. Conectores solo en EE.UU., planes Pro/Max. Nota: producto de Anthropic, conflicto de interés al evaluarlo. [Vuelta 2] Sin cambios fuera de EE.UU. (HealthEx y Function para Pro/Max).</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -953,12 +953,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones.</t>
+          <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones. [Vuelta 2] App concreta: Mi Alemana Go (Clínica Alemana, Chile), con historial desde 2018, recetas, órdenes, familiar vinculado y resultados.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3926,6 +3926,262 @@
       <c r="F88" t="inlineStr">
         <is>
           <t>Búsqueda web (pkg.go.dev panacea-core)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Compartir datos con pareja o cuidador (pestaña Sharing)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Comparte de forma privada datos de salud (actividad, corazón, movilidad) con una persona de confianza, eligiendo qué y con quién.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Búsqueda web (HIT/Healthcare IT News); registros clínicos solo EE.UU., Reino Unido y Canadá</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Medicación y recordatorios</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Medicamentos: listas, horarios y escaneo de etiquetas</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Listas de medicamentos, vitaminas y suplementos con horarios; escaneo de etiqueta del frasco solo en EE.UU.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Búsqueda web (MobiHealthNews)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Conexión de registros con b.well (&gt;2,2 millones de proveedores)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Acceso a historiales electrónicos de proveedores de EE.UU. vía b.well; solo EE.UU., sin plazo anunciado para Latinoamérica.</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Analytics Insight, HT World)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Integración con Android Health Connect</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Integración beta con Health Connect en la app móvil; conectores de registros (HealthEx, Function) solo para Pro/Max en EE.UU.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Fortune, Help Net Security)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Notificación de resultados y compartir por email/WhatsApp (Mi Alemana Go)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Avisa cuando hay exámenes/documentos disponibles; resultados de laboratorio y anatomía patológica compartibles por email o WhatsApp.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ficha App Store Chile (Mi Alemana Go)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Historial de consultas, urgencias y hospitalizaciones desde 2018</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Historial institucional de consultas, urgencias y hospitalizaciones (solo datos de esa clínica).</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Ficha App Store Chile (Mi Alemana Go)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Descarga de recetas, órdenes de examen y derivaciones</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Ver y descargar recetas, órdenes de examen y derivaciones.</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Ficha App Store Chile (Mi Alemana Go)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Citas y agenda</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Reservar, cancelar y reprogramar horas, exámenes y procedimientos</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Gestión completa de agenda dentro de la institución.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Ficha App Store Chile (Mi Alemana Go)</t>
         </is>
       </c>
     </row>
@@ -6850,7 +7106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -6933,6 +7189,13 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Vuelta 2 (iter. 3, 2026-10-07 18:08 UTC): Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas revisados (+8 filas). Pendientes: Clinia, MiRedSalud, Mediko.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -518,11 +518,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -558,11 +558,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -598,11 +598,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -638,11 +638,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -678,11 +678,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -718,11 +718,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -758,11 +758,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -798,11 +798,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -838,11 +838,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -878,11 +878,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -918,11 +918,11 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar.</t>
+          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar. [Vuelta 2] Confirmado por el CEO de Reservo (LinkedIn): app para pacientes en App Store y Google Play; guarda y comparte exámenes, recetas, órdenes y certificados. Fecha exacta de lanzamiento, precio y modelo de datos sin verificar.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis).</t>
+          <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis). [Vuelta 2] La búsqueda no encontró fuentes adicionales ni ficha de la app chilena (solo una app RedSalud de otro país); funciones sin confirmar.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc.</t>
+          <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc. [Vuelta 2] Sin precios ni planes vigentes localizados; sitio oficial bloqueado.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4185,6 +4185,102 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Clinia (Reservo)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Almacén de exámenes, recetas, órdenes y certificados</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Guarda en un solo lugar exámenes, recetas, órdenes y certificados médicos.</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Búsqueda web (LinkedIn del CEO de Reservo, Chocale); app en App Store y Google Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Clinia (Reservo)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Compartición y consentimiento</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Compartir documentos con médicos cuando se necesite</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Comparte los documentos guardados con los profesionales en la consulta.</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Búsqueda web (LinkedIn del CEO de Reservo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Clinia (Reservo)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Apps iOS y Android</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Disponible en App Store y Google Play. Reservo opera en Chile, México y Argentina y está certificada por FONASA y CENS.</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Chocale, sep-2026)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4196,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4236,7 +4332,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4246,12 +4342,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Calendario de citas médicas</t>
+          <t>Búsqueda de profesionales de salud</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Agenda de citas.</t>
+          <t>Directorio filtrable por obra social, especialidad, subespecialidad y cercanía.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4263,7 +4359,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4273,24 +4369,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Calendario de citas médicas</t>
+          <t>Búsqueda de profesionales de salud</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Calendario para organizar citas médicas.</t>
+          <t>Busca profesionales y agenda citas desde la app.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4300,66 +4396,66 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reserva de citas médicas</t>
+          <t>Calendario de citas médicas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Reserva de horas en la institución.</t>
+          <t>Agenda de citas.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Compartición y consentimiento</t>
+          <t>Citas y agenda</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+          <t>Calendario de citas médicas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Permite compartir información con médicos, familia y amistades.</t>
+          <t>Calendario para organizar citas médicas.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Compartición y consentimiento</t>
+          <t>Citas y agenda</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+          <t>Localización de centros médicos y farmacias</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Comparte registros con familiares o profesionales.</t>
+          <t>Localiza centros médicos y farmacias.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4371,61 +4467,61 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Compartición y consentimiento</t>
+          <t>Citas y agenda</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+          <t>Reserva de citas médicas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Traspaso de registros a hospitales.</t>
+          <t>Reserva de horas en la institución.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Compartición y consentimiento</t>
+          <t>Citas y agenda</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+          <t>Reserva de citas médicas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Compartir información con profesionales de salud.</t>
+          <t>Gestión completa de agenda dentro de la institución.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4435,24 +4531,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+          <t>Acceso del profesional al historial del paciente</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Acceso de clínicos limitado en el tiempo.</t>
+          <t>El médico puede revisar el historial e ingresar datos automáticamente.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4462,24 +4558,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+          <t>Compartir con personas sin cuenta mediante clave segura</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>El usuario decide con qué profesionales comparte su información.</t>
+          <t>Datos compartibles con personas sin cuenta mediante clave de acceso segura enviada por email.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4489,12 +4585,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gestión de consentimiento sobre uso de datos</t>
+          <t>Compartir datos con cuidador o persona de confianza</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>El usuario decide si sus registros se usan para análisis de big data.</t>
+          <t>Comparte de forma privada datos de salud (actividad, corazón, movilidad) con una persona de confianza, eligiendo qué y con quién.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4506,7 +4602,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4516,125 +4612,125 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ingreso de datos por profesional con consentimiento</t>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>El médico puede ingresar datos al historial con autorización del paciente.</t>
+          <t>Permite compartir información con médicos, familia y amistades.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Emergencia</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ficha de emergencia (alergias y medicación)</t>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Disponibilidad del historial en situaciones de atención.</t>
+          <t>Comparte los documentos guardados con los profesionales en la consulta.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Emergencia</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ficha de emergencia (alergias y medicación)</t>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Acceso a datos clave del paciente en emergencias.</t>
+          <t>Comparte registros con familiares o profesionales.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Emergencia</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ficha de emergencia (alergias y medicación)</t>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ficha de emergencia con alergias y medicación accesible rápidamente.</t>
+          <t>Traspaso de registros a hospitales.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Familia y dependientes</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Perfiles familiares / dependientes</t>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Vincula familiares a la cuenta.</t>
+          <t>Compartir información con profesionales de salud.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
@@ -4646,17 +4742,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Familia y dependientes</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Perfiles familiares / dependientes</t>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Historial por perfil para cada miembro de la familia.</t>
+          <t>Comparte información con cuidadores, maestros o profesionales de confianza.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -4668,49 +4764,49 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MiRedSalud (RedSalud)</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Familia y dependientes</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Perfiles familiares / dependientes</t>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Guardar y administrar historial propio y familiar.</t>
+          <t>Acceso de clínicos limitado en el tiempo.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gestión documental</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Almacenamiento de documentos médicos</t>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Reúne recetas, diagnósticos y laboratorios en un solo lugar.</t>
+          <t>El usuario decide con qué profesionales comparte su información.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4722,157 +4818,157 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gestión documental</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Almacenamiento de documentos médicos</t>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Organiza registros con carpetas y etiquetas.</t>
+          <t>El usuario autoriza a proveedores a acceder y usar sus datos de salud.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gestión documental</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Almacenamiento de documentos médicos</t>
+          <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Almacena documentos clínicos del usuario en la app.</t>
+          <t>El usuario decide si sus registros se usan para análisis de big data.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gestión documental</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Almacenamiento de recetas</t>
+          <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Guarda recetas digitales.</t>
+          <t>El médico puede ingresar datos al historial con autorización del paciente.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gestión documental</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Importación de órdenes/solicitudes médicas</t>
+          <t>Red social con profesionales y familiares</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Descarga/genera órdenes médicas digitales.</t>
+          <t>Interacción con médicos, dentistas, kinesiólogos, entrenadores y familiares dentro de la red.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gestión documental</t>
+          <t>Emergencia</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Importación de órdenes/solicitudes médicas</t>
+          <t>Ficha de emergencia (alergias y medicación)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Importa solicitudes (órdenes) médicas a la app.</t>
+          <t>Disponibilidad del historial en situaciones de atención.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Emergencia</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Historial institucional (solo datos de la propia red)</t>
+          <t>Ficha de emergencia (alergias y medicación)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ve historial de esa institución.</t>
+          <t>Acceso a datos clave del paciente en emergencias.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4884,22 +4980,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MiRedSalud (RedSalud)</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Emergencia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Historial institucional (solo datos de la propia red)</t>
+          <t>Ficha de emergencia (alergias y medicación)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Acceso a información clínica de la red.</t>
+          <t>Ficha de emergencia con alergias y medicación accesible rápidamente.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4911,27 +5007,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Familia y dependientes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Información clínica unificada.</t>
+          <t>Vincula familiares a la cuenta.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -4943,17 +5039,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Familia y dependientes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>El usuario registra sus antecedentes médicos en la app.</t>
+          <t>Los padres pueden monitorear la salud de hijos pequeños.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4965,211 +5061,211 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Familia y dependientes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Centraliza el historial médico personal en el móvil.</t>
+          <t>Historial por perfil para cada miembro de la familia.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>MiRedSalud (RedSalud)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Familia y dependientes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Permite compilar datos de vida/salud, gestionarlos y pasarlos a instituciones médicas.</t>
+          <t>Guardar y administrar historial propio y familiar.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Almacenamiento de documentos médicos</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Centralizar registros y monitoreo desde el móvil.</t>
+          <t>Sube estudios, imágenes, indicaciones médicas y notas personales; accesible en consulta o por terceros en emergencias.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Línea de tiempo de salud</t>
+          <t>Almacenamiento de documentos médicos</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Línea de tiempo con medicación, exámenes, citas y dieta.</t>
+          <t>Reúne recetas, diagnósticos y laboratorios en un solo lugar.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas</t>
+          <t>Almacenamiento de documentos médicos</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas.</t>
+          <t>Guarda en un solo lugar exámenes, recetas, órdenes y certificados médicos.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Incentivos y monetización de datos</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Recompensas / monetización de datos del usuario</t>
+          <t>Almacenamiento de documentos médicos</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>El usuario puede agregar y monetizar sus datos; recompensas en cripto.</t>
+          <t>Organiza registros con carpetas y etiquetas.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Coaching de salud con IA</t>
+          <t>Almacenamiento de documentos médicos</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Coaching personalizado con IA.</t>
+          <t>Almacena documentos clínicos del usuario en la app.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Detección de patrones en métricas de salud con IA</t>
+          <t>Almacenamiento de documentos médicos</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Detecta patrones entre métricas de salud y fitness.</t>
+          <t>Administra fechas, prescripciones, archivos y citas desde la app.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5181,81 +5277,81 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
+          <t>Almacenamiento de recetas</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Explica resultados complejos en lenguaje simple.</t>
+          <t>Ver y descargar recetas, órdenes de examen y derivaciones.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
+          <t>Almacenamiento de recetas</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Explica exámenes en lenguaje simple.</t>
+          <t>Guarda recetas digitales.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
+          <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Interpreta exámenes de laboratorio.</t>
+          <t>Guarda resultados de laboratorio, imágenes y PDFs; búsqueda y filtros.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
@@ -5267,17 +5363,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Orientación médica con IA</t>
+          <t>Importación de órdenes/solicitudes médicas</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Orientación médica instantánea mediante IA.</t>
+          <t>Descarga/genera órdenes médicas digitales.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5289,157 +5385,157 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Preparación de consultas médicas con IA</t>
+          <t>Importación de órdenes/solicitudes médicas</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Prepara preguntas para el médico.</t>
+          <t>Importa solicitudes (órdenes) médicas a la app.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Preparación de consultas médicas con IA</t>
+          <t>Notificación y envío de resultados</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Prepara preguntas para el médico.</t>
+          <t>Avisa cuando hay exámenes/documentos disponibles; resultados de laboratorio y anatomía patológica compartibles por email o WhatsApp.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Resumen de historial con IA</t>
+          <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Resume instrucciones de atención.</t>
+          <t>Ve historial de esa institución.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Resumen de historial con IA</t>
+          <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Resume el historial del usuario.</t>
+          <t>Historial institucional de consultas, urgencias y hospitalizaciones (solo datos de esa clínica).</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MiRedSalud (RedSalud)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Vista central de alergias, condiciones, vacunas, laboratorio, medicación, procedimientos y signos vitales.</t>
+          <t>Acceso a información clínica de la red.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Conexión de historiales electrónicos y apps como Apple Health, MyFitnessPal, Peloton.</t>
+          <t>Información clínica unificada.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5451,49 +5547,49 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Acceso a resultados y registros de salud (beta, Pro/Max, EE.UU.).</t>
+          <t>El usuario registra sus antecedentes médicos en la app.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Datos desde profesionales/centros que usan Reservo (fichas clínicas, agenda, telemedicina).</t>
+          <t>Centraliza el historial médico personal en el móvil.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5505,22 +5601,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Reúne registros de hospitales, resultados de laboratorio y datos genómicos.</t>
+          <t>Permite compilar datos de vida/salud, gestionarlos y pasarlos a instituciones médicas.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5532,27 +5628,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Analítica poblacional B2B</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Analítica poblacional on-chain; integrada con Epic, Cerner, Meditech y Allscripts (B2B).</t>
+          <t>Centralizar registros y monitoreo desde el móvil.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -5564,17 +5660,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+          <t>Línea de tiempo de salud</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Disponible en web, iOS y Android.</t>
+          <t>Línea de tiempo con medicación, exámenes, citas y dieta.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5586,54 +5682,54 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Línea de tiempo de salud</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Versión digital de los registros con acceso por móvil o web.</t>
+          <t>Registra notas de medicación, exámenes (laboratorio e imagen), actividad física, recetas, dieta y citas.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Registro de alergias y vacunas</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Integración beta en apps iOS/Android.</t>
+          <t>Registro de alergias y vacunas.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
@@ -5645,17 +5741,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Incentivos y monetización de datos</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
+          <t>El usuario puede agregar y monetizar sus datos; recompensas en cripto.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5667,22 +5763,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
+          <t>Coaching de salud con IA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Recordatorios desde el app.</t>
+          <t>Coaching personalizado con IA.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5694,76 +5790,76 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
+          <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Recordatorios de citas/medicación.</t>
+          <t>Detecta patrones entre métricas de salud y fitness.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores</t>
+          <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores de salud.</t>
+          <t>Explica resultados complejos en lenguaje simple.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Datos de pasos, sueño, peso junto a registros.</t>
+          <t>Explica exámenes en lenguaje simple.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5775,76 +5871,76 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Panel de seguimiento de salud y bienestar</t>
+          <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
+          <t>Interpreta exámenes de laboratorio.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Orientación médica con IA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
+          <t>Orientación médica instantánea mediante IA.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
+          <t>Prepara preguntas para el médico.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5856,22 +5952,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
+          <t>Prepara preguntas para el médico.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5883,22 +5979,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso biométrico</t>
+          <t>Resumen de historial con IA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
+          <t>Resume instrucciones de atención.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5910,22 +6006,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
+          <t>Resumen de historial con IA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
+          <t>Resume el historial del usuario.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5937,49 +6033,49 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Modelo freemium y suscripción</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Planes para personas y empresas.</t>
+          <t>Vista central de alergias, condiciones, vacunas, laboratorio, medicación, procedimientos y signos vitales.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pagos con criptomoneda</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Pago de consultas con token.</t>
+          <t>Conexión de historiales electrónicos y apps como Apple Health, MyFitnessPal, Peloton.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5991,22 +6087,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
+          <t>Acceso a historiales electrónicos de proveedores de EE.UU. vía b.well; solo EE.UU., sin plazo anunciado para Latinoamérica.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6018,25 +6114,862 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Agregación de registros de múltiples instituciones</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Acceso a resultados y registros de salud (beta, Pro/Max, EE.UU.).</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Clinia (Reservo)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Agregación de registros de múltiples instituciones</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Datos desde profesionales/centros que usan Reservo (fichas clínicas, agenda, telemedicina).</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Agregación de registros de múltiples instituciones</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Reúne registros de hospitales, resultados de laboratorio y datos genómicos.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Analítica poblacional B2B</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Analítica poblacional on-chain; integrada con Epic, Cerner, Meditech y Allscripts (B2B).</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Clingot</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Android, iOS y escritorio; médicos acceden a historias digitalizadas, envían estudios e indicaciones y organizan agenda.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Clinia (Reservo)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Disponible en App Store y Google Play. Reservo opera en Chile, México y Argentina y está certificada por FONASA y CENS.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Healfies</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Disponible en web, iOS y Android.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>Medicalchain</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Versión digital de los registros con acceso por móvil o web.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Integración beta en apps iOS/Android.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Integración beta con Health Connect en la app móvil; conectores de registros (HealthEx, Function) solo para Pro/Max en EE.UU.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Medicación y recordatorios</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Gestión de lista de medicamentos</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Listas de medicamentos, vitaminas y suplementos con horarios; escaneo de etiqueta del frasco solo en EE.UU.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Medicación y recordatorios</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Recordatorios de medicación y citas</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Recordatorios desde el app.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Meedika</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Medicación y recordatorios</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Recordatorios de medicación y citas</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Recordatorios de citas/medicación.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Medicación y recordatorios</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Registro de tomas y adherencia al tratamiento</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Registro de cada toma y control de adherencia; gestiona medicamentos propios y de familiares.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Infomed</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Contenido educativo sobre salud</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Busca que el paciente aprenda sobre sus enfermedades y sea más autónomo.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Gráficas de evolución de indicadores</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Gráficas de evolución de indicadores de salud.</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Datos de pasos, sueño, peso junto a registros.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Panel de seguimiento de salud y bienestar</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Clingot</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Valoración de profesionales</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Calificación de la atención de profesionales con autorización previa, compartible con otros usuarios.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Almacena huellas de datos médicos en un registro de solo escritura, sin guardar datos clínicos en cadena.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Cifrado y control de acceso</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Infomed</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Cifrado y control de acceso</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Almacenamiento seguro del historial con criterios de seguridad estrictos, comparable a apps bancarias.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Identidad descentralizada (DID)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Gestión de identificadores descentralizados en Panacea.</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Privacidad reforzada para datos de salud</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Modelo freemium y suscripción</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Planes para personas y empresas.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Pagos con criptomoneda</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Pago de consultas con token.</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
         <is>
           <t>Telemedicina y atención remota</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>Teleconsultas con GP.</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
@@ -6053,7 +6986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -6176,19 +7109,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Calendario de citas médicas</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+          <t>Búsqueda de profesionales de salud</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2">
         <f>COUNTIF(C2:Q2,"✓")</f>
         <v/>
@@ -6202,14 +7148,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Reserva de citas médicas</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+          <t>Calendario de citas médicas</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3">
         <f>COUNTIF(C3:Q3,"✓")</f>
         <v/>
@@ -6218,44 +7182,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Compartición y consentimiento</t>
+          <t>Citas y agenda</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Compartir información con profesionales (consentimiento del usuario)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+          <t>Localización de centros médicos y farmacias</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4">
         <f>COUNTIF(C4:Q4,"✓")</f>
         <v/>
@@ -6264,19 +7217,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Compartición y consentimiento</t>
+          <t>Citas y agenda</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gestión de consentimiento sobre uso de datos</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+          <t>Reserva de citas médicas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5">
         <f>COUNTIF(C5:Q5,"✓")</f>
         <v/>
@@ -6290,14 +7257,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ingreso de datos por profesional con consentimiento</t>
-        </is>
-      </c>
+          <t>Acceso del profesional al historial del paciente</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6">
         <f>COUNTIF(C6:Q6,"✓")</f>
         <v/>
@@ -6306,29 +7287,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Emergencia</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ficha de emergencia (alergias y medicación)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+          <t>Compartir con personas sin cuenta mediante clave segura</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7">
         <f>COUNTIF(C7:Q7,"✓")</f>
         <v/>
@@ -6337,29 +7322,33 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Familia y dependientes</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Perfiles familiares / dependientes</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+          <t>Compartir datos con cuidador o persona de confianza</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8">
         <f>COUNTIF(C8:Q8,"✓")</f>
         <v/>
@@ -6368,12 +7357,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gestión documental</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Almacenamiento de documentos médicos</t>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6381,16 +7370,48 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9">
         <f>COUNTIF(C9:Q9,"✓")</f>
         <v/>
@@ -6399,19 +7420,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gestión documental</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Almacenamiento de recetas</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+          <t>Gestión de consentimiento sobre uso de datos</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10">
         <f>COUNTIF(C10:Q10,"✓")</f>
         <v/>
@@ -6420,24 +7455,33 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gestión documental</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Importación de órdenes/solicitudes médicas</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+          <t>Ingreso de datos por profesional con consentimiento</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11">
         <f>COUNTIF(C11:Q11,"✓")</f>
         <v/>
@@ -6446,24 +7490,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Historial institucional (solo datos de la propia red)</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
+          <t>Red social con profesionales y familiares</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12">
         <f>COUNTIF(C12:Q12,"✓")</f>
         <v/>
@@ -6472,12 +7525,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Emergencia</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Ficha de emergencia (alergias y medicación)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6485,26 +7543,23 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13">
         <f>COUNTIF(C13:Q13,"✓")</f>
         <v/>
@@ -6513,19 +7568,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Familia y dependientes</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Línea de tiempo de salud</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+          <t>Perfiles familiares / dependientes</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14">
         <f>COUNTIF(C14:Q14,"✓")</f>
         <v/>
@@ -6534,19 +7615,49 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+          <t>Almacenamiento de documentos médicos</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15">
         <f>COUNTIF(C15:Q15,"✓")</f>
         <v/>
@@ -6555,19 +7666,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Incentivos y monetización de datos</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Recompensas / monetización de datos del usuario</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+          <t>Almacenamiento de recetas</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16">
         <f>COUNTIF(C16:Q16,"✓")</f>
         <v/>
@@ -6576,19 +7705,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Coaching de salud con IA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+          <t>Búsqueda y filtros de documentos</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17">
         <f>COUNTIF(C17:Q17,"✓")</f>
         <v/>
@@ -6597,15 +7740,33 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Detección de patrones en métricas de salud con IA</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+          <t>Importación de órdenes/solicitudes médicas</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -6618,29 +7779,33 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
+          <t>Notificación y envío de resultados</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19">
         <f>COUNTIF(C19:Q19,"✓")</f>
         <v/>
@@ -6649,19 +7814,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Orientación médica con IA</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
+          <t>Historial institucional (solo datos de la propia red)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20">
         <f>COUNTIF(C20:Q20,"✓")</f>
         <v/>
@@ -6670,20 +7853,45 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Preparación de consultas médicas con IA</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -6696,24 +7904,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Resumen de historial con IA</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
+          <t>Línea de tiempo de salud</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22">
         <f>COUNTIF(C22:Q22,"✓")</f>
         <v/>
@@ -6722,39 +7939,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+          <t>Registro de alergias y vacunas</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23">
         <f>COUNTIF(C23:Q23,"✓")</f>
         <v/>
@@ -6763,19 +7974,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Incentivos y monetización de datos</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Analítica poblacional B2B</t>
-        </is>
-      </c>
+          <t>Recompensas / monetización de datos del usuario</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24">
         <f>COUNTIF(C24:Q24,"✓")</f>
         <v/>
@@ -6784,19 +8009,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+          <t>Coaching de salud con IA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25">
         <f>COUNTIF(C25:Q25,"✓")</f>
         <v/>
@@ -6805,19 +8044,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+          <t>Detección de patrones en métricas de salud con IA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26">
         <f>COUNTIF(C26:Q26,"✓")</f>
         <v/>
@@ -6826,20 +8079,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
+          <t>Interpretación de exámenes con IA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -6852,20 +8122,29 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
+          <t>Orientación médica con IA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -6878,19 +8157,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+          <t>Preparación de consultas médicas con IA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29">
         <f>COUNTIF(C29:Q29,"✓")</f>
         <v/>
@@ -6899,19 +8196,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
+          <t>Resumen de historial con IA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30">
         <f>COUNTIF(C30:Q30,"✓")</f>
         <v/>
@@ -6920,19 +8235,49 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Panel de seguimiento de salud y bienestar</t>
-        </is>
-      </c>
+          <t>Agregación de registros de múltiples instituciones</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31">
         <f>COUNTIF(C31:Q31,"✓")</f>
         <v/>
@@ -6941,29 +8286,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
-        </is>
-      </c>
+          <t>Analítica poblacional B2B</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32">
         <f>COUNTIF(C32:Q32,"✓")</f>
         <v/>
@@ -6972,19 +8321,41 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso biométrico</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33">
         <f>COUNTIF(C33:Q33,"✓")</f>
         <v/>
@@ -6993,19 +8364,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34">
         <f>COUNTIF(C34:Q34,"✓")</f>
         <v/>
@@ -7014,19 +8399,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Modelo freemium y suscripción</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35">
         <f>COUNTIF(C35:Q35,"✓")</f>
         <v/>
@@ -7035,19 +8438,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pagos con criptomoneda</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+          <t>Gestión de lista de medicamentos</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36">
         <f>COUNTIF(C36:Q36,"✓")</f>
         <v/>
@@ -7056,19 +8473,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
+          <t>Recordatorios de medicación y citas</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37">
         <f>COUNTIF(C37:Q37,"✓")</f>
         <v/>
@@ -7077,21 +8512,502 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Telemedicina y atención remota</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Teleconsulta con profesionales</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+          <t>Registro de tomas y adherencia al tratamiento</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38">
         <f>COUNTIF(C38:Q38,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Contenido educativo sobre salud</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39">
+        <f>COUNTIF(C39:Q39,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Gráficas de evolución de indicadores</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40">
+        <f>COUNTIF(C40:Q40,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41">
+        <f>COUNTIF(C41:Q41,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Panel de seguimiento de salud y bienestar</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42">
+        <f>COUNTIF(C42:Q42,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Valoración de profesionales</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43">
+        <f>COUNTIF(C43:Q43,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44">
+        <f>COUNTIF(C44:Q44,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cifrado y control de acceso</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45">
+        <f>COUNTIF(C45:Q45,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Identidad descentralizada (DID)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46">
+        <f>COUNTIF(C46:Q46,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Privacidad reforzada para datos de salud</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47">
+        <f>COUNTIF(C47:Q47,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Modelo freemium y suscripción</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48">
+        <f>COUNTIF(C48:Q48,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Pagos con criptomoneda</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49">
+        <f>COUNTIF(C49:Q49,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50">
+        <f>COUNTIF(C50:Q50,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Telemedicina y atención remota</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Teleconsulta con profesionales</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51">
+        <f>COUNTIF(C51:Q51,"✓")</f>
         <v/>
       </c>
     </row>
@@ -7106,7 +9022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -7196,6 +9112,13 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>VUELTA 2 COMPLETA (2026-10-07 20:08 UTC): Clinia, MiRedSalud y Mediko revisados (+3 filas). Contador de loops = 2 para todos, Revisado reiniciado a "No". func_norm (98 filas) y tabla_frecuencia (50 funcionalidades normalizadas) regenerados. Vuelta 3 parte con Meedika, Infomed, MediPlanner, Clingot.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -513,12 +513,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar.</t>
+          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar. [Vuelta 3] Sin novedades 2026 ni confirmación de la app Android en Google Play; usuarios actuales desconocidos. Nota de prensa no indica año de lanzamiento explícito.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -553,12 +553,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapa A] Fundada 2019 por Diego Ibarra, Andrés Fantuzzi y Gabriel Zamora. Lanzada mar-2021 en App Store y Play Store con 1.200 usuarios; planeaba nueva versión jul-2021 y ronda de US$500 mil. Objetivo: llevar el historial en el celular, acceso en emergencias, médico puede ingresar datos con consentimiento. Estado actual NO verificado (posible app inactiva). URL es la nota de prensa; sitio oficial por confirmar.</t>
+          <t>[DIRECTO · Chile · etapa A] Fundada 2019 por Diego Ibarra, Andrés Fantuzzi y Gabriel Zamora. Lanzada mar-2021 en App Store y Play Store con 1.200 usuarios; planeaba nueva versión jul-2021 y ronda de US$500 mil. Objetivo: llevar el historial en el celular, acceso en emergencias, médico puede ingresar datos con consentimiento. Estado actual NO verificado (posible app inactiva). URL es la nota de prensa; sitio oficial por confirmar. [Vuelta 3] Sin evidencia posterior a 2021; relanzamiento previsto jul-2021 no confirmado. Probable app inactiva.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -593,12 +593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · México] Historial por perfil familiar, alergias, vacunas, recetas digitales, gráficas de evolución, agendamiento, compartir con profesionales. Gratis en App Store MX. Sin evidencia de uso en Chile. Cubre parte de la etapa C (familia).</t>
+          <t>[REGIONAL · México] Historial por perfil familiar, alergias, vacunas, recetas digitales, gráficas de evolución, agendamiento, compartir con profesionales. Gratis en App Store MX. Sin evidencia de uso en Chile. Cubre parte de la etapa C (familia). [Vuelta 3] Existen dos apps distintas: MediPlanner (gratis, Rym Solutions, MX, 3,7/5 con 3 calificaciones) y MediPlanner Pro (otro desarrollador, $39 MXN). Sin presencia verificada en Chile.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · Argentina · débil] App para cargar antecedentes médicos propios. Única referencia: nota de opinión en grupoanimal.mx sin fecha verificada. Estado y sitio por confirmar.</t>
+          <t>[REGIONAL · Argentina · débil] App para cargar antecedentes médicos propios. Única referencia: nota de opinión en grupoanimal.mx sin fecha verificada. Estado y sitio por confirmar. [Vuelta 3] Referencias de 2017 (apps4citizens, La Nación); sitio y precio no verificados; puede estar inactiva.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4278,6 +4278,102 @@
       <c r="F99" t="inlineStr">
         <is>
           <t>Búsqueda web (Chocale, sep-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Meedika</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Sincronización de resultados desde centros de salud</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Sincroniza resultados desde centros de salud y permite subir fotos o documentos de las solicitudes médicas.</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Diario Estrategia / Europa Press); vuelta 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Importar y exportar información (versión Pro)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Importar/exportar datos para compartir de forma segura con familias o cuidadores. Es MediPlanner Pro, de otro desarrollador (App Store MX, $39 MXN).</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Búsqueda web (ficha App Store MX); vuelta 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Citas y agenda</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Integración con el calendario del dispositivo</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Permite añadir las citas a la app Calendario del teléfono (versión Pro).</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Búsqueda web (ficha App Store MX); vuelta 3</t>
         </is>
       </c>
     </row>
@@ -7112,8 +7208,6 @@
           <t>Búsqueda de profesionales de salud</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7124,17 +7218,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2">
         <f>COUNTIF(C2:Q2,"✓")</f>
         <v/>
@@ -7156,24 +7239,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3">
         <f>COUNTIF(C3:Q3,"✓")</f>
         <v/>
@@ -7190,25 +7260,11 @@
           <t>Localización de centros médicos y farmacias</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4">
         <f>COUNTIF(C4:Q4,"✓")</f>
         <v/>
@@ -7225,25 +7281,11 @@
           <t>Reserva de citas médicas</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5">
         <f>COUNTIF(C5:Q5,"✓")</f>
         <v/>
@@ -7260,25 +7302,11 @@
           <t>Acceso del profesional al historial del paciente</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6">
         <f>COUNTIF(C6:Q6,"✓")</f>
         <v/>
@@ -7295,25 +7323,11 @@
           <t>Compartir con personas sin cuenta mediante clave segura</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7">
         <f>COUNTIF(C7:Q7,"✓")</f>
         <v/>
@@ -7330,25 +7344,11 @@
           <t>Compartir datos con cuidador o persona de confianza</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8">
         <f>COUNTIF(C8:Q8,"✓")</f>
         <v/>
@@ -7370,13 +7370,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7402,16 +7400,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9">
         <f>COUNTIF(C9:Q9,"✓")</f>
         <v/>
@@ -7428,25 +7421,11 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10">
         <f>COUNTIF(C10:Q10,"✓")</f>
         <v/>
@@ -7463,25 +7442,11 @@
           <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11">
         <f>COUNTIF(C11:Q11,"✓")</f>
         <v/>
@@ -7498,25 +7463,11 @@
           <t>Red social con profesionales y familiares</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12">
         <f>COUNTIF(C12:Q12,"✓")</f>
         <v/>
@@ -7543,23 +7494,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13">
         <f>COUNTIF(C13:Q13,"✓")</f>
         <v/>
@@ -7576,8 +7515,6 @@
           <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7588,25 +7525,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14">
         <f>COUNTIF(C14:Q14,"✓")</f>
         <v/>
@@ -7628,8 +7556,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7645,19 +7571,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15">
         <f>COUNTIF(C15:Q15,"✓")</f>
         <v/>
@@ -7674,29 +7592,16 @@
           <t>Almacenamiento de recetas</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16">
         <f>COUNTIF(C16:Q16,"✓")</f>
         <v/>
@@ -7713,25 +7618,11 @@
           <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17">
         <f>COUNTIF(C17:Q17,"✓")</f>
         <v/>
@@ -7753,19 +7644,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7787,25 +7665,11 @@
           <t>Notificación y envío de resultados</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19">
         <f>COUNTIF(C19:Q19,"✓")</f>
         <v/>
@@ -7822,29 +7686,16 @@
           <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20">
         <f>COUNTIF(C20:Q20,"✓")</f>
         <v/>
@@ -7861,36 +7712,26 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7912,25 +7753,11 @@
           <t>Línea de tiempo de salud</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22">
         <f>COUNTIF(C22:Q22,"✓")</f>
         <v/>
@@ -7947,25 +7774,11 @@
           <t>Registro de alergias y vacunas</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23">
         <f>COUNTIF(C23:Q23,"✓")</f>
         <v/>
@@ -7982,25 +7795,11 @@
           <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24">
         <f>COUNTIF(C24:Q24,"✓")</f>
         <v/>
@@ -8017,25 +7816,11 @@
           <t>Coaching de salud con IA</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25">
         <f>COUNTIF(C25:Q25,"✓")</f>
         <v/>
@@ -8052,25 +7837,11 @@
           <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26">
         <f>COUNTIF(C26:Q26,"✓")</f>
         <v/>
@@ -8087,15 +7858,6 @@
           <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8106,9 +7868,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8130,20 +7889,6 @@
           <t>Orientación médica con IA</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8165,15 +7910,6 @@
           <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8184,10 +7920,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29">
         <f>COUNTIF(C29:Q29,"✓")</f>
         <v/>
@@ -8204,15 +7936,6 @@
           <t>Resumen de historial con IA</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8223,10 +7946,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30">
         <f>COUNTIF(C30:Q30,"✓")</f>
         <v/>
@@ -8243,18 +7962,11 @@
           <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8270,14 +7982,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31">
         <f>COUNTIF(C31:Q31,"✓")</f>
         <v/>
@@ -8294,25 +8003,11 @@
           <t>Analítica poblacional B2B</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32">
         <f>COUNTIF(C32:Q32,"✓")</f>
         <v/>
@@ -8329,9 +8024,6 @@
           <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8342,20 +8034,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33">
         <f>COUNTIF(C33:Q33,"✓")</f>
         <v/>
@@ -8372,25 +8055,11 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34">
         <f>COUNTIF(C34:Q34,"✓")</f>
         <v/>
@@ -8407,29 +8076,16 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35">
         <f>COUNTIF(C35:Q35,"✓")</f>
         <v/>
@@ -8446,25 +8102,11 @@
           <t>Gestión de lista de medicamentos</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36">
         <f>COUNTIF(C36:Q36,"✓")</f>
         <v/>
@@ -8486,24 +8128,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37">
         <f>COUNTIF(C37:Q37,"✓")</f>
         <v/>
@@ -8520,25 +8149,11 @@
           <t>Registro de tomas y adherencia al tratamiento</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38">
         <f>COUNTIF(C38:Q38,"✓")</f>
         <v/>
@@ -8555,25 +8170,11 @@
           <t>Contenido educativo sobre salud</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39">
         <f>COUNTIF(C39:Q39,"✓")</f>
         <v/>
@@ -8590,25 +8191,11 @@
           <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40">
         <f>COUNTIF(C40:Q40,"✓")</f>
         <v/>
@@ -8625,25 +8212,11 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41">
         <f>COUNTIF(C41:Q41,"✓")</f>
         <v/>
@@ -8660,25 +8233,11 @@
           <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42">
         <f>COUNTIF(C42:Q42,"✓")</f>
         <v/>
@@ -8695,25 +8254,11 @@
           <t>Valoración de profesionales</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43">
         <f>COUNTIF(C43:Q43,"✓")</f>
         <v/>
@@ -8730,11 +8275,6 @@
           <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8750,13 +8290,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44">
         <f>COUNTIF(C44:Q44,"✓")</f>
         <v/>
@@ -8773,29 +8306,16 @@
           <t>Cifrado y control de acceso</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45">
         <f>COUNTIF(C45:Q45,"✓")</f>
         <v/>
@@ -8812,25 +8332,11 @@
           <t>Identidad descentralizada (DID)</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46">
         <f>COUNTIF(C46:Q46,"✓")</f>
         <v/>
@@ -8847,25 +8353,11 @@
           <t>Privacidad reforzada para datos de salud</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47">
         <f>COUNTIF(C47:Q47,"✓")</f>
         <v/>
@@ -8882,20 +8374,6 @@
           <t>Modelo freemium y suscripción</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8917,25 +8395,11 @@
           <t>Pagos con criptomoneda</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49">
         <f>COUNTIF(C49:Q49,"✓")</f>
         <v/>
@@ -8952,25 +8416,11 @@
           <t>Reclamos y trámites con seguros</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50">
         <f>COUNTIF(C50:Q50,"✓")</f>
         <v/>
@@ -8987,25 +8437,11 @@
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51">
         <f>COUNTIF(C51:Q51,"✓")</f>
         <v/>
@@ -9022,7 +8458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -9119,6 +8555,13 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Vuelta 3 (iter. 1, 2026-10-07 22:08 UTC): Meedika, Infomed, MediPlanner, Clingot verificados (+3 filas). Pendientes: Healfies, Patientory, MediBloc, Medicalchain, etc. Las filas nuevas aún no están en func_norm/tabla_frecuencia (se regeneran al cerrar la vuelta).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B. [Vuelta 2] Lanzada simultáneamente en Brasil, Argentina y EE.UU.; permite compartir con no registrados vía clave por email. Sin novedades posteriores a 2016.</t>
+          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B. [Vuelta 2] Lanzada simultáneamente en Brasil, Argentina y EE.UU.; permite compartir con no registrados vía clave por email. Sin novedades posteriores a 2016. [Vuelta 3] Sin evidencia de actividad reciente ni de cierre; Gust/Dealroom la listan en Florianópolis (10 empleados, healfies.com) sin fecha de actualización. Estado sin confirmar.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain. [Vuelta 2] Sin noticias 2026 encontradas en búsqueda; sitio oficial bloqueado.</t>
+          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain. [Vuelta 2] Sin noticias 2026 encontradas en búsqueda; sitio oficial bloqueado. [Vuelta 3] Búsqueda adicional solo devuelve hitos de 2017 (token sale US$7,2M) y 2019 (Serie A de US$5,3M, cierre no confirmado); sin datos 2025-26 propios.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain. [Vuelta 2] Panacea incluye DID, Append Only Log, IBC y PNFT; sin anuncios 2026 localizados.</t>
+          <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain. [Vuelta 2] Panacea incluye DID, Append Only Log, IBC y PNFT; sin anuncios 2026 localizados. [Vuelta 3] Medipass: app en Corea con 20 hospitales/aseguradoras integrados (fecha de la lista desconocida) y plan 2022 de superapp con marketplace de datos; operación actual sin confirmar.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · Reino Unido · INACTIVO] Londres, 2017, Ethereum, con telemedicina. Piloto según registro de la UE (2020). Tracxn/PitchBook lo marcan fuera de operación (ago-2025). Solo caso de aprendizaje: no cuenta como competidor activo. [Vuelta 2] Token MTN deslistado de Bitfinex el 26-mar-2021; sin hallazgos de actividad posterior.</t>
+          <t>[BLOCKCHAIN · Reino Unido · INACTIVO] Londres, 2017, Ethereum, con telemedicina. Piloto según registro de la UE (2020). Tracxn/PitchBook lo marcan fuera de operación (ago-2025). Solo caso de aprendizaje: no cuenta como competidor activo. [Vuelta 2] Token MTN deslistado de Bitfinex el 26-mar-2021; sin hallazgos de actividad posterior. [Vuelta 3] Seedtable la marca activa sin fuente; no hallé registro en Companies House. Sigue tratándose como caso de aprendizaje.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4374,6 +4374,134 @@
       <c r="F102" t="inlineStr">
         <is>
           <t>Búsqueda web (ficha App Store MX); vuelta 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Consulta de historial de hospitales conectados (3 años)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Tras autenticación simple, trae los últimos 3 años de historial de hospitales integrados (p. ej. Samsung Seoul, SNUH, Severance).</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Dealsite, Blockmedia, ficha App Store Corea); app Medipass</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Reclamación de seguro desde el móvil en segundos</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Reclamo de seguro médico (indemnización) desde la app, con verificación de autenticidad de los registros vía blockchain por la aseguradora.</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Blockmedia 2019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Emisión de certificados y consulta de chequeos</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>La ficha de la app incluye consulta de chequeos de salud y emisión de certificados médicos.</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Búsqueda web (ficha App Store Corea)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Incentivos y monetización de datos</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Marketplace de datos (planificado 2022)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Plan de convertir Medipass en superapp con gestión de salud diaria y mercado de datos, integrada con la EMR Dr.Palette.</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Dealsite 2022); sin confirmación de ejecución</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -8562,6 +8690,13 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Vuelta 3 (iter. 2, 2026-10-08 00:08 UTC): Healfies, Patientory, MediBloc, Medicalchain verificados (+4 filas, todas de MediBloc). Pendientes: Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas, Clinia, MiRedSalud, Mediko.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -833,12 +833,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Agrega registros clínicos vía FHIR; &gt;500 instituciones conectadas en EE.UU. (2018). Sin evidencia de disponibilidad en Chile. Incluida en el dispositivo. Amenaza si FHIR/IPS-CL se adopta en Chile. [Vuelta 2] Sin disponibilidad de registros clínicos en Chile (solo EE.UU., Reino Unido, Canadá).</t>
+          <t>[ADYACENTE · global] Agrega registros clínicos vía FHIR; &gt;500 instituciones conectadas en EE.UU. (2018). Sin evidencia de disponibilidad en Chile. Incluida en el dispositivo. Amenaza si FHIR/IPS-CL se adopta en Chile. [Vuelta 2] Sin disponibilidad de registros clínicos en Chile (solo EE.UU., Reino Unido, Canadá). [Vuelta 3] iOS 27 (WWDC 8-jun-2026; publicado ~14-sep-2026): rediseño del app Health, menopausia, nutrición por cámara. El coach de salud con IA no se anunció. Sin ampliación de Health Records a Chile.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Lanzado 7-ene-2026. Conecta registros médicos; conectores solo en EE.UU. Dentro de suscripción del asistente. Fija la expectativa de consultar y resumir el historial. [Vuelta 2] Confirmado: registros solo EE.UU.; sin anuncios para Latinoamérica. Hay inconsistencia de fechas entre fuentes (7-ene-2026 lanzamiento vs. jul-2026 despliegue de registros).</t>
+          <t>[ADYACENTE · global] Lanzado 7-ene-2026. Conecta registros médicos; conectores solo en EE.UU. Dentro de suscripción del asistente. Fija la expectativa de consultar y resumir el historial. [Vuelta 2] Confirmado: registros solo EE.UU.; sin anuncios para Latinoamérica. Hay inconsistencia de fechas entre fuentes (7-ene-2026 lanzamiento vs. jul-2026 despliegue de registros). [Vuelta 3] Fechas aclaradas: presentación 7-ene-2026 (acceso limitado); despliegue de Health in ChatGPT con Apple Health y registros en EE.UU. el 23-jul-2026; mejora de salud jun-2026. Sin anuncios para Latinoamérica ni para sep-oct 2026.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -886,7 +886,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Lanzado 11-ene-2026. Conectores solo en EE.UU., planes Pro/Max. Nota: producto de Anthropic, conflicto de interés al evaluarlo. [Vuelta 2] Sin cambios fuera de EE.UU. (HealthEx y Function para Pro/Max).</t>
+          <t>[ADYACENTE · global] Lanzado 11-ene-2026. Conectores solo en EE.UU., planes Pro/Max. Nota: producto de Anthropic, conflicto de interés al evaluarlo. [Vuelta 2] Sin cambios fuera de EE.UU. (HealthEx y Function para Pro/Max). [Vuelta 3] Sin anuncios posteriores a enero de 2026. Hoja de ruta de HealthEx (agendar, buscar prestadores, recetas) sin confirmar como lanzada.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -926,7 +926,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones. [Vuelta 2] App concreta: Mi Alemana Go (Clínica Alemana, Chile), con historial desde 2018, recetas, órdenes, familiar vinculado y resultados.</t>
+          <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones. [Vuelta 2] App concreta: Mi Alemana Go (Clínica Alemana, Chile), con historial desde 2018, recetas, órdenes, familiar vinculado y resultados. [Vuelta 3] Búsqueda de otras clínicas (Las Condes, Santa María, UC Christus) sin ficha de app confirmada; solo canales digitales genéricos.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4502,6 +4502,198 @@
       <c r="F106" t="inlineStr">
         <is>
           <t>Búsqueda web (Dealsite 2022); sin confirmación de ejecución</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Seguimiento de perimenopausia y menopausia (iOS 27)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Extiende el seguimiento de ciclo con perimenopausia y menopausia.</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Búsqueda web (MacRumors, Sahha, Macwelt); iOS 27 publicado 14-sep-2026 según un reporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Registro de nutrición con cámara (iOS 27)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Escaneo de etiquetas nutricionales con la cámara; según un análisis, no escribe en HealthKit.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Búsqueda web (MacRumors, Sahha)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Conectores a One Medical y Function Health</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Además de b.well y Apple Health, vincula registros de One Medical y Function Health (solo EE.UU., Free/Go/Plus/Pro, web e iOS).</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Búsqueda web (IT Brief, OpenAI); lanzamiento EE.UU. 23-jul-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Detección de cambios en contexto de datos conectados</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Interpreta datos de Apple Health y registros en contexto y detecta cambios.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Búsqueda web (OpenAI, IT Brief)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Reconocimiento de urgencia y explicación de incertidumbre</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Mejora de jun-2026 (GPT-5.5 Instant): detecta cuándo puede requerirse atención urgente, pide contexto y explica la incertidumbre.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Búsqueda web (OpenAI, jun-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Permisos opt-in y revocables; datos fuera de memoria y entrenamiento</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>El usuario activa y revoca permisos; los datos de salud compartidos se excluyen de la memoria de Claude y del entrenamiento.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Help Net Security, NBC News)</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -8697,6 +8889,13 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Vuelta 3 (iter. 3, 2026-10-08 02:08 UTC): Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas verificados (+6 filas). Aclarada discrepancia de fechas de ChatGPT Health. Pendientes: Clinia, MiRedSalud, Mediko (cierran la vuelta 3).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -518,15 +518,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -558,15 +558,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -598,15 +598,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -638,15 +638,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -678,11 +678,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -718,11 +718,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -758,11 +758,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -798,11 +798,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -838,11 +838,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -878,11 +878,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -918,11 +918,11 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar. [Vuelta 2] Confirmado por el CEO de Reservo (LinkedIn): app para pacientes en App Store y Google Play; guarda y comparte exámenes, recetas, órdenes y certificados. Fecha exacta de lanzamiento, precio y modelo de datos sin verificar.</t>
+          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar. [Vuelta 2] Confirmado por el CEO de Reservo (LinkedIn): app para pacientes en App Store y Google Play; guarda y comparte exámenes, recetas, órdenes y certificados. Fecha exacta de lanzamiento, precio y modelo de datos sin verificar. [Vuelta 3] Sin novedades de oct-2026. Reservo (Chile, México, Argentina) declara certificación Fonasa/CENS y cumplimiento de la nueva ley de datos personales; el Portal de Agendamiento de Reservo complementa a Clinia. Precio y modelo de datos sin verificar.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1002,11 +1002,11 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis). [Vuelta 2] La búsqueda no encontró fuentes adicionales ni ficha de la app chilena (solo una app RedSalud de otro país); funciones sin confirmar.</t>
+          <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis). [Vuelta 2] La búsqueda no encontró fuentes adicionales ni ficha de la app chilena (solo una app RedSalud de otro país); funciones sin confirmar. [Vuelta 3] Rankings de terceros la ubican como app médica gratuita nº 1 en App Store y Google Play Chile (fecha desconocida); sin descripción de funciones ni confirmación del desarrollador en Google Play.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc. [Vuelta 2] Sin precios ni planes vigentes localizados; sitio oficial bloqueado.</t>
+          <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc. [Vuelta 2] Sin precios ni planes vigentes localizados; sitio oficial bloqueado. [Vuelta 3] Pauta (oct-2024): su fundador, Tomás Riddell, dice que no reemplaza a médicos y apunta a lo ambulatorio y a la espera de derivación a especialidad en el sistema público. Financiamiento: fuentes discrepan (CLP 25M en dic-2023 según Bouncewatch; ~$40M según Descubre.vc). Precios vigentes sin verificar.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1082,11 +1082,11 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4697,6 +4697,70 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Clinia (Reservo)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Cumplimiento regulatorio (Fonasa, CENS, ley de datos personales)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Reservo declara plataforma certificada por Fonasa y CENS, cumplimiento de estándares de telemedicina del Minsal y de la nueva ley chilena de datos personales (declaración de la empresa).</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Chocale, sep-2026; LinkedIn); autodeclarado</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Clinia (Reservo)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Citas y agenda</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Portal de agendamiento de Reservo (ecosistema)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Los pacientes pueden encontrar un profesional y reservar hora en el Portal de Agendamiento de Reservo, complemento de Clinia.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Medesk, Comparasoftware); no es parte de la app Clinia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4708,7 +4772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4856,7 +4920,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4866,12 +4930,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Localización de centros médicos y farmacias</t>
+          <t>Integración con calendario del dispositivo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Localiza centros médicos y farmacias.</t>
+          <t>Permite añadir las citas a la app Calendario del teléfono (versión Pro).</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4883,7 +4947,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4893,17 +4957,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reserva de citas médicas</t>
+          <t>Localización de centros médicos y farmacias</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Reserva de horas en la institución.</t>
+          <t>Localiza centros médicos y farmacias.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4989,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Gestión completa de agenda dentro de la institución.</t>
+          <t>Reserva de horas en la institución.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4937,22 +5001,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Compartición y consentimiento</t>
+          <t>Citas y agenda</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Acceso del profesional al historial del paciente</t>
+          <t>Reserva de citas médicas</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>El médico puede revisar el historial e ingresar datos automáticamente.</t>
+          <t>Gestión completa de agenda dentro de la institución.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4964,34 +5028,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Compartición y consentimiento</t>
+          <t>Citas y agenda</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Compartir con personas sin cuenta mediante clave segura</t>
+          <t>Reserva de citas médicas</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Datos compartibles con personas sin cuenta mediante clave de acceso segura enviada por email.</t>
+          <t>Los pacientes pueden encontrar un profesional y reservar hora en el Portal de Agendamiento de Reservo, complemento de Clinia.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5001,24 +5065,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Compartir datos con cuidador o persona de confianza</t>
+          <t>Acceso del profesional al historial del paciente</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Comparte de forma privada datos de salud (actividad, corazón, movilidad) con una persona de confianza, eligiendo qué y con quién.</t>
+          <t>El médico puede revisar el historial e ingresar datos automáticamente.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5028,24 +5092,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+          <t>Compartir con personas sin cuenta mediante clave segura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Permite compartir información con médicos, familia y amistades.</t>
+          <t>Datos compartibles con personas sin cuenta mediante clave de acceso segura enviada por email.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5055,24 +5119,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+          <t>Compartir datos con cuidador o persona de confianza</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Comparte los documentos guardados con los profesionales en la consulta.</t>
+          <t>Comparte de forma privada datos de salud (actividad, corazón, movilidad) con una persona de confianza, eligiendo qué y con quién.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5087,19 +5151,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Comparte registros con familiares o profesionales.</t>
+          <t>Permite compartir información con médicos, familia y amistades.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5114,19 +5178,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Traspaso de registros a hospitales.</t>
+          <t>Comparte los documentos guardados con los profesionales en la consulta.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5141,7 +5205,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Compartir información con profesionales de salud.</t>
+          <t>Comparte registros con familiares o profesionales.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5153,7 +5217,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5168,19 +5232,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Comparte información con cuidadores, maestros o profesionales de confianza.</t>
+          <t>Traspaso de registros a hospitales.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5195,19 +5259,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Acceso de clínicos limitado en el tiempo.</t>
+          <t>Compartir información con profesionales de salud.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5222,19 +5286,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>El usuario decide con qué profesionales comparte su información.</t>
+          <t>Comparte información con cuidadores, maestros o profesionales de confianza.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5249,7 +5313,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>El usuario autoriza a proveedores a acceder y usar sus datos de salud.</t>
+          <t>Acceso de clínicos limitado en el tiempo.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -5261,7 +5325,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5271,24 +5335,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gestión de consentimiento sobre uso de datos</t>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>El usuario decide si sus registros se usan para análisis de big data.</t>
+          <t>El usuario decide con qué profesionales comparte su información.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5298,24 +5362,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ingreso de datos por profesional con consentimiento</t>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>El médico puede ingresar datos al historial con autorización del paciente.</t>
+          <t>El usuario autoriza a proveedores a acceder y usar sus datos de salud.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5325,78 +5389,78 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Red social con profesionales y familiares</t>
+          <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Interacción con médicos, dentistas, kinesiólogos, entrenadores y familiares dentro de la red.</t>
+          <t>El usuario decide si sus registros se usan para análisis de big data.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Emergencia</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ficha de emergencia (alergias y medicación)</t>
+          <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Disponibilidad del historial en situaciones de atención.</t>
+          <t>El médico puede ingresar datos al historial con autorización del paciente.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Emergencia</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ficha de emergencia (alergias y medicación)</t>
+          <t>Red social con profesionales y familiares</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Acceso a datos clave del paciente en emergencias.</t>
+          <t>Interacción con médicos, dentistas, kinesiólogos, entrenadores y familiares dentro de la red.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5411,34 +5475,34 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ficha de emergencia con alergias y medicación accesible rápidamente.</t>
+          <t>Disponibilidad del historial en situaciones de atención.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Familia y dependientes</t>
+          <t>Emergencia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Perfiles familiares / dependientes</t>
+          <t>Ficha de emergencia (alergias y medicación)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Vincula familiares a la cuenta.</t>
+          <t>Acceso a datos clave del paciente en emergencias.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -5450,34 +5514,34 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Familia y dependientes</t>
+          <t>Emergencia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Perfiles familiares / dependientes</t>
+          <t>Ficha de emergencia (alergias y medicación)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Los padres pueden monitorear la salud de hijos pequeños.</t>
+          <t>Ficha de emergencia con alergias y medicación accesible rápidamente.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5492,19 +5556,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Historial por perfil para cada miembro de la familia.</t>
+          <t>Vincula familiares a la cuenta.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MiRedSalud (RedSalud)</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5519,34 +5583,34 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Guardar y administrar historial propio y familiar.</t>
+          <t>Los padres pueden monitorear la salud de hijos pequeños.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gestión documental</t>
+          <t>Familia y dependientes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Almacenamiento de documentos médicos</t>
+          <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sube estudios, imágenes, indicaciones médicas y notas personales; accesible en consulta o por terceros en emergencias.</t>
+          <t>Historial por perfil para cada miembro de la familia.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -5558,22 +5622,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>MiRedSalud (RedSalud)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Gestión documental</t>
+          <t>Familia y dependientes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Almacenamiento de documentos médicos</t>
+          <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Reúne recetas, diagnósticos y laboratorios en un solo lugar.</t>
+          <t>Guardar y administrar historial propio y familiar.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5585,7 +5649,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5600,19 +5664,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Guarda en un solo lugar exámenes, recetas, órdenes y certificados médicos.</t>
+          <t>Sube estudios, imágenes, indicaciones médicas y notas personales; accesible en consulta o por terceros en emergencias.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5627,19 +5691,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Organiza registros con carpetas y etiquetas.</t>
+          <t>Reúne recetas, diagnósticos y laboratorios en un solo lugar.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5654,7 +5718,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Almacena documentos clínicos del usuario en la app.</t>
+          <t>Guarda en un solo lugar exámenes, recetas, órdenes y certificados médicos.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -5666,7 +5730,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5681,19 +5745,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Administra fechas, prescripciones, archivos y citas desde la app.</t>
+          <t>Organiza registros con carpetas y etiquetas.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5703,12 +5767,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Almacenamiento de recetas</t>
+          <t>Almacenamiento de documentos médicos</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ver y descargar recetas, órdenes de examen y derivaciones.</t>
+          <t>Almacena documentos clínicos del usuario en la app.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5720,7 +5784,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5730,24 +5794,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Almacenamiento de recetas</t>
+          <t>Almacenamiento de documentos médicos</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Guarda recetas digitales.</t>
+          <t>Administra fechas, prescripciones, archivos y citas desde la app.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5757,24 +5821,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Búsqueda y filtros de documentos</t>
+          <t>Almacenamiento de recetas</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Guarda resultados de laboratorio, imágenes y PDFs; búsqueda y filtros.</t>
+          <t>Ver y descargar recetas, órdenes de examen y derivaciones.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5784,24 +5848,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Importación de órdenes/solicitudes médicas</t>
+          <t>Almacenamiento de recetas</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Descarga/genera órdenes médicas digitales.</t>
+          <t>Guarda recetas digitales.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5811,24 +5875,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Importación de órdenes/solicitudes médicas</t>
+          <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Importa solicitudes (órdenes) médicas a la app.</t>
+          <t>Guarda resultados de laboratorio, imágenes y PDFs; búsqueda y filtros.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5838,39 +5902,39 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Notificación y envío de resultados</t>
+          <t>Emisión de certificados médicos</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Avisa cuando hay exámenes/documentos disponibles; resultados de laboratorio y anatomía patológica compartibles por email o WhatsApp.</t>
+          <t>La ficha de la app incluye consulta de chequeos de salud y emisión de certificados médicos.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Historial institucional (solo datos de la propia red)</t>
+          <t>Importación de órdenes/solicitudes médicas</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ve historial de esa institución.</t>
+          <t>Descarga/genera órdenes médicas digitales.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5882,22 +5946,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Historial institucional (solo datos de la propia red)</t>
+          <t>Importación de órdenes/solicitudes médicas</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Historial institucional de consultas, urgencias y hospitalizaciones (solo datos de esa clínica).</t>
+          <t>Importa solicitudes (órdenes) médicas a la app.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5909,22 +5973,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MiRedSalud (RedSalud)</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Historial institucional (solo datos de la propia red)</t>
+          <t>Notificación y envío de resultados</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Acceso a información clínica de la red.</t>
+          <t>Avisa cuando hay exámenes/documentos disponibles; resultados de laboratorio y anatomía patológica compartibles por email o WhatsApp.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5936,7 +6000,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5946,24 +6010,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Información clínica unificada.</t>
+          <t>Ve historial de esa institución.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5973,24 +6037,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>El usuario registra sus antecedentes médicos en la app.</t>
+          <t>Historial institucional de consultas, urgencias y hospitalizaciones (solo datos de esa clínica).</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>MiRedSalud (RedSalud)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6000,12 +6064,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Centraliza el historial médico personal en el móvil.</t>
+          <t>Acceso a información clínica de la red.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6017,7 +6081,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6032,7 +6096,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Permite compilar datos de vida/salud, gestionarlos y pasarlos a instituciones médicas.</t>
+          <t>Información clínica unificada.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6044,7 +6108,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6059,19 +6123,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Centralizar registros y monitoreo desde el móvil.</t>
+          <t>El usuario registra sus antecedentes médicos en la app.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6081,24 +6145,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Línea de tiempo de salud</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Línea de tiempo con medicación, exámenes, citas y dieta.</t>
+          <t>Centraliza el historial médico personal en el móvil.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6108,24 +6172,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Línea de tiempo de salud</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Registra notas de medicación, exámenes (laboratorio e imagen), actividad física, recetas, dieta y citas.</t>
+          <t>Permite compilar datos de vida/salud, gestionarlos y pasarlos a instituciones médicas.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6135,120 +6199,120 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas.</t>
+          <t>Centralizar registros y monitoreo desde el móvil.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Incentivos y monetización de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Recompensas / monetización de datos del usuario</t>
+          <t>Línea de tiempo de salud</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>El usuario puede agregar y monetizar sus datos; recompensas en cripto.</t>
+          <t>Línea de tiempo con medicación, exámenes, citas y dieta.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Coaching de salud con IA</t>
+          <t>Línea de tiempo de salud</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Coaching personalizado con IA.</t>
+          <t>Registra notas de medicación, exámenes (laboratorio e imagen), actividad física, recetas, dieta y citas.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Detección de patrones en métricas de salud con IA</t>
+          <t>Registro de alergias y vacunas</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Detecta patrones entre métricas de salud y fitness.</t>
+          <t>Registro de alergias y vacunas.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Incentivos y monetización de datos</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
+          <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Explica resultados complejos en lenguaje simple.</t>
+          <t>Plan de convertir Medipass en superapp con gestión de salud diaria y mercado de datos, integrada con la EMR Dr.Palette.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6260,22 +6324,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Incentivos y monetización de datos</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
+          <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Explica exámenes en lenguaje simple.</t>
+          <t>El usuario puede agregar y monetizar sus datos; recompensas en cripto.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6287,7 +6351,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6297,24 +6361,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
+          <t>Coaching de salud con IA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Interpreta exámenes de laboratorio.</t>
+          <t>Coaching personalizado con IA.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6324,24 +6388,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Orientación médica con IA</t>
+          <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Orientación médica instantánea mediante IA.</t>
+          <t>Interpreta datos de Apple Health y registros en contexto y detecta cambios.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6351,12 +6415,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Preparación de consultas médicas con IA</t>
+          <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Prepara preguntas para el médico.</t>
+          <t>Detecta patrones entre métricas de salud y fitness.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6368,7 +6432,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6378,12 +6442,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Preparación de consultas médicas con IA</t>
+          <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Prepara preguntas para el médico.</t>
+          <t>Explica resultados complejos en lenguaje simple.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6395,7 +6459,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6405,12 +6469,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Resumen de historial con IA</t>
+          <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Resume instrucciones de atención.</t>
+          <t>Explica exámenes en lenguaje simple.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6422,7 +6486,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6432,39 +6496,39 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Resumen de historial con IA</t>
+          <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Resume el historial del usuario.</t>
+          <t>Interpreta exámenes de laboratorio.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Orientación médica con IA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Vista central de alergias, condiciones, vacunas, laboratorio, medicación, procedimientos y signos vitales.</t>
+          <t>Mejora de jun-2026 (GPT-5.5 Instant): detecta cuándo puede requerirse atención urgente, pide contexto y explica la incertidumbre.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6476,27 +6540,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Orientación médica con IA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Conexión de historiales electrónicos y apps como Apple Health, MyFitnessPal, Peloton.</t>
+          <t>Orientación médica instantánea mediante IA.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -6508,17 +6572,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Acceso a historiales electrónicos de proveedores de EE.UU. vía b.well; solo EE.UU., sin plazo anunciado para Latinoamérica.</t>
+          <t>Prepara preguntas para el médico.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6535,17 +6599,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Acceso a resultados y registros de salud (beta, Pro/Max, EE.UU.).</t>
+          <t>Prepara preguntas para el médico.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6557,49 +6621,49 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Resumen de historial con IA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Datos desde profesionales/centros que usan Reservo (fichas clínicas, agenda, telemedicina).</t>
+          <t>Resume instrucciones de atención.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Resumen de historial con IA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Reúne registros de hospitales, resultados de laboratorio y datos genómicos.</t>
+          <t>Resume el historial del usuario.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6611,7 +6675,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6621,12 +6685,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Analítica poblacional B2B</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Analítica poblacional on-chain; integrada con Epic, Cerner, Meditech y Allscripts (B2B).</t>
+          <t>Vista central de alergias, condiciones, vacunas, laboratorio, medicación, procedimientos y signos vitales.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6638,7 +6702,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6648,24 +6712,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Android, iOS y escritorio; médicos acceden a historias digitalizadas, envían estudios e indicaciones y organizan agenda.</t>
+          <t>Conexión de historiales electrónicos y apps como Apple Health, MyFitnessPal, Peloton.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6675,24 +6739,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Disponible en App Store y Google Play. Reservo opera en Chile, México y Argentina y está certificada por FONASA y CENS.</t>
+          <t>Acceso a historiales electrónicos de proveedores de EE.UU. vía b.well; solo EE.UU., sin plazo anunciado para Latinoamérica.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6702,24 +6766,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Disponible en web, iOS y Android.</t>
+          <t>Además de b.well y Apple Health, vincula registros de One Medical y Function Health (solo EE.UU., Free/Go/Plus/Pro, web e iOS).</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6729,12 +6793,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Versión digital de los registros con acceso por móvil o web.</t>
+          <t>Acceso a resultados y registros de salud (beta, Pro/Max, EE.UU.).</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6746,7 +6810,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6756,24 +6820,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Integración beta en apps iOS/Android.</t>
+          <t>Datos desde profesionales/centros que usan Reservo (fichas clínicas, agenda, telemedicina).</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6783,12 +6847,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Integración beta con Health Connect en la app móvil; conectores de registros (HealthEx, Function) solo para Pro/Max en EE.UU.</t>
+          <t>Tras autenticación simple, trae los últimos 3 años de historial de hospitales integrados (p. ej. Samsung Seoul, SNUH, Severance).</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6800,7 +6864,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6810,39 +6874,39 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
+          <t>Sincroniza resultados desde centros de salud y permite subir fotos o documentos de las solicitudes médicas.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Gestión de lista de medicamentos</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Listas de medicamentos, vitaminas y suplementos con horarios; escaneo de etiqueta del frasco solo en EE.UU.</t>
+          <t>Reúne registros de hospitales, resultados de laboratorio y datos genómicos.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6854,22 +6918,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
+          <t>Analítica poblacional B2B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Recordatorios desde el app.</t>
+          <t>Analítica poblacional on-chain; integrada con Epic, Cerner, Meditech y Allscripts (B2B).</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6881,157 +6945,157 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Recordatorios de citas/medicación.</t>
+          <t>Android, iOS y escritorio; médicos acceden a historias digitalizadas, envían estudios e indicaciones y organizan agenda.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Registro de tomas y adherencia al tratamiento</t>
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Registro de cada toma y control de adherencia; gestiona medicamentos propios y de familiares.</t>
+          <t>Disponible en App Store y Google Play. Reservo opera en Chile, México y Argentina y está certificada por FONASA y CENS.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Contenido educativo sobre salud</t>
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Busca que el paciente aprenda sobre sus enfermedades y sea más autónomo.</t>
+          <t>Disponible en web, iOS y Android.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores de salud.</t>
+          <t>Versión digital de los registros con acceso por móvil o web.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Importación y exportación de datos</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Datos de pasos, sueño, peso junto a registros.</t>
+          <t>Importar/exportar datos para compartir de forma segura con familias o cuidadores. Es MediPlanner Pro, de otro desarrollador (App Store MX, $39 MXN).</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Panel de seguimiento de salud y bienestar</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
+          <t>Integración beta en apps iOS/Android.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7043,49 +7107,49 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Valoración de profesionales</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Calificación de la atención de profesionales con autorización previa, compartible con otros usuarios.</t>
+          <t>Integración beta con Health Connect en la app móvil; conectores de registros (HealthEx, Function) solo para Pro/Max en EE.UU.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
+          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7097,22 +7161,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Gestión de lista de medicamentos</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Almacena huellas de datos médicos en un registro de solo escritura, sin guardar datos clínicos en cadena.</t>
+          <t>Listas de medicamentos, vitaminas y suplementos con horarios; escaneo de etiqueta del frasco solo en EE.UU.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7124,22 +7188,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Recordatorios de medicación y citas</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
+          <t>Recordatorios desde el app.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -7151,54 +7215,54 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Recordatorios de medicación y citas</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
+          <t>Recordatorios de citas/medicación.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso</t>
+          <t>Registro de tomas y adherencia al tratamiento</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
+          <t>Registro de cada toma y control de adherencia; gestiona medicamentos propios y de familiares.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
@@ -7210,17 +7274,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso</t>
+          <t>Contenido educativo sobre salud</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Almacenamiento seguro del historial con criterios de seguridad estrictos, comparable a apps bancarias.</t>
+          <t>Busca que el paciente aprenda sobre sus enfermedades y sea más autónomo.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7232,49 +7296,49 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Identidad descentralizada (DID)</t>
+          <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Gestión de identificadores descentralizados en Panacea.</t>
+          <t>Gráficas de evolución de indicadores de salud.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
+          <t>Datos de pasos, sueño, peso junto a registros.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7286,49 +7350,49 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Modelo freemium y suscripción</t>
+          <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Planes para personas y empresas.</t>
+          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pagos con criptomoneda</t>
+          <t>Registro de nutrición</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Pago de consultas con token.</t>
+          <t>Escaneo de etiquetas nutricionales con la cámara; según un análisis, no escribe en HealthKit.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -7340,22 +7404,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
+          <t>Seguimiento de salud femenina</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
+          <t>Extiende el seguimiento de ciclo con perimenopausia y menopausia.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -7367,25 +7431,430 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>Clingot</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Valoración de profesionales</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Calificación de la atención de profesionales con autorización previa, compartible con otros usuarios.</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Almacena huellas de datos médicos en un registro de solo escritura, sin guardar datos clínicos en cadena.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
           <t>Medicalchain</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Cifrado y control de acceso</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Infomed</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Cifrado y control de acceso</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Almacenamiento seguro del historial con criterios de seguridad estrictos, comparable a apps bancarias.</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Clinia (Reservo)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Cumplimiento regulatorio de salud y datos</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Reservo declara plataforma certificada por Fonasa y CENS, cumplimiento de estándares de telemedicina del Minsal y de la nueva ley chilena de datos personales (declaración de la empresa).</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Identidad descentralizada (DID)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Gestión de identificadores descentralizados en Panacea.</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Privacidad reforzada para datos de salud</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Privacidad reforzada para datos de salud</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>El usuario activa y revoca permisos; los datos de salud compartidos se excluyen de la memoria de Claude y del entrenamiento.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Modelo freemium y suscripción</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Planes para personas y empresas.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Pagos con criptomoneda</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Pago de consultas con token.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Reclamo de seguro médico (indemnización) desde la app, con verificación de autenticidad de los registros vía blockchain por la aseguradora.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
         <is>
           <t>Telemedicina y atención remota</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>Teleconsultas con GP.</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
@@ -7402,7 +7871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -7528,6 +7997,8 @@
           <t>Búsqueda de profesionales de salud</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7538,6 +8009,17 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2">
         <f>COUNTIF(C2:Q2,"✓")</f>
         <v/>
@@ -7559,11 +8041,24 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3">
         <f>COUNTIF(C3:Q3,"✓")</f>
         <v/>
@@ -7577,14 +8072,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Localización de centros médicos y farmacias</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+          <t>Integración con calendario del dispositivo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4">
         <f>COUNTIF(C4:Q4,"✓")</f>
         <v/>
@@ -7598,14 +8107,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reserva de citas médicas</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+          <t>Localización de centros médicos y farmacias</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5">
         <f>COUNTIF(C5:Q5,"✓")</f>
         <v/>
@@ -7614,19 +8137,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Compartición y consentimiento</t>
+          <t>Citas y agenda</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Acceso del profesional al historial del paciente</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>Reserva de citas médicas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6">
         <f>COUNTIF(C6:Q6,"✓")</f>
         <v/>
@@ -7640,14 +8181,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Compartir con personas sin cuenta mediante clave segura</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+          <t>Acceso del profesional al historial del paciente</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7">
         <f>COUNTIF(C7:Q7,"✓")</f>
         <v/>
@@ -7661,14 +8216,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Compartir datos con cuidador o persona de confianza</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+          <t>Compartir con personas sin cuenta mediante clave segura</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8">
         <f>COUNTIF(C8:Q8,"✓")</f>
         <v/>
@@ -7682,49 +8251,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Compartir información con profesionales (consentimiento del usuario)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+          <t>Compartir datos con cuidador o persona de confianza</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9">
         <f>COUNTIF(C9:Q9,"✓")</f>
         <v/>
@@ -7738,7 +8286,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gestión de consentimiento sobre uso de datos</t>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -7746,6 +8316,26 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10">
         <f>COUNTIF(C10:Q10,"✓")</f>
         <v/>
@@ -7759,14 +8349,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ingreso de datos por profesional con consentimiento</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>Gestión de consentimiento sobre uso de datos</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11">
         <f>COUNTIF(C11:Q11,"✓")</f>
         <v/>
@@ -7780,14 +8384,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Red social con profesionales y familiares</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+          <t>Ingreso de datos por profesional con consentimiento</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12">
         <f>COUNTIF(C12:Q12,"✓")</f>
         <v/>
@@ -7796,29 +8414,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Emergencia</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ficha de emergencia (alergias y medicación)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+          <t>Red social con profesionales y familiares</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13">
         <f>COUNTIF(C13:Q13,"✓")</f>
         <v/>
@@ -7827,34 +8449,41 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Familia y dependientes</t>
+          <t>Emergencia</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Perfiles familiares / dependientes</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+          <t>Ficha de emergencia (alergias y medicación)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14">
         <f>COUNTIF(C14:Q14,"✓")</f>
         <v/>
@@ -7863,15 +8492,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gestión documental</t>
+          <t>Familia y dependientes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Almacenamiento de documentos médicos</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+          <t>Perfiles familiares / dependientes</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -7881,21 +8512,25 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15">
         <f>COUNTIF(C15:Q15,"✓")</f>
         <v/>
@@ -7909,19 +8544,44 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Almacenamiento de recetas</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+          <t>Almacenamiento de documentos médicos</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16">
         <f>COUNTIF(C16:Q16,"✓")</f>
         <v/>
@@ -7935,14 +8595,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Búsqueda y filtros de documentos</t>
-        </is>
-      </c>
+          <t>Almacenamiento de recetas</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17">
         <f>COUNTIF(C17:Q17,"✓")</f>
         <v/>
@@ -7956,19 +8634,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Importación de órdenes/solicitudes médicas</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+          <t>Búsqueda y filtros de documentos</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18">
         <f>COUNTIF(C18:Q18,"✓")</f>
         <v/>
@@ -7982,14 +8669,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Notificación y envío de resultados</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
+          <t>Emisión de certificados médicos</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19">
         <f>COUNTIF(C19:Q19,"✓")</f>
         <v/>
@@ -7998,20 +8699,33 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Historial institucional (solo datos de la propia red)</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
+          <t>Importación de órdenes/solicitudes médicas</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -8024,39 +8738,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+          <t>Notificación y envío de resultados</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21">
         <f>COUNTIF(C21:Q21,"✓")</f>
         <v/>
@@ -8070,14 +8778,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Línea de tiempo de salud</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+          <t>Historial institucional (solo datos de la propia red)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22">
         <f>COUNTIF(C22:Q22,"✓")</f>
         <v/>
@@ -8091,10 +8817,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -8107,19 +8863,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Incentivos y monetización de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Recompensas / monetización de datos del usuario</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+          <t>Línea de tiempo de salud</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24">
         <f>COUNTIF(C24:Q24,"✓")</f>
         <v/>
@@ -8128,19 +8898,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Coaching de salud con IA</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+          <t>Registro de alergias y vacunas</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25">
         <f>COUNTIF(C25:Q25,"✓")</f>
         <v/>
@@ -8149,19 +8933,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Incentivos y monetización de datos</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Detección de patrones en métricas de salud con IA</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
+          <t>Recompensas / monetización de datos del usuario</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26">
         <f>COUNTIF(C26:Q26,"✓")</f>
         <v/>
@@ -8175,24 +8977,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
+          <t>Coaching de salud con IA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27">
         <f>COUNTIF(C27:Q27,"✓")</f>
         <v/>
@@ -8206,14 +9012,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Orientación médica con IA</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
+          <t>Detección de patrones en métricas de salud con IA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28">
         <f>COUNTIF(C28:Q28,"✓")</f>
         <v/>
@@ -8227,15 +9051,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Preparación de consultas médicas con IA</t>
-        </is>
-      </c>
+          <t>Interpretación de exámenes con IA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -8253,15 +9094,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Resumen de historial con IA</t>
-        </is>
-      </c>
+          <t>Orientación médica con IA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -8274,39 +9128,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
+          <t>Preparación de consultas médicas con IA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31">
         <f>COUNTIF(C31:Q31,"✓")</f>
         <v/>
@@ -8315,19 +9167,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Analítica poblacional B2B</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
+          <t>Resumen de historial con IA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32">
         <f>COUNTIF(C32:Q32,"✓")</f>
         <v/>
@@ -8341,24 +9211,52 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
+          <t>Agregación de registros de múltiples instituciones</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33">
         <f>COUNTIF(C33:Q33,"✓")</f>
         <v/>
@@ -8372,14 +9270,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+          <t>Analítica poblacional B2B</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34">
         <f>COUNTIF(C34:Q34,"✓")</f>
         <v/>
@@ -8393,19 +9305,36 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35">
         <f>COUNTIF(C35:Q35,"✓")</f>
         <v/>
@@ -8414,19 +9343,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gestión de lista de medicamentos</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36">
         <f>COUNTIF(C36:Q36,"✓")</f>
         <v/>
@@ -8435,24 +9378,33 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
+          <t>Importación y exportación de datos</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37">
         <f>COUNTIF(C37:Q37,"✓")</f>
         <v/>
@@ -8461,19 +9413,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Registro de tomas y adherencia al tratamiento</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38">
         <f>COUNTIF(C38:Q38,"✓")</f>
         <v/>
@@ -8482,19 +9452,33 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Contenido educativo sobre salud</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+          <t>Gestión de lista de medicamentos</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39">
         <f>COUNTIF(C39:Q39,"✓")</f>
         <v/>
@@ -8503,19 +9487,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
+          <t>Recordatorios de medicación y citas</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40">
         <f>COUNTIF(C40:Q40,"✓")</f>
         <v/>
@@ -8524,19 +9526,33 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
+          <t>Registro de tomas y adherencia al tratamiento</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41">
         <f>COUNTIF(C41:Q41,"✓")</f>
         <v/>
@@ -8550,14 +9566,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Panel de seguimiento de salud y bienestar</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
+          <t>Contenido educativo sobre salud</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42">
         <f>COUNTIF(C42:Q42,"✓")</f>
         <v/>
@@ -8571,14 +9601,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Valoración de profesionales</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
+          <t>Gráficas de evolución de indicadores</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43">
         <f>COUNTIF(C43:Q43,"✓")</f>
         <v/>
@@ -8587,29 +9631,33 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44">
         <f>COUNTIF(C44:Q44,"✓")</f>
         <v/>
@@ -8618,24 +9666,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+          <t>Panel de seguimiento de salud y bienestar</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45">
         <f>COUNTIF(C45:Q45,"✓")</f>
         <v/>
@@ -8644,19 +9701,33 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Identidad descentralizada (DID)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
+          <t>Registro de nutrición</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46">
         <f>COUNTIF(C46:Q46,"✓")</f>
         <v/>
@@ -8665,19 +9736,33 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
+          <t>Seguimiento de salud femenina</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47">
         <f>COUNTIF(C47:Q47,"✓")</f>
         <v/>
@@ -8686,19 +9771,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Modelo freemium y suscripción</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
+          <t>Valoración de profesionales</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48">
         <f>COUNTIF(C48:Q48,"✓")</f>
         <v/>
@@ -8707,12 +9806,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pagos con criptomoneda</t>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -8720,6 +9834,13 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49">
         <f>COUNTIF(C49:Q49,"✓")</f>
         <v/>
@@ -8728,19 +9849,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
+          <t>Cifrado y control de acceso</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50">
         <f>COUNTIF(C50:Q50,"✓")</f>
         <v/>
@@ -8749,21 +9888,249 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Telemedicina y atención remota</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Teleconsulta con profesionales</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+          <t>Cumplimiento regulatorio de salud y datos</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
       <c r="R51">
         <f>COUNTIF(C51:Q51,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Identidad descentralizada (DID)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52">
+        <f>COUNTIF(C52:Q52,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Privacidad reforzada para datos de salud</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53">
+        <f>COUNTIF(C53:Q53,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Modelo freemium y suscripción</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54">
+        <f>COUNTIF(C54:Q54,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Pagos con criptomoneda</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55">
+        <f>COUNTIF(C55:Q55,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56">
+        <f>COUNTIF(C56:Q56,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Telemedicina y atención remota</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Teleconsulta con profesionales</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57">
+        <f>COUNTIF(C57:Q57,"✓")</f>
         <v/>
       </c>
     </row>
@@ -8778,7 +10145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -8896,6 +10263,13 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>VUELTA 3 COMPLETA (2026-10-08 04:08 UTC): Clinia, MiRedSalud y Mediko verificados (+2 filas). Contador de loops = 3 para todos, Revisado reiniciado a "No". func_norm (113 filas) y tabla_frecuencia (56 funcionalidades) regenerados. Vuelta 4 parte con Meedika, Infomed, MediPlanner, Clingot.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -513,12 +513,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar. [Vuelta 3] Sin novedades 2026 ni confirmación de la app Android en Google Play; usuarios actuales desconocidos. Nota de prensa no indica año de lanzamiento explícito.</t>
+          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar. [Vuelta 3] Sin novedades 2026 ni confirmación de la app Android en Google Play; usuarios actuales desconocidos. Nota de prensa no indica año de lanzamiento explícito. [Vuelta 4] Sin fuentes nuevas; portalinnova.cl no aparece en búsquedas. Sigue dependiendo de una sola nota de prensa.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -553,12 +553,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapa A] Fundada 2019 por Diego Ibarra, Andrés Fantuzzi y Gabriel Zamora. Lanzada mar-2021 en App Store y Play Store con 1.200 usuarios; planeaba nueva versión jul-2021 y ronda de US$500 mil. Objetivo: llevar el historial en el celular, acceso en emergencias, médico puede ingresar datos con consentimiento. Estado actual NO verificado (posible app inactiva). URL es la nota de prensa; sitio oficial por confirmar. [Vuelta 3] Sin evidencia posterior a 2021; relanzamiento previsto jul-2021 no confirmado. Probable app inactiva.</t>
+          <t>[DIRECTO · Chile · etapa A] Fundada 2019 por Diego Ibarra, Andrés Fantuzzi y Gabriel Zamora. Lanzada mar-2021 en App Store y Play Store con 1.200 usuarios; planeaba nueva versión jul-2021 y ronda de US$500 mil. Objetivo: llevar el historial en el celular, acceso en emergencias, médico puede ingresar datos con consentimiento. Estado actual NO verificado (posible app inactiva). URL es la nota de prensa; sitio oficial por confirmar. [Vuelta 3] Sin evidencia posterior a 2021; relanzamiento previsto jul-2021 no confirmado. Probable app inactiva. [Vuelta 4] Sin cambios; sigue sin evidencia posterior a 2021.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -593,12 +593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · México] Historial por perfil familiar, alergias, vacunas, recetas digitales, gráficas de evolución, agendamiento, compartir con profesionales. Gratis en App Store MX. Sin evidencia de uso en Chile. Cubre parte de la etapa C (familia). [Vuelta 3] Existen dos apps distintas: MediPlanner (gratis, Rym Solutions, MX, 3,7/5 con 3 calificaciones) y MediPlanner Pro (otro desarrollador, $39 MXN). Sin presencia verificada en Chile.</t>
+          <t>[REGIONAL · México] Historial por perfil familiar, alergias, vacunas, recetas digitales, gráficas de evolución, agendamiento, compartir con profesionales. Gratis en App Store MX. Sin evidencia de uso en Chile. Cubre parte de la etapa C (familia). [Vuelta 3] Existen dos apps distintas: MediPlanner (gratis, Rym Solutions, MX, 3,7/5 con 3 calificaciones) y MediPlanner Pro (otro desarrollador, $39 MXN). Sin presencia verificada en Chile. [Vuelta 4] No pude confirmar el desarrollador de la versión gratuita (Rym Solutions no se repite en esta búsqueda). MediPlanner Pro (fichas BR/OM) guardaría datos solo en el dispositivo, sin nube; no confundir con MedPlanner/AskHEMI (otra empresa).</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · Argentina · débil] App para cargar antecedentes médicos propios. Única referencia: nota de opinión en grupoanimal.mx sin fecha verificada. Estado y sitio por confirmar. [Vuelta 3] Referencias de 2017 (apps4citizens, La Nación); sitio y precio no verificados; puede estar inactiva.</t>
+          <t>[REGIONAL · Argentina · débil] App para cargar antecedentes médicos propios. Única referencia: nota de opinión en grupoanimal.mx sin fecha verificada. Estado y sitio por confirmar. [Vuelta 3] Referencias de 2017 (apps4citizens, La Nación); sitio y precio no verificados; puede estar inactiva. [Vuelta 4] Sin fuentes nuevas.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4758,6 +4758,38 @@
       <c r="F114" t="inlineStr">
         <is>
           <t>Búsqueda web (Medesk, Comparasoftware); no es parte de la app Clinia</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>MediPlanner</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Medicación y recordatorios</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Tratamientos automáticos desde la receta digital del médico</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Según la ficha de la App Store MX, los tratamientos llegan automáticamente desde la receta digital del médico (autodeclarado, sin verificar).</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Búsqueda web (ficha App Store MX); vuelta 4</t>
         </is>
       </c>
     </row>
@@ -7997,8 +8029,6 @@
           <t>Búsqueda de profesionales de salud</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8009,17 +8039,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2">
         <f>COUNTIF(C2:Q2,"✓")</f>
         <v/>
@@ -8041,24 +8060,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3">
         <f>COUNTIF(C3:Q3,"✓")</f>
         <v/>
@@ -8075,25 +8081,11 @@
           <t>Integración con calendario del dispositivo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4">
         <f>COUNTIF(C4:Q4,"✓")</f>
         <v/>
@@ -8110,25 +8102,11 @@
           <t>Localización de centros médicos y farmacias</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5">
         <f>COUNTIF(C5:Q5,"✓")</f>
         <v/>
@@ -8145,17 +8123,6 @@
           <t>Reserva de citas médicas</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8166,8 +8133,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6">
         <f>COUNTIF(C6:Q6,"✓")</f>
         <v/>
@@ -8184,25 +8149,11 @@
           <t>Acceso del profesional al historial del paciente</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7">
         <f>COUNTIF(C7:Q7,"✓")</f>
         <v/>
@@ -8219,25 +8170,11 @@
           <t>Compartir con personas sin cuenta mediante clave segura</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8">
         <f>COUNTIF(C8:Q8,"✓")</f>
         <v/>
@@ -8254,25 +8191,11 @@
           <t>Compartir datos con cuidador o persona de confianza</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9">
         <f>COUNTIF(C9:Q9,"✓")</f>
         <v/>
@@ -8294,13 +8217,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8326,16 +8247,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10">
         <f>COUNTIF(C10:Q10,"✓")</f>
         <v/>
@@ -8352,25 +8268,11 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11">
         <f>COUNTIF(C11:Q11,"✓")</f>
         <v/>
@@ -8387,25 +8289,11 @@
           <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12">
         <f>COUNTIF(C12:Q12,"✓")</f>
         <v/>
@@ -8422,25 +8310,11 @@
           <t>Red social con profesionales y familiares</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13">
         <f>COUNTIF(C13:Q13,"✓")</f>
         <v/>
@@ -8467,23 +8341,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14">
         <f>COUNTIF(C14:Q14,"✓")</f>
         <v/>
@@ -8500,8 +8362,6 @@
           <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8512,25 +8372,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15">
         <f>COUNTIF(C15:Q15,"✓")</f>
         <v/>
@@ -8552,8 +8403,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8569,19 +8418,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16">
         <f>COUNTIF(C16:Q16,"✓")</f>
         <v/>
@@ -8598,29 +8439,16 @@
           <t>Almacenamiento de recetas</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17">
         <f>COUNTIF(C17:Q17,"✓")</f>
         <v/>
@@ -8637,25 +8465,11 @@
           <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18">
         <f>COUNTIF(C18:Q18,"✓")</f>
         <v/>
@@ -8672,25 +8486,11 @@
           <t>Emisión de certificados médicos</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19">
         <f>COUNTIF(C19:Q19,"✓")</f>
         <v/>
@@ -8712,19 +8512,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8746,25 +8533,11 @@
           <t>Notificación y envío de resultados</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21">
         <f>COUNTIF(C21:Q21,"✓")</f>
         <v/>
@@ -8781,29 +8554,16 @@
           <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22">
         <f>COUNTIF(C22:Q22,"✓")</f>
         <v/>
@@ -8820,36 +8580,26 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8871,25 +8621,11 @@
           <t>Línea de tiempo de salud</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24">
         <f>COUNTIF(C24:Q24,"✓")</f>
         <v/>
@@ -8906,25 +8642,11 @@
           <t>Registro de alergias y vacunas</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25">
         <f>COUNTIF(C25:Q25,"✓")</f>
         <v/>
@@ -8941,11 +8663,6 @@
           <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8956,14 +8673,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26">
         <f>COUNTIF(C26:Q26,"✓")</f>
         <v/>
@@ -8980,25 +8689,11 @@
           <t>Coaching de salud con IA</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27">
         <f>COUNTIF(C27:Q27,"✓")</f>
         <v/>
@@ -9015,15 +8710,6 @@
           <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9034,10 +8720,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28">
         <f>COUNTIF(C28:Q28,"✓")</f>
         <v/>
@@ -9054,15 +8736,6 @@
           <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9073,9 +8746,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9097,24 +8767,11 @@
           <t>Orientación médica con IA</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9136,15 +8793,6 @@
           <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9155,10 +8803,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31">
         <f>COUNTIF(C31:Q31,"✓")</f>
         <v/>
@@ -9175,15 +8819,6 @@
           <t>Resumen de historial con IA</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9194,10 +8829,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32">
         <f>COUNTIF(C32:Q32,"✓")</f>
         <v/>
@@ -9219,10 +8850,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9233,7 +8860,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9249,14 +8875,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33">
         <f>COUNTIF(C33:Q33,"✓")</f>
         <v/>
@@ -9273,25 +8896,11 @@
           <t>Analítica poblacional B2B</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34">
         <f>COUNTIF(C34:Q34,"✓")</f>
         <v/>
@@ -9308,9 +8917,6 @@
           <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9321,20 +8927,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35">
         <f>COUNTIF(C35:Q35,"✓")</f>
         <v/>
@@ -9351,25 +8948,11 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36">
         <f>COUNTIF(C36:Q36,"✓")</f>
         <v/>
@@ -9386,25 +8969,11 @@
           <t>Importación y exportación de datos</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37">
         <f>COUNTIF(C37:Q37,"✓")</f>
         <v/>
@@ -9421,29 +8990,16 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38">
         <f>COUNTIF(C38:Q38,"✓")</f>
         <v/>
@@ -9460,25 +9016,11 @@
           <t>Gestión de lista de medicamentos</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39">
         <f>COUNTIF(C39:Q39,"✓")</f>
         <v/>
@@ -9500,24 +9042,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40">
         <f>COUNTIF(C40:Q40,"✓")</f>
         <v/>
@@ -9534,25 +9063,11 @@
           <t>Registro de tomas y adherencia al tratamiento</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41">
         <f>COUNTIF(C41:Q41,"✓")</f>
         <v/>
@@ -9569,25 +9084,11 @@
           <t>Contenido educativo sobre salud</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42">
         <f>COUNTIF(C42:Q42,"✓")</f>
         <v/>
@@ -9604,25 +9105,11 @@
           <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43">
         <f>COUNTIF(C43:Q43,"✓")</f>
         <v/>
@@ -9639,25 +9126,11 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44">
         <f>COUNTIF(C44:Q44,"✓")</f>
         <v/>
@@ -9674,25 +9147,11 @@
           <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45">
         <f>COUNTIF(C45:Q45,"✓")</f>
         <v/>
@@ -9709,25 +9168,11 @@
           <t>Registro de nutrición</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46">
         <f>COUNTIF(C46:Q46,"✓")</f>
         <v/>
@@ -9744,25 +9189,11 @@
           <t>Seguimiento de salud femenina</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47">
         <f>COUNTIF(C47:Q47,"✓")</f>
         <v/>
@@ -9779,25 +9210,11 @@
           <t>Valoración de profesionales</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48">
         <f>COUNTIF(C48:Q48,"✓")</f>
         <v/>
@@ -9814,11 +9231,6 @@
           <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9834,13 +9246,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49">
         <f>COUNTIF(C49:Q49,"✓")</f>
         <v/>
@@ -9857,29 +9262,16 @@
           <t>Cifrado y control de acceso</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50">
         <f>COUNTIF(C50:Q50,"✓")</f>
         <v/>
@@ -9896,25 +9288,11 @@
           <t>Cumplimiento regulatorio de salud y datos</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51">
         <f>COUNTIF(C51:Q51,"✓")</f>
         <v/>
@@ -9931,25 +9309,11 @@
           <t>Identidad descentralizada (DID)</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52">
         <f>COUNTIF(C52:Q52,"✓")</f>
         <v/>
@@ -9966,15 +9330,6 @@
           <t>Privacidad reforzada para datos de salud</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9985,10 +9340,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
       <c r="R53">
         <f>COUNTIF(C53:Q53,"✓")</f>
         <v/>
@@ -10005,20 +9356,6 @@
           <t>Modelo freemium y suscripción</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10040,25 +9377,11 @@
           <t>Pagos con criptomoneda</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55">
         <f>COUNTIF(C55:Q55,"✓")</f>
         <v/>
@@ -10075,25 +9398,11 @@
           <t>Reclamos y trámites con seguros</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56">
         <f>COUNTIF(C56:Q56,"✓")</f>
         <v/>
@@ -10110,25 +9419,11 @@
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57">
         <f>COUNTIF(C57:Q57,"✓")</f>
         <v/>
@@ -10145,7 +9440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -10270,6 +9565,13 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Vuelta 4 (iter. 1, 2026-10-08 06:08 UTC): Meedika, Infomed, MediPlanner, Clingot verificados (+1 fila). CANDIDATO A COMPETIDOR (no agregado a la lista, a decisión del usuario): HealthChain (Chile), startup de registros médicos con blockchain; CEO Javier Leyton; fuente: entrevista en Diario Bitcoin sin fecha visible. Pendientes: Healfies, Patientory, MediBloc, Medicalchain, etc.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B. [Vuelta 2] Lanzada simultáneamente en Brasil, Argentina y EE.UU.; permite compartir con no registrados vía clave por email. Sin novedades posteriores a 2016. [Vuelta 3] Sin evidencia de actividad reciente ni de cierre; Gust/Dealroom la listan en Florianópolis (10 empleados, healfies.com) sin fecha de actualización. Estado sin confirmar.</t>
+          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B. [Vuelta 2] Lanzada simultáneamente en Brasil, Argentina y EE.UU.; permite compartir con no registrados vía clave por email. Sin novedades posteriores a 2016. [Vuelta 3] Sin evidencia de actividad reciente ni de cierre; Gust/Dealroom la listan en Florianópolis (10 empleados, healfies.com) sin fecha de actualización. Estado sin confirmar. [Vuelta 4] Sin Google Play localizado; no confundir con la app Healfy (otro producto). Sin novedades.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -713,12 +713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain. [Vuelta 2] Sin noticias 2026 encontradas en búsqueda; sitio oficial bloqueado. [Vuelta 3] Búsqueda adicional solo devuelve hitos de 2017 (token sale US$7,2M) y 2019 (Serie A de US$5,3M, cierre no confirmado); sin datos 2025-26 propios.</t>
+          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain. [Vuelta 2] Sin noticias 2026 encontradas en búsqueda; sitio oficial bloqueado. [Vuelta 3] Búsqueda adicional solo devuelve hitos de 2017 (token sale US$7,2M) y 2019 (Serie A de US$5,3M, cierre no confirmado); sin datos 2025-26 propios. [Vuelta 4] App pública lanzada en la conferencia JP Morgan Healthcare (2019); red PTOYMatrix (blockchain HIPAA); socios reportados: StartUp Health y Kaiser Permanente (beta). Estado actual en App Store/Google Play sin confirmar.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -753,12 +753,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain. [Vuelta 2] Panacea incluye DID, Append Only Log, IBC y PNFT; sin anuncios 2026 localizados. [Vuelta 3] Medipass: app en Corea con 20 hospitales/aseguradoras integrados (fecha de la lista desconocida) y plan 2022 de superapp con marketplace de datos; operación actual sin confirmar.</t>
+          <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain. [Vuelta 2] Panacea incluye DID, Append Only Log, IBC y PNFT; sin anuncios 2026 localizados. [Vuelta 3] Medipass: app en Corea con 20 hospitales/aseguradoras integrados (fecha de la lista desconocida) y plan 2022 de superapp con marketplace de datos; operación actual sin confirmar. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -793,12 +793,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · Reino Unido · INACTIVO] Londres, 2017, Ethereum, con telemedicina. Piloto según registro de la UE (2020). Tracxn/PitchBook lo marcan fuera de operación (ago-2025). Solo caso de aprendizaje: no cuenta como competidor activo. [Vuelta 2] Token MTN deslistado de Bitfinex el 26-mar-2021; sin hallazgos de actividad posterior. [Vuelta 3] Seedtable la marca activa sin fuente; no hallé registro en Companies House. Sigue tratándose como caso de aprendizaje.</t>
+          <t>[BLOCKCHAIN · Reino Unido · INACTIVO] Londres, 2017, Ethereum, con telemedicina. Piloto según registro de la UE (2020). Tracxn/PitchBook lo marcan fuera de operación (ago-2025). Solo caso de aprendizaje: no cuenta como competidor activo. [Vuelta 2] Token MTN deslistado de Bitfinex el 26-mar-2021; sin hallazgos de actividad posterior. [Vuelta 3] Seedtable la marca activa sin fuente; no hallé registro en Companies House. Sigue tratándose como caso de aprendizaje. [Vuelta 4] Pre-venta reportada de US$20M en MedTokens (un solo artículo secundario, sin verificar); modelo de token en revisión y exploración de security token según AMA; integraciones y servicios de 2019 sin confirmar.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4790,6 +4790,166 @@
       <c r="F115" t="inlineStr">
         <is>
           <t>Búsqueda web (ficha App Store MX); vuelta 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Comunidad de pacientes con condiciones similares</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Los usuarios con condiciones similares pueden preguntar, recibir recomendaciones y compartir experiencias.</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Búsqueda web (BioSpace, Bitcoin Magazine; app pública 2019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Patientory</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Historial y perfil clínico</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Seguimiento de visitas, facturas médicas, seguros, vacunas y medicamentos</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>App gratuita para seguir visitas al médico, facturas médicas, datos personales, seguros, inmunizaciones y medicamentos de farmacia.</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Búsqueda web (BioSpace); estado actual sin verificar</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Pago de consultas con tarjeta o MedTokens (piloto The Groves Medical Centre)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Piloto en New Malden (Londres): consultas por video pagables con tarjeta o con MedTokens.</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Digital Health 2018, HTN); inactivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Incentivos y monetización de datos</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Recompensas por compartir datos con investigación (planificado)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Centros de investigación y farmacéuticas recompensarían con MedTokens a quienes compartan sus datos; no confirmado como ejecutado.</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Digital Health, HTN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Integración con sistemas de médicos generales del Reino Unido (planificado)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Según una AMA sin fecha, integraba dos sistemas de GP que cubren ~80% del mercado UK; no confirmado como ejecutado.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Búsqueda web (AMA comunitaria); confianza baja</t>
         </is>
       </c>
     </row>
@@ -9440,7 +9600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -9572,6 +9732,13 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Vuelta 4 (iter. 2, 2026-10-08 08:08 UTC): Healfies, Patientory, MediBloc, Medicalchain verificados (+5 filas). Pendientes: Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas, Clinia, MiRedSalud, Mediko.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -833,12 +833,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Agrega registros clínicos vía FHIR; &gt;500 instituciones conectadas en EE.UU. (2018). Sin evidencia de disponibilidad en Chile. Incluida en el dispositivo. Amenaza si FHIR/IPS-CL se adopta en Chile. [Vuelta 2] Sin disponibilidad de registros clínicos en Chile (solo EE.UU., Reino Unido, Canadá). [Vuelta 3] iOS 27 (WWDC 8-jun-2026; publicado ~14-sep-2026): rediseño del app Health, menopausia, nutrición por cámara. El coach de salud con IA no se anunció. Sin ampliación de Health Records a Chile.</t>
+          <t>[ADYACENTE · global] Agrega registros clínicos vía FHIR; &gt;500 instituciones conectadas en EE.UU. (2018). Sin evidencia de disponibilidad en Chile. Incluida en el dispositivo. Amenaza si FHIR/IPS-CL se adopta en Chile. [Vuelta 2] Sin disponibilidad de registros clínicos en Chile (solo EE.UU., Reino Unido, Canadá). [Vuelta 3] iOS 27 (WWDC 8-jun-2026; publicado ~14-sep-2026): rediseño del app Health, menopausia, nutrición por cámara. El coach de salud con IA no se anunció. Sin ampliación de Health Records a Chile. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -873,12 +873,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Lanzado 7-ene-2026. Conecta registros médicos; conectores solo en EE.UU. Dentro de suscripción del asistente. Fija la expectativa de consultar y resumir el historial. [Vuelta 2] Confirmado: registros solo EE.UU.; sin anuncios para Latinoamérica. Hay inconsistencia de fechas entre fuentes (7-ene-2026 lanzamiento vs. jul-2026 despliegue de registros). [Vuelta 3] Fechas aclaradas: presentación 7-ene-2026 (acceso limitado); despliegue de Health in ChatGPT con Apple Health y registros en EE.UU. el 23-jul-2026; mejora de salud jun-2026. Sin anuncios para Latinoamérica ni para sep-oct 2026.</t>
+          <t>[ADYACENTE · global] Lanzado 7-ene-2026. Conecta registros médicos; conectores solo en EE.UU. Dentro de suscripción del asistente. Fija la expectativa de consultar y resumir el historial. [Vuelta 2] Confirmado: registros solo EE.UU.; sin anuncios para Latinoamérica. Hay inconsistencia de fechas entre fuentes (7-ene-2026 lanzamiento vs. jul-2026 despliegue de registros). [Vuelta 3] Fechas aclaradas: presentación 7-ene-2026 (acceso limitado); despliegue de Health in ChatGPT con Apple Health y registros en EE.UU. el 23-jul-2026; mejora de salud jun-2026. Sin anuncios para Latinoamérica ni para sep-oct 2026. [Vuelta 4] Septiembre 2026: permisos por defecto para datos conectados (14-sep) y explicaciones por gráfico/métrica (28-sep); ChatGPT for Clinicians (abr-2026) para clínicos verificados de EE.UU. Más del 70% de usuarios de Health permite usar datos conectados sin pedir permiso (según OpenAI). Sigue solo EE.UU.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -913,12 +913,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Lanzado 11-ene-2026. Conectores solo en EE.UU., planes Pro/Max. Nota: producto de Anthropic, conflicto de interés al evaluarlo. [Vuelta 2] Sin cambios fuera de EE.UU. (HealthEx y Function para Pro/Max). [Vuelta 3] Sin anuncios posteriores a enero de 2026. Hoja de ruta de HealthEx (agendar, buscar prestadores, recetas) sin confirmar como lanzada.</t>
+          <t>[ADYACENTE · global] Lanzado 11-ene-2026. Conectores solo en EE.UU., planes Pro/Max. Nota: producto de Anthropic, conflicto de interés al evaluarlo. [Vuelta 2] Sin cambios fuera de EE.UU. (HealthEx y Function para Pro/Max). [Vuelta 3] Sin anuncios posteriores a enero de 2026. Hoja de ruta de HealthEx (agendar, buscar prestadores, recetas) sin confirmar como lanzada. [Vuelta 4] Sin anuncios nuevos. Fuentes discrepan en el acceso (Pro/Max según Fortune y la mayoría; Pro/Team según Times of AI); sin evidencia de disponibilidad fuera de EE.UU.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -953,12 +953,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones. [Vuelta 2] App concreta: Mi Alemana Go (Clínica Alemana, Chile), con historial desde 2018, recetas, órdenes, familiar vinculado y resultados. [Vuelta 3] Búsqueda de otras clínicas (Las Condes, Santa María, UC Christus) sin ficha de app confirmada; solo canales digitales genéricos.</t>
+          <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones. [Vuelta 2] App concreta: Mi Alemana Go (Clínica Alemana, Chile), con historial desde 2018, recetas, órdenes, familiar vinculado y resultados. [Vuelta 3] Búsqueda de otras clínicas (Las Condes, Santa María, UC Christus) sin ficha de app confirmada; solo canales digitales genéricos. [Vuelta 4] Mi Alemana Go: 3,1/5 con 137 calificaciones (App Store Chile), pantalla de inicio rediseñada para gestionar salud propia y familiar; sin evidencia de teleconsulta ni pagos en la app.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4950,6 +4950,134 @@
       <c r="F120" t="inlineStr">
         <is>
           <t>Búsqueda web (AMA comunitaria); confianza baja</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Explicaciones personalizadas al seleccionar gráfico, métrica o registro</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Desde 28-sep-2026, en la pestaña Health se puede elegir un gráfico, métrica o registro y obtener explicaciones basadas en los datos conectados.</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Búsqueda web (notas de versión de OpenAI); solo EE.UU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Permiso por defecto para usar datos de Health conectados</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Desde 14-sep-2026, las nuevas conexiones heredan la configuración global de plugins: ChatGPT puede usar datos de Health sin pedir permiso cada vez salvo acciones sensibles (web primero, móvil después).</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Búsqueda web (notas de versión de OpenAI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Inteligencia artificial</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ChatGPT for Clinicians y Healthcare Public Data</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Producto para clínicos verificados de EE.UU. (gratis, abr-2026); desde 1-sep-2026 un plugin con nueve apps de fuentes públicas (investigación, ensayos, medicamentos, Medicare, prestadores), de solo lectura y sin acceso a fichas de pacientes.</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Fierce Healthcare, PYMNTS, notas de OpenAI); adyacente a nuestro foco</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Familia y dependientes</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Pantalla única para gestionar salud propia y familiar (Mi Alemana Go)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Rediseño de la pantalla de inicio para gestionar la salud propia y la de la familia en una sola vista.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Ficha App Store Chile (Mi Alemana Go, 3,1/5 con 137 calificaciones)</t>
         </is>
       </c>
     </row>
@@ -9600,7 +9728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -9739,6 +9867,13 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Vuelta 4 (iter. 3, 2026-10-08 10:08 UTC): Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas verificados (+4 filas). Pendientes: Clinia, MiRedSalud, Mediko (cierran la vuelta 4 y regeneran func_norm/tabla_frecuencia).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -518,11 +518,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -558,11 +558,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -598,11 +598,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -638,11 +638,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -678,11 +678,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -718,11 +718,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -758,11 +758,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -798,11 +798,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -838,11 +838,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -878,11 +878,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -918,11 +918,11 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -958,11 +958,11 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar. [Vuelta 2] Confirmado por el CEO de Reservo (LinkedIn): app para pacientes en App Store y Google Play; guarda y comparte exámenes, recetas, órdenes y certificados. Fecha exacta de lanzamiento, precio y modelo de datos sin verificar. [Vuelta 3] Sin novedades de oct-2026. Reservo (Chile, México, Argentina) declara certificación Fonasa/CENS y cumplimiento de la nueva ley de datos personales; el Portal de Agendamiento de Reservo complementa a Clinia. Precio y modelo de datos sin verificar.</t>
+          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar. [Vuelta 2] Confirmado por el CEO de Reservo (LinkedIn): app para pacientes en App Store y Google Play; guarda y comparte exámenes, recetas, órdenes y certificados. Fecha exacta de lanzamiento, precio y modelo de datos sin verificar. [Vuelta 3] Sin novedades de oct-2026. Reservo (Chile, México, Argentina) declara certificación Fonasa/CENS y cumplimiento de la nueva ley de datos personales; el Portal de Agendamiento de Reservo complementa a Clinia. Precio y modelo de datos sin verificar. [Vuelta 4] Una búsqueda adicional no encontró fuentes independientes sobre Clinia de Reservo (aparecen otras empresas llamadas Clinia); la evidencia sigue siendo la publicación del CEO en LinkedIn y notas de Reservo. Confianza media.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis). [Vuelta 2] La búsqueda no encontró fuentes adicionales ni ficha de la app chilena (solo una app RedSalud de otro país); funciones sin confirmar. [Vuelta 3] Rankings de terceros la ubican como app médica gratuita nº 1 en App Store y Google Play Chile (fecha desconocida); sin descripción de funciones ni confirmación del desarrollador en Google Play.</t>
+          <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis). [Vuelta 2] La búsqueda no encontró fuentes adicionales ni ficha de la app chilena (solo una app RedSalud de otro país); funciones sin confirmar. [Vuelta 3] Rankings de terceros la ubican como app médica gratuita nº 1 en App Store y Google Play Chile (fecha desconocida); sin descripción de funciones ni confirmación del desarrollador en Google Play. [Vuelta 4] Sin documentación oficial chilena localizada; las fichas con funciones (agendar, telemedicina, historial de hijos) corresponden a una app RedSalud de otro país. Quejas públicas 2020-21 sobre acceso en línea a resultados. Funciones de MiRedSalud sin confirmar.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc. [Vuelta 2] Sin precios ni planes vigentes localizados; sitio oficial bloqueado. [Vuelta 3] Pauta (oct-2024): su fundador, Tomás Riddell, dice que no reemplaza a médicos y apunta a lo ambulatorio y a la espera de derivación a especialidad en el sistema público. Financiamiento: fuentes discrepan (CLP 25M en dic-2023 según Bouncewatch; ~$40M según Descubre.vc). Precios vigentes sin verificar.</t>
+          <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc. [Vuelta 2] Sin precios ni planes vigentes localizados; sitio oficial bloqueado. [Vuelta 3] Pauta (oct-2024): su fundador, Tomás Riddell, dice que no reemplaza a médicos y apunta a lo ambulatorio y a la espera de derivación a especialidad en el sistema público. Financiamiento: fuentes discrepan (CLP 25M en dic-2023 según Bouncewatch; ~$40M según Descubre.vc). Precios vigentes sin verificar. [Vuelta 4] Entrevista oct-2024 menciona integración con la pasarela Flow. Sin novedades 2025-26 ni rondas verificadas; la cifra de US$40M de Bouncewatch es dudosa (perfil con 2 empleados).</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5081,6 +5081,38 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Integración con la pasarela de pagos Flow</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Pagos dentro de la plataforma mediante la pasarela Flow (según resumen de entrevista de Pauta, oct-2024; esperada para mejorar la experiencia).</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Pauta / Descubre.vc, 2024); estado actual sin verificar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5092,7 +5124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5888,7 +5920,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5903,19 +5935,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Los padres pueden monitorear la salud de hijos pequeños.</t>
+          <t>Rediseño de la pantalla de inicio para gestionar la salud propia y la de la familia en una sola vista.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5930,7 +5962,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Historial por perfil para cada miembro de la familia.</t>
+          <t>Los padres pueden monitorear la salud de hijos pequeños.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -5942,7 +5974,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MiRedSalud (RedSalud)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5957,46 +5989,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Guardar y administrar historial propio y familiar.</t>
+          <t>Historial por perfil para cada miembro de la familia.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>MiRedSalud (RedSalud)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gestión documental</t>
+          <t>Familia y dependientes</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Almacenamiento de documentos médicos</t>
+          <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sube estudios, imágenes, indicaciones médicas y notas personales; accesible en consulta o por terceros en emergencias.</t>
+          <t>Guardar y administrar historial propio y familiar.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6011,12 +6043,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Reúne recetas, diagnósticos y laboratorios en un solo lugar.</t>
+          <t>Sube estudios, imágenes, indicaciones médicas y notas personales; accesible en consulta o por terceros en emergencias.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6070,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Guarda en un solo lugar exámenes, recetas, órdenes y certificados médicos.</t>
+          <t>Reúne recetas, diagnósticos y laboratorios en un solo lugar.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6050,7 +6082,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6065,19 +6097,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Organiza registros con carpetas y etiquetas.</t>
+          <t>Guarda en un solo lugar exámenes, recetas, órdenes y certificados médicos.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6092,19 +6124,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Almacena documentos clínicos del usuario en la app.</t>
+          <t>Organiza registros con carpetas y etiquetas.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6119,19 +6151,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Administra fechas, prescripciones, archivos y citas desde la app.</t>
+          <t>Almacena documentos clínicos del usuario en la app.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6141,24 +6173,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Almacenamiento de recetas</t>
+          <t>Almacenamiento de documentos médicos</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ver y descargar recetas, órdenes de examen y derivaciones.</t>
+          <t>Administra fechas, prescripciones, archivos y citas desde la app.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6173,12 +6205,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Guarda recetas digitales.</t>
+          <t>Ver y descargar recetas, órdenes de examen y derivaciones.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -6195,12 +6227,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Búsqueda y filtros de documentos</t>
+          <t>Almacenamiento de recetas</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Guarda resultados de laboratorio, imágenes y PDFs; búsqueda y filtros.</t>
+          <t>Guarda recetas digitales.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -6212,7 +6244,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6222,24 +6254,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Emisión de certificados médicos</t>
+          <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>La ficha de la app incluye consulta de chequeos de salud y emisión de certificados médicos.</t>
+          <t>Guarda resultados de laboratorio, imágenes y PDFs; búsqueda y filtros.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6249,24 +6281,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Importación de órdenes/solicitudes médicas</t>
+          <t>Emisión de certificados médicos</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Descarga/genera órdenes médicas digitales.</t>
+          <t>La ficha de la app incluye consulta de chequeos de salud y emisión de certificados médicos.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6281,7 +6313,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Importa solicitudes (órdenes) médicas a la app.</t>
+          <t>Descarga/genera órdenes médicas digitales.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6293,7 +6325,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6303,12 +6335,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Notificación y envío de resultados</t>
+          <t>Importación de órdenes/solicitudes médicas</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Avisa cuando hay exámenes/documentos disponibles; resultados de laboratorio y anatomía patológica compartibles por email o WhatsApp.</t>
+          <t>Importa solicitudes (órdenes) médicas a la app.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6325,17 +6357,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Historial institucional (solo datos de la propia red)</t>
+          <t>Notificación y envío de resultados</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ve historial de esa institución.</t>
+          <t>Avisa cuando hay exámenes/documentos disponibles; resultados de laboratorio y anatomía patológica compartibles por email o WhatsApp.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6362,7 +6394,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Historial institucional de consultas, urgencias y hospitalizaciones (solo datos de esa clínica).</t>
+          <t>Ve historial de esa institución.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6374,7 +6406,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MiRedSalud (RedSalud)</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6389,7 +6421,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Acceso a información clínica de la red.</t>
+          <t>Historial institucional de consultas, urgencias y hospitalizaciones (solo datos de esa clínica).</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6401,7 +6433,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MiRedSalud (RedSalud)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6411,24 +6443,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Información clínica unificada.</t>
+          <t>Acceso a información clínica de la red.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6443,19 +6475,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>El usuario registra sus antecedentes médicos en la app.</t>
+          <t>Información clínica unificada.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6470,19 +6502,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Centraliza el historial médico personal en el móvil.</t>
+          <t>El usuario registra sus antecedentes médicos en la app.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6497,19 +6529,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Permite compilar datos de vida/salud, gestionarlos y pasarlos a instituciones médicas.</t>
+          <t>Centraliza el historial médico personal en el móvil.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6524,19 +6556,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Centralizar registros y monitoreo desde el móvil.</t>
+          <t>Permite compilar datos de vida/salud, gestionarlos y pasarlos a instituciones médicas.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6546,17 +6578,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Línea de tiempo de salud</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Línea de tiempo con medicación, exámenes, citas y dieta.</t>
+          <t>Centralizar registros y monitoreo desde el móvil.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6610,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Registra notas de medicación, exámenes (laboratorio e imagen), actividad física, recetas, dieta y citas.</t>
+          <t>Línea de tiempo con medicación, exámenes, citas y dieta.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6590,7 +6622,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6600,12 +6632,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas</t>
+          <t>Línea de tiempo de salud</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas.</t>
+          <t>Registra notas de medicación, exámenes (laboratorio e imagen), actividad física, recetas, dieta y citas.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6617,27 +6649,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Incentivos y monetización de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Recompensas / monetización de datos del usuario</t>
+          <t>Registro de alergias y vacunas</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Plan de convertir Medipass en superapp con gestión de salud diaria y mercado de datos, integrada con la EMR Dr.Palette.</t>
+          <t>Registro de alergias y vacunas.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
@@ -6649,17 +6681,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Incentivos y monetización de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Recompensas / monetización de datos del usuario</t>
+          <t>Seguimiento de visitas, gastos y seguros</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>El usuario puede agregar y monetizar sus datos; recompensas en cripto.</t>
+          <t>App gratuita para seguir visitas al médico, facturas médicas, datos personales, seguros, inmunizaciones y medicamentos de farmacia.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6671,22 +6703,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Incentivos y monetización de datos</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Coaching de salud con IA</t>
+          <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Coaching personalizado con IA.</t>
+          <t>Plan de convertir Medipass en superapp con gestión de salud diaria y mercado de datos, integrada con la EMR Dr.Palette.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6698,22 +6730,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Incentivos y monetización de datos</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Detección de patrones en métricas de salud con IA</t>
+          <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Interpreta datos de Apple Health y registros en contexto y detecta cambios.</t>
+          <t>Centros de investigación y farmacéuticas recompensarían con MedTokens a quienes compartan sus datos; no confirmado como ejecutado.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6725,22 +6757,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Incentivos y monetización de datos</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Detección de patrones en métricas de salud con IA</t>
+          <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Detecta patrones entre métricas de salud y fitness.</t>
+          <t>El usuario puede agregar y monetizar sus datos; recompensas en cripto.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6762,12 +6794,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
+          <t>Asistente de IA para profesionales de salud</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Explica resultados complejos en lenguaje simple.</t>
+          <t>Producto para clínicos verificados de EE.UU. (gratis, abr-2026); desde 1-sep-2026 un plugin con nueve apps de fuentes públicas (investigación, ensayos, medicamentos, Medicare, prestadores), de solo lectura y sin acceso a fichas de pacientes.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6779,7 +6811,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6789,12 +6821,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
+          <t>Coaching de salud con IA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Explica exámenes en lenguaje simple.</t>
+          <t>Coaching personalizado con IA.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6806,7 +6838,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6816,24 +6848,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
+          <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Interpreta exámenes de laboratorio.</t>
+          <t>Interpreta datos de Apple Health y registros en contexto y detecta cambios.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6843,12 +6875,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Orientación médica con IA</t>
+          <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mejora de jun-2026 (GPT-5.5 Instant): detecta cuándo puede requerirse atención urgente, pide contexto y explica la incertidumbre.</t>
+          <t>Detecta patrones entre métricas de salud y fitness.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6860,7 +6892,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6870,17 +6902,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Orientación médica con IA</t>
+          <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Orientación médica instantánea mediante IA.</t>
+          <t>Explica resultados complejos en lenguaje simple.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6929,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Preparación de consultas médicas con IA</t>
+          <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Prepara preguntas para el médico.</t>
+          <t>Desde 28-sep-2026, en la pestaña Health se puede elegir un gráfico, métrica o registro y obtener explicaciones basadas en los datos conectados.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6924,12 +6956,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Preparación de consultas médicas con IA</t>
+          <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Prepara preguntas para el médico.</t>
+          <t>Explica exámenes en lenguaje simple.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6941,7 +6973,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6951,24 +6983,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Resumen de historial con IA</t>
+          <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Resume instrucciones de atención.</t>
+          <t>Interpreta exámenes de laboratorio.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6978,12 +7010,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Resumen de historial con IA</t>
+          <t>Orientación médica con IA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Resume el historial del usuario.</t>
+          <t>Mejora de jun-2026 (GPT-5.5 Instant): detecta cuándo puede requerirse atención urgente, pide contexto y explica la incertidumbre.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6995,27 +7027,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Orientación médica con IA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Vista central de alergias, condiciones, vacunas, laboratorio, medicación, procedimientos y signos vitales.</t>
+          <t>Orientación médica instantánea mediante IA.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -7027,17 +7059,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Conexión de historiales electrónicos y apps como Apple Health, MyFitnessPal, Peloton.</t>
+          <t>Prepara preguntas para el médico.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7049,22 +7081,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Acceso a historiales electrónicos de proveedores de EE.UU. vía b.well; solo EE.UU., sin plazo anunciado para Latinoamérica.</t>
+          <t>Prepara preguntas para el médico.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7081,17 +7113,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Resumen de historial con IA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Además de b.well y Apple Health, vincula registros de One Medical y Function Health (solo EE.UU., Free/Go/Plus/Pro, web e iOS).</t>
+          <t>Resume instrucciones de atención.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7108,17 +7140,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Resumen de historial con IA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Acceso a resultados y registros de salud (beta, Pro/Max, EE.UU.).</t>
+          <t>Resume el historial del usuario.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7130,7 +7162,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7145,19 +7177,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Datos desde profesionales/centros que usan Reservo (fichas clínicas, agenda, telemedicina).</t>
+          <t>Vista central de alergias, condiciones, vacunas, laboratorio, medicación, procedimientos y signos vitales.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7172,7 +7204,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tras autenticación simple, trae los últimos 3 años de historial de hospitales integrados (p. ej. Samsung Seoul, SNUH, Severance).</t>
+          <t>Conexión de historiales electrónicos y apps como Apple Health, MyFitnessPal, Peloton.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7184,7 +7216,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7199,19 +7231,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Sincroniza resultados desde centros de salud y permite subir fotos o documentos de las solicitudes médicas.</t>
+          <t>Acceso a historiales electrónicos de proveedores de EE.UU. vía b.well; solo EE.UU., sin plazo anunciado para Latinoamérica.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7226,7 +7258,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Reúne registros de hospitales, resultados de laboratorio y datos genómicos.</t>
+          <t>Además de b.well y Apple Health, vincula registros de One Medical y Function Health (solo EE.UU., Free/Go/Plus/Pro, web e iOS).</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7238,7 +7270,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7248,12 +7280,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Analítica poblacional B2B</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Analítica poblacional on-chain; integrada con Epic, Cerner, Meditech y Allscripts (B2B).</t>
+          <t>Acceso a resultados y registros de salud (beta, Pro/Max, EE.UU.).</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7265,7 +7297,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7275,24 +7307,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Android, iOS y escritorio; médicos acceden a historias digitalizadas, envían estudios e indicaciones y organizan agenda.</t>
+          <t>Datos desde profesionales/centros que usan Reservo (fichas clínicas, agenda, telemedicina).</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7302,24 +7334,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Disponible en App Store y Google Play. Reservo opera en Chile, México y Argentina y está certificada por FONASA y CENS.</t>
+          <t>Tras autenticación simple, trae los últimos 3 años de historial de hospitales integrados (p. ej. Samsung Seoul, SNUH, Severance).</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7329,24 +7361,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Disponible en web, iOS y Android.</t>
+          <t>Sincroniza resultados desde centros de salud y permite subir fotos o documentos de las solicitudes médicas.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7356,12 +7388,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Versión digital de los registros con acceso por móvil o web.</t>
+          <t>Reúne registros de hospitales, resultados de laboratorio y datos genómicos.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7373,7 +7405,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7383,24 +7415,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Importación y exportación de datos</t>
+          <t>Analítica poblacional B2B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Importar/exportar datos para compartir de forma segura con familias o cuidadores. Es MediPlanner Pro, de otro desarrollador (App Store MX, $39 MXN).</t>
+          <t>Analítica poblacional on-chain; integrada con Epic, Cerner, Meditech y Allscripts (B2B).</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7410,24 +7442,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Integración beta en apps iOS/Android.</t>
+          <t>Android, iOS y escritorio; médicos acceden a historias digitalizadas, envían estudios e indicaciones y organizan agenda.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7437,24 +7469,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Integración beta con Health Connect en la app móvil; conectores de registros (HealthEx, Function) solo para Pro/Max en EE.UU.</t>
+          <t>Disponible en App Store y Google Play. Reservo opera en Chile, México y Argentina y está certificada por FONASA y CENS.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7464,39 +7496,39 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
+          <t>Disponible en web, iOS y Android.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Gestión de lista de medicamentos</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Listas de medicamentos, vitaminas y suplementos con horarios; escaneo de etiqueta del frasco solo en EE.UU.</t>
+          <t>Versión digital de los registros con acceso por móvil o web.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7508,135 +7540,135 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
+          <t>Importación y exportación de datos</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Recordatorios desde el app.</t>
+          <t>Importar/exportar datos para compartir de forma segura con familias o cuidadores. Es MediPlanner Pro, de otro desarrollador (App Store MX, $39 MXN).</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
+          <t>Integración con EHR de proveedores</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Recordatorios de citas/medicación.</t>
+          <t>Según una AMA sin fecha, integraba dos sistemas de GP que cubren ~80% del mercado UK; no confirmado como ejecutado.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Registro de tomas y adherencia al tratamiento</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Registro de cada toma y control de adherencia; gestiona medicamentos propios y de familiares.</t>
+          <t>Integración beta en apps iOS/Android.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Contenido educativo sobre salud</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Busca que el paciente aprenda sobre sus enfermedades y sea más autónomo.</t>
+          <t>Integración beta con Health Connect en la app móvil; conectores de registros (HealthEx, Function) solo para Pro/Max en EE.UU.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores de salud.</t>
+          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
@@ -7648,17 +7680,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Gestión de lista de medicamentos</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Datos de pasos, sueño, peso junto a registros.</t>
+          <t>Listas de medicamentos, vitaminas y suplementos con horarios; escaneo de etiqueta del frasco solo en EE.UU.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7670,27 +7702,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Panel de seguimiento de salud y bienestar</t>
+          <t>Importación automática de tratamientos desde receta digital</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
+          <t>Según la ficha de la App Store MX, los tratamientos llegan automáticamente desde la receta digital del médico (autodeclarado, sin verificar).</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
@@ -7702,17 +7734,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Registro de nutrición</t>
+          <t>Recordatorios de medicación y citas</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Escaneo de etiquetas nutricionales con la cámara; según un análisis, no escribe en HealthKit.</t>
+          <t>Recordatorios desde el app.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -7724,49 +7756,49 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seguimiento de salud femenina</t>
+          <t>Recordatorios de medicación y citas</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Extiende el seguimiento de ciclo con perimenopausia y menopausia.</t>
+          <t>Recordatorios de citas/medicación.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Valoración de profesionales</t>
+          <t>Registro de tomas y adherencia al tratamiento</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Calificación de la atención de profesionales con autorización previa, compartible con otros usuarios.</t>
+          <t>Registro de cada toma y control de adherencia; gestiona medicamentos propios y de familiares.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -7778,22 +7810,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Comunidad de pacientes</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
+          <t>Los usuarios con condiciones similares pueden preguntar, recibir recomendaciones y compartir experiencias.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -7805,76 +7837,76 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Contenido educativo sobre salud</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Almacena huellas de datos médicos en un registro de solo escritura, sin guardar datos clínicos en cadena.</t>
+          <t>Busca que el paciente aprenda sobre sus enfermedades y sea más autónomo.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
+          <t>Gráficas de evolución de indicadores de salud.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
+          <t>Datos de pasos, sueño, peso junto a registros.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -7886,22 +7918,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso</t>
+          <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
+          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7913,88 +7945,88 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso</t>
+          <t>Registro de nutrición</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Almacenamiento seguro del historial con criterios de seguridad estrictos, comparable a apps bancarias.</t>
+          <t>Escaneo de etiquetas nutricionales con la cámara; según un análisis, no escribe en HealthKit.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cumplimiento regulatorio de salud y datos</t>
+          <t>Seguimiento de salud femenina</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Reservo declara plataforma certificada por Fonasa y CENS, cumplimiento de estándares de telemedicina del Minsal y de la nueva ley chilena de datos personales (declaración de la empresa).</t>
+          <t>Extiende el seguimiento de ciclo con perimenopausia y menopausia.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Identidad descentralizada (DID)</t>
+          <t>Valoración de profesionales</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Gestión de identificadores descentralizados en Panacea.</t>
+          <t>Calificación de la atención de profesionales con autorización previa, compartible con otros usuarios.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8004,12 +8036,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
+          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8021,7 +8053,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8031,12 +8063,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>El usuario activa y revoca permisos; los datos de salud compartidos se excluyen de la memoria de Claude y del entrenamiento.</t>
+          <t>Almacena huellas de datos médicos en un registro de solo escritura, sin guardar datos clínicos en cadena.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8048,49 +8080,49 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Modelo freemium y suscripción</t>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Planes para personas y empresas.</t>
+          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Pagos con criptomoneda</t>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Pago de consultas con token.</t>
+          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8102,22 +8134,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
+          <t>Cifrado y control de acceso</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
+          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8129,52 +8161,349 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
+          <t>Cifrado y control de acceso</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Reclamo de seguro médico (indemnización) desde la app, con verificación de autenticidad de los registros vía blockchain por la aseguradora.</t>
+          <t>Almacenamiento seguro del historial con criterios de seguridad estrictos, comparable a apps bancarias.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>Clinia (Reservo)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Cumplimiento regulatorio de salud y datos</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Reservo declara plataforma certificada por Fonasa y CENS, cumplimiento de estándares de telemedicina del Minsal y de la nueva ley chilena de datos personales (declaración de la empresa).</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Gestión de consentimiento sobre uso de datos</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Desde 14-sep-2026, las nuevas conexiones heredan la configuración global de plugins: ChatGPT puede usar datos de Health sin pedir permiso cada vez salvo acciones sensibles (web primero, móvil después).</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Identidad descentralizada (DID)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Gestión de identificadores descentralizados en Panacea.</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Privacidad reforzada para datos de salud</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Privacidad reforzada para datos de salud</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>El usuario activa y revoca permisos; los datos de salud compartidos se excluyen de la memoria de Claude y del entrenamiento.</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Modelo freemium y suscripción</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Planes para personas y empresas.</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
           <t>Medicalchain</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Pagos con criptomoneda</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Pago de consultas con token.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Pagos con criptomoneda</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Piloto en New Malden (Londres): consultas por video pagables con tarjeta o con MedTokens.</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Pagos dentro de la app</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Pagos dentro de la plataforma mediante la pasarela Flow (según resumen de entrevista de Pauta, oct-2024; esperada para mejorar la experiencia).</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Reclamo de seguro médico (indemnización) desde la app, con verificación de autenticidad de los registros vía blockchain por la aseguradora.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Medicalchain</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
         <is>
           <t>Telemedicina y atención remota</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>Teleconsultas con GP.</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
@@ -8191,7 +8520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R57"/>
+  <dimension ref="A1:R64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8317,6 +8646,8 @@
           <t>Búsqueda de profesionales de salud</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8327,6 +8658,17 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2">
         <f>COUNTIF(C2:Q2,"✓")</f>
         <v/>
@@ -8348,11 +8690,24 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3">
         <f>COUNTIF(C3:Q3,"✓")</f>
         <v/>
@@ -8369,11 +8724,25 @@
           <t>Integración con calendario del dispositivo</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4">
         <f>COUNTIF(C4:Q4,"✓")</f>
         <v/>
@@ -8390,11 +8759,25 @@
           <t>Localización de centros médicos y farmacias</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5">
         <f>COUNTIF(C5:Q5,"✓")</f>
         <v/>
@@ -8411,6 +8794,17 @@
           <t>Reserva de citas médicas</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8421,6 +8815,8 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6">
         <f>COUNTIF(C6:Q6,"✓")</f>
         <v/>
@@ -8437,11 +8833,25 @@
           <t>Acceso del profesional al historial del paciente</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7">
         <f>COUNTIF(C7:Q7,"✓")</f>
         <v/>
@@ -8458,11 +8868,25 @@
           <t>Compartir con personas sin cuenta mediante clave segura</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8">
         <f>COUNTIF(C8:Q8,"✓")</f>
         <v/>
@@ -8479,11 +8903,25 @@
           <t>Compartir datos con cuidador o persona de confianza</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9">
         <f>COUNTIF(C9:Q9,"✓")</f>
         <v/>
@@ -8505,11 +8943,13 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8535,11 +8975,16 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10">
         <f>COUNTIF(C10:Q10,"✓")</f>
         <v/>
@@ -8556,11 +9001,25 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11">
         <f>COUNTIF(C11:Q11,"✓")</f>
         <v/>
@@ -8577,11 +9036,25 @@
           <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12">
         <f>COUNTIF(C12:Q12,"✓")</f>
         <v/>
@@ -8598,11 +9071,25 @@
           <t>Red social con profesionales y familiares</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13">
         <f>COUNTIF(C13:Q13,"✓")</f>
         <v/>
@@ -8629,11 +9116,23 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14">
         <f>COUNTIF(C14:Q14,"✓")</f>
         <v/>
@@ -8650,6 +9149,8 @@
           <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8660,16 +9161,25 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15">
         <f>COUNTIF(C15:Q15,"✓")</f>
         <v/>
@@ -8691,6 +9201,8 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8706,11 +9218,19 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16">
         <f>COUNTIF(C16:Q16,"✓")</f>
         <v/>
@@ -8727,16 +9247,29 @@
           <t>Almacenamiento de recetas</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17">
         <f>COUNTIF(C17:Q17,"✓")</f>
         <v/>
@@ -8753,11 +9286,25 @@
           <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18">
         <f>COUNTIF(C18:Q18,"✓")</f>
         <v/>
@@ -8774,11 +9321,25 @@
           <t>Emisión de certificados médicos</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19">
         <f>COUNTIF(C19:Q19,"✓")</f>
         <v/>
@@ -8800,6 +9361,19 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8821,11 +9395,25 @@
           <t>Notificación y envío de resultados</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21">
         <f>COUNTIF(C21:Q21,"✓")</f>
         <v/>
@@ -8842,16 +9430,29 @@
           <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22">
         <f>COUNTIF(C22:Q22,"✓")</f>
         <v/>
@@ -8868,26 +9469,36 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8909,11 +9520,25 @@
           <t>Línea de tiempo de salud</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24">
         <f>COUNTIF(C24:Q24,"✓")</f>
         <v/>
@@ -8930,11 +9555,25 @@
           <t>Registro de alergias y vacunas</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25">
         <f>COUNTIF(C25:Q25,"✓")</f>
         <v/>
@@ -8943,24 +9582,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Incentivos y monetización de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Recompensas / monetización de datos del usuario</t>
-        </is>
-      </c>
+          <t>Seguimiento de visitas, gastos y seguros</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26">
         <f>COUNTIF(C26:Q26,"✓")</f>
         <v/>
@@ -8969,19 +9617,41 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Incentivos y monetización de datos</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Coaching de salud con IA</t>
-        </is>
-      </c>
+          <t>Recompensas / monetización de datos del usuario</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27">
         <f>COUNTIF(C27:Q27,"✓")</f>
         <v/>
@@ -8995,19 +9665,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Detección de patrones en métricas de salud con IA</t>
-        </is>
-      </c>
+          <t>Asistente de IA para profesionales de salud</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28">
         <f>COUNTIF(C28:Q28,"✓")</f>
         <v/>
@@ -9021,24 +9700,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
+          <t>Coaching de salud con IA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29">
         <f>COUNTIF(C29:Q29,"✓")</f>
         <v/>
@@ -9052,19 +9735,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Orientación médica con IA</t>
-        </is>
-      </c>
+          <t>Detección de patrones en métricas de salud con IA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30">
         <f>COUNTIF(C30:Q30,"✓")</f>
         <v/>
@@ -9078,15 +9774,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Preparación de consultas médicas con IA</t>
-        </is>
-      </c>
+          <t>Interpretación de exámenes con IA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -9104,15 +9817,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Resumen de historial con IA</t>
-        </is>
-      </c>
+          <t>Orientación médica con IA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -9125,49 +9851,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+          <t>Preparación de consultas médicas con IA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33">
         <f>COUNTIF(C33:Q33,"✓")</f>
         <v/>
@@ -9176,19 +9890,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Analítica poblacional B2B</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
+          <t>Resumen de historial con IA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34">
         <f>COUNTIF(C34:Q34,"✓")</f>
         <v/>
@@ -9202,24 +9934,52 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
+          <t>Agregación de registros de múltiples instituciones</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35">
         <f>COUNTIF(C35:Q35,"✓")</f>
         <v/>
@@ -9233,14 +9993,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+          <t>Analítica poblacional B2B</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36">
         <f>COUNTIF(C36:Q36,"✓")</f>
         <v/>
@@ -9254,14 +10028,36 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Importación y exportación de datos</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37">
         <f>COUNTIF(C37:Q37,"✓")</f>
         <v/>
@@ -9275,19 +10071,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38">
         <f>COUNTIF(C38:Q38,"✓")</f>
         <v/>
@@ -9296,19 +10101,33 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gestión de lista de medicamentos</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
+          <t>Importación y exportación de datos</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39">
         <f>COUNTIF(C39:Q39,"✓")</f>
         <v/>
@@ -9317,24 +10136,33 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
+          <t>Integración con EHR de proveedores</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40">
         <f>COUNTIF(C40:Q40,"✓")</f>
         <v/>
@@ -9343,19 +10171,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Registro de tomas y adherencia al tratamiento</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41">
         <f>COUNTIF(C41:Q41,"✓")</f>
         <v/>
@@ -9364,19 +10210,33 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Contenido educativo sobre salud</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+          <t>Gestión de lista de medicamentos</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42">
         <f>COUNTIF(C42:Q42,"✓")</f>
         <v/>
@@ -9385,19 +10245,33 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores</t>
-        </is>
-      </c>
+          <t>Importación automática de tratamientos desde receta digital</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43">
         <f>COUNTIF(C43:Q43,"✓")</f>
         <v/>
@@ -9406,19 +10280,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
-        </is>
-      </c>
+          <t>Recordatorios de medicación y citas</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44">
         <f>COUNTIF(C44:Q44,"✓")</f>
         <v/>
@@ -9427,19 +10319,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Panel de seguimiento de salud y bienestar</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
+          <t>Registro de tomas y adherencia al tratamiento</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45">
         <f>COUNTIF(C45:Q45,"✓")</f>
         <v/>
@@ -9453,14 +10359,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Registro de nutrición</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
+          <t>Comunidad de pacientes</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46">
         <f>COUNTIF(C46:Q46,"✓")</f>
         <v/>
@@ -9474,14 +10394,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Seguimiento de salud femenina</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
+          <t>Contenido educativo sobre salud</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47">
         <f>COUNTIF(C47:Q47,"✓")</f>
         <v/>
@@ -9495,14 +10429,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Valoración de profesionales</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
+          <t>Gráficas de evolución de indicadores</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48">
         <f>COUNTIF(C48:Q48,"✓")</f>
         <v/>
@@ -9511,29 +10459,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49">
         <f>COUNTIF(C49:Q49,"✓")</f>
         <v/>
@@ -9542,24 +10494,33 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+          <t>Panel de seguimiento de salud y bienestar</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50">
         <f>COUNTIF(C50:Q50,"✓")</f>
         <v/>
@@ -9568,19 +10529,33 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cumplimiento regulatorio de salud y datos</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
+          <t>Registro de nutrición</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
       <c r="R51">
         <f>COUNTIF(C51:Q51,"✓")</f>
         <v/>
@@ -9589,19 +10564,33 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Identidad descentralizada (DID)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
+          <t>Seguimiento de salud femenina</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52">
         <f>COUNTIF(C52:Q52,"✓")</f>
         <v/>
@@ -9610,24 +10599,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
+          <t>Valoración de profesionales</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53">
         <f>COUNTIF(C53:Q53,"✓")</f>
         <v/>
@@ -9636,19 +10634,41 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Modelo freemium y suscripción</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54">
         <f>COUNTIF(C54:Q54,"✓")</f>
         <v/>
@@ -9657,19 +10677,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pagos con criptomoneda</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+          <t>Cifrado y control de acceso</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55">
         <f>COUNTIF(C55:Q55,"✓")</f>
         <v/>
@@ -9678,19 +10716,33 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
+          <t>Cumplimiento regulatorio de salud y datos</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56">
         <f>COUNTIF(C56:Q56,"✓")</f>
         <v/>
@@ -9699,21 +10751,284 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Telemedicina y atención remota</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Teleconsulta con profesionales</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+          <t>Gestión de consentimiento sobre uso de datos</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57">
         <f>COUNTIF(C57:Q57,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Identidad descentralizada (DID)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58">
+        <f>COUNTIF(C58:Q58,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Privacidad reforzada para datos de salud</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59">
+        <f>COUNTIF(C59:Q59,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Modelo freemium y suscripción</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60">
+        <f>COUNTIF(C60:Q60,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pagos con criptomoneda</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61">
+        <f>COUNTIF(C61:Q61,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Pagos dentro de la app</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R62">
+        <f>COUNTIF(C62:Q62,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63">
+        <f>COUNTIF(C63:Q63,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Telemedicina y atención remota</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Teleconsulta con profesionales</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64">
+        <f>COUNTIF(C64:Q64,"✓")</f>
         <v/>
       </c>
     </row>
@@ -9728,7 +11043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -9874,6 +11189,13 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>VUELTA 4 COMPLETA (2026-10-08 12:08 UTC): Clinia, MiRedSalud y Mediko verificados (+1 fila). Contador de loops = 4 para todos, Revisado reiniciado a "No". func_norm (124 filas) y tabla_frecuencia (63 funcionalidades) regenerados. Vuelta 5 parte con Meedika, Infomed, MediPlanner, Clingot. Candidato a competidor sin agregar: HealthChain (Chile).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -513,12 +513,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar. [Vuelta 3] Sin novedades 2026 ni confirmación de la app Android en Google Play; usuarios actuales desconocidos. Nota de prensa no indica año de lanzamiento explícito. [Vuelta 4] Sin fuentes nuevas; portalinnova.cl no aparece en búsquedas. Sigue dependiendo de una sola nota de prensa.</t>
+          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar. [Vuelta 3] Sin novedades 2026 ni confirmación de la app Android en Google Play; usuarios actuales desconocidos. Nota de prensa no indica año de lanzamiento explícito. [Vuelta 4] Sin fuentes nuevas; portalinnova.cl no aparece en búsquedas. Sigue dependiendo de una sola nota de prensa. [Vuelta 5] Sin fuentes nuevas (ni entrevistas ni financiamiento); sigue dependiendo de una sola nota de prensa sin año explícito.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -526,7 +526,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -553,12 +553,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapa A] Fundada 2019 por Diego Ibarra, Andrés Fantuzzi y Gabriel Zamora. Lanzada mar-2021 en App Store y Play Store con 1.200 usuarios; planeaba nueva versión jul-2021 y ronda de US$500 mil. Objetivo: llevar el historial en el celular, acceso en emergencias, médico puede ingresar datos con consentimiento. Estado actual NO verificado (posible app inactiva). URL es la nota de prensa; sitio oficial por confirmar. [Vuelta 3] Sin evidencia posterior a 2021; relanzamiento previsto jul-2021 no confirmado. Probable app inactiva. [Vuelta 4] Sin cambios; sigue sin evidencia posterior a 2021.</t>
+          <t>[DIRECTO · Chile · etapa A] Fundada 2019 por Diego Ibarra, Andrés Fantuzzi y Gabriel Zamora. Lanzada mar-2021 en App Store y Play Store con 1.200 usuarios; planeaba nueva versión jul-2021 y ronda de US$500 mil. Objetivo: llevar el historial en el celular, acceso en emergencias, médico puede ingresar datos con consentimiento. Estado actual NO verificado (posible app inactiva). URL es la nota de prensa; sitio oficial por confirmar. [Vuelta 3] Sin evidencia posterior a 2021; relanzamiento previsto jul-2021 no confirmado. Probable app inactiva. [Vuelta 4] Sin cambios; sigue sin evidencia posterior a 2021. [Vuelta 5] Cofundador Andrés Fantuzzi es cardiólogo de la Clínica Santa María. Sin ronda de inversión ni relanzamiento confirmados; no confundir con Infomed de Cuba (portal del Minsap).</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -593,12 +593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · México] Historial por perfil familiar, alergias, vacunas, recetas digitales, gráficas de evolución, agendamiento, compartir con profesionales. Gratis en App Store MX. Sin evidencia de uso en Chile. Cubre parte de la etapa C (familia). [Vuelta 3] Existen dos apps distintas: MediPlanner (gratis, Rym Solutions, MX, 3,7/5 con 3 calificaciones) y MediPlanner Pro (otro desarrollador, $39 MXN). Sin presencia verificada en Chile. [Vuelta 4] No pude confirmar el desarrollador de la versión gratuita (Rym Solutions no se repite en esta búsqueda). MediPlanner Pro (fichas BR/OM) guardaría datos solo en el dispositivo, sin nube; no confundir con MedPlanner/AskHEMI (otra empresa).</t>
+          <t>[REGIONAL · México] Historial por perfil familiar, alergias, vacunas, recetas digitales, gráficas de evolución, agendamiento, compartir con profesionales. Gratis en App Store MX. Sin evidencia de uso en Chile. Cubre parte de la etapa C (familia). [Vuelta 3] Existen dos apps distintas: MediPlanner (gratis, Rym Solutions, MX, 3,7/5 con 3 calificaciones) y MediPlanner Pro (otro desarrollador, $39 MXN). Sin presencia verificada en Chile. [Vuelta 4] No pude confirmar el desarrollador de la versión gratuita (Rym Solutions no se repite en esta búsqueda). MediPlanner Pro (fichas BR/OM) guardaría datos solo en el dispositivo, sin nube; no confundir con MedPlanner/AskHEMI (otra empresa). [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -606,7 +606,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · Argentina · débil] App para cargar antecedentes médicos propios. Única referencia: nota de opinión en grupoanimal.mx sin fecha verificada. Estado y sitio por confirmar. [Vuelta 3] Referencias de 2017 (apps4citizens, La Nación); sitio y precio no verificados; puede estar inactiva. [Vuelta 4] Sin fuentes nuevas.</t>
+          <t>[REGIONAL · Argentina · débil] App para cargar antecedentes médicos propios. Única referencia: nota de opinión en grupoanimal.mx sin fecha verificada. Estado y sitio por confirmar. [Vuelta 3] Referencias de 2017 (apps4citizens, La Nación); sitio y precio no verificados; puede estar inactiva. [Vuelta 4] Sin fuentes nuevas. [Vuelta 5] Registro empresarial (indicadores.ar, datos a jul-2026) muestra CLINGOT S.A. activa en CABA, constituida el 4-abr-2016; no confirma que la app siga operando. Programa federal argentino de historias clínicas digitales como contexto regulatorio.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -8646,8 +8646,6 @@
           <t>Búsqueda de profesionales de salud</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8658,17 +8656,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2">
         <f>COUNTIF(C2:Q2,"✓")</f>
         <v/>
@@ -8690,24 +8677,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3">
         <f>COUNTIF(C3:Q3,"✓")</f>
         <v/>
@@ -8724,25 +8698,11 @@
           <t>Integración con calendario del dispositivo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4">
         <f>COUNTIF(C4:Q4,"✓")</f>
         <v/>
@@ -8759,25 +8719,11 @@
           <t>Localización de centros médicos y farmacias</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5">
         <f>COUNTIF(C5:Q5,"✓")</f>
         <v/>
@@ -8794,17 +8740,6 @@
           <t>Reserva de citas médicas</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8815,8 +8750,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6">
         <f>COUNTIF(C6:Q6,"✓")</f>
         <v/>
@@ -8833,25 +8766,11 @@
           <t>Acceso del profesional al historial del paciente</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7">
         <f>COUNTIF(C7:Q7,"✓")</f>
         <v/>
@@ -8868,25 +8787,11 @@
           <t>Compartir con personas sin cuenta mediante clave segura</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8">
         <f>COUNTIF(C8:Q8,"✓")</f>
         <v/>
@@ -8903,25 +8808,11 @@
           <t>Compartir datos con cuidador o persona de confianza</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9">
         <f>COUNTIF(C9:Q9,"✓")</f>
         <v/>
@@ -8943,13 +8834,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8975,16 +8864,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10">
         <f>COUNTIF(C10:Q10,"✓")</f>
         <v/>
@@ -9001,25 +8885,11 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11">
         <f>COUNTIF(C11:Q11,"✓")</f>
         <v/>
@@ -9036,25 +8906,11 @@
           <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12">
         <f>COUNTIF(C12:Q12,"✓")</f>
         <v/>
@@ -9071,25 +8927,11 @@
           <t>Red social con profesionales y familiares</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13">
         <f>COUNTIF(C13:Q13,"✓")</f>
         <v/>
@@ -9116,23 +8958,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14">
         <f>COUNTIF(C14:Q14,"✓")</f>
         <v/>
@@ -9149,8 +8979,6 @@
           <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9161,25 +8989,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15">
         <f>COUNTIF(C15:Q15,"✓")</f>
         <v/>
@@ -9201,8 +9020,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9218,19 +9035,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16">
         <f>COUNTIF(C16:Q16,"✓")</f>
         <v/>
@@ -9247,29 +9056,16 @@
           <t>Almacenamiento de recetas</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17">
         <f>COUNTIF(C17:Q17,"✓")</f>
         <v/>
@@ -9286,25 +9082,11 @@
           <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18">
         <f>COUNTIF(C18:Q18,"✓")</f>
         <v/>
@@ -9321,25 +9103,11 @@
           <t>Emisión de certificados médicos</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19">
         <f>COUNTIF(C19:Q19,"✓")</f>
         <v/>
@@ -9361,19 +9129,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9395,25 +9150,11 @@
           <t>Notificación y envío de resultados</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21">
         <f>COUNTIF(C21:Q21,"✓")</f>
         <v/>
@@ -9430,29 +9171,16 @@
           <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22">
         <f>COUNTIF(C22:Q22,"✓")</f>
         <v/>
@@ -9469,36 +9197,26 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9520,25 +9238,11 @@
           <t>Línea de tiempo de salud</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24">
         <f>COUNTIF(C24:Q24,"✓")</f>
         <v/>
@@ -9555,25 +9259,11 @@
           <t>Registro de alergias y vacunas</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25">
         <f>COUNTIF(C25:Q25,"✓")</f>
         <v/>
@@ -9590,25 +9280,11 @@
           <t>Seguimiento de visitas, gastos y seguros</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26">
         <f>COUNTIF(C26:Q26,"✓")</f>
         <v/>
@@ -9625,11 +9301,6 @@
           <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9645,13 +9316,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27">
         <f>COUNTIF(C27:Q27,"✓")</f>
         <v/>
@@ -9668,25 +9332,11 @@
           <t>Asistente de IA para profesionales de salud</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28">
         <f>COUNTIF(C28:Q28,"✓")</f>
         <v/>
@@ -9703,25 +9353,11 @@
           <t>Coaching de salud con IA</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29">
         <f>COUNTIF(C29:Q29,"✓")</f>
         <v/>
@@ -9738,15 +9374,6 @@
           <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9757,10 +9384,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30">
         <f>COUNTIF(C30:Q30,"✓")</f>
         <v/>
@@ -9777,15 +9400,6 @@
           <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9796,9 +9410,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9820,24 +9431,11 @@
           <t>Orientación médica con IA</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9859,15 +9457,6 @@
           <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9878,10 +9467,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33">
         <f>COUNTIF(C33:Q33,"✓")</f>
         <v/>
@@ -9898,15 +9483,6 @@
           <t>Resumen de historial con IA</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9917,10 +9493,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34">
         <f>COUNTIF(C34:Q34,"✓")</f>
         <v/>
@@ -9942,10 +9514,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9956,7 +9524,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9972,14 +9539,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35">
         <f>COUNTIF(C35:Q35,"✓")</f>
         <v/>
@@ -9996,25 +9560,11 @@
           <t>Analítica poblacional B2B</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36">
         <f>COUNTIF(C36:Q36,"✓")</f>
         <v/>
@@ -10031,9 +9581,6 @@
           <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10044,20 +9591,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37">
         <f>COUNTIF(C37:Q37,"✓")</f>
         <v/>
@@ -10074,25 +9612,11 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38">
         <f>COUNTIF(C38:Q38,"✓")</f>
         <v/>
@@ -10109,25 +9633,11 @@
           <t>Importación y exportación de datos</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39">
         <f>COUNTIF(C39:Q39,"✓")</f>
         <v/>
@@ -10144,25 +9654,11 @@
           <t>Integración con EHR de proveedores</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40">
         <f>COUNTIF(C40:Q40,"✓")</f>
         <v/>
@@ -10179,29 +9675,16 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41">
         <f>COUNTIF(C41:Q41,"✓")</f>
         <v/>
@@ -10218,25 +9701,11 @@
           <t>Gestión de lista de medicamentos</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42">
         <f>COUNTIF(C42:Q42,"✓")</f>
         <v/>
@@ -10253,25 +9722,11 @@
           <t>Importación automática de tratamientos desde receta digital</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43">
         <f>COUNTIF(C43:Q43,"✓")</f>
         <v/>
@@ -10293,24 +9748,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44">
         <f>COUNTIF(C44:Q44,"✓")</f>
         <v/>
@@ -10327,25 +9769,11 @@
           <t>Registro de tomas y adherencia al tratamiento</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45">
         <f>COUNTIF(C45:Q45,"✓")</f>
         <v/>
@@ -10362,25 +9790,11 @@
           <t>Comunidad de pacientes</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46">
         <f>COUNTIF(C46:Q46,"✓")</f>
         <v/>
@@ -10397,25 +9811,11 @@
           <t>Contenido educativo sobre salud</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47">
         <f>COUNTIF(C47:Q47,"✓")</f>
         <v/>
@@ -10432,25 +9832,11 @@
           <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48">
         <f>COUNTIF(C48:Q48,"✓")</f>
         <v/>
@@ -10467,25 +9853,11 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49">
         <f>COUNTIF(C49:Q49,"✓")</f>
         <v/>
@@ -10502,25 +9874,11 @@
           <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50">
         <f>COUNTIF(C50:Q50,"✓")</f>
         <v/>
@@ -10537,25 +9895,11 @@
           <t>Registro de nutrición</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51">
         <f>COUNTIF(C51:Q51,"✓")</f>
         <v/>
@@ -10572,25 +9916,11 @@
           <t>Seguimiento de salud femenina</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52">
         <f>COUNTIF(C52:Q52,"✓")</f>
         <v/>
@@ -10607,25 +9937,11 @@
           <t>Valoración de profesionales</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
       <c r="R53">
         <f>COUNTIF(C53:Q53,"✓")</f>
         <v/>
@@ -10642,11 +9958,6 @@
           <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10662,13 +9973,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54">
         <f>COUNTIF(C54:Q54,"✓")</f>
         <v/>
@@ -10685,29 +9989,16 @@
           <t>Cifrado y control de acceso</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55">
         <f>COUNTIF(C55:Q55,"✓")</f>
         <v/>
@@ -10724,25 +10015,11 @@
           <t>Cumplimiento regulatorio de salud y datos</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56">
         <f>COUNTIF(C56:Q56,"✓")</f>
         <v/>
@@ -10759,25 +10036,11 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57">
         <f>COUNTIF(C57:Q57,"✓")</f>
         <v/>
@@ -10794,25 +10057,11 @@
           <t>Identidad descentralizada (DID)</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
       <c r="R58">
         <f>COUNTIF(C58:Q58,"✓")</f>
         <v/>
@@ -10829,15 +10078,6 @@
           <t>Privacidad reforzada para datos de salud</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10848,10 +10088,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
       <c r="R59">
         <f>COUNTIF(C59:Q59,"✓")</f>
         <v/>
@@ -10868,20 +10104,6 @@
           <t>Modelo freemium y suscripción</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10903,25 +10125,11 @@
           <t>Pagos con criptomoneda</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
       <c r="R61">
         <f>COUNTIF(C61:Q61,"✓")</f>
         <v/>
@@ -10938,20 +10146,6 @@
           <t>Pagos dentro de la app</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10973,25 +10167,11 @@
           <t>Reclamos y trámites con seguros</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
       <c r="R63">
         <f>COUNTIF(C63:Q63,"✓")</f>
         <v/>
@@ -11008,25 +10188,11 @@
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
       <c r="R64">
         <f>COUNTIF(C64:Q64,"✓")</f>
         <v/>
@@ -11043,7 +10209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -11196,6 +10362,13 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Vuelta 5 (iter. 1, 2026-10-09 12:16 UTC): Meedika, Infomed, MediPlanner, Clingot verificados (+0 filas). Nota: la rutina pasó a ejecución diaria (12:15 UTC) por cambio del usuario del 2026-10-08. Pendientes: Healfies, Patientory, MediBloc, Medicalchain, Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas, Clinia, MiRedSalud, Mediko.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B. [Vuelta 2] Lanzada simultáneamente en Brasil, Argentina y EE.UU.; permite compartir con no registrados vía clave por email. Sin novedades posteriores a 2016. [Vuelta 3] Sin evidencia de actividad reciente ni de cierre; Gust/Dealroom la listan en Florianópolis (10 empleados, healfies.com) sin fecha de actualización. Estado sin confirmar. [Vuelta 4] Sin Google Play localizado; no confundir con la app Healfy (otro producto). Sin novedades.</t>
+          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B. [Vuelta 2] Lanzada simultáneamente en Brasil, Argentina y EE.UU.; permite compartir con no registrados vía clave por email. Sin novedades posteriores a 2016. [Vuelta 3] Sin evidencia de actividad reciente ni de cierre; Gust/Dealroom la listan en Florianópolis (10 empleados, healfies.com) sin fecha de actualización. Estado sin confirmar. [Vuelta 4] Sin Google Play localizado; no confundir con la app Healfy (otro producto). Sin novedades. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain. [Vuelta 2] Sin noticias 2026 encontradas en búsqueda; sitio oficial bloqueado. [Vuelta 3] Búsqueda adicional solo devuelve hitos de 2017 (token sale US$7,2M) y 2019 (Serie A de US$5,3M, cierre no confirmado); sin datos 2025-26 propios. [Vuelta 4] App pública lanzada en la conferencia JP Morgan Healthcare (2019); red PTOYMatrix (blockchain HIPAA); socios reportados: StartUp Health y Kaiser Permanente (beta). Estado actual en App Store/Google Play sin confirmar.</t>
+          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain. [Vuelta 2] Sin noticias 2026 encontradas en búsqueda; sitio oficial bloqueado. [Vuelta 3] Búsqueda adicional solo devuelve hitos de 2017 (token sale US$7,2M) y 2019 (Serie A de US$5,3M, cierre no confirmado); sin datos 2025-26 propios. [Vuelta 4] App pública lanzada en la conferencia JP Morgan Healthcare (2019); red PTOYMatrix (blockchain HIPAA); socios reportados: StartUp Health y Kaiser Permanente (beta). Estado actual en App Store/Google Play sin confirmar. [Vuelta 5] Sin noticias 2026 del equipo. Token PTOY con capitalización de ~US$53K a fines de ago-2026 según Phantom (KuCoin discrepa en la circulación): señal de baja actividad, no prueba de cierre. Esto relativiza la actividad hasta abr-2026 mencionada en la ficha original.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain. [Vuelta 2] Panacea incluye DID, Append Only Log, IBC y PNFT; sin anuncios 2026 localizados. [Vuelta 3] Medipass: app en Corea con 20 hospitales/aseguradoras integrados (fecha de la lista desconocida) y plan 2022 de superapp con marketplace de datos; operación actual sin confirmar. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios.</t>
+          <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain. [Vuelta 2] Panacea incluye DID, Append Only Log, IBC y PNFT; sin anuncios 2026 localizados. [Vuelta 3] Medipass: app en Corea con 20 hospitales/aseguradoras integrados (fecha de la lista desconocida) y plan 2022 de superapp con marketplace de datos; operación actual sin confirmar. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Medipass: ~400.000 usuarios acumulados (CEO, jun-2022); integración con aseguradoras Shinhan Life, Samsung Fire y Hyundai Marine (2020); renovación completa en mar-2023 (dashboard de salud, gestión familiar, certificados). Sin noticias 2026 encontradas.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · Reino Unido · INACTIVO] Londres, 2017, Ethereum, con telemedicina. Piloto según registro de la UE (2020). Tracxn/PitchBook lo marcan fuera de operación (ago-2025). Solo caso de aprendizaje: no cuenta como competidor activo. [Vuelta 2] Token MTN deslistado de Bitfinex el 26-mar-2021; sin hallazgos de actividad posterior. [Vuelta 3] Seedtable la marca activa sin fuente; no hallé registro en Companies House. Sigue tratándose como caso de aprendizaje. [Vuelta 4] Pre-venta reportada de US$20M en MedTokens (un solo artículo secundario, sin verificar); modelo de token en revisión y exploración de security token según AMA; integraciones y servicios de 2019 sin confirmar.</t>
+          <t>[BLOCKCHAIN · Reino Unido · INACTIVO] Londres, 2017, Ethereum, con telemedicina. Piloto según registro de la UE (2020). Tracxn/PitchBook lo marcan fuera de operación (ago-2025). Solo caso de aprendizaje: no cuenta como competidor activo. [Vuelta 2] Token MTN deslistado de Bitfinex el 26-mar-2021; sin hallazgos de actividad posterior. [Vuelta 3] Seedtable la marca activa sin fuente; no hallé registro en Companies House. Sigue tratándose como caso de aprendizaje. [Vuelta 4] Pre-venta reportada de US$20M en MedTokens (un solo artículo secundario, sin verificar); modelo de token en revisión y exploración de security token según AMA; integraciones y servicios de 2019 sin confirmar. [Vuelta 5] Un agregador indica sitio medicalchain.com fuera de línea desde 15-feb-2025, último commit en GitHub hace ~3 años y proyecto en «fase de mantenimiento»; preventa de MedTokens reportada entre US$20M y US$24M (fuentes discrepan). Confirma tratarlo como inactivo.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5110,6 +5110,70 @@
       <c r="F125" t="inlineStr">
         <is>
           <t>Búsqueda web (Pauta / Descubre.vc, 2024); estado actual sin verificar</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Familia y dependientes</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Gestión familiar (Medipass renovado, 2023)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>El relanzamiento de Medipass (mar-2023) incorporó gestión de la salud de familiares.</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Medigate News, mar-2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Seguimiento y bienestar</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Dashboard de gestión de información de salud</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>El relanzamiento de Medipass (mar-2023) agregó un panel para gestionar la información de salud del usuario.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Medigate News, mar-2023)</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -10369,6 +10433,13 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Vuelta 5 (iter. 2, 2026-10-10 12:15 UTC): Healfies, Patientory, MediBloc, Medicalchain verificados (+2 filas, de MediBloc). Pendientes: Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas, Clinia, MiRedSalud, Mediko.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -833,12 +833,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Agrega registros clínicos vía FHIR; &gt;500 instituciones conectadas en EE.UU. (2018). Sin evidencia de disponibilidad en Chile. Incluida en el dispositivo. Amenaza si FHIR/IPS-CL se adopta en Chile. [Vuelta 2] Sin disponibilidad de registros clínicos en Chile (solo EE.UU., Reino Unido, Canadá). [Vuelta 3] iOS 27 (WWDC 8-jun-2026; publicado ~14-sep-2026): rediseño del app Health, menopausia, nutrición por cámara. El coach de salud con IA no se anunció. Sin ampliación de Health Records a Chile. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios.</t>
+          <t>[ADYACENTE · global] Agrega registros clínicos vía FHIR; &gt;500 instituciones conectadas en EE.UU. (2018). Sin evidencia de disponibilidad en Chile. Incluida en el dispositivo. Amenaza si FHIR/IPS-CL se adopta en Chile. [Vuelta 2] Sin disponibilidad de registros clínicos en Chile (solo EE.UU., Reino Unido, Canadá). [Vuelta 3] iOS 27 (WWDC 8-jun-2026; publicado ~14-sep-2026): rediseño del app Health, menopausia, nutrición por cámara. El coach de salud con IA no se anunció. Sin ampliación de Health Records a Chile. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Sin ampliación de Health Records a Australia, Europa ni Latinoamérica (solo EE.UU., UK, Canadá). Funciones de dispositivo (apnea del sueño, prueba auditiva) sí se amplían a países latinoamericanos, pero no son registros clínicos.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Lanzado 7-ene-2026. Conecta registros médicos; conectores solo en EE.UU. Dentro de suscripción del asistente. Fija la expectativa de consultar y resumir el historial. [Vuelta 2] Confirmado: registros solo EE.UU.; sin anuncios para Latinoamérica. Hay inconsistencia de fechas entre fuentes (7-ene-2026 lanzamiento vs. jul-2026 despliegue de registros). [Vuelta 3] Fechas aclaradas: presentación 7-ene-2026 (acceso limitado); despliegue de Health in ChatGPT con Apple Health y registros en EE.UU. el 23-jul-2026; mejora de salud jun-2026. Sin anuncios para Latinoamérica ni para sep-oct 2026. [Vuelta 4] Septiembre 2026: permisos por defecto para datos conectados (14-sep) y explicaciones por gráfico/métrica (28-sep); ChatGPT for Clinicians (abr-2026) para clínicos verificados de EE.UU. Más del 70% de usuarios de Health permite usar datos conectados sin pedir permiso (según OpenAI). Sigue solo EE.UU.</t>
+          <t>[ADYACENTE · global] Lanzado 7-ene-2026. Conecta registros médicos; conectores solo en EE.UU. Dentro de suscripción del asistente. Fija la expectativa de consultar y resumir el historial. [Vuelta 2] Confirmado: registros solo EE.UU.; sin anuncios para Latinoamérica. Hay inconsistencia de fechas entre fuentes (7-ene-2026 lanzamiento vs. jul-2026 despliegue de registros). [Vuelta 3] Fechas aclaradas: presentación 7-ene-2026 (acceso limitado); despliegue de Health in ChatGPT con Apple Health y registros en EE.UU. el 23-jul-2026; mejora de salud jun-2026. Sin anuncios para Latinoamérica ni para sep-oct 2026. [Vuelta 4] Septiembre 2026: permisos por defecto para datos conectados (14-sep) y explicaciones por gráfico/métrica (28-sep); ChatGPT for Clinicians (abr-2026) para clínicos verificados de EE.UU. Más del 70% de usuarios de Health permite usar datos conectados sin pedir permiso (según OpenAI). Sigue solo EE.UU. [Vuelta 5] Nota de jul-2026: Health no está disponible en México, Android, modo de voz ni Codex; web e iOS en EE.UU., adultos con sesión iniciada. Sin anuncio para Chile ni Latinoamérica.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -886,7 +886,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Lanzado 11-ene-2026. Conectores solo en EE.UU., planes Pro/Max. Nota: producto de Anthropic, conflicto de interés al evaluarlo. [Vuelta 2] Sin cambios fuera de EE.UU. (HealthEx y Function para Pro/Max). [Vuelta 3] Sin anuncios posteriores a enero de 2026. Hoja de ruta de HealthEx (agendar, buscar prestadores, recetas) sin confirmar como lanzada. [Vuelta 4] Sin anuncios nuevos. Fuentes discrepan en el acceso (Pro/Max según Fortune y la mayoría; Pro/Team según Times of AI); sin evidencia de disponibilidad fuera de EE.UU.</t>
+          <t>[ADYACENTE · global] Lanzado 11-ene-2026. Conectores solo en EE.UU., planes Pro/Max. Nota: producto de Anthropic, conflicto de interés al evaluarlo. [Vuelta 2] Sin cambios fuera de EE.UU. (HealthEx y Function para Pro/Max). [Vuelta 3] Sin anuncios posteriores a enero de 2026. Hoja de ruta de HealthEx (agendar, buscar prestadores, recetas) sin confirmar como lanzada. [Vuelta 4] Sin anuncios nuevos. Fuentes discrepan en el acceso (Pro/Max según Fortune y la mayoría; Pro/Team según Times of AI); sin evidencia de disponibilidad fuera de EE.UU. [Vuelta 5] Sin noticias de oct-2026; HealthEx agrega datos de &gt;50.000 sistemas de EE.UU. y Claude pide solo las categorías relevantes vía MCP.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -926,7 +926,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones. [Vuelta 2] App concreta: Mi Alemana Go (Clínica Alemana, Chile), con historial desde 2018, recetas, órdenes, familiar vinculado y resultados. [Vuelta 3] Búsqueda de otras clínicas (Las Condes, Santa María, UC Christus) sin ficha de app confirmada; solo canales digitales genéricos. [Vuelta 4] Mi Alemana Go: 3,1/5 con 137 calificaciones (App Store Chile), pantalla de inicio rediseñada para gestionar salud propia y familiar; sin evidencia de teleconsulta ni pagos en la app.</t>
+          <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones. [Vuelta 2] App concreta: Mi Alemana Go (Clínica Alemana, Chile), con historial desde 2018, recetas, órdenes, familiar vinculado y resultados. [Vuelta 3] Búsqueda de otras clínicas (Las Condes, Santa María, UC Christus) sin ficha de app confirmada; solo canales digitales genéricos. [Vuelta 4] Mi Alemana Go: 3,1/5 con 137 calificaciones (App Store Chile), pantalla de inicio rediseñada para gestionar salud propia y familiar; sin evidencia de teleconsulta ni pagos en la app. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5174,6 +5174,38 @@
       <c r="F127" t="inlineStr">
         <is>
           <t>Búsqueda web (Medigate News, mar-2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Claude for Healthcare (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Seguridad, privacidad y blockchain</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Acceso por categorías de datos vía MCP (HealthEx)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Claude solicita solo las categorías relevantes (p. ej. medicamentos o laboratorio) y no fichas completas; HealthEx agrega datos de más de 50.000 sistemas de salud de EE.UU.</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Unite.ai, Fortune, TechStrong); solo EE.UU., Pro/Max</t>
         </is>
       </c>
     </row>
@@ -10273,7 +10305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -10440,6 +10472,13 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Vuelta 5 (iter. 3, 2026-10-11 12:16 UTC): Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas verificados (+1 fila). Pendientes: Clinia, MiRedSalud, Mediko (cierran la vuelta 5 y regeneran func_norm/tabla_frecuencia).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -518,15 +518,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -558,15 +558,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -598,15 +598,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -638,15 +638,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -678,15 +678,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -718,15 +718,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -758,15 +758,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -798,15 +798,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -838,15 +838,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -878,15 +878,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -918,15 +918,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -958,15 +958,15 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar. [Vuelta 2] Confirmado por el CEO de Reservo (LinkedIn): app para pacientes en App Store y Google Play; guarda y comparte exámenes, recetas, órdenes y certificados. Fecha exacta de lanzamiento, precio y modelo de datos sin verificar. [Vuelta 3] Sin novedades de oct-2026. Reservo (Chile, México, Argentina) declara certificación Fonasa/CENS y cumplimiento de la nueva ley de datos personales; el Portal de Agendamiento de Reservo complementa a Clinia. Precio y modelo de datos sin verificar. [Vuelta 4] Una búsqueda adicional no encontró fuentes independientes sobre Clinia de Reservo (aparecen otras empresas llamadas Clinia); la evidencia sigue siendo la publicación del CEO en LinkedIn y notas de Reservo. Confianza media.</t>
+          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar. [Vuelta 2] Confirmado por el CEO de Reservo (LinkedIn): app para pacientes en App Store y Google Play; guarda y comparte exámenes, recetas, órdenes y certificados. Fecha exacta de lanzamiento, precio y modelo de datos sin verificar. [Vuelta 3] Sin novedades de oct-2026. Reservo (Chile, México, Argentina) declara certificación Fonasa/CENS y cumplimiento de la nueva ley de datos personales; el Portal de Agendamiento de Reservo complementa a Clinia. Precio y modelo de datos sin verificar. [Vuelta 4] Una búsqueda adicional no encontró fuentes independientes sobre Clinia de Reservo (aparecen otras empresas llamadas Clinia); la evidencia sigue siendo la publicación del CEO en LinkedIn y notas de Reservo. Confianza media. [Vuelta 5] Sin fecha verificable del lanzamiento (publicación de LinkedIn del CEO sin fecha visible); existe otra empresa homónima en Brasil (Porto Alegre, IA para clínicas) que no es este producto. Sin funciones nuevas.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1002,11 +1002,11 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis). [Vuelta 2] La búsqueda no encontró fuentes adicionales ni ficha de la app chilena (solo una app RedSalud de otro país); funciones sin confirmar. [Vuelta 3] Rankings de terceros la ubican como app médica gratuita nº 1 en App Store y Google Play Chile (fecha desconocida); sin descripción de funciones ni confirmación del desarrollador en Google Play. [Vuelta 4] Sin documentación oficial chilena localizada; las fichas con funciones (agendar, telemedicina, historial de hijos) corresponden a una app RedSalud de otro país. Quejas públicas 2020-21 sobre acceso en línea a resultados. Funciones de MiRedSalud sin confirmar.</t>
+          <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis). [Vuelta 2] La búsqueda no encontró fuentes adicionales ni ficha de la app chilena (solo una app RedSalud de otro país); funciones sin confirmar. [Vuelta 3] Rankings de terceros la ubican como app médica gratuita nº 1 en App Store y Google Play Chile (fecha desconocida); sin descripción de funciones ni confirmación del desarrollador en Google Play. [Vuelta 4] Sin documentación oficial chilena localizada; las fichas con funciones (agendar, telemedicina, historial de hijos) corresponden a una app RedSalud de otro país. Quejas públicas 2020-21 sobre acceso en línea a resultados. Funciones de MiRedSalud sin confirmar. [Vuelta 5] Una búsqueda adicional no halló cobertura del lanzamiento de dic-2025 ni de la app chilena; solo apps de otras empresas Red Salud (Paraguay, Perú). Sigue sin confirmarse más allá de la nota de RedSalud.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc. [Vuelta 2] Sin precios ni planes vigentes localizados; sitio oficial bloqueado. [Vuelta 3] Pauta (oct-2024): su fundador, Tomás Riddell, dice que no reemplaza a médicos y apunta a lo ambulatorio y a la espera de derivación a especialidad en el sistema público. Financiamiento: fuentes discrepan (CLP 25M en dic-2023 según Bouncewatch; ~$40M según Descubre.vc). Precios vigentes sin verificar. [Vuelta 4] Entrevista oct-2024 menciona integración con la pasarela Flow. Sin novedades 2025-26 ni rondas verificadas; la cifra de US$40M de Bouncewatch es dudosa (perfil con 2 empleados).</t>
+          <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc. [Vuelta 2] Sin precios ni planes vigentes localizados; sitio oficial bloqueado. [Vuelta 3] Pauta (oct-2024): su fundador, Tomás Riddell, dice que no reemplaza a médicos y apunta a lo ambulatorio y a la espera de derivación a especialidad en el sistema público. Financiamiento: fuentes discrepan (CLP 25M en dic-2023 según Bouncewatch; ~$40M según Descubre.vc). Precios vigentes sin verificar. [Vuelta 4] Entrevista oct-2024 menciona integración con la pasarela Flow. Sin novedades 2025-26 ni rondas verificadas; la cifra de US$40M de Bouncewatch es dudosa (perfil con 2 empleados). [Vuelta 5] CORRECCIÓN de financiamiento: Bouncewatch registra dos subvenciones (CLP 15M en ago-2022 y CLP 25M en dic-2023 = CLP 40M en total), no US$40M; 2 empleados; etapa Seed según Descubre.vc. No hay inversionistas de capital listados.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1082,11 +1082,11 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:E128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6070,7 +6070,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6085,19 +6085,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Historial por perfil para cada miembro de la familia.</t>
+          <t>El relanzamiento de Medipass (mar-2023) incorporó gestión de la salud de familiares.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MiRedSalud (RedSalud)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6112,46 +6112,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Guardar y administrar historial propio y familiar.</t>
+          <t>Historial por perfil para cada miembro de la familia.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>MiRedSalud (RedSalud)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gestión documental</t>
+          <t>Familia y dependientes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Almacenamiento de documentos médicos</t>
+          <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sube estudios, imágenes, indicaciones médicas y notas personales; accesible en consulta o por terceros en emergencias.</t>
+          <t>Guardar y administrar historial propio y familiar.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Reúne recetas, diagnósticos y laboratorios en un solo lugar.</t>
+          <t>Sube estudios, imágenes, indicaciones médicas y notas personales; accesible en consulta o por terceros en emergencias.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Guarda en un solo lugar exámenes, recetas, órdenes y certificados médicos.</t>
+          <t>Reúne recetas, diagnósticos y laboratorios en un solo lugar.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6205,7 +6205,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6220,19 +6220,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Organiza registros con carpetas y etiquetas.</t>
+          <t>Guarda en un solo lugar exámenes, recetas, órdenes y certificados médicos.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6247,19 +6247,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Almacena documentos clínicos del usuario en la app.</t>
+          <t>Organiza registros con carpetas y etiquetas.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6274,19 +6274,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Administra fechas, prescripciones, archivos y citas desde la app.</t>
+          <t>Almacena documentos clínicos del usuario en la app.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6296,24 +6296,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Almacenamiento de recetas</t>
+          <t>Almacenamiento de documentos médicos</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ver y descargar recetas, órdenes de examen y derivaciones.</t>
+          <t>Administra fechas, prescripciones, archivos y citas desde la app.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Guarda recetas digitales.</t>
+          <t>Ver y descargar recetas, órdenes de examen y derivaciones.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -6350,12 +6350,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Búsqueda y filtros de documentos</t>
+          <t>Almacenamiento de recetas</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Guarda resultados de laboratorio, imágenes y PDFs; búsqueda y filtros.</t>
+          <t>Guarda recetas digitales.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -6367,7 +6367,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6377,24 +6377,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Emisión de certificados médicos</t>
+          <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>La ficha de la app incluye consulta de chequeos de salud y emisión de certificados médicos.</t>
+          <t>Guarda resultados de laboratorio, imágenes y PDFs; búsqueda y filtros.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6404,24 +6404,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Importación de órdenes/solicitudes médicas</t>
+          <t>Emisión de certificados médicos</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Descarga/genera órdenes médicas digitales.</t>
+          <t>La ficha de la app incluye consulta de chequeos de salud y emisión de certificados médicos.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Importa solicitudes (órdenes) médicas a la app.</t>
+          <t>Descarga/genera órdenes médicas digitales.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6448,7 +6448,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Notificación y envío de resultados</t>
+          <t>Importación de órdenes/solicitudes médicas</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Avisa cuando hay exámenes/documentos disponibles; resultados de laboratorio y anatomía patológica compartibles por email o WhatsApp.</t>
+          <t>Importa solicitudes (órdenes) médicas a la app.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Historial institucional (solo datos de la propia red)</t>
+          <t>Notificación y envío de resultados</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ve historial de esa institución.</t>
+          <t>Avisa cuando hay exámenes/documentos disponibles; resultados de laboratorio y anatomía patológica compartibles por email o WhatsApp.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Historial institucional de consultas, urgencias y hospitalizaciones (solo datos de esa clínica).</t>
+          <t>Ve historial de esa institución.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6529,7 +6529,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MiRedSalud (RedSalud)</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Acceso a información clínica de la red.</t>
+          <t>Historial institucional de consultas, urgencias y hospitalizaciones (solo datos de esa clínica).</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6556,7 +6556,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MiRedSalud (RedSalud)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6566,24 +6566,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Información clínica unificada.</t>
+          <t>Acceso a información clínica de la red.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6598,19 +6598,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>El usuario registra sus antecedentes médicos en la app.</t>
+          <t>Información clínica unificada.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6625,19 +6625,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Centraliza el historial médico personal en el móvil.</t>
+          <t>El usuario registra sus antecedentes médicos en la app.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6652,19 +6652,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Permite compilar datos de vida/salud, gestionarlos y pasarlos a instituciones médicas.</t>
+          <t>Centraliza el historial médico personal en el móvil.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6679,19 +6679,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Centralizar registros y monitoreo desde el móvil.</t>
+          <t>Permite compilar datos de vida/salud, gestionarlos y pasarlos a instituciones médicas.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6701,17 +6701,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Línea de tiempo de salud</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Línea de tiempo con medicación, exámenes, citas y dieta.</t>
+          <t>Centralizar registros y monitoreo desde el móvil.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Registra notas de medicación, exámenes (laboratorio e imagen), actividad física, recetas, dieta y citas.</t>
+          <t>Línea de tiempo con medicación, exámenes, citas y dieta.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6745,7 +6745,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6755,12 +6755,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas</t>
+          <t>Línea de tiempo de salud</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas.</t>
+          <t>Registra notas de medicación, exámenes (laboratorio e imagen), actividad física, recetas, dieta y citas.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6772,7 +6772,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6782,39 +6782,39 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seguimiento de visitas, gastos y seguros</t>
+          <t>Registro de alergias y vacunas</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>App gratuita para seguir visitas al médico, facturas médicas, datos personales, seguros, inmunizaciones y medicamentos de farmacia.</t>
+          <t>Registro de alergias y vacunas.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Incentivos y monetización de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Recompensas / monetización de datos del usuario</t>
+          <t>Seguimiento de visitas, gastos y seguros</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Plan de convertir Medipass en superapp con gestión de salud diaria y mercado de datos, integrada con la EMR Dr.Palette.</t>
+          <t>App gratuita para seguir visitas al médico, facturas médicas, datos personales, seguros, inmunizaciones y medicamentos de farmacia.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6826,7 +6826,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Centros de investigación y farmacéuticas recompensarían con MedTokens a quienes compartan sus datos; no confirmado como ejecutado.</t>
+          <t>Plan de convertir Medipass en superapp con gestión de salud diaria y mercado de datos, integrada con la EMR Dr.Palette.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6853,7 +6853,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>El usuario puede agregar y monetizar sus datos; recompensas en cripto.</t>
+          <t>Centros de investigación y farmacéuticas recompensarían con MedTokens a quienes compartan sus datos; no confirmado como ejecutado.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6880,22 +6880,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Incentivos y monetización de datos</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Asistente de IA para profesionales de salud</t>
+          <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Producto para clínicos verificados de EE.UU. (gratis, abr-2026); desde 1-sep-2026 un plugin con nueve apps de fuentes públicas (investigación, ensayos, medicamentos, Medicare, prestadores), de solo lectura y sin acceso a fichas de pacientes.</t>
+          <t>El usuario puede agregar y monetizar sus datos; recompensas en cripto.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6907,7 +6907,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Coaching de salud con IA</t>
+          <t>Asistente de IA para profesionales de salud</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Coaching personalizado con IA.</t>
+          <t>Producto para clínicos verificados de EE.UU. (gratis, abr-2026); desde 1-sep-2026 un plugin con nueve apps de fuentes públicas (investigación, ensayos, medicamentos, Medicare, prestadores), de solo lectura y sin acceso a fichas de pacientes.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6934,7 +6934,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Detección de patrones en métricas de salud con IA</t>
+          <t>Coaching de salud con IA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Interpreta datos de Apple Health y registros en contexto y detecta cambios.</t>
+          <t>Coaching personalizado con IA.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6961,7 +6961,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Detecta patrones entre métricas de salud y fitness.</t>
+          <t>Interpreta datos de Apple Health y registros en contexto y detecta cambios.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6988,7 +6988,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
+          <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Explica resultados complejos en lenguaje simple.</t>
+          <t>Detecta patrones entre métricas de salud y fitness.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Desde 28-sep-2026, en la pestaña Health se puede elegir un gráfico, métrica o registro y obtener explicaciones basadas en los datos conectados.</t>
+          <t>Explica resultados complejos en lenguaje simple.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7042,7 +7042,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Explica exámenes en lenguaje simple.</t>
+          <t>Desde 28-sep-2026, en la pestaña Health se puede elegir un gráfico, métrica o registro y obtener explicaciones basadas en los datos conectados.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7069,7 +7069,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7084,19 +7084,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Interpreta exámenes de laboratorio.</t>
+          <t>Explica exámenes en lenguaje simple.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7106,24 +7106,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Orientación médica con IA</t>
+          <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Mejora de jun-2026 (GPT-5.5 Instant): detecta cuándo puede requerirse atención urgente, pide contexto y explica la incertidumbre.</t>
+          <t>Interpreta exámenes de laboratorio.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7138,19 +7138,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Orientación médica instantánea mediante IA.</t>
+          <t>Mejora de jun-2026 (GPT-5.5 Instant): detecta cuándo puede requerirse atención urgente, pide contexto y explica la incertidumbre.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7160,24 +7160,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Preparación de consultas médicas con IA</t>
+          <t>Orientación médica con IA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Prepara preguntas para el médico.</t>
+          <t>Orientación médica instantánea mediante IA.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7204,7 +7204,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Resumen de historial con IA</t>
+          <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Resume instrucciones de atención.</t>
+          <t>Prepara preguntas para el médico.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7231,7 +7231,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Resume el historial del usuario.</t>
+          <t>Resume instrucciones de atención.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7258,22 +7258,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Resumen de historial con IA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Vista central de alergias, condiciones, vacunas, laboratorio, medicación, procedimientos y signos vitales.</t>
+          <t>Resume el historial del usuario.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7285,7 +7285,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Conexión de historiales electrónicos y apps como Apple Health, MyFitnessPal, Peloton.</t>
+          <t>Vista central de alergias, condiciones, vacunas, laboratorio, medicación, procedimientos y signos vitales.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Acceso a historiales electrónicos de proveedores de EE.UU. vía b.well; solo EE.UU., sin plazo anunciado para Latinoamérica.</t>
+          <t>Conexión de historiales electrónicos y apps como Apple Health, MyFitnessPal, Peloton.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Además de b.well y Apple Health, vincula registros de One Medical y Function Health (solo EE.UU., Free/Go/Plus/Pro, web e iOS).</t>
+          <t>Acceso a historiales electrónicos de proveedores de EE.UU. vía b.well; solo EE.UU., sin plazo anunciado para Latinoamérica.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7366,7 +7366,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Acceso a resultados y registros de salud (beta, Pro/Max, EE.UU.).</t>
+          <t>Además de b.well y Apple Health, vincula registros de One Medical y Function Health (solo EE.UU., Free/Go/Plus/Pro, web e iOS).</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7393,7 +7393,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7408,19 +7408,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Datos desde profesionales/centros que usan Reservo (fichas clínicas, agenda, telemedicina).</t>
+          <t>Acceso a resultados y registros de salud (beta, Pro/Max, EE.UU.).</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7435,19 +7435,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Tras autenticación simple, trae los últimos 3 años de historial de hospitales integrados (p. ej. Samsung Seoul, SNUH, Severance).</t>
+          <t>Datos desde profesionales/centros que usan Reservo (fichas clínicas, agenda, telemedicina).</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7462,19 +7462,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sincroniza resultados desde centros de salud y permite subir fotos o documentos de las solicitudes médicas.</t>
+          <t>Tras autenticación simple, trae los últimos 3 años de historial de hospitales integrados (p. ej. Samsung Seoul, SNUH, Severance).</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Reúne registros de hospitales, resultados de laboratorio y datos genómicos.</t>
+          <t>Sincroniza resultados desde centros de salud y permite subir fotos o documentos de las solicitudes médicas.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -7511,12 +7511,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Analítica poblacional B2B</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Analítica poblacional on-chain; integrada con Epic, Cerner, Meditech y Allscripts (B2B).</t>
+          <t>Reúne registros de hospitales, resultados de laboratorio y datos genómicos.</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7528,7 +7528,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7538,24 +7538,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+          <t>Analítica poblacional B2B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Android, iOS y escritorio; médicos acceden a historias digitalizadas, envían estudios e indicaciones y organizan agenda.</t>
+          <t>Analítica poblacional on-chain; integrada con Epic, Cerner, Meditech y Allscripts (B2B).</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7570,19 +7570,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Disponible en App Store y Google Play. Reservo opera en Chile, México y Argentina y está certificada por FONASA y CENS.</t>
+          <t>Android, iOS y escritorio; médicos acceden a historias digitalizadas, envían estudios e indicaciones y organizan agenda.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7597,19 +7597,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Disponible en web, iOS y Android.</t>
+          <t>Disponible en App Store y Google Play. Reservo opera en Chile, México y Argentina y está certificada por FONASA y CENS.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7619,24 +7619,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Versión digital de los registros con acceso por móvil o web.</t>
+          <t>Disponible en web, iOS y Android.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7646,24 +7646,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Importación y exportación de datos</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Importar/exportar datos para compartir de forma segura con familias o cuidadores. Es MediPlanner Pro, de otro desarrollador (App Store MX, $39 MXN).</t>
+          <t>Versión digital de los registros con acceso por móvil o web.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7673,24 +7673,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Integración con EHR de proveedores</t>
+          <t>Importación y exportación de datos</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Según una AMA sin fecha, integraba dos sistemas de GP que cubren ~80% del mercado UK; no confirmado como ejecutado.</t>
+          <t>Importar/exportar datos para compartir de forma segura con familias o cuidadores. Es MediPlanner Pro, de otro desarrollador (App Store MX, $39 MXN).</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7700,12 +7700,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Integración con EHR de proveedores</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Integración beta en apps iOS/Android.</t>
+          <t>Según una AMA sin fecha, integraba dos sistemas de GP que cubren ~80% del mercado UK; no confirmado como ejecutado.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Integración beta con Health Connect en la app móvil; conectores de registros (HealthEx, Function) solo para Pro/Max en EE.UU.</t>
+          <t>Integración beta en apps iOS/Android.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7744,7 +7744,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
+          <t>Integración beta con Health Connect en la app móvil; conectores de registros (HealthEx, Function) solo para Pro/Max en EE.UU.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -7771,22 +7771,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Gestión de lista de medicamentos</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Listas de medicamentos, vitaminas y suplementos con horarios; escaneo de etiqueta del frasco solo en EE.UU.</t>
+          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7798,7 +7798,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7808,24 +7808,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Importación automática de tratamientos desde receta digital</t>
+          <t>Gestión de lista de medicamentos</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Según la ficha de la App Store MX, los tratamientos llegan automáticamente desde la receta digital del médico (autodeclarado, sin verificar).</t>
+          <t>Listas de medicamentos, vitaminas y suplementos con horarios; escaneo de etiqueta del frasco solo en EE.UU.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7835,24 +7835,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
+          <t>Importación automática de tratamientos desde receta digital</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Recordatorios desde el app.</t>
+          <t>Según la ficha de la App Store MX, los tratamientos llegan automáticamente desde la receta digital del médico (autodeclarado, sin verificar).</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7867,19 +7867,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Recordatorios de citas/medicación.</t>
+          <t>Recordatorios desde el app.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7889,51 +7889,51 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Registro de tomas y adherencia al tratamiento</t>
+          <t>Recordatorios de medicación y citas</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Registro de cada toma y control de adherencia; gestiona medicamentos propios y de familiares.</t>
+          <t>Recordatorios de citas/medicación.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Comunidad de pacientes</t>
+          <t>Registro de tomas y adherencia al tratamiento</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Los usuarios con condiciones similares pueden preguntar, recibir recomendaciones y compartir experiencias.</t>
+          <t>Registro de cada toma y control de adherencia; gestiona medicamentos propios y de familiares.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7943,24 +7943,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Contenido educativo sobre salud</t>
+          <t>Comunidad de pacientes</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Busca que el paciente aprenda sobre sus enfermedades y sea más autónomo.</t>
+          <t>Los usuarios con condiciones similares pueden preguntar, recibir recomendaciones y compartir experiencias.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7970,24 +7970,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores</t>
+          <t>Contenido educativo sobre salud</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores de salud.</t>
+          <t>Busca que el paciente aprenda sobre sus enfermedades y sea más autónomo.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7997,24 +7997,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Datos de pasos, sueño, peso junto a registros.</t>
+          <t>Gráficas de evolución de indicadores de salud.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8024,12 +8024,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Panel de seguimiento de salud y bienestar</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
+          <t>Datos de pasos, sueño, peso junto a registros.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -8041,7 +8041,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Registro de nutrición</t>
+          <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Escaneo de etiquetas nutricionales con la cámara; según un análisis, no escribe en HealthKit.</t>
+          <t>El relanzamiento de Medipass (mar-2023) agregó un panel para gestionar la información de salud del usuario.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -8068,7 +8068,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seguimiento de salud femenina</t>
+          <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Extiende el seguimiento de ciclo con perimenopausia y menopausia.</t>
+          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -8095,7 +8095,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8105,39 +8105,39 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Valoración de profesionales</t>
+          <t>Registro de nutrición</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Calificación de la atención de profesionales con autorización previa, compartible con otros usuarios.</t>
+          <t>Escaneo de etiquetas nutricionales con la cámara; según un análisis, no escribe en HealthKit.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Seguimiento de salud femenina</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
+          <t>Extiende el seguimiento de ciclo con perimenopausia y menopausia.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8149,34 +8149,34 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Valoración de profesionales</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Almacena huellas de datos médicos en un registro de solo escritura, sin guardar datos clínicos en cadena.</t>
+          <t>Calificación de la atención de profesionales con autorización previa, compartible con otros usuarios.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Acceso mínimo por categorías de datos</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
+          <t>Claude solicita solo las categorías relevantes (p. ej. medicamentos o laboratorio) y no fichas completas; HealthEx agrega datos de más de 50.000 sistemas de salud de EE.UU.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8203,7 +8203,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
+          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8230,7 +8230,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso</t>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
+          <t>Almacena huellas de datos médicos en un registro de solo escritura, sin guardar datos clínicos en cadena.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8257,7 +8257,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8267,24 +8267,24 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso</t>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Almacenamiento seguro del historial con criterios de seguridad estrictos, comparable a apps bancarias.</t>
+          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8294,24 +8294,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cumplimiento regulatorio de salud y datos</t>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Reservo declara plataforma certificada por Fonasa y CENS, cumplimiento de estándares de telemedicina del Minsal y de la nueva ley chilena de datos personales (declaración de la empresa).</t>
+          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Gestión de consentimiento sobre uso de datos</t>
+          <t>Cifrado y control de acceso</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Desde 14-sep-2026, las nuevas conexiones heredan la configuración global de plugins: ChatGPT puede usar datos de Health sin pedir permiso cada vez salvo acciones sensibles (web primero, móvil después).</t>
+          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8338,7 +8338,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8348,24 +8348,24 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Identidad descentralizada (DID)</t>
+          <t>Cifrado y control de acceso</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Gestión de identificadores descentralizados en Panacea.</t>
+          <t>Almacenamiento seguro del historial con criterios de seguridad estrictos, comparable a apps bancarias.</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8375,24 +8375,24 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
+          <t>Cumplimiento regulatorio de salud y datos</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
+          <t>Reservo declara plataforma certificada por Fonasa y CENS, cumplimiento de estándares de telemedicina del Minsal y de la nueva ley chilena de datos personales (declaración de la empresa).</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
+          <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>El usuario activa y revoca permisos; los datos de salud compartidos se excluyen de la memoria de Claude y del entrenamiento.</t>
+          <t>Desde 14-sep-2026, las nuevas conexiones heredan la configuración global de plugins: ChatGPT puede usar datos de Health sin pedir permiso cada vez salvo acciones sensibles (web primero, móvil después).</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8419,49 +8419,49 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Modelo freemium y suscripción</t>
+          <t>Identidad descentralizada (DID)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Planes para personas y empresas.</t>
+          <t>Gestión de identificadores descentralizados en Panacea.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Pagos con criptomoneda</t>
+          <t>Privacidad reforzada para datos de salud</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Pago de consultas con token.</t>
+          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8473,22 +8473,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Pagos con criptomoneda</t>
+          <t>Privacidad reforzada para datos de salud</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Piloto en New Malden (Londres): consultas por video pagables con tarjeta o con MedTokens.</t>
+          <t>El usuario activa y revoca permisos; los datos de salud compartidos se excluyen de la memoria de Claude y del entrenamiento.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Pagos dentro de la app</t>
+          <t>Modelo freemium y suscripción</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Pagos dentro de la plataforma mediante la pasarela Flow (según resumen de entrevista de Pauta, oct-2024; esperada para mejorar la experiencia).</t>
+          <t>Planes para personas y empresas.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8527,7 +8527,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
+          <t>Pagos con criptomoneda</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
+          <t>Pago de consultas con token.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8554,7 +8554,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
+          <t>Pagos con criptomoneda</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Reclamo de seguro médico (indemnización) desde la app, con verificación de autenticidad de los registros vía blockchain por la aseguradora.</t>
+          <t>Piloto en New Malden (Londres): consultas por video pagables con tarjeta o con MedTokens.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8581,25 +8581,106 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
+          <t>Mediko</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Pagos dentro de la app</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Pagos dentro de la plataforma mediante la pasarela Flow (según resumen de entrevista de Pauta, oct-2024; esperada para mejorar la experiencia).</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Reclamo de seguro médico (indemnización) desde la app, con verificación de autenticidad de los registros vía blockchain por la aseguradora.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
           <t>Medicalchain</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>Telemedicina y atención remota</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>Teleconsultas con GP.</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
@@ -8616,7 +8697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R64"/>
+  <dimension ref="A1:R65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8742,6 +8823,8 @@
           <t>Búsqueda de profesionales de salud</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8752,6 +8835,17 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2">
         <f>COUNTIF(C2:Q2,"✓")</f>
         <v/>
@@ -8773,11 +8867,24 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3">
         <f>COUNTIF(C3:Q3,"✓")</f>
         <v/>
@@ -8794,11 +8901,25 @@
           <t>Integración con calendario del dispositivo</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4">
         <f>COUNTIF(C4:Q4,"✓")</f>
         <v/>
@@ -8815,11 +8936,25 @@
           <t>Localización de centros médicos y farmacias</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5">
         <f>COUNTIF(C5:Q5,"✓")</f>
         <v/>
@@ -8836,6 +8971,17 @@
           <t>Reserva de citas médicas</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8846,6 +8992,8 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6">
         <f>COUNTIF(C6:Q6,"✓")</f>
         <v/>
@@ -8862,11 +9010,25 @@
           <t>Acceso del profesional al historial del paciente</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7">
         <f>COUNTIF(C7:Q7,"✓")</f>
         <v/>
@@ -8883,11 +9045,25 @@
           <t>Compartir con personas sin cuenta mediante clave segura</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8">
         <f>COUNTIF(C8:Q8,"✓")</f>
         <v/>
@@ -8904,11 +9080,25 @@
           <t>Compartir datos con cuidador o persona de confianza</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9">
         <f>COUNTIF(C9:Q9,"✓")</f>
         <v/>
@@ -8930,11 +9120,13 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8960,11 +9152,16 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10">
         <f>COUNTIF(C10:Q10,"✓")</f>
         <v/>
@@ -8981,11 +9178,25 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11">
         <f>COUNTIF(C11:Q11,"✓")</f>
         <v/>
@@ -9002,11 +9213,25 @@
           <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12">
         <f>COUNTIF(C12:Q12,"✓")</f>
         <v/>
@@ -9023,11 +9248,25 @@
           <t>Red social con profesionales y familiares</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13">
         <f>COUNTIF(C13:Q13,"✓")</f>
         <v/>
@@ -9054,11 +9293,23 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14">
         <f>COUNTIF(C14:Q14,"✓")</f>
         <v/>
@@ -9075,6 +9326,8 @@
           <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9085,16 +9338,29 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15">
         <f>COUNTIF(C15:Q15,"✓")</f>
         <v/>
@@ -9116,6 +9382,8 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9131,11 +9399,19 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16">
         <f>COUNTIF(C16:Q16,"✓")</f>
         <v/>
@@ -9152,16 +9428,29 @@
           <t>Almacenamiento de recetas</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17">
         <f>COUNTIF(C17:Q17,"✓")</f>
         <v/>
@@ -9178,11 +9467,25 @@
           <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18">
         <f>COUNTIF(C18:Q18,"✓")</f>
         <v/>
@@ -9199,11 +9502,25 @@
           <t>Emisión de certificados médicos</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19">
         <f>COUNTIF(C19:Q19,"✓")</f>
         <v/>
@@ -9225,6 +9542,19 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9246,11 +9576,25 @@
           <t>Notificación y envío de resultados</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21">
         <f>COUNTIF(C21:Q21,"✓")</f>
         <v/>
@@ -9267,16 +9611,29 @@
           <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22">
         <f>COUNTIF(C22:Q22,"✓")</f>
         <v/>
@@ -9293,26 +9650,36 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9334,11 +9701,25 @@
           <t>Línea de tiempo de salud</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24">
         <f>COUNTIF(C24:Q24,"✓")</f>
         <v/>
@@ -9355,11 +9736,25 @@
           <t>Registro de alergias y vacunas</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25">
         <f>COUNTIF(C25:Q25,"✓")</f>
         <v/>
@@ -9376,11 +9771,25 @@
           <t>Seguimiento de visitas, gastos y seguros</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26">
         <f>COUNTIF(C26:Q26,"✓")</f>
         <v/>
@@ -9397,6 +9806,11 @@
           <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9412,6 +9826,13 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27">
         <f>COUNTIF(C27:Q27,"✓")</f>
         <v/>
@@ -9428,11 +9849,25 @@
           <t>Asistente de IA para profesionales de salud</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28">
         <f>COUNTIF(C28:Q28,"✓")</f>
         <v/>
@@ -9449,11 +9884,25 @@
           <t>Coaching de salud con IA</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29">
         <f>COUNTIF(C29:Q29,"✓")</f>
         <v/>
@@ -9470,6 +9919,15 @@
           <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9480,6 +9938,10 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30">
         <f>COUNTIF(C30:Q30,"✓")</f>
         <v/>
@@ -9496,6 +9958,15 @@
           <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9506,6 +9977,9 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9527,11 +10001,24 @@
           <t>Orientación médica con IA</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9553,6 +10040,15 @@
           <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9563,6 +10059,10 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33">
         <f>COUNTIF(C33:Q33,"✓")</f>
         <v/>
@@ -9579,6 +10079,15 @@
           <t>Resumen de historial con IA</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9589,6 +10098,10 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34">
         <f>COUNTIF(C34:Q34,"✓")</f>
         <v/>
@@ -9610,6 +10123,10 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9620,6 +10137,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9635,11 +10153,14 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35">
         <f>COUNTIF(C35:Q35,"✓")</f>
         <v/>
@@ -9656,11 +10177,25 @@
           <t>Analítica poblacional B2B</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36">
         <f>COUNTIF(C36:Q36,"✓")</f>
         <v/>
@@ -9677,6 +10212,9 @@
           <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9687,11 +10225,20 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37">
         <f>COUNTIF(C37:Q37,"✓")</f>
         <v/>
@@ -9708,11 +10255,25 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38">
         <f>COUNTIF(C38:Q38,"✓")</f>
         <v/>
@@ -9729,11 +10290,25 @@
           <t>Importación y exportación de datos</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39">
         <f>COUNTIF(C39:Q39,"✓")</f>
         <v/>
@@ -9750,11 +10325,25 @@
           <t>Integración con EHR de proveedores</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40">
         <f>COUNTIF(C40:Q40,"✓")</f>
         <v/>
@@ -9771,16 +10360,29 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41">
         <f>COUNTIF(C41:Q41,"✓")</f>
         <v/>
@@ -9797,11 +10399,25 @@
           <t>Gestión de lista de medicamentos</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42">
         <f>COUNTIF(C42:Q42,"✓")</f>
         <v/>
@@ -9818,11 +10434,25 @@
           <t>Importación automática de tratamientos desde receta digital</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43">
         <f>COUNTIF(C43:Q43,"✓")</f>
         <v/>
@@ -9844,11 +10474,24 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44">
         <f>COUNTIF(C44:Q44,"✓")</f>
         <v/>
@@ -9865,11 +10508,25 @@
           <t>Registro de tomas y adherencia al tratamiento</t>
         </is>
       </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45">
         <f>COUNTIF(C45:Q45,"✓")</f>
         <v/>
@@ -9886,11 +10543,25 @@
           <t>Comunidad de pacientes</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46">
         <f>COUNTIF(C46:Q46,"✓")</f>
         <v/>
@@ -9907,11 +10578,25 @@
           <t>Contenido educativo sobre salud</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47">
         <f>COUNTIF(C47:Q47,"✓")</f>
         <v/>
@@ -9928,11 +10613,25 @@
           <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48">
         <f>COUNTIF(C48:Q48,"✓")</f>
         <v/>
@@ -9949,11 +10648,25 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49">
         <f>COUNTIF(C49:Q49,"✓")</f>
         <v/>
@@ -9970,11 +10683,29 @@
           <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50">
         <f>COUNTIF(C50:Q50,"✓")</f>
         <v/>
@@ -9991,11 +10722,25 @@
           <t>Registro de nutrición</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
       <c r="R51">
         <f>COUNTIF(C51:Q51,"✓")</f>
         <v/>
@@ -10012,11 +10757,25 @@
           <t>Seguimiento de salud femenina</t>
         </is>
       </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52">
         <f>COUNTIF(C52:Q52,"✓")</f>
         <v/>
@@ -10033,11 +10792,25 @@
           <t>Valoración de profesionales</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53">
         <f>COUNTIF(C53:Q53,"✓")</f>
         <v/>
@@ -10051,24 +10824,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
+          <t>Acceso mínimo por categorías de datos</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54">
         <f>COUNTIF(C54:Q54,"✓")</f>
         <v/>
@@ -10082,19 +10859,36 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55">
         <f>COUNTIF(C55:Q55,"✓")</f>
         <v/>
@@ -10108,14 +10902,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cumplimiento regulatorio de salud y datos</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
+          <t>Cifrado y control de acceso</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56">
         <f>COUNTIF(C56:Q56,"✓")</f>
         <v/>
@@ -10129,14 +10941,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gestión de consentimiento sobre uso de datos</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
+          <t>Cumplimiento regulatorio de salud y datos</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57">
         <f>COUNTIF(C57:Q57,"✓")</f>
         <v/>
@@ -10150,14 +10976,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Identidad descentralizada (DID)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
+          <t>Gestión de consentimiento sobre uso de datos</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58">
         <f>COUNTIF(C58:Q58,"✓")</f>
         <v/>
@@ -10171,19 +11011,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
+          <t>Identidad descentralizada (DID)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
       <c r="R59">
         <f>COUNTIF(C59:Q59,"✓")</f>
         <v/>
@@ -10192,19 +11041,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Modelo freemium y suscripción</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
+          <t>Privacidad reforzada para datos de salud</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60">
         <f>COUNTIF(C60:Q60,"✓")</f>
         <v/>
@@ -10218,10 +11085,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pagos con criptomoneda</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+          <t>Modelo freemium y suscripción</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -10239,14 +11120,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pagos dentro de la app</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
+          <t>Pagos con criptomoneda</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62">
         <f>COUNTIF(C62:Q62,"✓")</f>
         <v/>
@@ -10260,10 +11155,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
+          <t>Pagos dentro de la app</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -10276,21 +11185,70 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Telemedicina y atención remota</t>
+          <t>Seguros y pagos</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Teleconsulta con profesionales</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
       <c r="R64">
         <f>COUNTIF(C64:Q64,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Telemedicina y atención remota</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Teleconsulta con profesionales</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65">
+        <f>COUNTIF(C65:Q65,"✓")</f>
         <v/>
       </c>
     </row>
@@ -10305,7 +11263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -10479,6 +11437,13 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>VUELTA 5 COMPLETA (2026-10-12 12:16 UTC): Clinia, MiRedSalud y Mediko verificados (+0 filas en esta iteración). Contador de loops = 5 para todos, Revisado reiniciado a "No". func_norm (127 filas) y tabla_frecuencia (64 funcionalidades) regenerados. Corregido financiamiento de Mediko (CLP 40M, no US$40M). Vuelta 6 parte con Meedika, Infomed, MediPlanner, Clingot. Candidato a competidor sin agregar: HealthChain (Chile).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -513,12 +513,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar. [Vuelta 3] Sin novedades 2026 ni confirmación de la app Android en Google Play; usuarios actuales desconocidos. Nota de prensa no indica año de lanzamiento explícito. [Vuelta 4] Sin fuentes nuevas; portalinnova.cl no aparece en búsquedas. Sigue dependiendo de una sola nota de prensa. [Vuelta 5] Sin fuentes nuevas (ni entrevistas ni financiamiento); sigue dependiendo de una sola nota de prensa sin año explícito.</t>
+          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar. [Vuelta 3] Sin novedades 2026 ni confirmación de la app Android en Google Play; usuarios actuales desconocidos. Nota de prensa no indica año de lanzamiento explícito. [Vuelta 4] Sin fuentes nuevas; portalinnova.cl no aparece en búsquedas. Sigue dependiendo de una sola nota de prensa. [Vuelta 5] Sin fuentes nuevas (ni entrevistas ni financiamiento); sigue dependiendo de una sola nota de prensa sin año explícito. [Vuelta 6] Sin ficha de Google Play ni fuentes nuevas; disponibilidad en Android sin confirmar.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -526,7 +526,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -553,12 +553,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapa A] Fundada 2019 por Diego Ibarra, Andrés Fantuzzi y Gabriel Zamora. Lanzada mar-2021 en App Store y Play Store con 1.200 usuarios; planeaba nueva versión jul-2021 y ronda de US$500 mil. Objetivo: llevar el historial en el celular, acceso en emergencias, médico puede ingresar datos con consentimiento. Estado actual NO verificado (posible app inactiva). URL es la nota de prensa; sitio oficial por confirmar. [Vuelta 3] Sin evidencia posterior a 2021; relanzamiento previsto jul-2021 no confirmado. Probable app inactiva. [Vuelta 4] Sin cambios; sigue sin evidencia posterior a 2021. [Vuelta 5] Cofundador Andrés Fantuzzi es cardiólogo de la Clínica Santa María. Sin ronda de inversión ni relanzamiento confirmados; no confundir con Infomed de Cuba (portal del Minsap).</t>
+          <t>[DIRECTO · Chile · etapa A] Fundada 2019 por Diego Ibarra, Andrés Fantuzzi y Gabriel Zamora. Lanzada mar-2021 en App Store y Play Store con 1.200 usuarios; planeaba nueva versión jul-2021 y ronda de US$500 mil. Objetivo: llevar el historial en el celular, acceso en emergencias, médico puede ingresar datos con consentimiento. Estado actual NO verificado (posible app inactiva). URL es la nota de prensa; sitio oficial por confirmar. [Vuelta 3] Sin evidencia posterior a 2021; relanzamiento previsto jul-2021 no confirmado. Probable app inactiva. [Vuelta 4] Sin cambios; sigue sin evidencia posterior a 2021. [Vuelta 5] Cofundador Andrés Fantuzzi es cardiólogo de la Clínica Santa María. Sin ronda de inversión ni relanzamiento confirmados; no confundir con Infomed de Cuba (portal del Minsap). [Vuelta 6] Sin búsqueda nueva (fuentes agotadas en vueltas 3-5); sin cambios.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -593,12 +593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · México] Historial por perfil familiar, alergias, vacunas, recetas digitales, gráficas de evolución, agendamiento, compartir con profesionales. Gratis en App Store MX. Sin evidencia de uso en Chile. Cubre parte de la etapa C (familia). [Vuelta 3] Existen dos apps distintas: MediPlanner (gratis, Rym Solutions, MX, 3,7/5 con 3 calificaciones) y MediPlanner Pro (otro desarrollador, $39 MXN). Sin presencia verificada en Chile. [Vuelta 4] No pude confirmar el desarrollador de la versión gratuita (Rym Solutions no se repite en esta búsqueda). MediPlanner Pro (fichas BR/OM) guardaría datos solo en el dispositivo, sin nube; no confundir con MedPlanner/AskHEMI (otra empresa). [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios.</t>
+          <t>[REGIONAL · México] Historial por perfil familiar, alergias, vacunas, recetas digitales, gráficas de evolución, agendamiento, compartir con profesionales. Gratis en App Store MX. Sin evidencia de uso en Chile. Cubre parte de la etapa C (familia). [Vuelta 3] Existen dos apps distintas: MediPlanner (gratis, Rym Solutions, MX, 3,7/5 con 3 calificaciones) y MediPlanner Pro (otro desarrollador, $39 MXN). Sin presencia verificada en Chile. [Vuelta 4] No pude confirmar el desarrollador de la versión gratuita (Rym Solutions no se repite en esta búsqueda). MediPlanner Pro (fichas BR/OM) guardaría datos solo en el dispositivo, sin nube; no confundir con MedPlanner/AskHEMI (otra empresa). [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Se reconfirma en la ficha de App Store MX que el desarrollador de la versión gratuita es Rym Solutions S. de R.L. de C.V. (3,7/5, 3 calificaciones); MediPlanner Pro no menciona a esa empresa, por lo que no se puede asegurar que sea el mismo desarrollador.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -606,7 +606,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · Argentina · débil] App para cargar antecedentes médicos propios. Única referencia: nota de opinión en grupoanimal.mx sin fecha verificada. Estado y sitio por confirmar. [Vuelta 3] Referencias de 2017 (apps4citizens, La Nación); sitio y precio no verificados; puede estar inactiva. [Vuelta 4] Sin fuentes nuevas. [Vuelta 5] Registro empresarial (indicadores.ar, datos a jul-2026) muestra CLINGOT S.A. activa en CABA, constituida el 4-abr-2016; no confirma que la app siga operando. Programa federal argentino de historias clínicas digitales como contexto regulatorio.</t>
+          <t>[REGIONAL · Argentina · débil] App para cargar antecedentes médicos propios. Única referencia: nota de opinión en grupoanimal.mx sin fecha verificada. Estado y sitio por confirmar. [Vuelta 3] Referencias de 2017 (apps4citizens, La Nación); sitio y precio no verificados; puede estar inactiva. [Vuelta 4] Sin fuentes nuevas. [Vuelta 5] Registro empresarial (indicadores.ar, datos a jul-2026) muestra CLINGOT S.A. activa en CABA, constituida el 4-abr-2016; no confirma que la app siga operando. Programa federal argentino de historias clínicas digitales como contexto regulatorio. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -8823,8 +8823,6 @@
           <t>Búsqueda de profesionales de salud</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8835,17 +8833,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2">
         <f>COUNTIF(C2:Q2,"✓")</f>
         <v/>
@@ -8867,24 +8854,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3">
         <f>COUNTIF(C3:Q3,"✓")</f>
         <v/>
@@ -8901,25 +8875,11 @@
           <t>Integración con calendario del dispositivo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4">
         <f>COUNTIF(C4:Q4,"✓")</f>
         <v/>
@@ -8936,25 +8896,11 @@
           <t>Localización de centros médicos y farmacias</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5">
         <f>COUNTIF(C5:Q5,"✓")</f>
         <v/>
@@ -8971,17 +8917,6 @@
           <t>Reserva de citas médicas</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8992,8 +8927,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6">
         <f>COUNTIF(C6:Q6,"✓")</f>
         <v/>
@@ -9010,25 +8943,11 @@
           <t>Acceso del profesional al historial del paciente</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7">
         <f>COUNTIF(C7:Q7,"✓")</f>
         <v/>
@@ -9045,25 +8964,11 @@
           <t>Compartir con personas sin cuenta mediante clave segura</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8">
         <f>COUNTIF(C8:Q8,"✓")</f>
         <v/>
@@ -9080,25 +8985,11 @@
           <t>Compartir datos con cuidador o persona de confianza</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9">
         <f>COUNTIF(C9:Q9,"✓")</f>
         <v/>
@@ -9120,13 +9011,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9152,16 +9041,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10">
         <f>COUNTIF(C10:Q10,"✓")</f>
         <v/>
@@ -9178,25 +9062,11 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11">
         <f>COUNTIF(C11:Q11,"✓")</f>
         <v/>
@@ -9213,25 +9083,11 @@
           <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12">
         <f>COUNTIF(C12:Q12,"✓")</f>
         <v/>
@@ -9248,25 +9104,11 @@
           <t>Red social con profesionales y familiares</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13">
         <f>COUNTIF(C13:Q13,"✓")</f>
         <v/>
@@ -9293,23 +9135,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14">
         <f>COUNTIF(C14:Q14,"✓")</f>
         <v/>
@@ -9326,8 +9156,6 @@
           <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9338,29 +9166,21 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15">
         <f>COUNTIF(C15:Q15,"✓")</f>
         <v/>
@@ -9382,8 +9202,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9399,19 +9217,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16">
         <f>COUNTIF(C16:Q16,"✓")</f>
         <v/>
@@ -9428,29 +9238,16 @@
           <t>Almacenamiento de recetas</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17">
         <f>COUNTIF(C17:Q17,"✓")</f>
         <v/>
@@ -9467,25 +9264,11 @@
           <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18">
         <f>COUNTIF(C18:Q18,"✓")</f>
         <v/>
@@ -9502,25 +9285,11 @@
           <t>Emisión de certificados médicos</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19">
         <f>COUNTIF(C19:Q19,"✓")</f>
         <v/>
@@ -9542,19 +9311,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9576,25 +9332,11 @@
           <t>Notificación y envío de resultados</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21">
         <f>COUNTIF(C21:Q21,"✓")</f>
         <v/>
@@ -9611,29 +9353,16 @@
           <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22">
         <f>COUNTIF(C22:Q22,"✓")</f>
         <v/>
@@ -9650,36 +9379,26 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9701,25 +9420,11 @@
           <t>Línea de tiempo de salud</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24">
         <f>COUNTIF(C24:Q24,"✓")</f>
         <v/>
@@ -9736,25 +9441,11 @@
           <t>Registro de alergias y vacunas</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25">
         <f>COUNTIF(C25:Q25,"✓")</f>
         <v/>
@@ -9771,25 +9462,11 @@
           <t>Seguimiento de visitas, gastos y seguros</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26">
         <f>COUNTIF(C26:Q26,"✓")</f>
         <v/>
@@ -9806,11 +9483,6 @@
           <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9826,13 +9498,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27">
         <f>COUNTIF(C27:Q27,"✓")</f>
         <v/>
@@ -9849,25 +9514,11 @@
           <t>Asistente de IA para profesionales de salud</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28">
         <f>COUNTIF(C28:Q28,"✓")</f>
         <v/>
@@ -9884,25 +9535,11 @@
           <t>Coaching de salud con IA</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29">
         <f>COUNTIF(C29:Q29,"✓")</f>
         <v/>
@@ -9919,15 +9556,6 @@
           <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9938,10 +9566,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30">
         <f>COUNTIF(C30:Q30,"✓")</f>
         <v/>
@@ -9958,15 +9582,6 @@
           <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9977,9 +9592,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10001,24 +9613,11 @@
           <t>Orientación médica con IA</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10040,15 +9639,6 @@
           <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10059,10 +9649,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33">
         <f>COUNTIF(C33:Q33,"✓")</f>
         <v/>
@@ -10079,15 +9665,6 @@
           <t>Resumen de historial con IA</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10098,10 +9675,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34">
         <f>COUNTIF(C34:Q34,"✓")</f>
         <v/>
@@ -10123,10 +9696,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10137,7 +9706,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10153,14 +9721,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35">
         <f>COUNTIF(C35:Q35,"✓")</f>
         <v/>
@@ -10177,25 +9742,11 @@
           <t>Analítica poblacional B2B</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36">
         <f>COUNTIF(C36:Q36,"✓")</f>
         <v/>
@@ -10212,9 +9763,6 @@
           <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10225,20 +9773,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37">
         <f>COUNTIF(C37:Q37,"✓")</f>
         <v/>
@@ -10255,25 +9794,11 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38">
         <f>COUNTIF(C38:Q38,"✓")</f>
         <v/>
@@ -10290,25 +9815,11 @@
           <t>Importación y exportación de datos</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39">
         <f>COUNTIF(C39:Q39,"✓")</f>
         <v/>
@@ -10325,25 +9836,11 @@
           <t>Integración con EHR de proveedores</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40">
         <f>COUNTIF(C40:Q40,"✓")</f>
         <v/>
@@ -10360,29 +9857,16 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41">
         <f>COUNTIF(C41:Q41,"✓")</f>
         <v/>
@@ -10399,25 +9883,11 @@
           <t>Gestión de lista de medicamentos</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42">
         <f>COUNTIF(C42:Q42,"✓")</f>
         <v/>
@@ -10434,25 +9904,11 @@
           <t>Importación automática de tratamientos desde receta digital</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43">
         <f>COUNTIF(C43:Q43,"✓")</f>
         <v/>
@@ -10474,24 +9930,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44">
         <f>COUNTIF(C44:Q44,"✓")</f>
         <v/>
@@ -10508,25 +9951,11 @@
           <t>Registro de tomas y adherencia al tratamiento</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45">
         <f>COUNTIF(C45:Q45,"✓")</f>
         <v/>
@@ -10543,25 +9972,11 @@
           <t>Comunidad de pacientes</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46">
         <f>COUNTIF(C46:Q46,"✓")</f>
         <v/>
@@ -10578,25 +9993,11 @@
           <t>Contenido educativo sobre salud</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47">
         <f>COUNTIF(C47:Q47,"✓")</f>
         <v/>
@@ -10613,25 +10014,11 @@
           <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48">
         <f>COUNTIF(C48:Q48,"✓")</f>
         <v/>
@@ -10648,25 +10035,11 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49">
         <f>COUNTIF(C49:Q49,"✓")</f>
         <v/>
@@ -10683,11 +10056,6 @@
           <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10698,14 +10066,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50">
         <f>COUNTIF(C50:Q50,"✓")</f>
         <v/>
@@ -10722,25 +10082,11 @@
           <t>Registro de nutrición</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51">
         <f>COUNTIF(C51:Q51,"✓")</f>
         <v/>
@@ -10757,25 +10103,11 @@
           <t>Seguimiento de salud femenina</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52">
         <f>COUNTIF(C52:Q52,"✓")</f>
         <v/>
@@ -10792,25 +10124,11 @@
           <t>Valoración de profesionales</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
       <c r="R53">
         <f>COUNTIF(C53:Q53,"✓")</f>
         <v/>
@@ -10827,25 +10145,11 @@
           <t>Acceso mínimo por categorías de datos</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54">
         <f>COUNTIF(C54:Q54,"✓")</f>
         <v/>
@@ -10862,11 +10166,6 @@
           <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10882,13 +10181,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55">
         <f>COUNTIF(C55:Q55,"✓")</f>
         <v/>
@@ -10905,29 +10197,16 @@
           <t>Cifrado y control de acceso</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56">
         <f>COUNTIF(C56:Q56,"✓")</f>
         <v/>
@@ -10944,25 +10223,11 @@
           <t>Cumplimiento regulatorio de salud y datos</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57">
         <f>COUNTIF(C57:Q57,"✓")</f>
         <v/>
@@ -10979,25 +10244,11 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
       <c r="R58">
         <f>COUNTIF(C58:Q58,"✓")</f>
         <v/>
@@ -11014,25 +10265,11 @@
           <t>Identidad descentralizada (DID)</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
       <c r="R59">
         <f>COUNTIF(C59:Q59,"✓")</f>
         <v/>
@@ -11049,15 +10286,6 @@
           <t>Privacidad reforzada para datos de salud</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11068,10 +10296,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
       <c r="R60">
         <f>COUNTIF(C60:Q60,"✓")</f>
         <v/>
@@ -11088,20 +10312,6 @@
           <t>Modelo freemium y suscripción</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11123,25 +10333,11 @@
           <t>Pagos con criptomoneda</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
       <c r="R62">
         <f>COUNTIF(C62:Q62,"✓")</f>
         <v/>
@@ -11158,20 +10354,6 @@
           <t>Pagos dentro de la app</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11193,25 +10375,11 @@
           <t>Reclamos y trámites con seguros</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
       <c r="R64">
         <f>COUNTIF(C64:Q64,"✓")</f>
         <v/>
@@ -11228,25 +10396,11 @@
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
       <c r="R65">
         <f>COUNTIF(C65:Q65,"✓")</f>
         <v/>
@@ -11263,7 +10417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -11444,6 +10598,13 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Vuelta 6 (iter. 1, 2026-10-13 12:16 UTC): Meedika, Infomed, MediPlanner, Clingot verificados (+0 filas; fuentes casi agotadas). Pendientes: Healfies, Patientory, MediBloc, Medicalchain, Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas, Clinia, MiRedSalud, Mediko.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B. [Vuelta 2] Lanzada simultáneamente en Brasil, Argentina y EE.UU.; permite compartir con no registrados vía clave por email. Sin novedades posteriores a 2016. [Vuelta 3] Sin evidencia de actividad reciente ni de cierre; Gust/Dealroom la listan en Florianópolis (10 empleados, healfies.com) sin fecha de actualización. Estado sin confirmar. [Vuelta 4] Sin Google Play localizado; no confundir con la app Healfy (otro producto). Sin novedades. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios.</t>
+          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B. [Vuelta 2] Lanzada simultáneamente en Brasil, Argentina y EE.UU.; permite compartir con no registrados vía clave por email. Sin novedades posteriores a 2016. [Vuelta 3] Sin evidencia de actividad reciente ni de cierre; Gust/Dealroom la listan en Florianópolis (10 empleados, healfies.com) sin fecha de actualización. Estado sin confirmar. [Vuelta 4] Sin Google Play localizado; no confundir con la app Healfy (otro producto). Sin novedades. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain. [Vuelta 2] Sin noticias 2026 encontradas en búsqueda; sitio oficial bloqueado. [Vuelta 3] Búsqueda adicional solo devuelve hitos de 2017 (token sale US$7,2M) y 2019 (Serie A de US$5,3M, cierre no confirmado); sin datos 2025-26 propios. [Vuelta 4] App pública lanzada en la conferencia JP Morgan Healthcare (2019); red PTOYMatrix (blockchain HIPAA); socios reportados: StartUp Health y Kaiser Permanente (beta). Estado actual en App Store/Google Play sin confirmar. [Vuelta 5] Sin noticias 2026 del equipo. Token PTOY con capitalización de ~US$53K a fines de ago-2026 según Phantom (KuCoin discrepa en la circulación): señal de baja actividad, no prueba de cierre. Esto relativiza la actividad hasta abr-2026 mencionada en la ficha original.</t>
+          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain. [Vuelta 2] Sin noticias 2026 encontradas en búsqueda; sitio oficial bloqueado. [Vuelta 3] Búsqueda adicional solo devuelve hitos de 2017 (token sale US$7,2M) y 2019 (Serie A de US$5,3M, cierre no confirmado); sin datos 2025-26 propios. [Vuelta 4] App pública lanzada en la conferencia JP Morgan Healthcare (2019); red PTOYMatrix (blockchain HIPAA); socios reportados: StartUp Health y Kaiser Permanente (beta). Estado actual en App Store/Google Play sin confirmar. [Vuelta 5] Sin noticias 2026 del equipo. Token PTOY con capitalización de ~US$53K a fines de ago-2026 según Phantom (KuCoin discrepa en la circulación): señal de baja actividad, no prueba de cierre. Esto relativiza la actividad hasta abr-2026 mencionada en la ficha original. [Vuelta 6] Sin noticias posteriores a 2020 localizadas (hitos: token sale 2017, consorcio Hyperledger, alianza con Georgia State, Series A de US$5,3M vía R/GA Ventures, Neith con Prosper Healthtech en Birmingham). Estado actual desconocido.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain. [Vuelta 2] Panacea incluye DID, Append Only Log, IBC y PNFT; sin anuncios 2026 localizados. [Vuelta 3] Medipass: app en Corea con 20 hospitales/aseguradoras integrados (fecha de la lista desconocida) y plan 2022 de superapp con marketplace de datos; operación actual sin confirmar. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Medipass: ~400.000 usuarios acumulados (CEO, jun-2022); integración con aseguradoras Shinhan Life, Samsung Fire y Hyundai Marine (2020); renovación completa en mar-2023 (dashboard de salud, gestión familiar, certificados). Sin noticias 2026 encontradas.</t>
+          <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain. [Vuelta 2] Panacea incluye DID, Append Only Log, IBC y PNFT; sin anuncios 2026 localizados. [Vuelta 3] Medipass: app en Corea con 20 hospitales/aseguradoras integrados (fecha de la lista desconocida) y plan 2022 de superapp con marketplace de datos; operación actual sin confirmar. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Medipass: ~400.000 usuarios acumulados (CEO, jun-2022); integración con aseguradoras Shinhan Life, Samsung Fire y Hyundai Marine (2020); renovación completa en mar-2023 (dashboard de salud, gestión familiar, certificados). Sin noticias 2026 encontradas. [Vuelta 6] Medipass 2023: comunicación bidireccional hospital-paciente y chat MediTalk; en 2019 fue seleccionada para el programa gubernamental de MyData médico con Samsung Fire y SNUH. Sin estrategia 2026 localizada. Meta declarada: usar Medipass como «identificación» de salud.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · Reino Unido · INACTIVO] Londres, 2017, Ethereum, con telemedicina. Piloto según registro de la UE (2020). Tracxn/PitchBook lo marcan fuera de operación (ago-2025). Solo caso de aprendizaje: no cuenta como competidor activo. [Vuelta 2] Token MTN deslistado de Bitfinex el 26-mar-2021; sin hallazgos de actividad posterior. [Vuelta 3] Seedtable la marca activa sin fuente; no hallé registro en Companies House. Sigue tratándose como caso de aprendizaje. [Vuelta 4] Pre-venta reportada de US$20M en MedTokens (un solo artículo secundario, sin verificar); modelo de token en revisión y exploración de security token según AMA; integraciones y servicios de 2019 sin confirmar. [Vuelta 5] Un agregador indica sitio medicalchain.com fuera de línea desde 15-feb-2025, último commit en GitHub hace ~3 años y proyecto en «fase de mantenimiento»; preventa de MedTokens reportada entre US$20M y US$24M (fuentes discrepan). Confirma tratarlo como inactivo.</t>
+          <t>[BLOCKCHAIN · Reino Unido · INACTIVO] Londres, 2017, Ethereum, con telemedicina. Piloto según registro de la UE (2020). Tracxn/PitchBook lo marcan fuera de operación (ago-2025). Solo caso de aprendizaje: no cuenta como competidor activo. [Vuelta 2] Token MTN deslistado de Bitfinex el 26-mar-2021; sin hallazgos de actividad posterior. [Vuelta 3] Seedtable la marca activa sin fuente; no hallé registro en Companies House. Sigue tratándose como caso de aprendizaje. [Vuelta 4] Pre-venta reportada de US$20M en MedTokens (un solo artículo secundario, sin verificar); modelo de token en revisión y exploración de security token según AMA; integraciones y servicios de 2019 sin confirmar. [Vuelta 5] Un agregador indica sitio medicalchain.com fuera de línea desde 15-feb-2025, último commit en GitHub hace ~3 años y proyecto en «fase de mantenimiento»; preventa de MedTokens reportada entre US$20M y US$24M (fuentes discrepan). Confirma tratarlo como inactivo. [Vuelta 6] Sin búsqueda nueva (revisada en vuelta 5; sitio fuera de línea desde feb-2025 según un agregador); sin cambios.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5206,6 +5206,70 @@
       <c r="F128" t="inlineStr">
         <is>
           <t>Búsqueda web (Unite.ai, Fortune, TechStrong); solo EE.UU., Pro/Max</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Telemedicina y atención remota</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Chat con hospitales (MediTalk)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Chat para consultas a hospitales, orientación simple de síntomas e información de tratamientos; comunicación bidireccional hospital-paciente (nov-2023).</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Medigate News, nov-2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Citas y agenda</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Reserva de citas en hospitales</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Reserva de citas en hospitales integrados, dentro de Medipass.</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Búsqueda web (ficha App Store Corea, notas de prensa)</t>
         </is>
       </c>
     </row>
@@ -10417,7 +10481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -10605,6 +10669,13 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Vuelta 6 (iter. 2, 2026-10-14 12:15 UTC): Healfies, Patientory, MediBloc, Medicalchain verificados (+2 filas, de MediBloc). Pendientes: Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas, Clinia, MiRedSalud, Mediko.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -833,12 +833,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Agrega registros clínicos vía FHIR; &gt;500 instituciones conectadas en EE.UU. (2018). Sin evidencia de disponibilidad en Chile. Incluida en el dispositivo. Amenaza si FHIR/IPS-CL se adopta en Chile. [Vuelta 2] Sin disponibilidad de registros clínicos en Chile (solo EE.UU., Reino Unido, Canadá). [Vuelta 3] iOS 27 (WWDC 8-jun-2026; publicado ~14-sep-2026): rediseño del app Health, menopausia, nutrición por cámara. El coach de salud con IA no se anunció. Sin ampliación de Health Records a Chile. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Sin ampliación de Health Records a Australia, Europa ni Latinoamérica (solo EE.UU., UK, Canadá). Funciones de dispositivo (apnea del sueño, prueba auditiva) sí se amplían a países latinoamericanos, pero no son registros clínicos.</t>
+          <t>[ADYACENTE · global] Agrega registros clínicos vía FHIR; &gt;500 instituciones conectadas en EE.UU. (2018). Sin evidencia de disponibilidad en Chile. Incluida en el dispositivo. Amenaza si FHIR/IPS-CL se adopta en Chile. [Vuelta 2] Sin disponibilidad de registros clínicos en Chile (solo EE.UU., Reino Unido, Canadá). [Vuelta 3] iOS 27 (WWDC 8-jun-2026; publicado ~14-sep-2026): rediseño del app Health, menopausia, nutrición por cámara. El coach de salud con IA no se anunció. Sin ampliación de Health Records a Chile. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Sin ampliación de Health Records a Australia, Europa ni Latinoamérica (solo EE.UU., UK, Canadá). Funciones de dispositivo (apnea del sueño, prueba auditiva) sí se amplían a países latinoamericanos, pero no son registros clínicos. [Vuelta 6] Sin novedades de iOS 27.x localizadas. Health Records API permite compartir registros con apps de terceros con control por app; opción de enviar datos de uso a Apple.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Lanzado 7-ene-2026. Conecta registros médicos; conectores solo en EE.UU. Dentro de suscripción del asistente. Fija la expectativa de consultar y resumir el historial. [Vuelta 2] Confirmado: registros solo EE.UU.; sin anuncios para Latinoamérica. Hay inconsistencia de fechas entre fuentes (7-ene-2026 lanzamiento vs. jul-2026 despliegue de registros). [Vuelta 3] Fechas aclaradas: presentación 7-ene-2026 (acceso limitado); despliegue de Health in ChatGPT con Apple Health y registros en EE.UU. el 23-jul-2026; mejora de salud jun-2026. Sin anuncios para Latinoamérica ni para sep-oct 2026. [Vuelta 4] Septiembre 2026: permisos por defecto para datos conectados (14-sep) y explicaciones por gráfico/métrica (28-sep); ChatGPT for Clinicians (abr-2026) para clínicos verificados de EE.UU. Más del 70% de usuarios de Health permite usar datos conectados sin pedir permiso (según OpenAI). Sigue solo EE.UU. [Vuelta 5] Nota de jul-2026: Health no está disponible en México, Android, modo de voz ni Codex; web e iOS en EE.UU., adultos con sesión iniciada. Sin anuncio para Chile ni Latinoamérica.</t>
+          <t>[ADYACENTE · global] Lanzado 7-ene-2026. Conecta registros médicos; conectores solo en EE.UU. Dentro de suscripción del asistente. Fija la expectativa de consultar y resumir el historial. [Vuelta 2] Confirmado: registros solo EE.UU.; sin anuncios para Latinoamérica. Hay inconsistencia de fechas entre fuentes (7-ene-2026 lanzamiento vs. jul-2026 despliegue de registros). [Vuelta 3] Fechas aclaradas: presentación 7-ene-2026 (acceso limitado); despliegue de Health in ChatGPT con Apple Health y registros en EE.UU. el 23-jul-2026; mejora de salud jun-2026. Sin anuncios para Latinoamérica ni para sep-oct 2026. [Vuelta 4] Septiembre 2026: permisos por defecto para datos conectados (14-sep) y explicaciones por gráfico/métrica (28-sep); ChatGPT for Clinicians (abr-2026) para clínicos verificados de EE.UU. Más del 70% de usuarios de Health permite usar datos conectados sin pedir permiso (según OpenAI). Sigue solo EE.UU. [Vuelta 5] Nota de jul-2026: Health no está disponible en México, Android, modo de voz ni Codex; web e iOS en EE.UU., adultos con sesión iniciada. Sin anuncio para Chile ni Latinoamérica. [Vuelta 6] Última entrada de Health en las notas de OpenAI sigue siendo la del 23-jul-2026 (más cambios de sep); sin entradas de octubre localizadas. Health tab: laboratorios, medicamentos, actividad y sueño en una vista; solo EE.UU., web e iOS.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -886,7 +886,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Lanzado 11-ene-2026. Conectores solo en EE.UU., planes Pro/Max. Nota: producto de Anthropic, conflicto de interés al evaluarlo. [Vuelta 2] Sin cambios fuera de EE.UU. (HealthEx y Function para Pro/Max). [Vuelta 3] Sin anuncios posteriores a enero de 2026. Hoja de ruta de HealthEx (agendar, buscar prestadores, recetas) sin confirmar como lanzada. [Vuelta 4] Sin anuncios nuevos. Fuentes discrepan en el acceso (Pro/Max según Fortune y la mayoría; Pro/Team según Times of AI); sin evidencia de disponibilidad fuera de EE.UU. [Vuelta 5] Sin noticias de oct-2026; HealthEx agrega datos de &gt;50.000 sistemas de EE.UU. y Claude pide solo las categorías relevantes vía MCP.</t>
+          <t>[ADYACENTE · global] Lanzado 11-ene-2026. Conectores solo en EE.UU., planes Pro/Max. Nota: producto de Anthropic, conflicto de interés al evaluarlo. [Vuelta 2] Sin cambios fuera de EE.UU. (HealthEx y Function para Pro/Max). [Vuelta 3] Sin anuncios posteriores a enero de 2026. Hoja de ruta de HealthEx (agendar, buscar prestadores, recetas) sin confirmar como lanzada. [Vuelta 4] Sin anuncios nuevos. Fuentes discrepan en el acceso (Pro/Max según Fortune y la mayoría; Pro/Team según Times of AI); sin evidencia de disponibilidad fuera de EE.UU. [Vuelta 5] Sin noticias de oct-2026; HealthEx agrega datos de &gt;50.000 sistemas de EE.UU. y Claude pide solo las categorías relevantes vía MCP. [Vuelta 6] Sin noticias posteriores a enero de 2026 localizadas.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -926,7 +926,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones. [Vuelta 2] App concreta: Mi Alemana Go (Clínica Alemana, Chile), con historial desde 2018, recetas, órdenes, familiar vinculado y resultados. [Vuelta 3] Búsqueda de otras clínicas (Las Condes, Santa María, UC Christus) sin ficha de app confirmada; solo canales digitales genéricos. [Vuelta 4] Mi Alemana Go: 3,1/5 con 137 calificaciones (App Store Chile), pantalla de inicio rediseñada para gestionar salud propia y familiar; sin evidencia de teleconsulta ni pagos en la app. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios.</t>
+          <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones. [Vuelta 2] App concreta: Mi Alemana Go (Clínica Alemana, Chile), con historial desde 2018, recetas, órdenes, familiar vinculado y resultados. [Vuelta 3] Búsqueda de otras clínicas (Las Condes, Santa María, UC Christus) sin ficha de app confirmada; solo canales digitales genéricos. [Vuelta 4] Mi Alemana Go: 3,1/5 con 137 calificaciones (App Store Chile), pantalla de inicio rediseñada para gestionar salud propia y familiar; sin evidencia de teleconsulta ni pagos en la app. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Sin búsqueda nueva; sin cambios.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F130"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5270,6 +5270,38 @@
       <c r="F130" t="inlineStr">
         <is>
           <t>Búsqueda web (ficha App Store Corea, notas de prensa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Apple Health (Health Records)</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>API de Health Records para apps de terceros</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>El usuario decide qué registros recibe cada app y si los nuevos se comparten automáticamente (por defecto pide permiso cada vez); ej. importar recetas a Medisafe.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Apple, TechCrunch, Pharmaphorum); registros solo EE.UU./UK/Canadá</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -10676,6 +10708,13 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Vuelta 6 (iter. 3, 2026-10-15 12:15 UTC): Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas verificados (+1 fila). Pendientes: Clinia, MiRedSalud, Mediko (cierran la vuelta 6 y regeneran func_norm/tabla_frecuencia).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -518,15 +518,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -558,15 +558,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -598,15 +598,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -638,15 +638,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -678,15 +678,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -718,15 +718,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -758,15 +758,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -798,15 +798,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -838,15 +838,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -878,15 +878,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -918,15 +918,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -958,15 +958,15 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar. [Vuelta 2] Confirmado por el CEO de Reservo (LinkedIn): app para pacientes en App Store y Google Play; guarda y comparte exámenes, recetas, órdenes y certificados. Fecha exacta de lanzamiento, precio y modelo de datos sin verificar. [Vuelta 3] Sin novedades de oct-2026. Reservo (Chile, México, Argentina) declara certificación Fonasa/CENS y cumplimiento de la nueva ley de datos personales; el Portal de Agendamiento de Reservo complementa a Clinia. Precio y modelo de datos sin verificar. [Vuelta 4] Una búsqueda adicional no encontró fuentes independientes sobre Clinia de Reservo (aparecen otras empresas llamadas Clinia); la evidencia sigue siendo la publicación del CEO en LinkedIn y notas de Reservo. Confianza media. [Vuelta 5] Sin fecha verificable del lanzamiento (publicación de LinkedIn del CEO sin fecha visible); existe otra empresa homónima en Brasil (Porto Alegre, IA para clínicas) que no es este producto. Sin funciones nuevas.</t>
+          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar. [Vuelta 2] Confirmado por el CEO de Reservo (LinkedIn): app para pacientes en App Store y Google Play; guarda y comparte exámenes, recetas, órdenes y certificados. Fecha exacta de lanzamiento, precio y modelo de datos sin verificar. [Vuelta 3] Sin novedades de oct-2026. Reservo (Chile, México, Argentina) declara certificación Fonasa/CENS y cumplimiento de la nueva ley de datos personales; el Portal de Agendamiento de Reservo complementa a Clinia. Precio y modelo de datos sin verificar. [Vuelta 4] Una búsqueda adicional no encontró fuentes independientes sobre Clinia de Reservo (aparecen otras empresas llamadas Clinia); la evidencia sigue siendo la publicación del CEO en LinkedIn y notas de Reservo. Confianza media. [Vuelta 5] Sin fecha verificable del lanzamiento (publicación de LinkedIn del CEO sin fecha visible); existe otra empresa homónima en Brasil (Porto Alegre, IA para clínicas) que no es este producto. Sin funciones nuevas. [Vuelta 6] Sin novedades de oct-2026. Reservo declara &gt;36.500 profesionales y centros y ~14 millones de reservas al año (Chile, México, Argentina), sello CENS y certificación Fonasa (autodeclarado); la publicación del CEO pide ideas de nuevas funciones. Sigue sin fecha de lanzamiento verificable.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1002,11 +1002,11 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis). [Vuelta 2] La búsqueda no encontró fuentes adicionales ni ficha de la app chilena (solo una app RedSalud de otro país); funciones sin confirmar. [Vuelta 3] Rankings de terceros la ubican como app médica gratuita nº 1 en App Store y Google Play Chile (fecha desconocida); sin descripción de funciones ni confirmación del desarrollador en Google Play. [Vuelta 4] Sin documentación oficial chilena localizada; las fichas con funciones (agendar, telemedicina, historial de hijos) corresponden a una app RedSalud de otro país. Quejas públicas 2020-21 sobre acceso en línea a resultados. Funciones de MiRedSalud sin confirmar. [Vuelta 5] Una búsqueda adicional no halló cobertura del lanzamiento de dic-2025 ni de la app chilena; solo apps de otras empresas Red Salud (Paraguay, Perú). Sigue sin confirmarse más allá de la nota de RedSalud.</t>
+          <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis). [Vuelta 2] La búsqueda no encontró fuentes adicionales ni ficha de la app chilena (solo una app RedSalud de otro país); funciones sin confirmar. [Vuelta 3] Rankings de terceros la ubican como app médica gratuita nº 1 en App Store y Google Play Chile (fecha desconocida); sin descripción de funciones ni confirmación del desarrollador en Google Play. [Vuelta 4] Sin documentación oficial chilena localizada; las fichas con funciones (agendar, telemedicina, historial de hijos) corresponden a una app RedSalud de otro país. Quejas públicas 2020-21 sobre acceso en línea a resultados. Funciones de MiRedSalud sin confirmar. [Vuelta 5] Una búsqueda adicional no halló cobertura del lanzamiento de dic-2025 ni de la app chilena; solo apps de otras empresas Red Salud (Paraguay, Perú). Sigue sin confirmarse más allá de la nota de RedSalud. [Vuelta 6] Sin cobertura adicional; los resultados corresponden a la plataforma Red Salud de Paraguay (Interasistencia, ~350 especialistas, call center por WhatsApp), que no es la red chilena. Funciones de MiRedSalud sin confirmar.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc. [Vuelta 2] Sin precios ni planes vigentes localizados; sitio oficial bloqueado. [Vuelta 3] Pauta (oct-2024): su fundador, Tomás Riddell, dice que no reemplaza a médicos y apunta a lo ambulatorio y a la espera de derivación a especialidad en el sistema público. Financiamiento: fuentes discrepan (CLP 25M en dic-2023 según Bouncewatch; ~$40M según Descubre.vc). Precios vigentes sin verificar. [Vuelta 4] Entrevista oct-2024 menciona integración con la pasarela Flow. Sin novedades 2025-26 ni rondas verificadas; la cifra de US$40M de Bouncewatch es dudosa (perfil con 2 empleados). [Vuelta 5] CORRECCIÓN de financiamiento: Bouncewatch registra dos subvenciones (CLP 15M en ago-2022 y CLP 25M en dic-2023 = CLP 40M en total), no US$40M; 2 empleados; etapa Seed según Descubre.vc. No hay inversionistas de capital listados.</t>
+          <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc. [Vuelta 2] Sin precios ni planes vigentes localizados; sitio oficial bloqueado. [Vuelta 3] Pauta (oct-2024): su fundador, Tomás Riddell, dice que no reemplaza a médicos y apunta a lo ambulatorio y a la espera de derivación a especialidad en el sistema público. Financiamiento: fuentes discrepan (CLP 25M en dic-2023 según Bouncewatch; ~$40M según Descubre.vc). Precios vigentes sin verificar. [Vuelta 4] Entrevista oct-2024 menciona integración con la pasarela Flow. Sin novedades 2025-26 ni rondas verificadas; la cifra de US$40M de Bouncewatch es dudosa (perfil con 2 empleados). [Vuelta 5] CORRECCIÓN de financiamiento: Bouncewatch registra dos subvenciones (CLP 15M en ago-2022 y CLP 25M en dic-2023 = CLP 40M en total), no US$40M; 2 empleados; etapa Seed según Descubre.vc. No hay inversionistas de capital listados. [Vuelta 6] Sin noticias 2026 propias. Contexto: evento «IA y Salud en Chile 2026» (12-may) sobre regulación, datos personales e interoperabilidad de fichas clínicas; Doctoralia lanzó Noa Evidence (jul-2026, asistente de IA para profesionales); programa PRISMA IA 2.0 (dic-2025).</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1082,11 +1082,11 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E128"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5599,34 +5599,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Compartición y consentimiento</t>
+          <t>Citas y agenda</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Acceso del profesional al historial del paciente</t>
+          <t>Reserva de citas médicas</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>El médico puede revisar el historial e ingresar datos automáticamente.</t>
+          <t>Reserva de citas en hospitales integrados, dentro de Medipass.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5636,24 +5636,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Compartir con personas sin cuenta mediante clave segura</t>
+          <t>Acceso del profesional al historial del paciente</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Datos compartibles con personas sin cuenta mediante clave de acceso segura enviada por email.</t>
+          <t>El médico puede revisar el historial e ingresar datos automáticamente.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5663,17 +5663,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Compartir datos con cuidador o persona de confianza</t>
+          <t>Compartir con personas sin cuenta mediante clave segura</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Comparte de forma privada datos de salud (actividad, corazón, movilidad) con una persona de confianza, eligiendo qué y con quién.</t>
+          <t>Datos compartibles con personas sin cuenta mediante clave de acceso segura enviada por email.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
@@ -5690,12 +5690,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+          <t>Compartir datos con cuidador o persona de confianza</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Permite compartir información con médicos, familia y amistades.</t>
+          <t>Comparte de forma privada datos de salud (actividad, corazón, movilidad) con una persona de confianza, eligiendo qué y con quién.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5707,7 +5707,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5722,19 +5722,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Comparte los documentos guardados con los profesionales en la consulta.</t>
+          <t>Permite compartir información con médicos, familia y amistades.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5749,19 +5749,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Comparte registros con familiares o profesionales.</t>
+          <t>Comparte los documentos guardados con los profesionales en la consulta.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5776,19 +5776,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Traspaso de registros a hospitales.</t>
+          <t>Comparte registros con familiares o profesionales.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Compartir información con profesionales de salud.</t>
+          <t>Traspaso de registros a hospitales.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Comparte información con cuidadores, maestros o profesionales de confianza.</t>
+          <t>Compartir información con profesionales de salud.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -5842,7 +5842,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5857,19 +5857,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Acceso de clínicos limitado en el tiempo.</t>
+          <t>Comparte información con cuidadores, maestros o profesionales de confianza.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5884,19 +5884,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>El usuario decide con qué profesionales comparte su información.</t>
+          <t>Acceso de clínicos limitado en el tiempo.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5911,19 +5911,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>El usuario autoriza a proveedores a acceder y usar sus datos de salud.</t>
+          <t>El usuario decide con qué profesionales comparte su información.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gestión de consentimiento sobre uso de datos</t>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>El usuario decide si sus registros se usan para análisis de big data.</t>
+          <t>El usuario autoriza a proveedores a acceder y usar sus datos de salud.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -5950,7 +5950,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5960,24 +5960,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ingreso de datos por profesional con consentimiento</t>
+          <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>El médico puede ingresar datos al historial con autorización del paciente.</t>
+          <t>El usuario decide si sus registros se usan para análisis de big data.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5987,39 +5987,39 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Red social con profesionales y familiares</t>
+          <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Interacción con médicos, dentistas, kinesiólogos, entrenadores y familiares dentro de la red.</t>
+          <t>El médico puede ingresar datos al historial con autorización del paciente.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Emergencia</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ficha de emergencia (alergias y medicación)</t>
+          <t>Red social con profesionales y familiares</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Disponibilidad del historial en situaciones de atención.</t>
+          <t>Interacción con médicos, dentistas, kinesiólogos, entrenadores y familiares dentro de la red.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -6031,7 +6031,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6046,19 +6046,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Acceso a datos clave del paciente en emergencias.</t>
+          <t>Disponibilidad del historial en situaciones de atención.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ficha de emergencia con alergias y medicación accesible rápidamente.</t>
+          <t>Acceso a datos clave del paciente en emergencias.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6085,22 +6085,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Familia y dependientes</t>
+          <t>Emergencia</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Perfiles familiares / dependientes</t>
+          <t>Ficha de emergencia (alergias y medicación)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Vincula familiares a la cuenta.</t>
+          <t>Ficha de emergencia con alergias y medicación accesible rápidamente.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Rediseño de la pantalla de inicio para gestionar la salud propia y la de la familia en una sola vista.</t>
+          <t>Vincula familiares a la cuenta.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6139,7 +6139,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6154,19 +6154,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Los padres pueden monitorear la salud de hijos pequeños.</t>
+          <t>Rediseño de la pantalla de inicio para gestionar la salud propia y la de la familia en una sola vista.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6181,19 +6181,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>El relanzamiento de Medipass (mar-2023) incorporó gestión de la salud de familiares.</t>
+          <t>Los padres pueden monitorear la salud de hijos pequeños.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6208,19 +6208,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Historial por perfil para cada miembro de la familia.</t>
+          <t>El relanzamiento de Medipass (mar-2023) incorporó gestión de la salud de familiares.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MiRedSalud (RedSalud)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6235,46 +6235,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Guardar y administrar historial propio y familiar.</t>
+          <t>Historial por perfil para cada miembro de la familia.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>MiRedSalud (RedSalud)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gestión documental</t>
+          <t>Familia y dependientes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Almacenamiento de documentos médicos</t>
+          <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sube estudios, imágenes, indicaciones médicas y notas personales; accesible en consulta o por terceros en emergencias.</t>
+          <t>Guardar y administrar historial propio y familiar.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6289,12 +6289,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Reúne recetas, diagnósticos y laboratorios en un solo lugar.</t>
+          <t>Sube estudios, imágenes, indicaciones médicas y notas personales; accesible en consulta o por terceros en emergencias.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Guarda en un solo lugar exámenes, recetas, órdenes y certificados médicos.</t>
+          <t>Reúne recetas, diagnósticos y laboratorios en un solo lugar.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -6328,7 +6328,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6343,19 +6343,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Organiza registros con carpetas y etiquetas.</t>
+          <t>Guarda en un solo lugar exámenes, recetas, órdenes y certificados médicos.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6370,19 +6370,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Almacena documentos clínicos del usuario en la app.</t>
+          <t>Organiza registros con carpetas y etiquetas.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6397,19 +6397,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Administra fechas, prescripciones, archivos y citas desde la app.</t>
+          <t>Almacena documentos clínicos del usuario en la app.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6419,24 +6419,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Almacenamiento de recetas</t>
+          <t>Almacenamiento de documentos médicos</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ver y descargar recetas, órdenes de examen y derivaciones.</t>
+          <t>Administra fechas, prescripciones, archivos y citas desde la app.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Guarda recetas digitales.</t>
+          <t>Ver y descargar recetas, órdenes de examen y derivaciones.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Búsqueda y filtros de documentos</t>
+          <t>Almacenamiento de recetas</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Guarda resultados de laboratorio, imágenes y PDFs; búsqueda y filtros.</t>
+          <t>Guarda recetas digitales.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6490,7 +6490,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6500,24 +6500,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Emisión de certificados médicos</t>
+          <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>La ficha de la app incluye consulta de chequeos de salud y emisión de certificados médicos.</t>
+          <t>Guarda resultados de laboratorio, imágenes y PDFs; búsqueda y filtros.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6527,24 +6527,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Importación de órdenes/solicitudes médicas</t>
+          <t>Emisión de certificados médicos</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Descarga/genera órdenes médicas digitales.</t>
+          <t>La ficha de la app incluye consulta de chequeos de salud y emisión de certificados médicos.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Importa solicitudes (órdenes) médicas a la app.</t>
+          <t>Descarga/genera órdenes médicas digitales.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6571,7 +6571,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6581,12 +6581,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Notificación y envío de resultados</t>
+          <t>Importación de órdenes/solicitudes médicas</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Avisa cuando hay exámenes/documentos disponibles; resultados de laboratorio y anatomía patológica compartibles por email o WhatsApp.</t>
+          <t>Importa solicitudes (órdenes) médicas a la app.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6603,17 +6603,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Historial institucional (solo datos de la propia red)</t>
+          <t>Notificación y envío de resultados</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ve historial de esa institución.</t>
+          <t>Avisa cuando hay exámenes/documentos disponibles; resultados de laboratorio y anatomía patológica compartibles por email o WhatsApp.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Historial institucional de consultas, urgencias y hospitalizaciones (solo datos de esa clínica).</t>
+          <t>Ve historial de esa institución.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6652,7 +6652,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MiRedSalud (RedSalud)</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Acceso a información clínica de la red.</t>
+          <t>Historial institucional de consultas, urgencias y hospitalizaciones (solo datos de esa clínica).</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6679,7 +6679,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MiRedSalud (RedSalud)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6689,24 +6689,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Información clínica unificada.</t>
+          <t>Acceso a información clínica de la red.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6721,19 +6721,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>El usuario registra sus antecedentes médicos en la app.</t>
+          <t>Información clínica unificada.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6748,19 +6748,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Centraliza el historial médico personal en el móvil.</t>
+          <t>El usuario registra sus antecedentes médicos en la app.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6775,19 +6775,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Permite compilar datos de vida/salud, gestionarlos y pasarlos a instituciones médicas.</t>
+          <t>Centraliza el historial médico personal en el móvil.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6802,19 +6802,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Centralizar registros y monitoreo desde el móvil.</t>
+          <t>Permite compilar datos de vida/salud, gestionarlos y pasarlos a instituciones médicas.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6824,17 +6824,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Línea de tiempo de salud</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Línea de tiempo con medicación, exámenes, citas y dieta.</t>
+          <t>Centralizar registros y monitoreo desde el móvil.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Registra notas de medicación, exámenes (laboratorio e imagen), actividad física, recetas, dieta y citas.</t>
+          <t>Línea de tiempo con medicación, exámenes, citas y dieta.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6868,7 +6868,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas</t>
+          <t>Línea de tiempo de salud</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas.</t>
+          <t>Registra notas de medicación, exámenes (laboratorio e imagen), actividad física, recetas, dieta y citas.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6895,7 +6895,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6905,39 +6905,39 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seguimiento de visitas, gastos y seguros</t>
+          <t>Registro de alergias y vacunas</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>App gratuita para seguir visitas al médico, facturas médicas, datos personales, seguros, inmunizaciones y medicamentos de farmacia.</t>
+          <t>Registro de alergias y vacunas.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Incentivos y monetización de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Recompensas / monetización de datos del usuario</t>
+          <t>Seguimiento de visitas, gastos y seguros</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Plan de convertir Medipass en superapp con gestión de salud diaria y mercado de datos, integrada con la EMR Dr.Palette.</t>
+          <t>App gratuita para seguir visitas al médico, facturas médicas, datos personales, seguros, inmunizaciones y medicamentos de farmacia.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6949,7 +6949,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Centros de investigación y farmacéuticas recompensarían con MedTokens a quienes compartan sus datos; no confirmado como ejecutado.</t>
+          <t>Plan de convertir Medipass en superapp con gestión de salud diaria y mercado de datos, integrada con la EMR Dr.Palette.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6976,7 +6976,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>El usuario puede agregar y monetizar sus datos; recompensas en cripto.</t>
+          <t>Centros de investigación y farmacéuticas recompensarían con MedTokens a quienes compartan sus datos; no confirmado como ejecutado.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7003,22 +7003,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Incentivos y monetización de datos</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Asistente de IA para profesionales de salud</t>
+          <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Producto para clínicos verificados de EE.UU. (gratis, abr-2026); desde 1-sep-2026 un plugin con nueve apps de fuentes públicas (investigación, ensayos, medicamentos, Medicare, prestadores), de solo lectura y sin acceso a fichas de pacientes.</t>
+          <t>El usuario puede agregar y monetizar sus datos; recompensas en cripto.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7030,7 +7030,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Coaching de salud con IA</t>
+          <t>Asistente de IA para profesionales de salud</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Coaching personalizado con IA.</t>
+          <t>Producto para clínicos verificados de EE.UU. (gratis, abr-2026); desde 1-sep-2026 un plugin con nueve apps de fuentes públicas (investigación, ensayos, medicamentos, Medicare, prestadores), de solo lectura y sin acceso a fichas de pacientes.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7057,7 +7057,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Detección de patrones en métricas de salud con IA</t>
+          <t>Coaching de salud con IA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Interpreta datos de Apple Health y registros en contexto y detecta cambios.</t>
+          <t>Coaching personalizado con IA.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7084,7 +7084,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Detecta patrones entre métricas de salud y fitness.</t>
+          <t>Interpreta datos de Apple Health y registros en contexto y detecta cambios.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7111,7 +7111,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
+          <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Explica resultados complejos en lenguaje simple.</t>
+          <t>Detecta patrones entre métricas de salud y fitness.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Desde 28-sep-2026, en la pestaña Health se puede elegir un gráfico, métrica o registro y obtener explicaciones basadas en los datos conectados.</t>
+          <t>Explica resultados complejos en lenguaje simple.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7165,7 +7165,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Explica exámenes en lenguaje simple.</t>
+          <t>Desde 28-sep-2026, en la pestaña Health se puede elegir un gráfico, métrica o registro y obtener explicaciones basadas en los datos conectados.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7192,7 +7192,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7207,19 +7207,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Interpreta exámenes de laboratorio.</t>
+          <t>Explica exámenes en lenguaje simple.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7229,24 +7229,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Orientación médica con IA</t>
+          <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mejora de jun-2026 (GPT-5.5 Instant): detecta cuándo puede requerirse atención urgente, pide contexto y explica la incertidumbre.</t>
+          <t>Interpreta exámenes de laboratorio.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7261,19 +7261,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Orientación médica instantánea mediante IA.</t>
+          <t>Mejora de jun-2026 (GPT-5.5 Instant): detecta cuándo puede requerirse atención urgente, pide contexto y explica la incertidumbre.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7283,24 +7283,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Preparación de consultas médicas con IA</t>
+          <t>Orientación médica con IA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Prepara preguntas para el médico.</t>
+          <t>Orientación médica instantánea mediante IA.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7327,7 +7327,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7337,12 +7337,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Resumen de historial con IA</t>
+          <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Resume instrucciones de atención.</t>
+          <t>Prepara preguntas para el médico.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7354,7 +7354,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Resume el historial del usuario.</t>
+          <t>Resume instrucciones de atención.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7381,22 +7381,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>Resumen de historial con IA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Vista central de alergias, condiciones, vacunas, laboratorio, medicación, procedimientos y signos vitales.</t>
+          <t>Resume el historial del usuario.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7408,7 +7408,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>API para apps de terceros</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Conexión de historiales electrónicos y apps como Apple Health, MyFitnessPal, Peloton.</t>
+          <t>El usuario decide qué registros recibe cada app y si los nuevos se comparten automáticamente (por defecto pide permiso cada vez); ej. importar recetas a Medisafe.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7435,7 +7435,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Acceso a historiales electrónicos de proveedores de EE.UU. vía b.well; solo EE.UU., sin plazo anunciado para Latinoamérica.</t>
+          <t>Vista central de alergias, condiciones, vacunas, laboratorio, medicación, procedimientos y signos vitales.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Además de b.well y Apple Health, vincula registros de One Medical y Function Health (solo EE.UU., Free/Go/Plus/Pro, web e iOS).</t>
+          <t>Conexión de historiales electrónicos y apps como Apple Health, MyFitnessPal, Peloton.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7489,7 +7489,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Acceso a resultados y registros de salud (beta, Pro/Max, EE.UU.).</t>
+          <t>Acceso a historiales electrónicos de proveedores de EE.UU. vía b.well; solo EE.UU., sin plazo anunciado para Latinoamérica.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7516,7 +7516,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7531,19 +7531,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Datos desde profesionales/centros que usan Reservo (fichas clínicas, agenda, telemedicina).</t>
+          <t>Además de b.well y Apple Health, vincula registros de One Medical y Function Health (solo EE.UU., Free/Go/Plus/Pro, web e iOS).</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Tras autenticación simple, trae los últimos 3 años de historial de hospitales integrados (p. ej. Samsung Seoul, SNUH, Severance).</t>
+          <t>Acceso a resultados y registros de salud (beta, Pro/Max, EE.UU.).</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7570,7 +7570,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Sincroniza resultados desde centros de salud y permite subir fotos o documentos de las solicitudes médicas.</t>
+          <t>Datos desde profesionales/centros que usan Reservo (fichas clínicas, agenda, telemedicina).</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7597,7 +7597,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Reúne registros de hospitales, resultados de laboratorio y datos genómicos.</t>
+          <t>Tras autenticación simple, trae los últimos 3 años de historial de hospitales integrados (p. ej. Samsung Seoul, SNUH, Severance).</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7624,7 +7624,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7634,24 +7634,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Analítica poblacional B2B</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Analítica poblacional on-chain; integrada con Epic, Cerner, Meditech y Allscripts (B2B).</t>
+          <t>Sincroniza resultados desde centros de salud y permite subir fotos o documentos de las solicitudes médicas.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7661,24 +7661,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Android, iOS y escritorio; médicos acceden a historias digitalizadas, envían estudios e indicaciones y organizan agenda.</t>
+          <t>Reúne registros de hospitales, resultados de laboratorio y datos genómicos.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7688,24 +7688,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+          <t>Analítica poblacional B2B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Disponible en App Store y Google Play. Reservo opera en Chile, México y Argentina y está certificada por FONASA y CENS.</t>
+          <t>Analítica poblacional on-chain; integrada con Epic, Cerner, Meditech y Allscripts (B2B).</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Disponible en web, iOS y Android.</t>
+          <t>Android, iOS y escritorio; médicos acceden a historias digitalizadas, envían estudios e indicaciones y organizan agenda.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7732,7 +7732,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7742,24 +7742,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Versión digital de los registros con acceso por móvil o web.</t>
+          <t>Disponible en App Store y Google Play. Reservo opera en Chile, México y Argentina y está certificada por FONASA y CENS.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Importación y exportación de datos</t>
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Importar/exportar datos para compartir de forma segura con familias o cuidadores. Es MediPlanner Pro, de otro desarrollador (App Store MX, $39 MXN).</t>
+          <t>Disponible en web, iOS y Android.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Integración con EHR de proveedores</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Según una AMA sin fecha, integraba dos sistemas de GP que cubren ~80% del mercado UK; no confirmado como ejecutado.</t>
+          <t>Versión digital de los registros con acceso por móvil o web.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -7813,7 +7813,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7823,24 +7823,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Importación y exportación de datos</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Integración beta en apps iOS/Android.</t>
+          <t>Importar/exportar datos para compartir de forma segura con familias o cuidadores. Es MediPlanner Pro, de otro desarrollador (App Store MX, $39 MXN).</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Integración con EHR de proveedores</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Integración beta con Health Connect en la app móvil; conectores de registros (HealthEx, Function) solo para Pro/Max en EE.UU.</t>
+          <t>Según una AMA sin fecha, integraba dos sistemas de GP que cubren ~80% del mercado UK; no confirmado como ejecutado.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -7867,7 +7867,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
+          <t>Integración beta en apps iOS/Android.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7894,22 +7894,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Gestión de lista de medicamentos</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Listas de medicamentos, vitaminas y suplementos con horarios; escaneo de etiqueta del frasco solo en EE.UU.</t>
+          <t>Integración beta con Health Connect en la app móvil; conectores de registros (HealthEx, Function) solo para Pro/Max en EE.UU.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7921,27 +7921,27 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Importación automática de tratamientos desde receta digital</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Según la ficha de la App Store MX, los tratamientos llegan automáticamente desde la receta digital del médico (autodeclarado, sin verificar).</t>
+          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
@@ -7958,12 +7958,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
+          <t>Gestión de lista de medicamentos</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Recordatorios desde el app.</t>
+          <t>Listas de medicamentos, vitaminas y suplementos con horarios; escaneo de etiqueta del frasco solo en EE.UU.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -7975,7 +7975,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7985,24 +7985,24 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
+          <t>Importación automática de tratamientos desde receta digital</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Recordatorios de citas/medicación.</t>
+          <t>Según la ficha de la App Store MX, los tratamientos llegan automáticamente desde la receta digital del médico (autodeclarado, sin verificar).</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8012,78 +8012,78 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Registro de tomas y adherencia al tratamiento</t>
+          <t>Recordatorios de medicación y citas</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Registro de cada toma y control de adherencia; gestiona medicamentos propios y de familiares.</t>
+          <t>Recordatorios desde el app.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Comunidad de pacientes</t>
+          <t>Recordatorios de medicación y citas</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Los usuarios con condiciones similares pueden preguntar, recibir recomendaciones y compartir experiencias.</t>
+          <t>Recordatorios de citas/medicación.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Contenido educativo sobre salud</t>
+          <t>Registro de tomas y adherencia al tratamiento</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Busca que el paciente aprenda sobre sus enfermedades y sea más autónomo.</t>
+          <t>Registro de cada toma y control de adherencia; gestiona medicamentos propios y de familiares.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8093,24 +8093,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores</t>
+          <t>Comunidad de pacientes</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores de salud.</t>
+          <t>Los usuarios con condiciones similares pueden preguntar, recibir recomendaciones y compartir experiencias.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8120,24 +8120,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Contenido educativo sobre salud</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Datos de pasos, sueño, peso junto a registros.</t>
+          <t>Busca que el paciente aprenda sobre sus enfermedades y sea más autónomo.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8147,24 +8147,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Panel de seguimiento de salud y bienestar</t>
+          <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>El relanzamiento de Medipass (mar-2023) agregó un panel para gestionar la información de salud del usuario.</t>
+          <t>Gráficas de evolución de indicadores de salud.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Panel de seguimiento de salud y bienestar</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
+          <t>Datos de pasos, sueño, peso junto a registros.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -8191,7 +8191,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8201,12 +8201,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Registro de nutrición</t>
+          <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Escaneo de etiquetas nutricionales con la cámara; según un análisis, no escribe en HealthKit.</t>
+          <t>El relanzamiento de Medipass (mar-2023) agregó un panel para gestionar la información de salud del usuario.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -8218,7 +8218,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Seguimiento de salud femenina</t>
+          <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Extiende el seguimiento de ciclo con perimenopausia y menopausia.</t>
+          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8245,7 +8245,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8255,39 +8255,39 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Valoración de profesionales</t>
+          <t>Registro de nutrición</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Calificación de la atención de profesionales con autorización previa, compartible con otros usuarios.</t>
+          <t>Escaneo de etiquetas nutricionales con la cámara; según un análisis, no escribe en HealthKit.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Acceso mínimo por categorías de datos</t>
+          <t>Seguimiento de salud femenina</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Claude solicita solo las categorías relevantes (p. ej. medicamentos o laboratorio) y no fichas completas; HealthEx agrega datos de más de 50.000 sistemas de salud de EE.UU.</t>
+          <t>Extiende el seguimiento de ciclo con perimenopausia y menopausia.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8299,34 +8299,34 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Valoración de profesionales</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
+          <t>Calificación de la atención de profesionales con autorización previa, compartible con otros usuarios.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Acceso mínimo por categorías de datos</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Almacena huellas de datos médicos en un registro de solo escritura, sin guardar datos clínicos en cadena.</t>
+          <t>Claude solicita solo las categorías relevantes (p. ej. medicamentos o laboratorio) y no fichas completas; HealthEx agrega datos de más de 50.000 sistemas de salud de EE.UU.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8353,7 +8353,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
+          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8380,7 +8380,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
+          <t>Almacena huellas de datos médicos en un registro de solo escritura, sin guardar datos clínicos en cadena.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8407,7 +8407,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso</t>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
+          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8434,7 +8434,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8444,24 +8444,24 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso</t>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Almacenamiento seguro del historial con criterios de seguridad estrictos, comparable a apps bancarias.</t>
+          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8471,24 +8471,24 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cumplimiento regulatorio de salud y datos</t>
+          <t>Cifrado y control de acceso</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Reservo declara plataforma certificada por Fonasa y CENS, cumplimiento de estándares de telemedicina del Minsal y de la nueva ley chilena de datos personales (declaración de la empresa).</t>
+          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8498,24 +8498,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Gestión de consentimiento sobre uso de datos</t>
+          <t>Cifrado y control de acceso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Desde 14-sep-2026, las nuevas conexiones heredan la configuración global de plugins: ChatGPT puede usar datos de Health sin pedir permiso cada vez salvo acciones sensibles (web primero, móvil después).</t>
+          <t>Almacenamiento seguro del historial con criterios de seguridad estrictos, comparable a apps bancarias.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8525,17 +8525,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Identidad descentralizada (DID)</t>
+          <t>Cumplimiento regulatorio de salud y datos</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Gestión de identificadores descentralizados en Panacea.</t>
+          <t>Reservo declara plataforma certificada por Fonasa y CENS, cumplimiento de estándares de telemedicina del Minsal y de la nueva ley chilena de datos personales (declaración de la empresa).</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -8552,12 +8552,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
+          <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
+          <t>Desde 14-sep-2026, las nuevas conexiones heredan la configuración global de plugins: ChatGPT puede usar datos de Health sin pedir permiso cada vez salvo acciones sensibles (web primero, móvil después).</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8569,7 +8569,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8579,12 +8579,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
+          <t>Identidad descentralizada (DID)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>El usuario activa y revoca permisos; los datos de salud compartidos se excluyen de la memoria de Claude y del entrenamiento.</t>
+          <t>Gestión de identificadores descentralizados en Panacea.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8596,49 +8596,49 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Modelo freemium y suscripción</t>
+          <t>Privacidad reforzada para datos de salud</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Planes para personas y empresas.</t>
+          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Pagos con criptomoneda</t>
+          <t>Privacidad reforzada para datos de salud</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Pago de consultas con token.</t>
+          <t>El usuario activa y revoca permisos; los datos de salud compartidos se excluyen de la memoria de Claude y del entrenamiento.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8650,7 +8650,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8660,24 +8660,24 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Pagos con criptomoneda</t>
+          <t>Modelo freemium y suscripción</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Piloto en New Malden (Londres): consultas por video pagables con tarjeta o con MedTokens.</t>
+          <t>Planes para personas y empresas.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8687,24 +8687,24 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Pagos dentro de la app</t>
+          <t>Pagos con criptomoneda</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Pagos dentro de la plataforma mediante la pasarela Flow (según resumen de entrevista de Pauta, oct-2024; esperada para mejorar la experiencia).</t>
+          <t>Pago de consultas con token.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
+          <t>Pagos con criptomoneda</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
+          <t>Piloto en New Malden (Londres): consultas por video pagables con tarjeta o con MedTokens.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8731,7 +8731,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8741,42 +8741,123 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
+          <t>Pagos dentro de la app</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Reclamo de seguro médico (indemnización) desde la app, con verificación de autenticidad de los registros vía blockchain por la aseguradora.</t>
+          <t>Pagos dentro de la plataforma mediante la pasarela Flow (según resumen de entrevista de Pauta, oct-2024; esperada para mejorar la experiencia).</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Reclamo de seguro médico (indemnización) desde la app, con verificación de autenticidad de los registros vía blockchain por la aseguradora.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Telemedicina y atención remota</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Mensajería paciente-institución</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Chat para consultas a hospitales, orientación simple de síntomas e información de tratamientos; comunicación bidireccional hospital-paciente (nov-2023).</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
           <t>Medicalchain</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Telemedicina y atención remota</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>Teleconsultas con GP.</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
@@ -8793,7 +8874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R65"/>
+  <dimension ref="A1:R67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8919,6 +9000,8 @@
           <t>Búsqueda de profesionales de salud</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8929,6 +9012,17 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2">
         <f>COUNTIF(C2:Q2,"✓")</f>
         <v/>
@@ -8950,11 +9044,24 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3">
         <f>COUNTIF(C3:Q3,"✓")</f>
         <v/>
@@ -8971,11 +9078,25 @@
           <t>Integración con calendario del dispositivo</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4">
         <f>COUNTIF(C4:Q4,"✓")</f>
         <v/>
@@ -8992,11 +9113,25 @@
           <t>Localización de centros médicos y farmacias</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5">
         <f>COUNTIF(C5:Q5,"✓")</f>
         <v/>
@@ -9013,6 +9148,21 @@
           <t>Reserva de citas médicas</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9023,6 +9173,8 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6">
         <f>COUNTIF(C6:Q6,"✓")</f>
         <v/>
@@ -9039,11 +9191,25 @@
           <t>Acceso del profesional al historial del paciente</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7">
         <f>COUNTIF(C7:Q7,"✓")</f>
         <v/>
@@ -9060,11 +9226,25 @@
           <t>Compartir con personas sin cuenta mediante clave segura</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8">
         <f>COUNTIF(C8:Q8,"✓")</f>
         <v/>
@@ -9081,11 +9261,25 @@
           <t>Compartir datos con cuidador o persona de confianza</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9">
         <f>COUNTIF(C9:Q9,"✓")</f>
         <v/>
@@ -9107,11 +9301,13 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9137,11 +9333,16 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10">
         <f>COUNTIF(C10:Q10,"✓")</f>
         <v/>
@@ -9158,11 +9359,25 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11">
         <f>COUNTIF(C11:Q11,"✓")</f>
         <v/>
@@ -9179,11 +9394,25 @@
           <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12">
         <f>COUNTIF(C12:Q12,"✓")</f>
         <v/>
@@ -9200,11 +9429,25 @@
           <t>Red social con profesionales y familiares</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13">
         <f>COUNTIF(C13:Q13,"✓")</f>
         <v/>
@@ -9231,11 +9474,23 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14">
         <f>COUNTIF(C14:Q14,"✓")</f>
         <v/>
@@ -9252,6 +9507,8 @@
           <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9262,21 +9519,29 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15">
         <f>COUNTIF(C15:Q15,"✓")</f>
         <v/>
@@ -9298,6 +9563,8 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9313,11 +9580,19 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16">
         <f>COUNTIF(C16:Q16,"✓")</f>
         <v/>
@@ -9334,16 +9609,29 @@
           <t>Almacenamiento de recetas</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17">
         <f>COUNTIF(C17:Q17,"✓")</f>
         <v/>
@@ -9360,11 +9648,25 @@
           <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18">
         <f>COUNTIF(C18:Q18,"✓")</f>
         <v/>
@@ -9381,11 +9683,25 @@
           <t>Emisión de certificados médicos</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19">
         <f>COUNTIF(C19:Q19,"✓")</f>
         <v/>
@@ -9407,6 +9723,19 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9428,11 +9757,25 @@
           <t>Notificación y envío de resultados</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21">
         <f>COUNTIF(C21:Q21,"✓")</f>
         <v/>
@@ -9449,16 +9792,29 @@
           <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22">
         <f>COUNTIF(C22:Q22,"✓")</f>
         <v/>
@@ -9475,26 +9831,36 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9516,11 +9882,25 @@
           <t>Línea de tiempo de salud</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24">
         <f>COUNTIF(C24:Q24,"✓")</f>
         <v/>
@@ -9537,11 +9917,25 @@
           <t>Registro de alergias y vacunas</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25">
         <f>COUNTIF(C25:Q25,"✓")</f>
         <v/>
@@ -9558,11 +9952,25 @@
           <t>Seguimiento de visitas, gastos y seguros</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26">
         <f>COUNTIF(C26:Q26,"✓")</f>
         <v/>
@@ -9579,6 +9987,11 @@
           <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9594,6 +10007,13 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27">
         <f>COUNTIF(C27:Q27,"✓")</f>
         <v/>
@@ -9610,11 +10030,25 @@
           <t>Asistente de IA para profesionales de salud</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28">
         <f>COUNTIF(C28:Q28,"✓")</f>
         <v/>
@@ -9631,11 +10065,25 @@
           <t>Coaching de salud con IA</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29">
         <f>COUNTIF(C29:Q29,"✓")</f>
         <v/>
@@ -9652,6 +10100,15 @@
           <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9662,6 +10119,10 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30">
         <f>COUNTIF(C30:Q30,"✓")</f>
         <v/>
@@ -9678,6 +10139,15 @@
           <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9688,6 +10158,9 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9709,11 +10182,24 @@
           <t>Orientación médica con IA</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9735,6 +10221,15 @@
           <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9745,6 +10240,10 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33">
         <f>COUNTIF(C33:Q33,"✓")</f>
         <v/>
@@ -9761,6 +10260,15 @@
           <t>Resumen de historial con IA</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9771,6 +10279,10 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34">
         <f>COUNTIF(C34:Q34,"✓")</f>
         <v/>
@@ -9784,44 +10296,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
+          <t>API para apps de terceros</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35">
         <f>COUNTIF(C35:Q35,"✓")</f>
         <v/>
@@ -9835,14 +10331,52 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Analítica poblacional B2B</t>
-        </is>
-      </c>
+          <t>Agregación de registros de múltiples instituciones</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36">
         <f>COUNTIF(C36:Q36,"✓")</f>
         <v/>
@@ -9856,24 +10390,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
+          <t>Analítica poblacional B2B</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37">
         <f>COUNTIF(C37:Q37,"✓")</f>
         <v/>
@@ -9887,14 +10425,36 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38">
         <f>COUNTIF(C38:Q38,"✓")</f>
         <v/>
@@ -9908,14 +10468,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Importación y exportación de datos</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39">
         <f>COUNTIF(C39:Q39,"✓")</f>
         <v/>
@@ -9929,14 +10503,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Integración con EHR de proveedores</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+          <t>Importación y exportación de datos</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40">
         <f>COUNTIF(C40:Q40,"✓")</f>
         <v/>
@@ -9950,19 +10538,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
+          <t>Integración con EHR de proveedores</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41">
         <f>COUNTIF(C41:Q41,"✓")</f>
         <v/>
@@ -9971,19 +10568,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gestión de lista de medicamentos</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42">
         <f>COUNTIF(C42:Q42,"✓")</f>
         <v/>
@@ -9997,14 +10612,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Importación automática de tratamientos desde receta digital</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
+          <t>Gestión de lista de medicamentos</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43">
         <f>COUNTIF(C43:Q43,"✓")</f>
         <v/>
@@ -10018,19 +10647,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+          <t>Importación automática de tratamientos desde receta digital</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44">
         <f>COUNTIF(C44:Q44,"✓")</f>
         <v/>
@@ -10044,14 +10682,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Registro de tomas y adherencia al tratamiento</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
+          <t>Recordatorios de medicación y citas</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45">
         <f>COUNTIF(C45:Q45,"✓")</f>
         <v/>
@@ -10060,19 +10716,33 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Comunidad de pacientes</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
+          <t>Registro de tomas y adherencia al tratamiento</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46">
         <f>COUNTIF(C46:Q46,"✓")</f>
         <v/>
@@ -10086,14 +10756,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Contenido educativo sobre salud</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+          <t>Comunidad de pacientes</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47">
         <f>COUNTIF(C47:Q47,"✓")</f>
         <v/>
@@ -10107,14 +10791,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
+          <t>Contenido educativo sobre salud</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48">
         <f>COUNTIF(C48:Q48,"✓")</f>
         <v/>
@@ -10128,14 +10826,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
+          <t>Gráficas de evolución de indicadores</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49">
         <f>COUNTIF(C49:Q49,"✓")</f>
         <v/>
@@ -10149,19 +10861,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Panel de seguimiento de salud y bienestar</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50">
         <f>COUNTIF(C50:Q50,"✓")</f>
         <v/>
@@ -10175,14 +10896,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Registro de nutrición</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
+          <t>Panel de seguimiento de salud y bienestar</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
       <c r="R51">
         <f>COUNTIF(C51:Q51,"✓")</f>
         <v/>
@@ -10196,14 +10935,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Seguimiento de salud femenina</t>
-        </is>
-      </c>
+          <t>Registro de nutrición</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52">
         <f>COUNTIF(C52:Q52,"✓")</f>
         <v/>
@@ -10217,14 +10970,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Valoración de profesionales</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
+          <t>Seguimiento de salud femenina</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53">
         <f>COUNTIF(C53:Q53,"✓")</f>
         <v/>
@@ -10233,19 +11000,33 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Acceso mínimo por categorías de datos</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
+          <t>Valoración de profesionales</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54">
         <f>COUNTIF(C54:Q54,"✓")</f>
         <v/>
@@ -10259,24 +11040,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
+          <t>Acceso mínimo por categorías de datos</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55">
         <f>COUNTIF(C55:Q55,"✓")</f>
         <v/>
@@ -10290,19 +11075,36 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56">
         <f>COUNTIF(C56:Q56,"✓")</f>
         <v/>
@@ -10316,14 +11118,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cumplimiento regulatorio de salud y datos</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
+          <t>Cifrado y control de acceso</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57">
         <f>COUNTIF(C57:Q57,"✓")</f>
         <v/>
@@ -10337,14 +11157,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gestión de consentimiento sobre uso de datos</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
+          <t>Cumplimiento regulatorio de salud y datos</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58">
         <f>COUNTIF(C58:Q58,"✓")</f>
         <v/>
@@ -10358,14 +11192,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Identidad descentralizada (DID)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
+          <t>Gestión de consentimiento sobre uso de datos</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
       <c r="R59">
         <f>COUNTIF(C59:Q59,"✓")</f>
         <v/>
@@ -10379,19 +11227,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
+          <t>Identidad descentralizada (DID)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60">
         <f>COUNTIF(C60:Q60,"✓")</f>
         <v/>
@@ -10400,19 +11257,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Modelo freemium y suscripción</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
+          <t>Privacidad reforzada para datos de salud</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61">
         <f>COUNTIF(C61:Q61,"✓")</f>
         <v/>
@@ -10426,10 +11301,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pagos con criptomoneda</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+          <t>Modelo freemium y suscripción</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -10447,14 +11336,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pagos dentro de la app</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
+          <t>Pagos con criptomoneda</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63">
         <f>COUNTIF(C63:Q63,"✓")</f>
         <v/>
@@ -10468,10 +11371,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
+          <t>Pagos dentro de la app</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -10484,21 +11401,105 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Telemedicina y atención remota</t>
+          <t>Seguros y pagos</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Teleconsulta con profesionales</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
       <c r="R65">
         <f>COUNTIF(C65:Q65,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Telemedicina y atención remota</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Mensajería paciente-institución</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66">
+        <f>COUNTIF(C66:Q66,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Telemedicina y atención remota</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Teleconsulta con profesionales</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67">
+        <f>COUNTIF(C67:Q67,"✓")</f>
         <v/>
       </c>
     </row>
@@ -10513,7 +11514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -10715,6 +11716,13 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>VUELTA 6 COMPLETA (2026-10-16 12:22 UTC): Clinia, MiRedSalud y Mediko verificados (+0 filas). Contador de loops = 6 para todos, Revisado reiniciado a "No". func_norm (130 filas) y tabla_frecuencia (66 funcionalidades) regenerados. Vuelta 7 parte con Meedika, Infomed, MediPlanner, Clingot. Candidato a competidor sin agregar: HealthChain (Chile).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -513,12 +513,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar. [Vuelta 3] Sin novedades 2026 ni confirmación de la app Android en Google Play; usuarios actuales desconocidos. Nota de prensa no indica año de lanzamiento explícito. [Vuelta 4] Sin fuentes nuevas; portalinnova.cl no aparece en búsquedas. Sigue dependiendo de una sola nota de prensa. [Vuelta 5] Sin fuentes nuevas (ni entrevistas ni financiamiento); sigue dependiendo de una sola nota de prensa sin año explícito. [Vuelta 6] Sin ficha de Google Play ni fuentes nuevas; disponibilidad en Android sin confirmar.</t>
+          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar. [Vuelta 3] Sin novedades 2026 ni confirmación de la app Android en Google Play; usuarios actuales desconocidos. Nota de prensa no indica año de lanzamiento explícito. [Vuelta 4] Sin fuentes nuevas; portalinnova.cl no aparece en búsquedas. Sigue dependiendo de una sola nota de prensa. [Vuelta 5] Sin fuentes nuevas (ni entrevistas ni financiamiento); sigue dependiendo de una sola nota de prensa sin año explícito. [Vuelta 6] Sin ficha de Google Play ni fuentes nuevas; disponibilidad en Android sin confirmar. [Vuelta 7] Sin fuentes nuevas; no hay ficha oficial localizada. No confundir con apps de nombre parecido (Medika App, MEDDI, AI Medik).</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -526,7 +526,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -553,12 +553,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapa A] Fundada 2019 por Diego Ibarra, Andrés Fantuzzi y Gabriel Zamora. Lanzada mar-2021 en App Store y Play Store con 1.200 usuarios; planeaba nueva versión jul-2021 y ronda de US$500 mil. Objetivo: llevar el historial en el celular, acceso en emergencias, médico puede ingresar datos con consentimiento. Estado actual NO verificado (posible app inactiva). URL es la nota de prensa; sitio oficial por confirmar. [Vuelta 3] Sin evidencia posterior a 2021; relanzamiento previsto jul-2021 no confirmado. Probable app inactiva. [Vuelta 4] Sin cambios; sigue sin evidencia posterior a 2021. [Vuelta 5] Cofundador Andrés Fantuzzi es cardiólogo de la Clínica Santa María. Sin ronda de inversión ni relanzamiento confirmados; no confundir con Infomed de Cuba (portal del Minsap). [Vuelta 6] Sin búsqueda nueva (fuentes agotadas en vueltas 3-5); sin cambios.</t>
+          <t>[DIRECTO · Chile · etapa A] Fundada 2019 por Diego Ibarra, Andrés Fantuzzi y Gabriel Zamora. Lanzada mar-2021 en App Store y Play Store con 1.200 usuarios; planeaba nueva versión jul-2021 y ronda de US$500 mil. Objetivo: llevar el historial en el celular, acceso en emergencias, médico puede ingresar datos con consentimiento. Estado actual NO verificado (posible app inactiva). URL es la nota de prensa; sitio oficial por confirmar. [Vuelta 3] Sin evidencia posterior a 2021; relanzamiento previsto jul-2021 no confirmado. Probable app inactiva. [Vuelta 4] Sin cambios; sigue sin evidencia posterior a 2021. [Vuelta 5] Cofundador Andrés Fantuzzi es cardiólogo de la Clínica Santa María. Sin ronda de inversión ni relanzamiento confirmados; no confundir con Infomed de Cuba (portal del Minsap). [Vuelta 6] Sin búsqueda nueva (fuentes agotadas en vueltas 3-5); sin cambios. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -593,12 +593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · México] Historial por perfil familiar, alergias, vacunas, recetas digitales, gráficas de evolución, agendamiento, compartir con profesionales. Gratis en App Store MX. Sin evidencia de uso en Chile. Cubre parte de la etapa C (familia). [Vuelta 3] Existen dos apps distintas: MediPlanner (gratis, Rym Solutions, MX, 3,7/5 con 3 calificaciones) y MediPlanner Pro (otro desarrollador, $39 MXN). Sin presencia verificada en Chile. [Vuelta 4] No pude confirmar el desarrollador de la versión gratuita (Rym Solutions no se repite en esta búsqueda). MediPlanner Pro (fichas BR/OM) guardaría datos solo en el dispositivo, sin nube; no confundir con MedPlanner/AskHEMI (otra empresa). [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Se reconfirma en la ficha de App Store MX que el desarrollador de la versión gratuita es Rym Solutions S. de R.L. de C.V. (3,7/5, 3 calificaciones); MediPlanner Pro no menciona a esa empresa, por lo que no se puede asegurar que sea el mismo desarrollador.</t>
+          <t>[REGIONAL · México] Historial por perfil familiar, alergias, vacunas, recetas digitales, gráficas de evolución, agendamiento, compartir con profesionales. Gratis en App Store MX. Sin evidencia de uso en Chile. Cubre parte de la etapa C (familia). [Vuelta 3] Existen dos apps distintas: MediPlanner (gratis, Rym Solutions, MX, 3,7/5 con 3 calificaciones) y MediPlanner Pro (otro desarrollador, $39 MXN). Sin presencia verificada en Chile. [Vuelta 4] No pude confirmar el desarrollador de la versión gratuita (Rym Solutions no se repite en esta búsqueda). MediPlanner Pro (fichas BR/OM) guardaría datos solo en el dispositivo, sin nube; no confundir con MedPlanner/AskHEMI (otra empresa). [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Se reconfirma en la ficha de App Store MX que el desarrollador de la versión gratuita es Rym Solutions S. de R.L. de C.V. (3,7/5, 3 calificaciones); MediPlanner Pro no menciona a esa empresa, por lo que no se puede asegurar que sea el mismo desarrollador. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -606,7 +606,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · Argentina · débil] App para cargar antecedentes médicos propios. Única referencia: nota de opinión en grupoanimal.mx sin fecha verificada. Estado y sitio por confirmar. [Vuelta 3] Referencias de 2017 (apps4citizens, La Nación); sitio y precio no verificados; puede estar inactiva. [Vuelta 4] Sin fuentes nuevas. [Vuelta 5] Registro empresarial (indicadores.ar, datos a jul-2026) muestra CLINGOT S.A. activa en CABA, constituida el 4-abr-2016; no confirma que la app siga operando. Programa federal argentino de historias clínicas digitales como contexto regulatorio. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios.</t>
+          <t>[REGIONAL · Argentina · débil] App para cargar antecedentes médicos propios. Única referencia: nota de opinión en grupoanimal.mx sin fecha verificada. Estado y sitio por confirmar. [Vuelta 3] Referencias de 2017 (apps4citizens, La Nación); sitio y precio no verificados; puede estar inactiva. [Vuelta 4] Sin fuentes nuevas. [Vuelta 5] Registro empresarial (indicadores.ar, datos a jul-2026) muestra CLINGOT S.A. activa en CABA, constituida el 4-abr-2016; no confirma que la app siga operando. Programa federal argentino de historias clínicas digitales como contexto regulatorio. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios. [Vuelta 7] Solo fuentes de 2017; sin evidencia nueva de operación más allá del registro societario.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -9000,8 +9000,6 @@
           <t>Búsqueda de profesionales de salud</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9012,17 +9010,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2">
         <f>COUNTIF(C2:Q2,"✓")</f>
         <v/>
@@ -9044,24 +9031,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3">
         <f>COUNTIF(C3:Q3,"✓")</f>
         <v/>
@@ -9078,25 +9052,11 @@
           <t>Integración con calendario del dispositivo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4">
         <f>COUNTIF(C4:Q4,"✓")</f>
         <v/>
@@ -9113,25 +9073,11 @@
           <t>Localización de centros médicos y farmacias</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5">
         <f>COUNTIF(C5:Q5,"✓")</f>
         <v/>
@@ -9148,21 +9094,11 @@
           <t>Reserva de citas médicas</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9173,8 +9109,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6">
         <f>COUNTIF(C6:Q6,"✓")</f>
         <v/>
@@ -9191,25 +9125,11 @@
           <t>Acceso del profesional al historial del paciente</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7">
         <f>COUNTIF(C7:Q7,"✓")</f>
         <v/>
@@ -9226,25 +9146,11 @@
           <t>Compartir con personas sin cuenta mediante clave segura</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8">
         <f>COUNTIF(C8:Q8,"✓")</f>
         <v/>
@@ -9261,25 +9167,11 @@
           <t>Compartir datos con cuidador o persona de confianza</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9">
         <f>COUNTIF(C9:Q9,"✓")</f>
         <v/>
@@ -9301,13 +9193,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9333,16 +9223,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10">
         <f>COUNTIF(C10:Q10,"✓")</f>
         <v/>
@@ -9359,25 +9244,11 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11">
         <f>COUNTIF(C11:Q11,"✓")</f>
         <v/>
@@ -9394,25 +9265,11 @@
           <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12">
         <f>COUNTIF(C12:Q12,"✓")</f>
         <v/>
@@ -9429,25 +9286,11 @@
           <t>Red social con profesionales y familiares</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13">
         <f>COUNTIF(C13:Q13,"✓")</f>
         <v/>
@@ -9474,23 +9317,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14">
         <f>COUNTIF(C14:Q14,"✓")</f>
         <v/>
@@ -9507,8 +9338,6 @@
           <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9519,29 +9348,21 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15">
         <f>COUNTIF(C15:Q15,"✓")</f>
         <v/>
@@ -9563,8 +9384,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9580,19 +9399,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16">
         <f>COUNTIF(C16:Q16,"✓")</f>
         <v/>
@@ -9609,29 +9420,16 @@
           <t>Almacenamiento de recetas</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17">
         <f>COUNTIF(C17:Q17,"✓")</f>
         <v/>
@@ -9648,25 +9446,11 @@
           <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18">
         <f>COUNTIF(C18:Q18,"✓")</f>
         <v/>
@@ -9683,25 +9467,11 @@
           <t>Emisión de certificados médicos</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19">
         <f>COUNTIF(C19:Q19,"✓")</f>
         <v/>
@@ -9723,19 +9493,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9757,25 +9514,11 @@
           <t>Notificación y envío de resultados</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21">
         <f>COUNTIF(C21:Q21,"✓")</f>
         <v/>
@@ -9792,29 +9535,16 @@
           <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22">
         <f>COUNTIF(C22:Q22,"✓")</f>
         <v/>
@@ -9831,36 +9561,26 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9882,25 +9602,11 @@
           <t>Línea de tiempo de salud</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24">
         <f>COUNTIF(C24:Q24,"✓")</f>
         <v/>
@@ -9917,25 +9623,11 @@
           <t>Registro de alergias y vacunas</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25">
         <f>COUNTIF(C25:Q25,"✓")</f>
         <v/>
@@ -9952,25 +9644,11 @@
           <t>Seguimiento de visitas, gastos y seguros</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26">
         <f>COUNTIF(C26:Q26,"✓")</f>
         <v/>
@@ -9987,11 +9665,6 @@
           <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10007,13 +9680,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27">
         <f>COUNTIF(C27:Q27,"✓")</f>
         <v/>
@@ -10030,25 +9696,11 @@
           <t>Asistente de IA para profesionales de salud</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28">
         <f>COUNTIF(C28:Q28,"✓")</f>
         <v/>
@@ -10065,25 +9717,11 @@
           <t>Coaching de salud con IA</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29">
         <f>COUNTIF(C29:Q29,"✓")</f>
         <v/>
@@ -10100,15 +9738,6 @@
           <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10119,10 +9748,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30">
         <f>COUNTIF(C30:Q30,"✓")</f>
         <v/>
@@ -10139,15 +9764,6 @@
           <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10158,9 +9774,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10182,24 +9795,11 @@
           <t>Orientación médica con IA</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10221,15 +9821,6 @@
           <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10240,10 +9831,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33">
         <f>COUNTIF(C33:Q33,"✓")</f>
         <v/>
@@ -10260,15 +9847,6 @@
           <t>Resumen de historial con IA</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10279,10 +9857,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34">
         <f>COUNTIF(C34:Q34,"✓")</f>
         <v/>
@@ -10299,25 +9873,11 @@
           <t>API para apps de terceros</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35">
         <f>COUNTIF(C35:Q35,"✓")</f>
         <v/>
@@ -10339,10 +9899,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10353,7 +9909,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10369,14 +9924,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36">
         <f>COUNTIF(C36:Q36,"✓")</f>
         <v/>
@@ -10393,25 +9945,11 @@
           <t>Analítica poblacional B2B</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37">
         <f>COUNTIF(C37:Q37,"✓")</f>
         <v/>
@@ -10428,9 +9966,6 @@
           <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10441,20 +9976,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38">
         <f>COUNTIF(C38:Q38,"✓")</f>
         <v/>
@@ -10471,25 +9997,11 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39">
         <f>COUNTIF(C39:Q39,"✓")</f>
         <v/>
@@ -10506,25 +10018,11 @@
           <t>Importación y exportación de datos</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40">
         <f>COUNTIF(C40:Q40,"✓")</f>
         <v/>
@@ -10541,25 +10039,11 @@
           <t>Integración con EHR de proveedores</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41">
         <f>COUNTIF(C41:Q41,"✓")</f>
         <v/>
@@ -10576,29 +10060,16 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42">
         <f>COUNTIF(C42:Q42,"✓")</f>
         <v/>
@@ -10615,25 +10086,11 @@
           <t>Gestión de lista de medicamentos</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43">
         <f>COUNTIF(C43:Q43,"✓")</f>
         <v/>
@@ -10650,25 +10107,11 @@
           <t>Importación automática de tratamientos desde receta digital</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44">
         <f>COUNTIF(C44:Q44,"✓")</f>
         <v/>
@@ -10690,24 +10133,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45">
         <f>COUNTIF(C45:Q45,"✓")</f>
         <v/>
@@ -10724,25 +10154,11 @@
           <t>Registro de tomas y adherencia al tratamiento</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46">
         <f>COUNTIF(C46:Q46,"✓")</f>
         <v/>
@@ -10759,25 +10175,11 @@
           <t>Comunidad de pacientes</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47">
         <f>COUNTIF(C47:Q47,"✓")</f>
         <v/>
@@ -10794,25 +10196,11 @@
           <t>Contenido educativo sobre salud</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48">
         <f>COUNTIF(C48:Q48,"✓")</f>
         <v/>
@@ -10829,25 +10217,11 @@
           <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49">
         <f>COUNTIF(C49:Q49,"✓")</f>
         <v/>
@@ -10864,25 +10238,11 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50">
         <f>COUNTIF(C50:Q50,"✓")</f>
         <v/>
@@ -10899,11 +10259,6 @@
           <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10914,14 +10269,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51">
         <f>COUNTIF(C51:Q51,"✓")</f>
         <v/>
@@ -10938,25 +10285,11 @@
           <t>Registro de nutrición</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52">
         <f>COUNTIF(C52:Q52,"✓")</f>
         <v/>
@@ -10973,25 +10306,11 @@
           <t>Seguimiento de salud femenina</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
       <c r="R53">
         <f>COUNTIF(C53:Q53,"✓")</f>
         <v/>
@@ -11008,25 +10327,11 @@
           <t>Valoración de profesionales</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54">
         <f>COUNTIF(C54:Q54,"✓")</f>
         <v/>
@@ -11043,25 +10348,11 @@
           <t>Acceso mínimo por categorías de datos</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55">
         <f>COUNTIF(C55:Q55,"✓")</f>
         <v/>
@@ -11078,11 +10369,6 @@
           <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11098,13 +10384,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56">
         <f>COUNTIF(C56:Q56,"✓")</f>
         <v/>
@@ -11121,29 +10400,16 @@
           <t>Cifrado y control de acceso</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57">
         <f>COUNTIF(C57:Q57,"✓")</f>
         <v/>
@@ -11160,25 +10426,11 @@
           <t>Cumplimiento regulatorio de salud y datos</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
       <c r="R58">
         <f>COUNTIF(C58:Q58,"✓")</f>
         <v/>
@@ -11195,25 +10447,11 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
       <c r="R59">
         <f>COUNTIF(C59:Q59,"✓")</f>
         <v/>
@@ -11230,25 +10468,11 @@
           <t>Identidad descentralizada (DID)</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
       <c r="R60">
         <f>COUNTIF(C60:Q60,"✓")</f>
         <v/>
@@ -11265,15 +10489,6 @@
           <t>Privacidad reforzada para datos de salud</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11284,10 +10499,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
       <c r="R61">
         <f>COUNTIF(C61:Q61,"✓")</f>
         <v/>
@@ -11304,20 +10515,6 @@
           <t>Modelo freemium y suscripción</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11339,25 +10536,11 @@
           <t>Pagos con criptomoneda</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
       <c r="R63">
         <f>COUNTIF(C63:Q63,"✓")</f>
         <v/>
@@ -11374,20 +10557,6 @@
           <t>Pagos dentro de la app</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11409,25 +10578,11 @@
           <t>Reclamos y trámites con seguros</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
       <c r="R65">
         <f>COUNTIF(C65:Q65,"✓")</f>
         <v/>
@@ -11444,25 +10599,11 @@
           <t>Mensajería paciente-institución</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
       <c r="R66">
         <f>COUNTIF(C66:Q66,"✓")</f>
         <v/>
@@ -11479,25 +10620,11 @@
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
       <c r="R67">
         <f>COUNTIF(C67:Q67,"✓")</f>
         <v/>
@@ -11514,7 +10641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -11723,6 +10850,13 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Vuelta 7 (iter. 1, 2026-10-17 12:15 UTC): Meedika, Infomed, MediPlanner, Clingot verificados (+0 filas; saturado). Pendientes: Healfies, Patientory, MediBloc, Medicalchain, Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas, Clinia, MiRedSalud, Mediko.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B. [Vuelta 2] Lanzada simultáneamente en Brasil, Argentina y EE.UU.; permite compartir con no registrados vía clave por email. Sin novedades posteriores a 2016. [Vuelta 3] Sin evidencia de actividad reciente ni de cierre; Gust/Dealroom la listan en Florianópolis (10 empleados, healfies.com) sin fecha de actualización. Estado sin confirmar. [Vuelta 4] Sin Google Play localizado; no confundir con la app Healfy (otro producto). Sin novedades. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios.</t>
+          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B. [Vuelta 2] Lanzada simultáneamente en Brasil, Argentina y EE.UU.; permite compartir con no registrados vía clave por email. Sin novedades posteriores a 2016. [Vuelta 3] Sin evidencia de actividad reciente ni de cierre; Gust/Dealroom la listan en Florianópolis (10 empleados, healfies.com) sin fecha de actualización. Estado sin confirmar. [Vuelta 4] Sin Google Play localizado; no confundir con la app Healfy (otro producto). Sin novedades. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios. [Vuelta 7] Solo fuentes de 2015-2016; alianza con ClinCard (feb-2016). Sin evidencia de actividad reciente.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain. [Vuelta 2] Sin noticias 2026 encontradas en búsqueda; sitio oficial bloqueado. [Vuelta 3] Búsqueda adicional solo devuelve hitos de 2017 (token sale US$7,2M) y 2019 (Serie A de US$5,3M, cierre no confirmado); sin datos 2025-26 propios. [Vuelta 4] App pública lanzada en la conferencia JP Morgan Healthcare (2019); red PTOYMatrix (blockchain HIPAA); socios reportados: StartUp Health y Kaiser Permanente (beta). Estado actual en App Store/Google Play sin confirmar. [Vuelta 5] Sin noticias 2026 del equipo. Token PTOY con capitalización de ~US$53K a fines de ago-2026 según Phantom (KuCoin discrepa en la circulación): señal de baja actividad, no prueba de cierre. Esto relativiza la actividad hasta abr-2026 mencionada en la ficha original. [Vuelta 6] Sin noticias posteriores a 2020 localizadas (hitos: token sale 2017, consorcio Hyperledger, alianza con Georgia State, Series A de US$5,3M vía R/GA Ventures, Neith con Prosper Healthtech en Birmingham). Estado actual desconocido.</t>
+          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain. [Vuelta 2] Sin noticias 2026 encontradas en búsqueda; sitio oficial bloqueado. [Vuelta 3] Búsqueda adicional solo devuelve hitos de 2017 (token sale US$7,2M) y 2019 (Serie A de US$5,3M, cierre no confirmado); sin datos 2025-26 propios. [Vuelta 4] App pública lanzada en la conferencia JP Morgan Healthcare (2019); red PTOYMatrix (blockchain HIPAA); socios reportados: StartUp Health y Kaiser Permanente (beta). Estado actual en App Store/Google Play sin confirmar. [Vuelta 5] Sin noticias 2026 del equipo. Token PTOY con capitalización de ~US$53K a fines de ago-2026 según Phantom (KuCoin discrepa en la circulación): señal de baja actividad, no prueba de cierre. Esto relativiza la actividad hasta abr-2026 mencionada en la ficha original. [Vuelta 6] Sin noticias posteriores a 2020 localizadas (hitos: token sale 2017, consorcio Hyperledger, alianza con Georgia State, Series A de US$5,3M vía R/GA Ventures, Neith con Prosper Healthtech en Birmingham). Estado actual desconocido. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain. [Vuelta 2] Panacea incluye DID, Append Only Log, IBC y PNFT; sin anuncios 2026 localizados. [Vuelta 3] Medipass: app en Corea con 20 hospitales/aseguradoras integrados (fecha de la lista desconocida) y plan 2022 de superapp con marketplace de datos; operación actual sin confirmar. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Medipass: ~400.000 usuarios acumulados (CEO, jun-2022); integración con aseguradoras Shinhan Life, Samsung Fire y Hyundai Marine (2020); renovación completa en mar-2023 (dashboard de salud, gestión familiar, certificados). Sin noticias 2026 encontradas. [Vuelta 6] Medipass 2023: comunicación bidireccional hospital-paciente y chat MediTalk; en 2019 fue seleccionada para el programa gubernamental de MyData médico con Samsung Fire y SNUH. Sin estrategia 2026 localizada. Meta declarada: usar Medipass como «identificación» de salud.</t>
+          <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain. [Vuelta 2] Panacea incluye DID, Append Only Log, IBC y PNFT; sin anuncios 2026 localizados. [Vuelta 3] Medipass: app en Corea con 20 hospitales/aseguradoras integrados (fecha de la lista desconocida) y plan 2022 de superapp con marketplace de datos; operación actual sin confirmar. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Medipass: ~400.000 usuarios acumulados (CEO, jun-2022); integración con aseguradoras Shinhan Life, Samsung Fire y Hyundai Marine (2020); renovación completa en mar-2023 (dashboard de salud, gestión familiar, certificados). Sin noticias 2026 encontradas. [Vuelta 6] Medipass 2023: comunicación bidireccional hospital-paciente y chat MediTalk; en 2019 fue seleccionada para el programa gubernamental de MyData médico con Samsung Fire y SNUH. Sin estrategia 2026 localizada. Meta declarada: usar Medipass como «identificación» de salud. [Vuelta 7] Una fuente sin fecha atribuye a Medipass más de 600.000 pacientes en 14 hospitales; MoU 2019 con Severance (plataforma de facturación de seguros y detección de falsificación de datos) y piloto con Massachusetts General Hospital. Sin datos 2025-26.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · Reino Unido · INACTIVO] Londres, 2017, Ethereum, con telemedicina. Piloto según registro de la UE (2020). Tracxn/PitchBook lo marcan fuera de operación (ago-2025). Solo caso de aprendizaje: no cuenta como competidor activo. [Vuelta 2] Token MTN deslistado de Bitfinex el 26-mar-2021; sin hallazgos de actividad posterior. [Vuelta 3] Seedtable la marca activa sin fuente; no hallé registro en Companies House. Sigue tratándose como caso de aprendizaje. [Vuelta 4] Pre-venta reportada de US$20M en MedTokens (un solo artículo secundario, sin verificar); modelo de token en revisión y exploración de security token según AMA; integraciones y servicios de 2019 sin confirmar. [Vuelta 5] Un agregador indica sitio medicalchain.com fuera de línea desde 15-feb-2025, último commit en GitHub hace ~3 años y proyecto en «fase de mantenimiento»; preventa de MedTokens reportada entre US$20M y US$24M (fuentes discrepan). Confirma tratarlo como inactivo. [Vuelta 6] Sin búsqueda nueva (revisada en vuelta 5; sitio fuera de línea desde feb-2025 según un agregador); sin cambios.</t>
+          <t>[BLOCKCHAIN · Reino Unido · INACTIVO] Londres, 2017, Ethereum, con telemedicina. Piloto según registro de la UE (2020). Tracxn/PitchBook lo marcan fuera de operación (ago-2025). Solo caso de aprendizaje: no cuenta como competidor activo. [Vuelta 2] Token MTN deslistado de Bitfinex el 26-mar-2021; sin hallazgos de actividad posterior. [Vuelta 3] Seedtable la marca activa sin fuente; no hallé registro en Companies House. Sigue tratándose como caso de aprendizaje. [Vuelta 4] Pre-venta reportada de US$20M en MedTokens (un solo artículo secundario, sin verificar); modelo de token en revisión y exploración de security token según AMA; integraciones y servicios de 2019 sin confirmar. [Vuelta 5] Un agregador indica sitio medicalchain.com fuera de línea desde 15-feb-2025, último commit en GitHub hace ~3 años y proyecto en «fase de mantenimiento»; preventa de MedTokens reportada entre US$20M y US$24M (fuentes discrepan). Confirma tratarlo como inactivo. [Vuelta 6] Sin búsqueda nueva (revisada en vuelta 5; sitio fuera de línea desde feb-2025 según un agregador); sin cambios. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5302,6 +5302,38 @@
       <c r="F131" t="inlineStr">
         <is>
           <t>Búsqueda web (Apple, TechCrunch, Pharmaphorum); registros solo EE.UU./UK/Canadá</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Healfies</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Gestión documental</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Entrega de documentos por terceros (ClinCard)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Desde feb-2016, la administradora de tarjetas ClinCard entregaba contratos y documentos a sus clientes dentro de la plataforma.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Latam</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Baguete, 2016); estado actual no verificado</t>
         </is>
       </c>
     </row>
@@ -10641,7 +10673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -10857,6 +10889,13 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Vuelta 7 (iter. 2, 2026-10-18 12:15 UTC): Healfies, Patientory, MediBloc, Medicalchain verificados (+1 fila, de Healfies). Pendientes: Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas, Clinia, MiRedSalud, Mediko.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -833,12 +833,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Agrega registros clínicos vía FHIR; &gt;500 instituciones conectadas en EE.UU. (2018). Sin evidencia de disponibilidad en Chile. Incluida en el dispositivo. Amenaza si FHIR/IPS-CL se adopta en Chile. [Vuelta 2] Sin disponibilidad de registros clínicos en Chile (solo EE.UU., Reino Unido, Canadá). [Vuelta 3] iOS 27 (WWDC 8-jun-2026; publicado ~14-sep-2026): rediseño del app Health, menopausia, nutrición por cámara. El coach de salud con IA no se anunció. Sin ampliación de Health Records a Chile. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Sin ampliación de Health Records a Australia, Europa ni Latinoamérica (solo EE.UU., UK, Canadá). Funciones de dispositivo (apnea del sueño, prueba auditiva) sí se amplían a países latinoamericanos, pero no son registros clínicos. [Vuelta 6] Sin novedades de iOS 27.x localizadas. Health Records API permite compartir registros con apps de terceros con control por app; opción de enviar datos de uso a Apple.</t>
+          <t>[ADYACENTE · global] Agrega registros clínicos vía FHIR; &gt;500 instituciones conectadas en EE.UU. (2018). Sin evidencia de disponibilidad en Chile. Incluida en el dispositivo. Amenaza si FHIR/IPS-CL se adopta en Chile. [Vuelta 2] Sin disponibilidad de registros clínicos en Chile (solo EE.UU., Reino Unido, Canadá). [Vuelta 3] iOS 27 (WWDC 8-jun-2026; publicado ~14-sep-2026): rediseño del app Health, menopausia, nutrición por cámara. El coach de salud con IA no se anunció. Sin ampliación de Health Records a Chile. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Sin ampliación de Health Records a Australia, Europa ni Latinoamérica (solo EE.UU., UK, Canadá). Funciones de dispositivo (apnea del sueño, prueba auditiva) sí se amplían a países latinoamericanos, pero no son registros clínicos. [Vuelta 6] Sin novedades de iOS 27.x localizadas. Health Records API permite compartir registros con apps de terceros con control por app; opción de enviar datos de uso a Apple. [Vuelta 7] Coach de salud con IA / Health+ de pago: solo rumores (Gurman), atrasado al menos a iOS 27; no confirmado ni anunciado.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Lanzado 7-ene-2026. Conecta registros médicos; conectores solo en EE.UU. Dentro de suscripción del asistente. Fija la expectativa de consultar y resumir el historial. [Vuelta 2] Confirmado: registros solo EE.UU.; sin anuncios para Latinoamérica. Hay inconsistencia de fechas entre fuentes (7-ene-2026 lanzamiento vs. jul-2026 despliegue de registros). [Vuelta 3] Fechas aclaradas: presentación 7-ene-2026 (acceso limitado); despliegue de Health in ChatGPT con Apple Health y registros en EE.UU. el 23-jul-2026; mejora de salud jun-2026. Sin anuncios para Latinoamérica ni para sep-oct 2026. [Vuelta 4] Septiembre 2026: permisos por defecto para datos conectados (14-sep) y explicaciones por gráfico/métrica (28-sep); ChatGPT for Clinicians (abr-2026) para clínicos verificados de EE.UU. Más del 70% de usuarios de Health permite usar datos conectados sin pedir permiso (según OpenAI). Sigue solo EE.UU. [Vuelta 5] Nota de jul-2026: Health no está disponible en México, Android, modo de voz ni Codex; web e iOS en EE.UU., adultos con sesión iniciada. Sin anuncio para Chile ni Latinoamérica. [Vuelta 6] Última entrada de Health en las notas de OpenAI sigue siendo la del 23-jul-2026 (más cambios de sep); sin entradas de octubre localizadas. Health tab: laboratorios, medicamentos, actividad y sueño en una vista; solo EE.UU., web e iOS.</t>
+          <t>[ADYACENTE · global] Lanzado 7-ene-2026. Conecta registros médicos; conectores solo en EE.UU. Dentro de suscripción del asistente. Fija la expectativa de consultar y resumir el historial. [Vuelta 2] Confirmado: registros solo EE.UU.; sin anuncios para Latinoamérica. Hay inconsistencia de fechas entre fuentes (7-ene-2026 lanzamiento vs. jul-2026 despliegue de registros). [Vuelta 3] Fechas aclaradas: presentación 7-ene-2026 (acceso limitado); despliegue de Health in ChatGPT con Apple Health y registros en EE.UU. el 23-jul-2026; mejora de salud jun-2026. Sin anuncios para Latinoamérica ni para sep-oct 2026. [Vuelta 4] Septiembre 2026: permisos por defecto para datos conectados (14-sep) y explicaciones por gráfico/métrica (28-sep); ChatGPT for Clinicians (abr-2026) para clínicos verificados de EE.UU. Más del 70% de usuarios de Health permite usar datos conectados sin pedir permiso (según OpenAI). Sigue solo EE.UU. [Vuelta 5] Nota de jul-2026: Health no está disponible en México, Android, modo de voz ni Codex; web e iOS en EE.UU., adultos con sesión iniciada. Sin anuncio para Chile ni Latinoamérica. [Vuelta 6] Última entrada de Health en las notas de OpenAI sigue siendo la del 23-jul-2026 (más cambios de sep); sin entradas de octubre localizadas. Health tab: laboratorios, medicamentos, actividad y sueño en una vista; solo EE.UU., web e iOS. [Vuelta 7] OpenAI afirma que más de 300 millones de personas usan ChatGPT cada semana para consultas de salud (dato de la empresa). No es una solución con cumplimiento HIPAA declarado. Sin novedades de oct-2026.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -886,7 +886,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Lanzado 11-ene-2026. Conectores solo en EE.UU., planes Pro/Max. Nota: producto de Anthropic, conflicto de interés al evaluarlo. [Vuelta 2] Sin cambios fuera de EE.UU. (HealthEx y Function para Pro/Max). [Vuelta 3] Sin anuncios posteriores a enero de 2026. Hoja de ruta de HealthEx (agendar, buscar prestadores, recetas) sin confirmar como lanzada. [Vuelta 4] Sin anuncios nuevos. Fuentes discrepan en el acceso (Pro/Max según Fortune y la mayoría; Pro/Team según Times of AI); sin evidencia de disponibilidad fuera de EE.UU. [Vuelta 5] Sin noticias de oct-2026; HealthEx agrega datos de &gt;50.000 sistemas de EE.UU. y Claude pide solo las categorías relevantes vía MCP. [Vuelta 6] Sin noticias posteriores a enero de 2026 localizadas.</t>
+          <t>[ADYACENTE · global] Lanzado 11-ene-2026. Conectores solo en EE.UU., planes Pro/Max. Nota: producto de Anthropic, conflicto de interés al evaluarlo. [Vuelta 2] Sin cambios fuera de EE.UU. (HealthEx y Function para Pro/Max). [Vuelta 3] Sin anuncios posteriores a enero de 2026. Hoja de ruta de HealthEx (agendar, buscar prestadores, recetas) sin confirmar como lanzada. [Vuelta 4] Sin anuncios nuevos. Fuentes discrepan en el acceso (Pro/Max según Fortune y la mayoría; Pro/Team según Times of AI); sin evidencia de disponibilidad fuera de EE.UU. [Vuelta 5] Sin noticias de oct-2026; HealthEx agrega datos de &gt;50.000 sistemas de EE.UU. y Claude pide solo las categorías relevantes vía MCP. [Vuelta 6] Sin noticias posteriores a enero de 2026 localizadas. [Vuelta 7] Sin novedades posteriores a enero de 2026.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -926,7 +926,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones. [Vuelta 2] App concreta: Mi Alemana Go (Clínica Alemana, Chile), con historial desde 2018, recetas, órdenes, familiar vinculado y resultados. [Vuelta 3] Búsqueda de otras clínicas (Las Condes, Santa María, UC Christus) sin ficha de app confirmada; solo canales digitales genéricos. [Vuelta 4] Mi Alemana Go: 3,1/5 con 137 calificaciones (App Store Chile), pantalla de inicio rediseñada para gestionar salud propia y familiar; sin evidencia de teleconsulta ni pagos en la app. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Sin búsqueda nueva; sin cambios.</t>
+          <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones. [Vuelta 2] App concreta: Mi Alemana Go (Clínica Alemana, Chile), con historial desde 2018, recetas, órdenes, familiar vinculado y resultados. [Vuelta 3] Búsqueda de otras clínicas (Las Condes, Santa María, UC Christus) sin ficha de app confirmada; solo canales digitales genéricos. [Vuelta 4] Mi Alemana Go: 3,1/5 con 137 calificaciones (App Store Chile), pantalla de inicio rediseñada para gestionar salud propia y familiar; sin evidencia de teleconsulta ni pagos en la app. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Sin búsqueda nueva; sin cambios. [Vuelta 7] Sin búsqueda nueva; sin cambios.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -10673,7 +10673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -10896,6 +10896,13 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Vuelta 7 (iter. 3, 2026-10-19 12:23 UTC): Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas verificados (+0 filas). Pendientes: Clinia, MiRedSalud, Mediko (cierran la vuelta 7 y regeneran func_norm/tabla_frecuencia).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -518,15 +518,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -558,15 +558,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -598,15 +598,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -638,15 +638,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -678,15 +678,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -718,15 +718,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -758,15 +758,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -798,15 +798,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -838,15 +838,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -878,15 +878,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -918,15 +918,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -958,15 +958,15 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar. [Vuelta 2] Confirmado por el CEO de Reservo (LinkedIn): app para pacientes en App Store y Google Play; guarda y comparte exámenes, recetas, órdenes y certificados. Fecha exacta de lanzamiento, precio y modelo de datos sin verificar. [Vuelta 3] Sin novedades de oct-2026. Reservo (Chile, México, Argentina) declara certificación Fonasa/CENS y cumplimiento de la nueva ley de datos personales; el Portal de Agendamiento de Reservo complementa a Clinia. Precio y modelo de datos sin verificar. [Vuelta 4] Una búsqueda adicional no encontró fuentes independientes sobre Clinia de Reservo (aparecen otras empresas llamadas Clinia); la evidencia sigue siendo la publicación del CEO en LinkedIn y notas de Reservo. Confianza media. [Vuelta 5] Sin fecha verificable del lanzamiento (publicación de LinkedIn del CEO sin fecha visible); existe otra empresa homónima en Brasil (Porto Alegre, IA para clínicas) que no es este producto. Sin funciones nuevas. [Vuelta 6] Sin novedades de oct-2026. Reservo declara &gt;36.500 profesionales y centros y ~14 millones de reservas al año (Chile, México, Argentina), sello CENS y certificación Fonasa (autodeclarado); la publicación del CEO pide ideas de nuevas funciones. Sigue sin fecha de lanzamiento verificable.</t>
+          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar. [Vuelta 2] Confirmado por el CEO de Reservo (LinkedIn): app para pacientes en App Store y Google Play; guarda y comparte exámenes, recetas, órdenes y certificados. Fecha exacta de lanzamiento, precio y modelo de datos sin verificar. [Vuelta 3] Sin novedades de oct-2026. Reservo (Chile, México, Argentina) declara certificación Fonasa/CENS y cumplimiento de la nueva ley de datos personales; el Portal de Agendamiento de Reservo complementa a Clinia. Precio y modelo de datos sin verificar. [Vuelta 4] Una búsqueda adicional no encontró fuentes independientes sobre Clinia de Reservo (aparecen otras empresas llamadas Clinia); la evidencia sigue siendo la publicación del CEO en LinkedIn y notas de Reservo. Confianza media. [Vuelta 5] Sin fecha verificable del lanzamiento (publicación de LinkedIn del CEO sin fecha visible); existe otra empresa homónima en Brasil (Porto Alegre, IA para clínicas) que no es este producto. Sin funciones nuevas. [Vuelta 6] Sin novedades de oct-2026. Reservo declara &gt;36.500 profesionales y centros y ~14 millones de reservas al año (Chile, México, Argentina), sello CENS y certificación Fonasa (autodeclarado); la publicación del CEO pide ideas de nuevas funciones. Sigue sin fecha de lanzamiento verificable. [Vuelta 7] Sin novedades; sin datos verificables de descargas ni calificación. Reservo: fundada en 2015 según una fuente (otra indica 2017). No confundir con Clinia de Brasil.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1002,11 +1002,11 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis). [Vuelta 2] La búsqueda no encontró fuentes adicionales ni ficha de la app chilena (solo una app RedSalud de otro país); funciones sin confirmar. [Vuelta 3] Rankings de terceros la ubican como app médica gratuita nº 1 en App Store y Google Play Chile (fecha desconocida); sin descripción de funciones ni confirmación del desarrollador en Google Play. [Vuelta 4] Sin documentación oficial chilena localizada; las fichas con funciones (agendar, telemedicina, historial de hijos) corresponden a una app RedSalud de otro país. Quejas públicas 2020-21 sobre acceso en línea a resultados. Funciones de MiRedSalud sin confirmar. [Vuelta 5] Una búsqueda adicional no halló cobertura del lanzamiento de dic-2025 ni de la app chilena; solo apps de otras empresas Red Salud (Paraguay, Perú). Sigue sin confirmarse más allá de la nota de RedSalud. [Vuelta 6] Sin cobertura adicional; los resultados corresponden a la plataforma Red Salud de Paraguay (Interasistencia, ~350 especialistas, call center por WhatsApp), que no es la red chilena. Funciones de MiRedSalud sin confirmar.</t>
+          <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis). [Vuelta 2] La búsqueda no encontró fuentes adicionales ni ficha de la app chilena (solo una app RedSalud de otro país); funciones sin confirmar. [Vuelta 3] Rankings de terceros la ubican como app médica gratuita nº 1 en App Store y Google Play Chile (fecha desconocida); sin descripción de funciones ni confirmación del desarrollador en Google Play. [Vuelta 4] Sin documentación oficial chilena localizada; las fichas con funciones (agendar, telemedicina, historial de hijos) corresponden a una app RedSalud de otro país. Quejas públicas 2020-21 sobre acceso en línea a resultados. Funciones de MiRedSalud sin confirmar. [Vuelta 5] Una búsqueda adicional no halló cobertura del lanzamiento de dic-2025 ni de la app chilena; solo apps de otras empresas Red Salud (Paraguay, Perú). Sigue sin confirmarse más allá de la nota de RedSalud. [Vuelta 6] Sin cobertura adicional; los resultados corresponden a la plataforma Red Salud de Paraguay (Interasistencia, ~350 especialistas, call center por WhatsApp), que no es la red chilena. Funciones de MiRedSalud sin confirmar. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc. [Vuelta 2] Sin precios ni planes vigentes localizados; sitio oficial bloqueado. [Vuelta 3] Pauta (oct-2024): su fundador, Tomás Riddell, dice que no reemplaza a médicos y apunta a lo ambulatorio y a la espera de derivación a especialidad en el sistema público. Financiamiento: fuentes discrepan (CLP 25M en dic-2023 según Bouncewatch; ~$40M según Descubre.vc). Precios vigentes sin verificar. [Vuelta 4] Entrevista oct-2024 menciona integración con la pasarela Flow. Sin novedades 2025-26 ni rondas verificadas; la cifra de US$40M de Bouncewatch es dudosa (perfil con 2 empleados). [Vuelta 5] CORRECCIÓN de financiamiento: Bouncewatch registra dos subvenciones (CLP 15M en ago-2022 y CLP 25M en dic-2023 = CLP 40M en total), no US$40M; 2 empleados; etapa Seed según Descubre.vc. No hay inversionistas de capital listados. [Vuelta 6] Sin noticias 2026 propias. Contexto: evento «IA y Salud en Chile 2026» (12-may) sobre regulación, datos personales e interoperabilidad de fichas clínicas; Doctoralia lanzó Noa Evidence (jul-2026, asistente de IA para profesionales); programa PRISMA IA 2.0 (dic-2025).</t>
+          <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc. [Vuelta 2] Sin precios ni planes vigentes localizados; sitio oficial bloqueado. [Vuelta 3] Pauta (oct-2024): su fundador, Tomás Riddell, dice que no reemplaza a médicos y apunta a lo ambulatorio y a la espera de derivación a especialidad en el sistema público. Financiamiento: fuentes discrepan (CLP 25M en dic-2023 según Bouncewatch; ~$40M según Descubre.vc). Precios vigentes sin verificar. [Vuelta 4] Entrevista oct-2024 menciona integración con la pasarela Flow. Sin novedades 2025-26 ni rondas verificadas; la cifra de US$40M de Bouncewatch es dudosa (perfil con 2 empleados). [Vuelta 5] CORRECCIÓN de financiamiento: Bouncewatch registra dos subvenciones (CLP 15M en ago-2022 y CLP 25M en dic-2023 = CLP 40M en total), no US$40M; 2 empleados; etapa Seed según Descubre.vc. No hay inversionistas de capital listados. [Vuelta 6] Sin noticias 2026 propias. Contexto: evento «IA y Salud en Chile 2026» (12-may) sobre regulación, datos personales e interoperabilidad de fichas clínicas; Doctoralia lanzó Noa Evidence (jul-2026, asistente de IA para profesionales); programa PRISMA IA 2.0 (dic-2025). [Vuelta 7] Sigue sin precios publicados de planes; un directorio la describe como gratuita y sin cuenta en su nivel básico (sin verificar).</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1082,11 +1082,11 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6657,27 +6657,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Historial institucional (solo datos de la propia red)</t>
+          <t>Recepción de documentos desde terceros</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ve historial de esa institución.</t>
+          <t>Desde feb-2016, la administradora de tarjetas ClinCard entregaba contratos y documentos a sus clientes dentro de la plataforma.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Historial institucional de consultas, urgencias y hospitalizaciones (solo datos de esa clínica).</t>
+          <t>Ve historial de esa institución.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6711,7 +6711,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MiRedSalud (RedSalud)</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Acceso a información clínica de la red.</t>
+          <t>Historial institucional de consultas, urgencias y hospitalizaciones (solo datos de esa clínica).</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6738,7 +6738,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MiRedSalud (RedSalud)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6748,24 +6748,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Información clínica unificada.</t>
+          <t>Acceso a información clínica de la red.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6780,19 +6780,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>El usuario registra sus antecedentes médicos en la app.</t>
+          <t>Información clínica unificada.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6807,19 +6807,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Centraliza el historial médico personal en el móvil.</t>
+          <t>El usuario registra sus antecedentes médicos en la app.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6834,19 +6834,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Permite compilar datos de vida/salud, gestionarlos y pasarlos a instituciones médicas.</t>
+          <t>Centraliza el historial médico personal en el móvil.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6861,19 +6861,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Centralizar registros y monitoreo desde el móvil.</t>
+          <t>Permite compilar datos de vida/salud, gestionarlos y pasarlos a instituciones médicas.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6883,17 +6883,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Línea de tiempo de salud</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Línea de tiempo con medicación, exámenes, citas y dieta.</t>
+          <t>Centralizar registros y monitoreo desde el móvil.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Registra notas de medicación, exámenes (laboratorio e imagen), actividad física, recetas, dieta y citas.</t>
+          <t>Línea de tiempo con medicación, exámenes, citas y dieta.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6927,7 +6927,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas</t>
+          <t>Línea de tiempo de salud</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas.</t>
+          <t>Registra notas de medicación, exámenes (laboratorio e imagen), actividad física, recetas, dieta y citas.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6954,7 +6954,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6964,39 +6964,39 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seguimiento de visitas, gastos y seguros</t>
+          <t>Registro de alergias y vacunas</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>App gratuita para seguir visitas al médico, facturas médicas, datos personales, seguros, inmunizaciones y medicamentos de farmacia.</t>
+          <t>Registro de alergias y vacunas.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Incentivos y monetización de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Recompensas / monetización de datos del usuario</t>
+          <t>Seguimiento de visitas, gastos y seguros</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Plan de convertir Medipass en superapp con gestión de salud diaria y mercado de datos, integrada con la EMR Dr.Palette.</t>
+          <t>App gratuita para seguir visitas al médico, facturas médicas, datos personales, seguros, inmunizaciones y medicamentos de farmacia.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7008,7 +7008,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Centros de investigación y farmacéuticas recompensarían con MedTokens a quienes compartan sus datos; no confirmado como ejecutado.</t>
+          <t>Plan de convertir Medipass en superapp con gestión de salud diaria y mercado de datos, integrada con la EMR Dr.Palette.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7035,7 +7035,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>El usuario puede agregar y monetizar sus datos; recompensas en cripto.</t>
+          <t>Centros de investigación y farmacéuticas recompensarían con MedTokens a quienes compartan sus datos; no confirmado como ejecutado.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7062,22 +7062,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Incentivos y monetización de datos</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Asistente de IA para profesionales de salud</t>
+          <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Producto para clínicos verificados de EE.UU. (gratis, abr-2026); desde 1-sep-2026 un plugin con nueve apps de fuentes públicas (investigación, ensayos, medicamentos, Medicare, prestadores), de solo lectura y sin acceso a fichas de pacientes.</t>
+          <t>El usuario puede agregar y monetizar sus datos; recompensas en cripto.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7089,7 +7089,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7099,12 +7099,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Coaching de salud con IA</t>
+          <t>Asistente de IA para profesionales de salud</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Coaching personalizado con IA.</t>
+          <t>Producto para clínicos verificados de EE.UU. (gratis, abr-2026); desde 1-sep-2026 un plugin con nueve apps de fuentes públicas (investigación, ensayos, medicamentos, Medicare, prestadores), de solo lectura y sin acceso a fichas de pacientes.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7116,7 +7116,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Detección de patrones en métricas de salud con IA</t>
+          <t>Coaching de salud con IA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Interpreta datos de Apple Health y registros en contexto y detecta cambios.</t>
+          <t>Coaching personalizado con IA.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7143,7 +7143,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Detecta patrones entre métricas de salud y fitness.</t>
+          <t>Interpreta datos de Apple Health y registros en contexto y detecta cambios.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7170,7 +7170,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
+          <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Explica resultados complejos en lenguaje simple.</t>
+          <t>Detecta patrones entre métricas de salud y fitness.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Desde 28-sep-2026, en la pestaña Health se puede elegir un gráfico, métrica o registro y obtener explicaciones basadas en los datos conectados.</t>
+          <t>Explica resultados complejos en lenguaje simple.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7224,7 +7224,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Explica exámenes en lenguaje simple.</t>
+          <t>Desde 28-sep-2026, en la pestaña Health se puede elegir un gráfico, métrica o registro y obtener explicaciones basadas en los datos conectados.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7251,7 +7251,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7266,19 +7266,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Interpreta exámenes de laboratorio.</t>
+          <t>Explica exámenes en lenguaje simple.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7288,24 +7288,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Orientación médica con IA</t>
+          <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mejora de jun-2026 (GPT-5.5 Instant): detecta cuándo puede requerirse atención urgente, pide contexto y explica la incertidumbre.</t>
+          <t>Interpreta exámenes de laboratorio.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7320,19 +7320,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Orientación médica instantánea mediante IA.</t>
+          <t>Mejora de jun-2026 (GPT-5.5 Instant): detecta cuándo puede requerirse atención urgente, pide contexto y explica la incertidumbre.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7342,24 +7342,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Preparación de consultas médicas con IA</t>
+          <t>Orientación médica con IA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Prepara preguntas para el médico.</t>
+          <t>Orientación médica instantánea mediante IA.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7386,7 +7386,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7396,12 +7396,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Resumen de historial con IA</t>
+          <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Resume instrucciones de atención.</t>
+          <t>Prepara preguntas para el médico.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7413,7 +7413,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Resume el historial del usuario.</t>
+          <t>Resume instrucciones de atención.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7440,22 +7440,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>API para apps de terceros</t>
+          <t>Resumen de historial con IA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>El usuario decide qué registros recibe cada app y si los nuevos se comparten automáticamente (por defecto pide permiso cada vez); ej. importar recetas a Medisafe.</t>
+          <t>Resume el historial del usuario.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>API para apps de terceros</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Vista central de alergias, condiciones, vacunas, laboratorio, medicación, procedimientos y signos vitales.</t>
+          <t>El usuario decide qué registros recibe cada app y si los nuevos se comparten automáticamente (por defecto pide permiso cada vez); ej. importar recetas a Medisafe.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7494,7 +7494,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Conexión de historiales electrónicos y apps como Apple Health, MyFitnessPal, Peloton.</t>
+          <t>Vista central de alergias, condiciones, vacunas, laboratorio, medicación, procedimientos y signos vitales.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Acceso a historiales electrónicos de proveedores de EE.UU. vía b.well; solo EE.UU., sin plazo anunciado para Latinoamérica.</t>
+          <t>Conexión de historiales electrónicos y apps como Apple Health, MyFitnessPal, Peloton.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Además de b.well y Apple Health, vincula registros de One Medical y Function Health (solo EE.UU., Free/Go/Plus/Pro, web e iOS).</t>
+          <t>Acceso a historiales electrónicos de proveedores de EE.UU. vía b.well; solo EE.UU., sin plazo anunciado para Latinoamérica.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7575,7 +7575,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Acceso a resultados y registros de salud (beta, Pro/Max, EE.UU.).</t>
+          <t>Además de b.well y Apple Health, vincula registros de One Medical y Function Health (solo EE.UU., Free/Go/Plus/Pro, web e iOS).</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7602,7 +7602,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7617,19 +7617,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Datos desde profesionales/centros que usan Reservo (fichas clínicas, agenda, telemedicina).</t>
+          <t>Acceso a resultados y registros de salud (beta, Pro/Max, EE.UU.).</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7644,19 +7644,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tras autenticación simple, trae los últimos 3 años de historial de hospitales integrados (p. ej. Samsung Seoul, SNUH, Severance).</t>
+          <t>Datos desde profesionales/centros que usan Reservo (fichas clínicas, agenda, telemedicina).</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7671,19 +7671,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Sincroniza resultados desde centros de salud y permite subir fotos o documentos de las solicitudes médicas.</t>
+          <t>Tras autenticación simple, trae los últimos 3 años de historial de hospitales integrados (p. ej. Samsung Seoul, SNUH, Severance).</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Reúne registros de hospitales, resultados de laboratorio y datos genómicos.</t>
+          <t>Sincroniza resultados desde centros de salud y permite subir fotos o documentos de las solicitudes médicas.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analítica poblacional B2B</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Analítica poblacional on-chain; integrada con Epic, Cerner, Meditech y Allscripts (B2B).</t>
+          <t>Reúne registros de hospitales, resultados de laboratorio y datos genómicos.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7737,7 +7737,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7747,24 +7747,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+          <t>Analítica poblacional B2B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Android, iOS y escritorio; médicos acceden a historias digitalizadas, envían estudios e indicaciones y organizan agenda.</t>
+          <t>Analítica poblacional on-chain; integrada con Epic, Cerner, Meditech y Allscripts (B2B).</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7779,19 +7779,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Disponible en App Store y Google Play. Reservo opera en Chile, México y Argentina y está certificada por FONASA y CENS.</t>
+          <t>Android, iOS y escritorio; médicos acceden a historias digitalizadas, envían estudios e indicaciones y organizan agenda.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7806,19 +7806,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Disponible en web, iOS y Android.</t>
+          <t>Disponible en App Store y Google Play. Reservo opera en Chile, México y Argentina y está certificada por FONASA y CENS.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7828,24 +7828,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Versión digital de los registros con acceso por móvil o web.</t>
+          <t>Disponible en web, iOS y Android.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7855,24 +7855,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Importación y exportación de datos</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Importar/exportar datos para compartir de forma segura con familias o cuidadores. Es MediPlanner Pro, de otro desarrollador (App Store MX, $39 MXN).</t>
+          <t>Versión digital de los registros con acceso por móvil o web.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7882,24 +7882,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Integración con EHR de proveedores</t>
+          <t>Importación y exportación de datos</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Según una AMA sin fecha, integraba dos sistemas de GP que cubren ~80% del mercado UK; no confirmado como ejecutado.</t>
+          <t>Importar/exportar datos para compartir de forma segura con familias o cuidadores. Es MediPlanner Pro, de otro desarrollador (App Store MX, $39 MXN).</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Integración con EHR de proveedores</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Integración beta en apps iOS/Android.</t>
+          <t>Según una AMA sin fecha, integraba dos sistemas de GP que cubren ~80% del mercado UK; no confirmado como ejecutado.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Integración beta con Health Connect en la app móvil; conectores de registros (HealthEx, Function) solo para Pro/Max en EE.UU.</t>
+          <t>Integración beta en apps iOS/Android.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7953,7 +7953,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
+          <t>Integración beta con Health Connect en la app móvil; conectores de registros (HealthEx, Function) solo para Pro/Max en EE.UU.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -7980,22 +7980,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Gestión de lista de medicamentos</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Listas de medicamentos, vitaminas y suplementos con horarios; escaneo de etiqueta del frasco solo en EE.UU.</t>
+          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8007,7 +8007,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8017,24 +8017,24 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Importación automática de tratamientos desde receta digital</t>
+          <t>Gestión de lista de medicamentos</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Según la ficha de la App Store MX, los tratamientos llegan automáticamente desde la receta digital del médico (autodeclarado, sin verificar).</t>
+          <t>Listas de medicamentos, vitaminas y suplementos con horarios; escaneo de etiqueta del frasco solo en EE.UU.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8044,24 +8044,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
+          <t>Importación automática de tratamientos desde receta digital</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Recordatorios desde el app.</t>
+          <t>Según la ficha de la App Store MX, los tratamientos llegan automáticamente desde la receta digital del médico (autodeclarado, sin verificar).</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8076,19 +8076,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Recordatorios de citas/medicación.</t>
+          <t>Recordatorios desde el app.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8098,51 +8098,51 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Registro de tomas y adherencia al tratamiento</t>
+          <t>Recordatorios de medicación y citas</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Registro de cada toma y control de adherencia; gestiona medicamentos propios y de familiares.</t>
+          <t>Recordatorios de citas/medicación.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Comunidad de pacientes</t>
+          <t>Registro de tomas y adherencia al tratamiento</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Los usuarios con condiciones similares pueden preguntar, recibir recomendaciones y compartir experiencias.</t>
+          <t>Registro de cada toma y control de adherencia; gestiona medicamentos propios y de familiares.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8152,24 +8152,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Contenido educativo sobre salud</t>
+          <t>Comunidad de pacientes</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Busca que el paciente aprenda sobre sus enfermedades y sea más autónomo.</t>
+          <t>Los usuarios con condiciones similares pueden preguntar, recibir recomendaciones y compartir experiencias.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8179,24 +8179,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores</t>
+          <t>Contenido educativo sobre salud</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores de salud.</t>
+          <t>Busca que el paciente aprenda sobre sus enfermedades y sea más autónomo.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8206,24 +8206,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Datos de pasos, sueño, peso junto a registros.</t>
+          <t>Gráficas de evolución de indicadores de salud.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8233,12 +8233,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Panel de seguimiento de salud y bienestar</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>El relanzamiento de Medipass (mar-2023) agregó un panel para gestionar la información de salud del usuario.</t>
+          <t>Datos de pasos, sueño, peso junto a registros.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -8250,7 +8250,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
+          <t>El relanzamiento de Medipass (mar-2023) agregó un panel para gestionar la información de salud del usuario.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8277,7 +8277,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8287,12 +8287,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Registro de nutrición</t>
+          <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Escaneo de etiquetas nutricionales con la cámara; según un análisis, no escribe en HealthKit.</t>
+          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Seguimiento de salud femenina</t>
+          <t>Registro de nutrición</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Extiende el seguimiento de ciclo con perimenopausia y menopausia.</t>
+          <t>Escaneo de etiquetas nutricionales con la cámara; según un análisis, no escribe en HealthKit.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8331,7 +8331,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8341,51 +8341,51 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Valoración de profesionales</t>
+          <t>Seguimiento de salud femenina</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Calificación de la atención de profesionales con autorización previa, compartible con otros usuarios.</t>
+          <t>Extiende el seguimiento de ciclo con perimenopausia y menopausia.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Acceso mínimo por categorías de datos</t>
+          <t>Valoración de profesionales</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Claude solicita solo las categorías relevantes (p. ej. medicamentos o laboratorio) y no fichas completas; HealthEx agrega datos de más de 50.000 sistemas de salud de EE.UU.</t>
+          <t>Calificación de la atención de profesionales con autorización previa, compartible con otros usuarios.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Acceso mínimo por categorías de datos</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
+          <t>Claude solicita solo las categorías relevantes (p. ej. medicamentos o laboratorio) y no fichas completas; HealthEx agrega datos de más de 50.000 sistemas de salud de EE.UU.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Almacena huellas de datos médicos en un registro de solo escritura, sin guardar datos clínicos en cadena.</t>
+          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8439,7 +8439,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
+          <t>Almacena huellas de datos médicos en un registro de solo escritura, sin guardar datos clínicos en cadena.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8466,7 +8466,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
+          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8493,7 +8493,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso</t>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
+          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -8520,7 +8520,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8535,19 +8535,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Almacenamiento seguro del historial con criterios de seguridad estrictos, comparable a apps bancarias.</t>
+          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8557,12 +8557,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cumplimiento regulatorio de salud y datos</t>
+          <t>Cifrado y control de acceso</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Reservo declara plataforma certificada por Fonasa y CENS, cumplimiento de estándares de telemedicina del Minsal y de la nueva ley chilena de datos personales (declaración de la empresa).</t>
+          <t>Almacenamiento seguro del historial con criterios de seguridad estrictos, comparable a apps bancarias.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -8574,7 +8574,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8584,24 +8584,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Gestión de consentimiento sobre uso de datos</t>
+          <t>Cumplimiento regulatorio de salud y datos</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Desde 14-sep-2026, las nuevas conexiones heredan la configuración global de plugins: ChatGPT puede usar datos de Health sin pedir permiso cada vez salvo acciones sensibles (web primero, móvil después).</t>
+          <t>Reservo declara plataforma certificada por Fonasa y CENS, cumplimiento de estándares de telemedicina del Minsal y de la nueva ley chilena de datos personales (declaración de la empresa).</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Identidad descentralizada (DID)</t>
+          <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Gestión de identificadores descentralizados en Panacea.</t>
+          <t>Desde 14-sep-2026, las nuevas conexiones heredan la configuración global de plugins: ChatGPT puede usar datos de Health sin pedir permiso cada vez salvo acciones sensibles (web primero, móvil después).</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8628,7 +8628,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
+          <t>Identidad descentralizada (DID)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
+          <t>Gestión de identificadores descentralizados en Panacea.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8655,7 +8655,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>El usuario activa y revoca permisos; los datos de salud compartidos se excluyen de la memoria de Claude y del entrenamiento.</t>
+          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8682,34 +8682,34 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Modelo freemium y suscripción</t>
+          <t>Privacidad reforzada para datos de salud</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Planes para personas y empresas.</t>
+          <t>El usuario activa y revoca permisos; los datos de salud compartidos se excluyen de la memoria de Claude y del entrenamiento.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8719,17 +8719,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Pagos con criptomoneda</t>
+          <t>Modelo freemium y suscripción</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Pago de consultas con token.</t>
+          <t>Planes para personas y empresas.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Piloto en New Malden (Londres): consultas por video pagables con tarjeta o con MedTokens.</t>
+          <t>Pago de consultas con token.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8763,7 +8763,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8773,24 +8773,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Pagos dentro de la app</t>
+          <t>Pagos con criptomoneda</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Pagos dentro de la plataforma mediante la pasarela Flow (según resumen de entrevista de Pauta, oct-2024; esperada para mejorar la experiencia).</t>
+          <t>Piloto en New Malden (Londres): consultas por video pagables con tarjeta o con MedTokens.</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8800,17 +8800,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
+          <t>Pagos dentro de la app</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
+          <t>Pagos dentro de la plataforma mediante la pasarela Flow (según resumen de entrevista de Pauta, oct-2024; esperada para mejorar la experiencia).</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Reclamo de seguro médico (indemnización) desde la app, con verificación de autenticidad de los registros vía blockchain por la aseguradora.</t>
+          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8849,17 +8849,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Telemedicina y atención remota</t>
+          <t>Seguros y pagos</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Mensajería paciente-institución</t>
+          <t>Reclamos y trámites con seguros</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Chat para consultas a hospitales, orientación simple de síntomas e información de tratamientos; comunicación bidireccional hospital-paciente (nov-2023).</t>
+          <t>Reclamo de seguro médico (indemnización) desde la app, con verificación de autenticidad de los registros vía blockchain por la aseguradora.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8871,25 +8871,52 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Telemedicina y atención remota</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Mensajería paciente-institución</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Chat para consultas a hospitales, orientación simple de síntomas e información de tratamientos; comunicación bidireccional hospital-paciente (nov-2023).</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
           <t>Medicalchain</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>Telemedicina y atención remota</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>Teleconsultas con GP.</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
@@ -8906,7 +8933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R67"/>
+  <dimension ref="A1:R68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9032,6 +9059,8 @@
           <t>Búsqueda de profesionales de salud</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9042,6 +9071,17 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2">
         <f>COUNTIF(C2:Q2,"✓")</f>
         <v/>
@@ -9063,11 +9103,24 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3">
         <f>COUNTIF(C3:Q3,"✓")</f>
         <v/>
@@ -9084,11 +9137,25 @@
           <t>Integración con calendario del dispositivo</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4">
         <f>COUNTIF(C4:Q4,"✓")</f>
         <v/>
@@ -9105,11 +9172,25 @@
           <t>Localización de centros médicos y farmacias</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5">
         <f>COUNTIF(C5:Q5,"✓")</f>
         <v/>
@@ -9126,11 +9207,21 @@
           <t>Reserva de citas médicas</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9141,6 +9232,8 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6">
         <f>COUNTIF(C6:Q6,"✓")</f>
         <v/>
@@ -9157,11 +9250,25 @@
           <t>Acceso del profesional al historial del paciente</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7">
         <f>COUNTIF(C7:Q7,"✓")</f>
         <v/>
@@ -9178,11 +9285,25 @@
           <t>Compartir con personas sin cuenta mediante clave segura</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8">
         <f>COUNTIF(C8:Q8,"✓")</f>
         <v/>
@@ -9199,11 +9320,25 @@
           <t>Compartir datos con cuidador o persona de confianza</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9">
         <f>COUNTIF(C9:Q9,"✓")</f>
         <v/>
@@ -9225,11 +9360,13 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9255,11 +9392,16 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10">
         <f>COUNTIF(C10:Q10,"✓")</f>
         <v/>
@@ -9276,11 +9418,25 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11">
         <f>COUNTIF(C11:Q11,"✓")</f>
         <v/>
@@ -9297,11 +9453,25 @@
           <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12">
         <f>COUNTIF(C12:Q12,"✓")</f>
         <v/>
@@ -9318,11 +9488,25 @@
           <t>Red social con profesionales y familiares</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13">
         <f>COUNTIF(C13:Q13,"✓")</f>
         <v/>
@@ -9349,11 +9533,23 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14">
         <f>COUNTIF(C14:Q14,"✓")</f>
         <v/>
@@ -9370,6 +9566,8 @@
           <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9380,21 +9578,29 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15">
         <f>COUNTIF(C15:Q15,"✓")</f>
         <v/>
@@ -9416,6 +9622,8 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9431,11 +9639,19 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16">
         <f>COUNTIF(C16:Q16,"✓")</f>
         <v/>
@@ -9452,16 +9668,29 @@
           <t>Almacenamiento de recetas</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17">
         <f>COUNTIF(C17:Q17,"✓")</f>
         <v/>
@@ -9478,11 +9707,25 @@
           <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18">
         <f>COUNTIF(C18:Q18,"✓")</f>
         <v/>
@@ -9499,11 +9742,25 @@
           <t>Emisión de certificados médicos</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19">
         <f>COUNTIF(C19:Q19,"✓")</f>
         <v/>
@@ -9525,6 +9782,19 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9546,11 +9816,25 @@
           <t>Notificación y envío de resultados</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21">
         <f>COUNTIF(C21:Q21,"✓")</f>
         <v/>
@@ -9559,24 +9843,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Historial institucional (solo datos de la propia red)</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
+          <t>Recepción de documentos desde terceros</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22">
         <f>COUNTIF(C22:Q22,"✓")</f>
         <v/>
@@ -9590,34 +9883,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+          <t>Historial institucional (solo datos de la propia red)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23">
         <f>COUNTIF(C23:Q23,"✓")</f>
         <v/>
@@ -9631,10 +9922,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Línea de tiempo de salud</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -9652,14 +9973,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+          <t>Línea de tiempo de salud</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25">
         <f>COUNTIF(C25:Q25,"✓")</f>
         <v/>
@@ -9673,14 +10008,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Seguimiento de visitas, gastos y seguros</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+          <t>Registro de alergias y vacunas</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26">
         <f>COUNTIF(C26:Q26,"✓")</f>
         <v/>
@@ -9689,29 +10038,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Incentivos y monetización de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Recompensas / monetización de datos del usuario</t>
-        </is>
-      </c>
+          <t>Seguimiento de visitas, gastos y seguros</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27">
         <f>COUNTIF(C27:Q27,"✓")</f>
         <v/>
@@ -9720,19 +10073,41 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Incentivos y monetización de datos</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Asistente de IA para profesionales de salud</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
+          <t>Recompensas / monetización de datos del usuario</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28">
         <f>COUNTIF(C28:Q28,"✓")</f>
         <v/>
@@ -9746,14 +10121,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Coaching de salud con IA</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
+          <t>Asistente de IA para profesionales de salud</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29">
         <f>COUNTIF(C29:Q29,"✓")</f>
         <v/>
@@ -9767,19 +10156,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Detección de patrones en métricas de salud con IA</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
+          <t>Coaching de salud con IA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30">
         <f>COUNTIF(C30:Q30,"✓")</f>
         <v/>
@@ -9793,9 +10191,18 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
-        </is>
-      </c>
+          <t>Detección de patrones en métricas de salud con IA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9806,11 +10213,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31">
         <f>COUNTIF(C31:Q31,"✓")</f>
         <v/>
@@ -9824,14 +10230,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Orientación médica con IA</t>
-        </is>
-      </c>
+          <t>Interpretación de exámenes con IA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9850,15 +10273,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Preparación de consultas médicas con IA</t>
-        </is>
-      </c>
+          <t>Orientación médica con IA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -9876,9 +10312,18 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Resumen de historial con IA</t>
-        </is>
-      </c>
+          <t>Preparación de consultas médicas con IA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9889,6 +10334,10 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34">
         <f>COUNTIF(C34:Q34,"✓")</f>
         <v/>
@@ -9897,19 +10346,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>API para apps de terceros</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+          <t>Resumen de historial con IA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35">
         <f>COUNTIF(C35:Q35,"✓")</f>
         <v/>
@@ -9923,44 +10390,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+          <t>API para apps de terceros</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36">
         <f>COUNTIF(C36:Q36,"✓")</f>
         <v/>
@@ -9974,14 +10425,52 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Analítica poblacional B2B</t>
-        </is>
-      </c>
+          <t>Agregación de registros de múltiples instituciones</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37">
         <f>COUNTIF(C37:Q37,"✓")</f>
         <v/>
@@ -9995,24 +10484,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
+          <t>Analítica poblacional B2B</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38">
         <f>COUNTIF(C38:Q38,"✓")</f>
         <v/>
@@ -10026,14 +10519,36 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39">
         <f>COUNTIF(C39:Q39,"✓")</f>
         <v/>
@@ -10047,14 +10562,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Importación y exportación de datos</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40">
         <f>COUNTIF(C40:Q40,"✓")</f>
         <v/>
@@ -10068,14 +10597,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Integración con EHR de proveedores</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+          <t>Importación y exportación de datos</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41">
         <f>COUNTIF(C41:Q41,"✓")</f>
         <v/>
@@ -10089,19 +10632,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
+          <t>Integración con EHR de proveedores</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42">
         <f>COUNTIF(C42:Q42,"✓")</f>
         <v/>
@@ -10110,19 +10662,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gestión de lista de medicamentos</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43">
         <f>COUNTIF(C43:Q43,"✓")</f>
         <v/>
@@ -10136,14 +10706,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Importación automática de tratamientos desde receta digital</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
+          <t>Gestión de lista de medicamentos</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44">
         <f>COUNTIF(C44:Q44,"✓")</f>
         <v/>
@@ -10157,19 +10741,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
+          <t>Importación automática de tratamientos desde receta digital</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45">
         <f>COUNTIF(C45:Q45,"✓")</f>
         <v/>
@@ -10183,14 +10776,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Registro de tomas y adherencia al tratamiento</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
+          <t>Recordatorios de medicación y citas</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46">
         <f>COUNTIF(C46:Q46,"✓")</f>
         <v/>
@@ -10199,19 +10810,33 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Comunidad de pacientes</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
+          <t>Registro de tomas y adherencia al tratamiento</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47">
         <f>COUNTIF(C47:Q47,"✓")</f>
         <v/>
@@ -10225,14 +10850,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Contenido educativo sobre salud</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+          <t>Comunidad de pacientes</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48">
         <f>COUNTIF(C48:Q48,"✓")</f>
         <v/>
@@ -10246,14 +10885,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
+          <t>Contenido educativo sobre salud</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49">
         <f>COUNTIF(C49:Q49,"✓")</f>
         <v/>
@@ -10267,14 +10920,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
+          <t>Gráficas de evolución de indicadores</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50">
         <f>COUNTIF(C50:Q50,"✓")</f>
         <v/>
@@ -10288,19 +10955,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Panel de seguimiento de salud y bienestar</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
       <c r="R51">
         <f>COUNTIF(C51:Q51,"✓")</f>
         <v/>
@@ -10314,14 +10990,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Registro de nutrición</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
+          <t>Panel de seguimiento de salud y bienestar</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52">
         <f>COUNTIF(C52:Q52,"✓")</f>
         <v/>
@@ -10335,14 +11029,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Seguimiento de salud femenina</t>
-        </is>
-      </c>
+          <t>Registro de nutrición</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53">
         <f>COUNTIF(C53:Q53,"✓")</f>
         <v/>
@@ -10356,14 +11064,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Valoración de profesionales</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
+          <t>Seguimiento de salud femenina</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54">
         <f>COUNTIF(C54:Q54,"✓")</f>
         <v/>
@@ -10372,19 +11094,33 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Acceso mínimo por categorías de datos</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
+          <t>Valoración de profesionales</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55">
         <f>COUNTIF(C55:Q55,"✓")</f>
         <v/>
@@ -10398,24 +11134,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
+          <t>Acceso mínimo por categorías de datos</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56">
         <f>COUNTIF(C56:Q56,"✓")</f>
         <v/>
@@ -10429,19 +11169,36 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57">
         <f>COUNTIF(C57:Q57,"✓")</f>
         <v/>
@@ -10455,14 +11212,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cumplimiento regulatorio de salud y datos</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
+          <t>Cifrado y control de acceso</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58">
         <f>COUNTIF(C58:Q58,"✓")</f>
         <v/>
@@ -10476,14 +11251,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Gestión de consentimiento sobre uso de datos</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
+          <t>Cumplimiento regulatorio de salud y datos</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
       <c r="R59">
         <f>COUNTIF(C59:Q59,"✓")</f>
         <v/>
@@ -10497,14 +11286,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Identidad descentralizada (DID)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
+          <t>Gestión de consentimiento sobre uso de datos</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60">
         <f>COUNTIF(C60:Q60,"✓")</f>
         <v/>
@@ -10518,19 +11321,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
+          <t>Identidad descentralizada (DID)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61">
         <f>COUNTIF(C61:Q61,"✓")</f>
         <v/>
@@ -10539,19 +11351,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Modelo freemium y suscripción</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
+          <t>Privacidad reforzada para datos de salud</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62">
         <f>COUNTIF(C62:Q62,"✓")</f>
         <v/>
@@ -10565,10 +11395,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pagos con criptomoneda</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+          <t>Modelo freemium y suscripción</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -10586,14 +11430,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pagos dentro de la app</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
+          <t>Pagos con criptomoneda</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
       <c r="R64">
         <f>COUNTIF(C64:Q64,"✓")</f>
         <v/>
@@ -10607,10 +11465,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
+          <t>Pagos dentro de la app</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -10623,19 +11495,33 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Telemedicina y atención remota</t>
+          <t>Seguros y pagos</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mensajería paciente-institución</t>
-        </is>
-      </c>
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
       <c r="R66">
         <f>COUNTIF(C66:Q66,"✓")</f>
         <v/>
@@ -10649,16 +11535,65 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Teleconsulta con profesionales</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+          <t>Mensajería paciente-institución</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67">
         <f>COUNTIF(C67:Q67,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Telemedicina y atención remota</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Teleconsulta con profesionales</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68">
+        <f>COUNTIF(C68:Q68,"✓")</f>
         <v/>
       </c>
     </row>
@@ -10673,7 +11608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -10903,6 +11838,13 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>VUELTA 7 COMPLETA (2026-10-20 12:19 UTC): Clinia, MiRedSalud y Mediko verificados (+0 filas). Contador de loops = 7 para todos, Revisado reiniciado a "No". func_norm (131 filas) y tabla_frecuencia (67 funcionalidades) regenerados. Vuelta 8 parte con Meedika, Infomed, MediPlanner, Clingot. Candidato a competidor sin agregar: HealthChain (Chile).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -513,12 +513,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar. [Vuelta 3] Sin novedades 2026 ni confirmación de la app Android en Google Play; usuarios actuales desconocidos. Nota de prensa no indica año de lanzamiento explícito. [Vuelta 4] Sin fuentes nuevas; portalinnova.cl no aparece en búsquedas. Sigue dependiendo de una sola nota de prensa. [Vuelta 5] Sin fuentes nuevas (ni entrevistas ni financiamiento); sigue dependiendo de una sola nota de prensa sin año explícito. [Vuelta 6] Sin ficha de Google Play ni fuentes nuevas; disponibilidad en Android sin confirmar. [Vuelta 7] Sin fuentes nuevas; no hay ficha oficial localizada. No confundir con apps de nombre parecido (Medika App, MEDDI, AI Medik).</t>
+          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar. [Vuelta 3] Sin novedades 2026 ni confirmación de la app Android en Google Play; usuarios actuales desconocidos. Nota de prensa no indica año de lanzamiento explícito. [Vuelta 4] Sin fuentes nuevas; portalinnova.cl no aparece en búsquedas. Sigue dependiendo de una sola nota de prensa. [Vuelta 5] Sin fuentes nuevas (ni entrevistas ni financiamiento); sigue dependiendo de una sola nota de prensa sin año explícito. [Vuelta 6] Sin ficha de Google Play ni fuentes nuevas; disponibilidad en Android sin confirmar. [Vuelta 7] Sin fuentes nuevas; no hay ficha oficial localizada. No confundir con apps de nombre parecido (Medika App, MEDDI, AI Medik). [Vuelta 8] Sin fuentes nuevas.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -526,7 +526,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -553,12 +553,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapa A] Fundada 2019 por Diego Ibarra, Andrés Fantuzzi y Gabriel Zamora. Lanzada mar-2021 en App Store y Play Store con 1.200 usuarios; planeaba nueva versión jul-2021 y ronda de US$500 mil. Objetivo: llevar el historial en el celular, acceso en emergencias, médico puede ingresar datos con consentimiento. Estado actual NO verificado (posible app inactiva). URL es la nota de prensa; sitio oficial por confirmar. [Vuelta 3] Sin evidencia posterior a 2021; relanzamiento previsto jul-2021 no confirmado. Probable app inactiva. [Vuelta 4] Sin cambios; sigue sin evidencia posterior a 2021. [Vuelta 5] Cofundador Andrés Fantuzzi es cardiólogo de la Clínica Santa María. Sin ronda de inversión ni relanzamiento confirmados; no confundir con Infomed de Cuba (portal del Minsap). [Vuelta 6] Sin búsqueda nueva (fuentes agotadas en vueltas 3-5); sin cambios. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios.</t>
+          <t>[DIRECTO · Chile · etapa A] Fundada 2019 por Diego Ibarra, Andrés Fantuzzi y Gabriel Zamora. Lanzada mar-2021 en App Store y Play Store con 1.200 usuarios; planeaba nueva versión jul-2021 y ronda de US$500 mil. Objetivo: llevar el historial en el celular, acceso en emergencias, médico puede ingresar datos con consentimiento. Estado actual NO verificado (posible app inactiva). URL es la nota de prensa; sitio oficial por confirmar. [Vuelta 3] Sin evidencia posterior a 2021; relanzamiento previsto jul-2021 no confirmado. Probable app inactiva. [Vuelta 4] Sin cambios; sigue sin evidencia posterior a 2021. [Vuelta 5] Cofundador Andrés Fantuzzi es cardiólogo de la Clínica Santa María. Sin ronda de inversión ni relanzamiento confirmados; no confundir con Infomed de Cuba (portal del Minsap). [Vuelta 6] Sin búsqueda nueva (fuentes agotadas en vueltas 3-5); sin cambios. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin fuentes nuevas; relanzamiento de jul-2021 sigue sin confirmarse.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -593,12 +593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · México] Historial por perfil familiar, alergias, vacunas, recetas digitales, gráficas de evolución, agendamiento, compartir con profesionales. Gratis en App Store MX. Sin evidencia de uso en Chile. Cubre parte de la etapa C (familia). [Vuelta 3] Existen dos apps distintas: MediPlanner (gratis, Rym Solutions, MX, 3,7/5 con 3 calificaciones) y MediPlanner Pro (otro desarrollador, $39 MXN). Sin presencia verificada en Chile. [Vuelta 4] No pude confirmar el desarrollador de la versión gratuita (Rym Solutions no se repite en esta búsqueda). MediPlanner Pro (fichas BR/OM) guardaría datos solo en el dispositivo, sin nube; no confundir con MedPlanner/AskHEMI (otra empresa). [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Se reconfirma en la ficha de App Store MX que el desarrollador de la versión gratuita es Rym Solutions S. de R.L. de C.V. (3,7/5, 3 calificaciones); MediPlanner Pro no menciona a esa empresa, por lo que no se puede asegurar que sea el mismo desarrollador. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios.</t>
+          <t>[REGIONAL · México] Historial por perfil familiar, alergias, vacunas, recetas digitales, gráficas de evolución, agendamiento, compartir con profesionales. Gratis en App Store MX. Sin evidencia de uso en Chile. Cubre parte de la etapa C (familia). [Vuelta 3] Existen dos apps distintas: MediPlanner (gratis, Rym Solutions, MX, 3,7/5 con 3 calificaciones) y MediPlanner Pro (otro desarrollador, $39 MXN). Sin presencia verificada en Chile. [Vuelta 4] No pude confirmar el desarrollador de la versión gratuita (Rym Solutions no se repite en esta búsqueda). MediPlanner Pro (fichas BR/OM) guardaría datos solo en el dispositivo, sin nube; no confundir con MedPlanner/AskHEMI (otra empresa). [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Se reconfirma en la ficha de App Store MX que el desarrollador de la versión gratuita es Rym Solutions S. de R.L. de C.V. (3,7/5, 3 calificaciones); MediPlanner Pro no menciona a esa empresa, por lo que no se puede asegurar que sea el mismo desarrollador. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin búsqueda nueva (saturado).</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -606,7 +606,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · Argentina · débil] App para cargar antecedentes médicos propios. Única referencia: nota de opinión en grupoanimal.mx sin fecha verificada. Estado y sitio por confirmar. [Vuelta 3] Referencias de 2017 (apps4citizens, La Nación); sitio y precio no verificados; puede estar inactiva. [Vuelta 4] Sin fuentes nuevas. [Vuelta 5] Registro empresarial (indicadores.ar, datos a jul-2026) muestra CLINGOT S.A. activa en CABA, constituida el 4-abr-2016; no confirma que la app siga operando. Programa federal argentino de historias clínicas digitales como contexto regulatorio. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios. [Vuelta 7] Solo fuentes de 2017; sin evidencia nueva de operación más allá del registro societario.</t>
+          <t>[REGIONAL · Argentina · débil] App para cargar antecedentes médicos propios. Única referencia: nota de opinión en grupoanimal.mx sin fecha verificada. Estado y sitio por confirmar. [Vuelta 3] Referencias de 2017 (apps4citizens, La Nación); sitio y precio no verificados; puede estar inactiva. [Vuelta 4] Sin fuentes nuevas. [Vuelta 5] Registro empresarial (indicadores.ar, datos a jul-2026) muestra CLINGOT S.A. activa en CABA, constituida el 4-abr-2016; no confirma que la app siga operando. Programa federal argentino de historias clínicas digitales como contexto regulatorio. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios. [Vuelta 7] Solo fuentes de 2017; sin evidencia nueva de operación más allá del registro societario. [Vuelta 8] Sin fuentes nuevas.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -9059,8 +9059,6 @@
           <t>Búsqueda de profesionales de salud</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9071,17 +9069,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2">
         <f>COUNTIF(C2:Q2,"✓")</f>
         <v/>
@@ -9103,24 +9090,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3">
         <f>COUNTIF(C3:Q3,"✓")</f>
         <v/>
@@ -9137,25 +9111,11 @@
           <t>Integración con calendario del dispositivo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4">
         <f>COUNTIF(C4:Q4,"✓")</f>
         <v/>
@@ -9172,25 +9132,11 @@
           <t>Localización de centros médicos y farmacias</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5">
         <f>COUNTIF(C5:Q5,"✓")</f>
         <v/>
@@ -9207,21 +9153,11 @@
           <t>Reserva de citas médicas</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9232,8 +9168,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6">
         <f>COUNTIF(C6:Q6,"✓")</f>
         <v/>
@@ -9250,25 +9184,11 @@
           <t>Acceso del profesional al historial del paciente</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7">
         <f>COUNTIF(C7:Q7,"✓")</f>
         <v/>
@@ -9285,25 +9205,11 @@
           <t>Compartir con personas sin cuenta mediante clave segura</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8">
         <f>COUNTIF(C8:Q8,"✓")</f>
         <v/>
@@ -9320,25 +9226,11 @@
           <t>Compartir datos con cuidador o persona de confianza</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9">
         <f>COUNTIF(C9:Q9,"✓")</f>
         <v/>
@@ -9360,13 +9252,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9392,16 +9282,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10">
         <f>COUNTIF(C10:Q10,"✓")</f>
         <v/>
@@ -9418,25 +9303,11 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11">
         <f>COUNTIF(C11:Q11,"✓")</f>
         <v/>
@@ -9453,25 +9324,11 @@
           <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12">
         <f>COUNTIF(C12:Q12,"✓")</f>
         <v/>
@@ -9488,25 +9345,11 @@
           <t>Red social con profesionales y familiares</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13">
         <f>COUNTIF(C13:Q13,"✓")</f>
         <v/>
@@ -9533,23 +9376,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14">
         <f>COUNTIF(C14:Q14,"✓")</f>
         <v/>
@@ -9566,8 +9397,6 @@
           <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9578,29 +9407,21 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15">
         <f>COUNTIF(C15:Q15,"✓")</f>
         <v/>
@@ -9622,8 +9443,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9639,19 +9458,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16">
         <f>COUNTIF(C16:Q16,"✓")</f>
         <v/>
@@ -9668,29 +9479,16 @@
           <t>Almacenamiento de recetas</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17">
         <f>COUNTIF(C17:Q17,"✓")</f>
         <v/>
@@ -9707,25 +9505,11 @@
           <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18">
         <f>COUNTIF(C18:Q18,"✓")</f>
         <v/>
@@ -9742,25 +9526,11 @@
           <t>Emisión de certificados médicos</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19">
         <f>COUNTIF(C19:Q19,"✓")</f>
         <v/>
@@ -9782,19 +9552,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9816,25 +9573,11 @@
           <t>Notificación y envío de resultados</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21">
         <f>COUNTIF(C21:Q21,"✓")</f>
         <v/>
@@ -9851,25 +9594,11 @@
           <t>Recepción de documentos desde terceros</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22">
         <f>COUNTIF(C22:Q22,"✓")</f>
         <v/>
@@ -9886,29 +9615,16 @@
           <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23">
         <f>COUNTIF(C23:Q23,"✓")</f>
         <v/>
@@ -9925,36 +9641,26 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9976,25 +9682,11 @@
           <t>Línea de tiempo de salud</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25">
         <f>COUNTIF(C25:Q25,"✓")</f>
         <v/>
@@ -10011,25 +9703,11 @@
           <t>Registro de alergias y vacunas</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26">
         <f>COUNTIF(C26:Q26,"✓")</f>
         <v/>
@@ -10046,25 +9724,11 @@
           <t>Seguimiento de visitas, gastos y seguros</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27">
         <f>COUNTIF(C27:Q27,"✓")</f>
         <v/>
@@ -10081,11 +9745,6 @@
           <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10101,13 +9760,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28">
         <f>COUNTIF(C28:Q28,"✓")</f>
         <v/>
@@ -10124,25 +9776,11 @@
           <t>Asistente de IA para profesionales de salud</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29">
         <f>COUNTIF(C29:Q29,"✓")</f>
         <v/>
@@ -10159,25 +9797,11 @@
           <t>Coaching de salud con IA</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30">
         <f>COUNTIF(C30:Q30,"✓")</f>
         <v/>
@@ -10194,15 +9818,6 @@
           <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10213,10 +9828,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31">
         <f>COUNTIF(C31:Q31,"✓")</f>
         <v/>
@@ -10233,15 +9844,6 @@
           <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10252,9 +9854,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10276,24 +9875,11 @@
           <t>Orientación médica con IA</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10315,15 +9901,6 @@
           <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10334,10 +9911,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34">
         <f>COUNTIF(C34:Q34,"✓")</f>
         <v/>
@@ -10354,15 +9927,6 @@
           <t>Resumen de historial con IA</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10373,10 +9937,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35">
         <f>COUNTIF(C35:Q35,"✓")</f>
         <v/>
@@ -10393,25 +9953,11 @@
           <t>API para apps de terceros</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36">
         <f>COUNTIF(C36:Q36,"✓")</f>
         <v/>
@@ -10433,10 +9979,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10447,7 +9989,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10463,14 +10004,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37">
         <f>COUNTIF(C37:Q37,"✓")</f>
         <v/>
@@ -10487,25 +10025,11 @@
           <t>Analítica poblacional B2B</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38">
         <f>COUNTIF(C38:Q38,"✓")</f>
         <v/>
@@ -10522,9 +10046,6 @@
           <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10535,20 +10056,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39">
         <f>COUNTIF(C39:Q39,"✓")</f>
         <v/>
@@ -10565,25 +10077,11 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40">
         <f>COUNTIF(C40:Q40,"✓")</f>
         <v/>
@@ -10600,25 +10098,11 @@
           <t>Importación y exportación de datos</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41">
         <f>COUNTIF(C41:Q41,"✓")</f>
         <v/>
@@ -10635,25 +10119,11 @@
           <t>Integración con EHR de proveedores</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42">
         <f>COUNTIF(C42:Q42,"✓")</f>
         <v/>
@@ -10670,29 +10140,16 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43">
         <f>COUNTIF(C43:Q43,"✓")</f>
         <v/>
@@ -10709,25 +10166,11 @@
           <t>Gestión de lista de medicamentos</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44">
         <f>COUNTIF(C44:Q44,"✓")</f>
         <v/>
@@ -10744,25 +10187,11 @@
           <t>Importación automática de tratamientos desde receta digital</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45">
         <f>COUNTIF(C45:Q45,"✓")</f>
         <v/>
@@ -10784,24 +10213,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46">
         <f>COUNTIF(C46:Q46,"✓")</f>
         <v/>
@@ -10818,25 +10234,11 @@
           <t>Registro de tomas y adherencia al tratamiento</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47">
         <f>COUNTIF(C47:Q47,"✓")</f>
         <v/>
@@ -10853,25 +10255,11 @@
           <t>Comunidad de pacientes</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48">
         <f>COUNTIF(C48:Q48,"✓")</f>
         <v/>
@@ -10888,25 +10276,11 @@
           <t>Contenido educativo sobre salud</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49">
         <f>COUNTIF(C49:Q49,"✓")</f>
         <v/>
@@ -10923,25 +10297,11 @@
           <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50">
         <f>COUNTIF(C50:Q50,"✓")</f>
         <v/>
@@ -10958,25 +10318,11 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51">
         <f>COUNTIF(C51:Q51,"✓")</f>
         <v/>
@@ -10993,11 +10339,6 @@
           <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11008,14 +10349,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52">
         <f>COUNTIF(C52:Q52,"✓")</f>
         <v/>
@@ -11032,25 +10365,11 @@
           <t>Registro de nutrición</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
       <c r="R53">
         <f>COUNTIF(C53:Q53,"✓")</f>
         <v/>
@@ -11067,25 +10386,11 @@
           <t>Seguimiento de salud femenina</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54">
         <f>COUNTIF(C54:Q54,"✓")</f>
         <v/>
@@ -11102,25 +10407,11 @@
           <t>Valoración de profesionales</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55">
         <f>COUNTIF(C55:Q55,"✓")</f>
         <v/>
@@ -11137,25 +10428,11 @@
           <t>Acceso mínimo por categorías de datos</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56">
         <f>COUNTIF(C56:Q56,"✓")</f>
         <v/>
@@ -11172,11 +10449,6 @@
           <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11192,13 +10464,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57">
         <f>COUNTIF(C57:Q57,"✓")</f>
         <v/>
@@ -11215,29 +10480,16 @@
           <t>Cifrado y control de acceso</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
       <c r="R58">
         <f>COUNTIF(C58:Q58,"✓")</f>
         <v/>
@@ -11254,25 +10506,11 @@
           <t>Cumplimiento regulatorio de salud y datos</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
       <c r="R59">
         <f>COUNTIF(C59:Q59,"✓")</f>
         <v/>
@@ -11289,25 +10527,11 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
       <c r="R60">
         <f>COUNTIF(C60:Q60,"✓")</f>
         <v/>
@@ -11324,25 +10548,11 @@
           <t>Identidad descentralizada (DID)</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
       <c r="R61">
         <f>COUNTIF(C61:Q61,"✓")</f>
         <v/>
@@ -11359,15 +10569,6 @@
           <t>Privacidad reforzada para datos de salud</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11378,10 +10579,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
       <c r="R62">
         <f>COUNTIF(C62:Q62,"✓")</f>
         <v/>
@@ -11398,20 +10595,6 @@
           <t>Modelo freemium y suscripción</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11433,25 +10616,11 @@
           <t>Pagos con criptomoneda</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
       <c r="R64">
         <f>COUNTIF(C64:Q64,"✓")</f>
         <v/>
@@ -11468,20 +10637,6 @@
           <t>Pagos dentro de la app</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11503,25 +10658,11 @@
           <t>Reclamos y trámites con seguros</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
       <c r="R66">
         <f>COUNTIF(C66:Q66,"✓")</f>
         <v/>
@@ -11538,25 +10679,11 @@
           <t>Mensajería paciente-institución</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
       <c r="R67">
         <f>COUNTIF(C67:Q67,"✓")</f>
         <v/>
@@ -11573,25 +10700,11 @@
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
       <c r="R68">
         <f>COUNTIF(C68:Q68,"✓")</f>
         <v/>
@@ -11608,7 +10721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -11845,6 +10958,20 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Vuelta 8 (iter. 1, 2026-10-21 12:23 UTC): Meedika, Infomed, MediPlanner, Clingot verificados (+0 filas; saturado). Pendientes: Healfies, Patientory, MediBloc, Medicalchain, Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas, Clinia, MiRedSalud, Mediko.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CANDIDATO A COMPETIDOR (no agregado a la lista; decide el usuario): HealthChain (Chile, Santiago). Cofundada en 2018 por Javier Leyton, Ivonne Beltrán y Génesis García; Startup Chile; red Hyperledger Fabric con protocolo de interoperabilidad y API para sistemas hospitalarios (BaaS); en may-2020 anunció una red para unificar el historial clínico en Latinoamérica con IBM Blockchain. Fuentes 2018-2020 (Diario Bitcoin, Meganoticias); estado actual desconocido. Funcionalidades inferidas: interoperabilidad entre instituciones, historial unificado, blockchain. Competidor B2B más que app de paciente.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B. [Vuelta 2] Lanzada simultáneamente en Brasil, Argentina y EE.UU.; permite compartir con no registrados vía clave por email. Sin novedades posteriores a 2016. [Vuelta 3] Sin evidencia de actividad reciente ni de cierre; Gust/Dealroom la listan en Florianópolis (10 empleados, healfies.com) sin fecha de actualización. Estado sin confirmar. [Vuelta 4] Sin Google Play localizado; no confundir con la app Healfy (otro producto). Sin novedades. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios. [Vuelta 7] Solo fuentes de 2015-2016; alianza con ClinCard (feb-2016). Sin evidencia de actividad reciente.</t>
+          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B. [Vuelta 2] Lanzada simultáneamente en Brasil, Argentina y EE.UU.; permite compartir con no registrados vía clave por email. Sin novedades posteriores a 2016. [Vuelta 3] Sin evidencia de actividad reciente ni de cierre; Gust/Dealroom la listan en Florianópolis (10 empleados, healfies.com) sin fecha de actualización. Estado sin confirmar. [Vuelta 4] Sin Google Play localizado; no confundir con la app Healfy (otro producto). Sin novedades. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios. [Vuelta 7] Solo fuentes de 2015-2016; alianza con ClinCard (feb-2016). Sin evidencia de actividad reciente. [Vuelta 8] Sin fuentes nuevas.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain. [Vuelta 2] Sin noticias 2026 encontradas en búsqueda; sitio oficial bloqueado. [Vuelta 3] Búsqueda adicional solo devuelve hitos de 2017 (token sale US$7,2M) y 2019 (Serie A de US$5,3M, cierre no confirmado); sin datos 2025-26 propios. [Vuelta 4] App pública lanzada en la conferencia JP Morgan Healthcare (2019); red PTOYMatrix (blockchain HIPAA); socios reportados: StartUp Health y Kaiser Permanente (beta). Estado actual en App Store/Google Play sin confirmar. [Vuelta 5] Sin noticias 2026 del equipo. Token PTOY con capitalización de ~US$53K a fines de ago-2026 según Phantom (KuCoin discrepa en la circulación): señal de baja actividad, no prueba de cierre. Esto relativiza la actividad hasta abr-2026 mencionada en la ficha original. [Vuelta 6] Sin noticias posteriores a 2020 localizadas (hitos: token sale 2017, consorcio Hyperledger, alianza con Georgia State, Series A de US$5,3M vía R/GA Ventures, Neith con Prosper Healthtech en Birmingham). Estado actual desconocido. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios.</t>
+          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain. [Vuelta 2] Sin noticias 2026 encontradas en búsqueda; sitio oficial bloqueado. [Vuelta 3] Búsqueda adicional solo devuelve hitos de 2017 (token sale US$7,2M) y 2019 (Serie A de US$5,3M, cierre no confirmado); sin datos 2025-26 propios. [Vuelta 4] App pública lanzada en la conferencia JP Morgan Healthcare (2019); red PTOYMatrix (blockchain HIPAA); socios reportados: StartUp Health y Kaiser Permanente (beta). Estado actual en App Store/Google Play sin confirmar. [Vuelta 5] Sin noticias 2026 del equipo. Token PTOY con capitalización de ~US$53K a fines de ago-2026 según Phantom (KuCoin discrepa en la circulación): señal de baja actividad, no prueba de cierre. Esto relativiza la actividad hasta abr-2026 mencionada en la ficha original. [Vuelta 6] Sin noticias posteriores a 2020 localizadas (hitos: token sale 2017, consorcio Hyperledger, alianza con Georgia State, Series A de US$5,3M vía R/GA Ventures, Neith con Prosper Healthtech en Birmingham). Estado actual desconocido. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin noticias 2025-26; en 2018 la oferta se dirigía a empresas de salud, con la versión individual planificada después.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain. [Vuelta 2] Panacea incluye DID, Append Only Log, IBC y PNFT; sin anuncios 2026 localizados. [Vuelta 3] Medipass: app en Corea con 20 hospitales/aseguradoras integrados (fecha de la lista desconocida) y plan 2022 de superapp con marketplace de datos; operación actual sin confirmar. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Medipass: ~400.000 usuarios acumulados (CEO, jun-2022); integración con aseguradoras Shinhan Life, Samsung Fire y Hyundai Marine (2020); renovación completa en mar-2023 (dashboard de salud, gestión familiar, certificados). Sin noticias 2026 encontradas. [Vuelta 6] Medipass 2023: comunicación bidireccional hospital-paciente y chat MediTalk; en 2019 fue seleccionada para el programa gubernamental de MyData médico con Samsung Fire y SNUH. Sin estrategia 2026 localizada. Meta declarada: usar Medipass como «identificación» de salud. [Vuelta 7] Una fuente sin fecha atribuye a Medipass más de 600.000 pacientes en 14 hospitales; MoU 2019 con Severance (plataforma de facturación de seguros y detección de falsificación de datos) y piloto con Massachusetts General Hospital. Sin datos 2025-26.</t>
+          <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain. [Vuelta 2] Panacea incluye DID, Append Only Log, IBC y PNFT; sin anuncios 2026 localizados. [Vuelta 3] Medipass: app en Corea con 20 hospitales/aseguradoras integrados (fecha de la lista desconocida) y plan 2022 de superapp con marketplace de datos; operación actual sin confirmar. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Medipass: ~400.000 usuarios acumulados (CEO, jun-2022); integración con aseguradoras Shinhan Life, Samsung Fire y Hyundai Marine (2020); renovación completa en mar-2023 (dashboard de salud, gestión familiar, certificados). Sin noticias 2026 encontradas. [Vuelta 6] Medipass 2023: comunicación bidireccional hospital-paciente y chat MediTalk; en 2019 fue seleccionada para el programa gubernamental de MyData médico con Samsung Fire y SNUH. Sin estrategia 2026 localizada. Meta declarada: usar Medipass como «identificación» de salud. [Vuelta 7] Una fuente sin fecha atribuye a Medipass más de 600.000 pacientes en 14 hospitales; MoU 2019 con Severance (plataforma de facturación de seguros y detección de falsificación de datos) y piloto con Massachusetts General Hospital. Sin datos 2025-26. [Vuelta 8] Sin noticias 2025-26.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · Reino Unido · INACTIVO] Londres, 2017, Ethereum, con telemedicina. Piloto según registro de la UE (2020). Tracxn/PitchBook lo marcan fuera de operación (ago-2025). Solo caso de aprendizaje: no cuenta como competidor activo. [Vuelta 2] Token MTN deslistado de Bitfinex el 26-mar-2021; sin hallazgos de actividad posterior. [Vuelta 3] Seedtable la marca activa sin fuente; no hallé registro en Companies House. Sigue tratándose como caso de aprendizaje. [Vuelta 4] Pre-venta reportada de US$20M en MedTokens (un solo artículo secundario, sin verificar); modelo de token en revisión y exploración de security token según AMA; integraciones y servicios de 2019 sin confirmar. [Vuelta 5] Un agregador indica sitio medicalchain.com fuera de línea desde 15-feb-2025, último commit en GitHub hace ~3 años y proyecto en «fase de mantenimiento»; preventa de MedTokens reportada entre US$20M y US$24M (fuentes discrepan). Confirma tratarlo como inactivo. [Vuelta 6] Sin búsqueda nueva (revisada en vuelta 5; sitio fuera de línea desde feb-2025 según un agregador); sin cambios. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios.</t>
+          <t>[BLOCKCHAIN · Reino Unido · INACTIVO] Londres, 2017, Ethereum, con telemedicina. Piloto según registro de la UE (2020). Tracxn/PitchBook lo marcan fuera de operación (ago-2025). Solo caso de aprendizaje: no cuenta como competidor activo. [Vuelta 2] Token MTN deslistado de Bitfinex el 26-mar-2021; sin hallazgos de actividad posterior. [Vuelta 3] Seedtable la marca activa sin fuente; no hallé registro en Companies House. Sigue tratándose como caso de aprendizaje. [Vuelta 4] Pre-venta reportada de US$20M en MedTokens (un solo artículo secundario, sin verificar); modelo de token en revisión y exploración de security token según AMA; integraciones y servicios de 2019 sin confirmar. [Vuelta 5] Un agregador indica sitio medicalchain.com fuera de línea desde 15-feb-2025, último commit en GitHub hace ~3 años y proyecto en «fase de mantenimiento»; preventa de MedTokens reportada entre US$20M y US$24M (fuentes discrepan). Confirma tratarlo como inactivo. [Vuelta 6] Sin búsqueda nueva (revisada en vuelta 5; sitio fuera de línea desde feb-2025 según un agregador); sin cambios. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin fuentes nuevas; se mantiene como inactivo.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A35"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -10972,6 +10972,13 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Vuelta 8 (iter. 2, 2026-10-22 12:28 UTC): Healfies, Patientory, MediBloc, Medicalchain verificados (+0 filas; saturado). Pendientes: Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas, Clinia, MiRedSalud, Mediko.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -833,12 +833,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Agrega registros clínicos vía FHIR; &gt;500 instituciones conectadas en EE.UU. (2018). Sin evidencia de disponibilidad en Chile. Incluida en el dispositivo. Amenaza si FHIR/IPS-CL se adopta en Chile. [Vuelta 2] Sin disponibilidad de registros clínicos en Chile (solo EE.UU., Reino Unido, Canadá). [Vuelta 3] iOS 27 (WWDC 8-jun-2026; publicado ~14-sep-2026): rediseño del app Health, menopausia, nutrición por cámara. El coach de salud con IA no se anunció. Sin ampliación de Health Records a Chile. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Sin ampliación de Health Records a Australia, Europa ni Latinoamérica (solo EE.UU., UK, Canadá). Funciones de dispositivo (apnea del sueño, prueba auditiva) sí se amplían a países latinoamericanos, pero no son registros clínicos. [Vuelta 6] Sin novedades de iOS 27.x localizadas. Health Records API permite compartir registros con apps de terceros con control por app; opción de enviar datos de uso a Apple. [Vuelta 7] Coach de salud con IA / Health+ de pago: solo rumores (Gurman), atrasado al menos a iOS 27; no confirmado ni anunciado.</t>
+          <t>[ADYACENTE · global] Agrega registros clínicos vía FHIR; &gt;500 instituciones conectadas en EE.UU. (2018). Sin evidencia de disponibilidad en Chile. Incluida en el dispositivo. Amenaza si FHIR/IPS-CL se adopta en Chile. [Vuelta 2] Sin disponibilidad de registros clínicos en Chile (solo EE.UU., Reino Unido, Canadá). [Vuelta 3] iOS 27 (WWDC 8-jun-2026; publicado ~14-sep-2026): rediseño del app Health, menopausia, nutrición por cámara. El coach de salud con IA no se anunció. Sin ampliación de Health Records a Chile. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Sin ampliación de Health Records a Australia, Europa ni Latinoamérica (solo EE.UU., UK, Canadá). Funciones de dispositivo (apnea del sueño, prueba auditiva) sí se amplían a países latinoamericanos, pero no son registros clínicos. [Vuelta 6] Sin novedades de iOS 27.x localizadas. Health Records API permite compartir registros con apps de terceros con control por app; opción de enviar datos de uso a Apple. [Vuelta 7] Coach de salud con IA / Health+ de pago: solo rumores (Gurman), atrasado al menos a iOS 27; no confirmado ni anunciado. [Vuelta 8] Sin novedades.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Lanzado 7-ene-2026. Conecta registros médicos; conectores solo en EE.UU. Dentro de suscripción del asistente. Fija la expectativa de consultar y resumir el historial. [Vuelta 2] Confirmado: registros solo EE.UU.; sin anuncios para Latinoamérica. Hay inconsistencia de fechas entre fuentes (7-ene-2026 lanzamiento vs. jul-2026 despliegue de registros). [Vuelta 3] Fechas aclaradas: presentación 7-ene-2026 (acceso limitado); despliegue de Health in ChatGPT con Apple Health y registros en EE.UU. el 23-jul-2026; mejora de salud jun-2026. Sin anuncios para Latinoamérica ni para sep-oct 2026. [Vuelta 4] Septiembre 2026: permisos por defecto para datos conectados (14-sep) y explicaciones por gráfico/métrica (28-sep); ChatGPT for Clinicians (abr-2026) para clínicos verificados de EE.UU. Más del 70% de usuarios de Health permite usar datos conectados sin pedir permiso (según OpenAI). Sigue solo EE.UU. [Vuelta 5] Nota de jul-2026: Health no está disponible en México, Android, modo de voz ni Codex; web e iOS en EE.UU., adultos con sesión iniciada. Sin anuncio para Chile ni Latinoamérica. [Vuelta 6] Última entrada de Health en las notas de OpenAI sigue siendo la del 23-jul-2026 (más cambios de sep); sin entradas de octubre localizadas. Health tab: laboratorios, medicamentos, actividad y sueño en una vista; solo EE.UU., web e iOS. [Vuelta 7] OpenAI afirma que más de 300 millones de personas usan ChatGPT cada semana para consultas de salud (dato de la empresa). No es una solución con cumplimiento HIPAA declarado. Sin novedades de oct-2026.</t>
+          <t>[ADYACENTE · global] Lanzado 7-ene-2026. Conecta registros médicos; conectores solo en EE.UU. Dentro de suscripción del asistente. Fija la expectativa de consultar y resumir el historial. [Vuelta 2] Confirmado: registros solo EE.UU.; sin anuncios para Latinoamérica. Hay inconsistencia de fechas entre fuentes (7-ene-2026 lanzamiento vs. jul-2026 despliegue de registros). [Vuelta 3] Fechas aclaradas: presentación 7-ene-2026 (acceso limitado); despliegue de Health in ChatGPT con Apple Health y registros en EE.UU. el 23-jul-2026; mejora de salud jun-2026. Sin anuncios para Latinoamérica ni para sep-oct 2026. [Vuelta 4] Septiembre 2026: permisos por defecto para datos conectados (14-sep) y explicaciones por gráfico/métrica (28-sep); ChatGPT for Clinicians (abr-2026) para clínicos verificados de EE.UU. Más del 70% de usuarios de Health permite usar datos conectados sin pedir permiso (según OpenAI). Sigue solo EE.UU. [Vuelta 5] Nota de jul-2026: Health no está disponible en México, Android, modo de voz ni Codex; web e iOS en EE.UU., adultos con sesión iniciada. Sin anuncio para Chile ni Latinoamérica. [Vuelta 6] Última entrada de Health en las notas de OpenAI sigue siendo la del 23-jul-2026 (más cambios de sep); sin entradas de octubre localizadas. Health tab: laboratorios, medicamentos, actividad y sueño en una vista; solo EE.UU., web e iOS. [Vuelta 7] OpenAI afirma que más de 300 millones de personas usan ChatGPT cada semana para consultas de salud (dato de la empresa). No es una solución con cumplimiento HIPAA declarado. Sin novedades de oct-2026. [Vuelta 8] Sin novedades de fines de oct-2026.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -886,7 +886,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Lanzado 11-ene-2026. Conectores solo en EE.UU., planes Pro/Max. Nota: producto de Anthropic, conflicto de interés al evaluarlo. [Vuelta 2] Sin cambios fuera de EE.UU. (HealthEx y Function para Pro/Max). [Vuelta 3] Sin anuncios posteriores a enero de 2026. Hoja de ruta de HealthEx (agendar, buscar prestadores, recetas) sin confirmar como lanzada. [Vuelta 4] Sin anuncios nuevos. Fuentes discrepan en el acceso (Pro/Max según Fortune y la mayoría; Pro/Team según Times of AI); sin evidencia de disponibilidad fuera de EE.UU. [Vuelta 5] Sin noticias de oct-2026; HealthEx agrega datos de &gt;50.000 sistemas de EE.UU. y Claude pide solo las categorías relevantes vía MCP. [Vuelta 6] Sin noticias posteriores a enero de 2026 localizadas. [Vuelta 7] Sin novedades posteriores a enero de 2026.</t>
+          <t>[ADYACENTE · global] Lanzado 11-ene-2026. Conectores solo en EE.UU., planes Pro/Max. Nota: producto de Anthropic, conflicto de interés al evaluarlo. [Vuelta 2] Sin cambios fuera de EE.UU. (HealthEx y Function para Pro/Max). [Vuelta 3] Sin anuncios posteriores a enero de 2026. Hoja de ruta de HealthEx (agendar, buscar prestadores, recetas) sin confirmar como lanzada. [Vuelta 4] Sin anuncios nuevos. Fuentes discrepan en el acceso (Pro/Max según Fortune y la mayoría; Pro/Team según Times of AI); sin evidencia de disponibilidad fuera de EE.UU. [Vuelta 5] Sin noticias de oct-2026; HealthEx agrega datos de &gt;50.000 sistemas de EE.UU. y Claude pide solo las categorías relevantes vía MCP. [Vuelta 6] Sin noticias posteriores a enero de 2026 localizadas. [Vuelta 7] Sin novedades posteriores a enero de 2026. [Vuelta 8] Sin novedades posteriores a enero de 2026.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -926,7 +926,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones. [Vuelta 2] App concreta: Mi Alemana Go (Clínica Alemana, Chile), con historial desde 2018, recetas, órdenes, familiar vinculado y resultados. [Vuelta 3] Búsqueda de otras clínicas (Las Condes, Santa María, UC Christus) sin ficha de app confirmada; solo canales digitales genéricos. [Vuelta 4] Mi Alemana Go: 3,1/5 con 137 calificaciones (App Store Chile), pantalla de inicio rediseñada para gestionar salud propia y familiar; sin evidencia de teleconsulta ni pagos en la app. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Sin búsqueda nueva; sin cambios. [Vuelta 7] Sin búsqueda nueva; sin cambios.</t>
+          <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones. [Vuelta 2] App concreta: Mi Alemana Go (Clínica Alemana, Chile), con historial desde 2018, recetas, órdenes, familiar vinculado y resultados. [Vuelta 3] Búsqueda de otras clínicas (Las Condes, Santa María, UC Christus) sin ficha de app confirmada; solo canales digitales genéricos. [Vuelta 4] Mi Alemana Go: 3,1/5 con 137 calificaciones (App Store Chile), pantalla de inicio rediseñada para gestionar salud propia y familiar; sin evidencia de teleconsulta ni pagos en la app. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Sin búsqueda nueva; sin cambios. [Vuelta 7] Sin búsqueda nueva; sin cambios. [Vuelta 8] Mi Alemana Go: notificaciones de deuda pendiente, check-in de admisión y encuestas de salud; DF la describe como segundo paso de la estrategia digital de la clínica (registros de exámenes, indicaciones, historial y recetas). Otras apps de red: Mi Dávila (Red Dávila, gestión de citas en todos sus centros, según un directorio); Clínica Las Condes sin app confirmada.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5334,6 +5334,70 @@
       <c r="F132" t="inlineStr">
         <is>
           <t>Búsqueda web (Baguete, 2016); estado actual no verificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Aviso de deudas pendientes y pago (Mi Alemana Go)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Sección de notificaciones que avisa cuando hay una deuda disponible para pagar (fecha de la actualización desconocida).</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Ficha App Store Chile (Mi Alemana Go)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Citas y agenda</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Check-in de admisión y encuestas de salud (Mi Alemana Go)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Notificaciones de check-in de admisión y encuestas de salud previas a la atención.</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Ficha App Store Chile (Mi Alemana Go)</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -10979,6 +11043,13 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Vuelta 8 (iter. 3, 2026-10-23 12:17 UTC): Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas verificados (+2 filas, de Apps de clínicas). Pendientes: Clinia, MiRedSalud, Mediko (cierran la vuelta 8 y regeneran func_norm/tabla_frecuencia).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -518,15 +518,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -558,15 +558,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -598,15 +598,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -638,15 +638,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -678,15 +678,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -718,15 +718,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -758,15 +758,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -798,15 +798,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -838,15 +838,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -878,15 +878,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -918,15 +918,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -958,15 +958,15 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar. [Vuelta 2] Confirmado por el CEO de Reservo (LinkedIn): app para pacientes en App Store y Google Play; guarda y comparte exámenes, recetas, órdenes y certificados. Fecha exacta de lanzamiento, precio y modelo de datos sin verificar. [Vuelta 3] Sin novedades de oct-2026. Reservo (Chile, México, Argentina) declara certificación Fonasa/CENS y cumplimiento de la nueva ley de datos personales; el Portal de Agendamiento de Reservo complementa a Clinia. Precio y modelo de datos sin verificar. [Vuelta 4] Una búsqueda adicional no encontró fuentes independientes sobre Clinia de Reservo (aparecen otras empresas llamadas Clinia); la evidencia sigue siendo la publicación del CEO en LinkedIn y notas de Reservo. Confianza media. [Vuelta 5] Sin fecha verificable del lanzamiento (publicación de LinkedIn del CEO sin fecha visible); existe otra empresa homónima en Brasil (Porto Alegre, IA para clínicas) que no es este producto. Sin funciones nuevas. [Vuelta 6] Sin novedades de oct-2026. Reservo declara &gt;36.500 profesionales y centros y ~14 millones de reservas al año (Chile, México, Argentina), sello CENS y certificación Fonasa (autodeclarado); la publicación del CEO pide ideas de nuevas funciones. Sigue sin fecha de lanzamiento verificable. [Vuelta 7] Sin novedades; sin datos verificables de descargas ni calificación. Reservo: fundada en 2015 según una fuente (otra indica 2017). No confundir con Clinia de Brasil.</t>
+          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar. [Vuelta 2] Confirmado por el CEO de Reservo (LinkedIn): app para pacientes en App Store y Google Play; guarda y comparte exámenes, recetas, órdenes y certificados. Fecha exacta de lanzamiento, precio y modelo de datos sin verificar. [Vuelta 3] Sin novedades de oct-2026. Reservo (Chile, México, Argentina) declara certificación Fonasa/CENS y cumplimiento de la nueva ley de datos personales; el Portal de Agendamiento de Reservo complementa a Clinia. Precio y modelo de datos sin verificar. [Vuelta 4] Una búsqueda adicional no encontró fuentes independientes sobre Clinia de Reservo (aparecen otras empresas llamadas Clinia); la evidencia sigue siendo la publicación del CEO en LinkedIn y notas de Reservo. Confianza media. [Vuelta 5] Sin fecha verificable del lanzamiento (publicación de LinkedIn del CEO sin fecha visible); existe otra empresa homónima en Brasil (Porto Alegre, IA para clínicas) que no es este producto. Sin funciones nuevas. [Vuelta 6] Sin novedades de oct-2026. Reservo declara &gt;36.500 profesionales y centros y ~14 millones de reservas al año (Chile, México, Argentina), sello CENS y certificación Fonasa (autodeclarado); la publicación del CEO pide ideas de nuevas funciones. Sigue sin fecha de lanzamiento verificable. [Vuelta 7] Sin novedades; sin datos verificables de descargas ni calificación. Reservo: fundada en 2015 según una fuente (otra indica 2017). No confundir con Clinia de Brasil. [Vuelta 8] Sin búsqueda nueva (saturado); sin cambios.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1002,11 +1002,11 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis). [Vuelta 2] La búsqueda no encontró fuentes adicionales ni ficha de la app chilena (solo una app RedSalud de otro país); funciones sin confirmar. [Vuelta 3] Rankings de terceros la ubican como app médica gratuita nº 1 en App Store y Google Play Chile (fecha desconocida); sin descripción de funciones ni confirmación del desarrollador en Google Play. [Vuelta 4] Sin documentación oficial chilena localizada; las fichas con funciones (agendar, telemedicina, historial de hijos) corresponden a una app RedSalud de otro país. Quejas públicas 2020-21 sobre acceso en línea a resultados. Funciones de MiRedSalud sin confirmar. [Vuelta 5] Una búsqueda adicional no halló cobertura del lanzamiento de dic-2025 ni de la app chilena; solo apps de otras empresas Red Salud (Paraguay, Perú). Sigue sin confirmarse más allá de la nota de RedSalud. [Vuelta 6] Sin cobertura adicional; los resultados corresponden a la plataforma Red Salud de Paraguay (Interasistencia, ~350 especialistas, call center por WhatsApp), que no es la red chilena. Funciones de MiRedSalud sin confirmar. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios.</t>
+          <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis). [Vuelta 2] La búsqueda no encontró fuentes adicionales ni ficha de la app chilena (solo una app RedSalud de otro país); funciones sin confirmar. [Vuelta 3] Rankings de terceros la ubican como app médica gratuita nº 1 en App Store y Google Play Chile (fecha desconocida); sin descripción de funciones ni confirmación del desarrollador en Google Play. [Vuelta 4] Sin documentación oficial chilena localizada; las fichas con funciones (agendar, telemedicina, historial de hijos) corresponden a una app RedSalud de otro país. Quejas públicas 2020-21 sobre acceso en línea a resultados. Funciones de MiRedSalud sin confirmar. [Vuelta 5] Una búsqueda adicional no halló cobertura del lanzamiento de dic-2025 ni de la app chilena; solo apps de otras empresas Red Salud (Paraguay, Perú). Sigue sin confirmarse más allá de la nota de RedSalud. [Vuelta 6] Sin cobertura adicional; los resultados corresponden a la plataforma Red Salud de Paraguay (Interasistencia, ~350 especialistas, call center por WhatsApp), que no es la red chilena. Funciones de MiRedSalud sin confirmar. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin búsqueda nueva (saturado); sin cambios.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc. [Vuelta 2] Sin precios ni planes vigentes localizados; sitio oficial bloqueado. [Vuelta 3] Pauta (oct-2024): su fundador, Tomás Riddell, dice que no reemplaza a médicos y apunta a lo ambulatorio y a la espera de derivación a especialidad en el sistema público. Financiamiento: fuentes discrepan (CLP 25M en dic-2023 según Bouncewatch; ~$40M según Descubre.vc). Precios vigentes sin verificar. [Vuelta 4] Entrevista oct-2024 menciona integración con la pasarela Flow. Sin novedades 2025-26 ni rondas verificadas; la cifra de US$40M de Bouncewatch es dudosa (perfil con 2 empleados). [Vuelta 5] CORRECCIÓN de financiamiento: Bouncewatch registra dos subvenciones (CLP 15M en ago-2022 y CLP 25M en dic-2023 = CLP 40M en total), no US$40M; 2 empleados; etapa Seed según Descubre.vc. No hay inversionistas de capital listados. [Vuelta 6] Sin noticias 2026 propias. Contexto: evento «IA y Salud en Chile 2026» (12-may) sobre regulación, datos personales e interoperabilidad de fichas clínicas; Doctoralia lanzó Noa Evidence (jul-2026, asistente de IA para profesionales); programa PRISMA IA 2.0 (dic-2025). [Vuelta 7] Sigue sin precios publicados de planes; un directorio la describe como gratuita y sin cuenta en su nivel básico (sin verificar).</t>
+          <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc. [Vuelta 2] Sin precios ni planes vigentes localizados; sitio oficial bloqueado. [Vuelta 3] Pauta (oct-2024): su fundador, Tomás Riddell, dice que no reemplaza a médicos y apunta a lo ambulatorio y a la espera de derivación a especialidad en el sistema público. Financiamiento: fuentes discrepan (CLP 25M en dic-2023 según Bouncewatch; ~$40M según Descubre.vc). Precios vigentes sin verificar. [Vuelta 4] Entrevista oct-2024 menciona integración con la pasarela Flow. Sin novedades 2025-26 ni rondas verificadas; la cifra de US$40M de Bouncewatch es dudosa (perfil con 2 empleados). [Vuelta 5] CORRECCIÓN de financiamiento: Bouncewatch registra dos subvenciones (CLP 15M en ago-2022 y CLP 25M en dic-2023 = CLP 40M en total), no US$40M; 2 empleados; etapa Seed según Descubre.vc. No hay inversionistas de capital listados. [Vuelta 6] Sin noticias 2026 propias. Contexto: evento «IA y Salud en Chile 2026» (12-may) sobre regulación, datos personales e interoperabilidad de fichas clínicas; Doctoralia lanzó Noa Evidence (jul-2026, asistente de IA para profesionales); programa PRISMA IA 2.0 (dic-2025). [Vuelta 7] Sigue sin precios publicados de planes; un directorio la describe como gratuita y sin cuenta en su nivel básico (sin verificar). [Vuelta 8] Sin búsqueda nueva (saturado); sin cambios.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1082,11 +1082,11 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E132"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5560,7 +5560,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5570,24 +5570,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Integración con calendario del dispositivo</t>
+          <t>Check-in de admisión digital</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Permite añadir las citas a la app Calendario del teléfono (versión Pro).</t>
+          <t>Notificaciones de check-in de admisión y encuestas de salud previas a la atención.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Localización de centros médicos y farmacias</t>
+          <t>Integración con calendario del dispositivo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Localiza centros médicos y farmacias.</t>
+          <t>Permite añadir las citas a la app Calendario del teléfono (versión Pro).</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5614,7 +5614,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5624,17 +5624,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reserva de citas médicas</t>
+          <t>Localización de centros médicos y farmacias</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Reserva de horas en la institución.</t>
+          <t>Localiza centros médicos y farmacias.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Gestión completa de agenda dentro de la institución.</t>
+          <t>Reserva de horas en la institución.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5668,7 +5668,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Los pacientes pueden encontrar un profesional y reservar hora en el Portal de Agendamiento de Reservo, complemento de Clinia.</t>
+          <t>Gestión completa de agenda dentro de la institución.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5695,7 +5695,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5710,46 +5710,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Reserva de citas en hospitales integrados, dentro de Medipass.</t>
+          <t>Los pacientes pueden encontrar un profesional y reservar hora en el Portal de Agendamiento de Reservo, complemento de Clinia.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Compartición y consentimiento</t>
+          <t>Citas y agenda</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Acceso del profesional al historial del paciente</t>
+          <t>Reserva de citas médicas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>El médico puede revisar el historial e ingresar datos automáticamente.</t>
+          <t>Reserva de citas en hospitales integrados, dentro de Medipass.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5759,24 +5759,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Compartir con personas sin cuenta mediante clave segura</t>
+          <t>Acceso del profesional al historial del paciente</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Datos compartibles con personas sin cuenta mediante clave de acceso segura enviada por email.</t>
+          <t>El médico puede revisar el historial e ingresar datos automáticamente.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5786,17 +5786,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Compartir datos con cuidador o persona de confianza</t>
+          <t>Compartir con personas sin cuenta mediante clave segura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Comparte de forma privada datos de salud (actividad, corazón, movilidad) con una persona de confianza, eligiendo qué y con quién.</t>
+          <t>Datos compartibles con personas sin cuenta mediante clave de acceso segura enviada por email.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
@@ -5813,12 +5813,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+          <t>Compartir datos con cuidador o persona de confianza</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Permite compartir información con médicos, familia y amistades.</t>
+          <t>Comparte de forma privada datos de salud (actividad, corazón, movilidad) con una persona de confianza, eligiendo qué y con quién.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5845,19 +5845,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Comparte los documentos guardados con los profesionales en la consulta.</t>
+          <t>Permite compartir información con médicos, familia y amistades.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5872,19 +5872,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Comparte registros con familiares o profesionales.</t>
+          <t>Comparte los documentos guardados con los profesionales en la consulta.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5899,19 +5899,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Traspaso de registros a hospitales.</t>
+          <t>Comparte registros con familiares o profesionales.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Compartir información con profesionales de salud.</t>
+          <t>Traspaso de registros a hospitales.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Comparte información con cuidadores, maestros o profesionales de confianza.</t>
+          <t>Compartir información con profesionales de salud.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -5965,7 +5965,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5980,19 +5980,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Acceso de clínicos limitado en el tiempo.</t>
+          <t>Comparte información con cuidadores, maestros o profesionales de confianza.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6007,19 +6007,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>El usuario decide con qué profesionales comparte su información.</t>
+          <t>Acceso de clínicos limitado en el tiempo.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6034,19 +6034,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>El usuario autoriza a proveedores a acceder y usar sus datos de salud.</t>
+          <t>El usuario decide con qué profesionales comparte su información.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gestión de consentimiento sobre uso de datos</t>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>El usuario decide si sus registros se usan para análisis de big data.</t>
+          <t>El usuario autoriza a proveedores a acceder y usar sus datos de salud.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -6073,7 +6073,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6083,24 +6083,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ingreso de datos por profesional con consentimiento</t>
+          <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>El médico puede ingresar datos al historial con autorización del paciente.</t>
+          <t>El usuario decide si sus registros se usan para análisis de big data.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6110,39 +6110,39 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Red social con profesionales y familiares</t>
+          <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Interacción con médicos, dentistas, kinesiólogos, entrenadores y familiares dentro de la red.</t>
+          <t>El médico puede ingresar datos al historial con autorización del paciente.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Emergencia</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ficha de emergencia (alergias y medicación)</t>
+          <t>Red social con profesionales y familiares</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Disponibilidad del historial en situaciones de atención.</t>
+          <t>Interacción con médicos, dentistas, kinesiólogos, entrenadores y familiares dentro de la red.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -6154,7 +6154,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6169,19 +6169,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Acceso a datos clave del paciente en emergencias.</t>
+          <t>Disponibilidad del historial en situaciones de atención.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ficha de emergencia con alergias y medicación accesible rápidamente.</t>
+          <t>Acceso a datos clave del paciente en emergencias.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -6208,22 +6208,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Familia y dependientes</t>
+          <t>Emergencia</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Perfiles familiares / dependientes</t>
+          <t>Ficha de emergencia (alergias y medicación)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Vincula familiares a la cuenta.</t>
+          <t>Ficha de emergencia con alergias y medicación accesible rápidamente.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Rediseño de la pantalla de inicio para gestionar la salud propia y la de la familia en una sola vista.</t>
+          <t>Vincula familiares a la cuenta.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -6262,7 +6262,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6277,19 +6277,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Los padres pueden monitorear la salud de hijos pequeños.</t>
+          <t>Rediseño de la pantalla de inicio para gestionar la salud propia y la de la familia en una sola vista.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6304,19 +6304,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>El relanzamiento de Medipass (mar-2023) incorporó gestión de la salud de familiares.</t>
+          <t>Los padres pueden monitorear la salud de hijos pequeños.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6331,19 +6331,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Historial por perfil para cada miembro de la familia.</t>
+          <t>El relanzamiento de Medipass (mar-2023) incorporó gestión de la salud de familiares.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MiRedSalud (RedSalud)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6358,46 +6358,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Guardar y administrar historial propio y familiar.</t>
+          <t>Historial por perfil para cada miembro de la familia.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>MiRedSalud (RedSalud)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gestión documental</t>
+          <t>Familia y dependientes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Almacenamiento de documentos médicos</t>
+          <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sube estudios, imágenes, indicaciones médicas y notas personales; accesible en consulta o por terceros en emergencias.</t>
+          <t>Guardar y administrar historial propio y familiar.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6412,12 +6412,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Reúne recetas, diagnósticos y laboratorios en un solo lugar.</t>
+          <t>Sube estudios, imágenes, indicaciones médicas y notas personales; accesible en consulta o por terceros en emergencias.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Guarda en un solo lugar exámenes, recetas, órdenes y certificados médicos.</t>
+          <t>Reúne recetas, diagnósticos y laboratorios en un solo lugar.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -6451,7 +6451,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6466,19 +6466,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Organiza registros con carpetas y etiquetas.</t>
+          <t>Guarda en un solo lugar exámenes, recetas, órdenes y certificados médicos.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6493,19 +6493,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Almacena documentos clínicos del usuario en la app.</t>
+          <t>Organiza registros con carpetas y etiquetas.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6520,19 +6520,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Administra fechas, prescripciones, archivos y citas desde la app.</t>
+          <t>Almacena documentos clínicos del usuario en la app.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6542,24 +6542,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Almacenamiento de recetas</t>
+          <t>Almacenamiento de documentos médicos</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ver y descargar recetas, órdenes de examen y derivaciones.</t>
+          <t>Administra fechas, prescripciones, archivos y citas desde la app.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Guarda recetas digitales.</t>
+          <t>Ver y descargar recetas, órdenes de examen y derivaciones.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -6596,12 +6596,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Búsqueda y filtros de documentos</t>
+          <t>Almacenamiento de recetas</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Guarda resultados de laboratorio, imágenes y PDFs; búsqueda y filtros.</t>
+          <t>Guarda recetas digitales.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6613,7 +6613,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6623,24 +6623,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Emisión de certificados médicos</t>
+          <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>La ficha de la app incluye consulta de chequeos de salud y emisión de certificados médicos.</t>
+          <t>Guarda resultados de laboratorio, imágenes y PDFs; búsqueda y filtros.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6650,24 +6650,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Importación de órdenes/solicitudes médicas</t>
+          <t>Emisión de certificados médicos</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Descarga/genera órdenes médicas digitales.</t>
+          <t>La ficha de la app incluye consulta de chequeos de salud y emisión de certificados médicos.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Importa solicitudes (órdenes) médicas a la app.</t>
+          <t>Descarga/genera órdenes médicas digitales.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6694,7 +6694,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Notificación y envío de resultados</t>
+          <t>Importación de órdenes/solicitudes médicas</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Avisa cuando hay exámenes/documentos disponibles; resultados de laboratorio y anatomía patológica compartibles por email o WhatsApp.</t>
+          <t>Importa solicitudes (órdenes) médicas a la app.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6721,7 +6721,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6731,44 +6731,44 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Recepción de documentos desde terceros</t>
+          <t>Notificación y envío de resultados</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Desde feb-2016, la administradora de tarjetas ClinCard entregaba contratos y documentos a sus clientes dentro de la plataforma.</t>
+          <t>Avisa cuando hay exámenes/documentos disponibles; resultados de laboratorio y anatomía patológica compartibles por email o WhatsApp.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Historial institucional (solo datos de la propia red)</t>
+          <t>Recepción de documentos desde terceros</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ve historial de esa institución.</t>
+          <t>Desde feb-2016, la administradora de tarjetas ClinCard entregaba contratos y documentos a sus clientes dentro de la plataforma.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Historial institucional de consultas, urgencias y hospitalizaciones (solo datos de esa clínica).</t>
+          <t>Ve historial de esa institución.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6802,7 +6802,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MiRedSalud (RedSalud)</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Acceso a información clínica de la red.</t>
+          <t>Historial institucional de consultas, urgencias y hospitalizaciones (solo datos de esa clínica).</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6829,7 +6829,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MiRedSalud (RedSalud)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6839,24 +6839,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Información clínica unificada.</t>
+          <t>Acceso a información clínica de la red.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6871,19 +6871,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>El usuario registra sus antecedentes médicos en la app.</t>
+          <t>Información clínica unificada.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6898,19 +6898,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Centraliza el historial médico personal en el móvil.</t>
+          <t>El usuario registra sus antecedentes médicos en la app.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6925,19 +6925,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Permite compilar datos de vida/salud, gestionarlos y pasarlos a instituciones médicas.</t>
+          <t>Centraliza el historial médico personal en el móvil.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6952,19 +6952,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Centralizar registros y monitoreo desde el móvil.</t>
+          <t>Permite compilar datos de vida/salud, gestionarlos y pasarlos a instituciones médicas.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6974,17 +6974,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Línea de tiempo de salud</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Línea de tiempo con medicación, exámenes, citas y dieta.</t>
+          <t>Centralizar registros y monitoreo desde el móvil.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Registra notas de medicación, exámenes (laboratorio e imagen), actividad física, recetas, dieta y citas.</t>
+          <t>Línea de tiempo con medicación, exámenes, citas y dieta.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7018,7 +7018,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7028,12 +7028,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas</t>
+          <t>Línea de tiempo de salud</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas.</t>
+          <t>Registra notas de medicación, exámenes (laboratorio e imagen), actividad física, recetas, dieta y citas.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -7045,7 +7045,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7055,39 +7055,39 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seguimiento de visitas, gastos y seguros</t>
+          <t>Registro de alergias y vacunas</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>App gratuita para seguir visitas al médico, facturas médicas, datos personales, seguros, inmunizaciones y medicamentos de farmacia.</t>
+          <t>Registro de alergias y vacunas.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Incentivos y monetización de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Recompensas / monetización de datos del usuario</t>
+          <t>Seguimiento de visitas, gastos y seguros</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Plan de convertir Medipass en superapp con gestión de salud diaria y mercado de datos, integrada con la EMR Dr.Palette.</t>
+          <t>App gratuita para seguir visitas al médico, facturas médicas, datos personales, seguros, inmunizaciones y medicamentos de farmacia.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7099,7 +7099,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Centros de investigación y farmacéuticas recompensarían con MedTokens a quienes compartan sus datos; no confirmado como ejecutado.</t>
+          <t>Plan de convertir Medipass en superapp con gestión de salud diaria y mercado de datos, integrada con la EMR Dr.Palette.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7126,7 +7126,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>El usuario puede agregar y monetizar sus datos; recompensas en cripto.</t>
+          <t>Centros de investigación y farmacéuticas recompensarían con MedTokens a quienes compartan sus datos; no confirmado como ejecutado.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7153,22 +7153,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Incentivos y monetización de datos</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Asistente de IA para profesionales de salud</t>
+          <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Producto para clínicos verificados de EE.UU. (gratis, abr-2026); desde 1-sep-2026 un plugin con nueve apps de fuentes públicas (investigación, ensayos, medicamentos, Medicare, prestadores), de solo lectura y sin acceso a fichas de pacientes.</t>
+          <t>El usuario puede agregar y monetizar sus datos; recompensas en cripto.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7180,7 +7180,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Coaching de salud con IA</t>
+          <t>Asistente de IA para profesionales de salud</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Coaching personalizado con IA.</t>
+          <t>Producto para clínicos verificados de EE.UU. (gratis, abr-2026); desde 1-sep-2026 un plugin con nueve apps de fuentes públicas (investigación, ensayos, medicamentos, Medicare, prestadores), de solo lectura y sin acceso a fichas de pacientes.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7207,7 +7207,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Detección de patrones en métricas de salud con IA</t>
+          <t>Coaching de salud con IA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Interpreta datos de Apple Health y registros en contexto y detecta cambios.</t>
+          <t>Coaching personalizado con IA.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7234,7 +7234,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Detecta patrones entre métricas de salud y fitness.</t>
+          <t>Interpreta datos de Apple Health y registros en contexto y detecta cambios.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7261,7 +7261,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
+          <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Explica resultados complejos en lenguaje simple.</t>
+          <t>Detecta patrones entre métricas de salud y fitness.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Desde 28-sep-2026, en la pestaña Health se puede elegir un gráfico, métrica o registro y obtener explicaciones basadas en los datos conectados.</t>
+          <t>Explica resultados complejos en lenguaje simple.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7315,7 +7315,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Explica exámenes en lenguaje simple.</t>
+          <t>Desde 28-sep-2026, en la pestaña Health se puede elegir un gráfico, métrica o registro y obtener explicaciones basadas en los datos conectados.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7342,7 +7342,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7357,19 +7357,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Interpreta exámenes de laboratorio.</t>
+          <t>Explica exámenes en lenguaje simple.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7379,24 +7379,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Orientación médica con IA</t>
+          <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mejora de jun-2026 (GPT-5.5 Instant): detecta cuándo puede requerirse atención urgente, pide contexto y explica la incertidumbre.</t>
+          <t>Interpreta exámenes de laboratorio.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7411,19 +7411,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Orientación médica instantánea mediante IA.</t>
+          <t>Mejora de jun-2026 (GPT-5.5 Instant): detecta cuándo puede requerirse atención urgente, pide contexto y explica la incertidumbre.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7433,24 +7433,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Preparación de consultas médicas con IA</t>
+          <t>Orientación médica con IA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Prepara preguntas para el médico.</t>
+          <t>Orientación médica instantánea mediante IA.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7477,7 +7477,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Resumen de historial con IA</t>
+          <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Resume instrucciones de atención.</t>
+          <t>Prepara preguntas para el médico.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7504,7 +7504,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Resume el historial del usuario.</t>
+          <t>Resume instrucciones de atención.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7531,22 +7531,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>API para apps de terceros</t>
+          <t>Resumen de historial con IA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>El usuario decide qué registros recibe cada app y si los nuevos se comparten automáticamente (por defecto pide permiso cada vez); ej. importar recetas a Medisafe.</t>
+          <t>Resume el historial del usuario.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
+          <t>API para apps de terceros</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Vista central de alergias, condiciones, vacunas, laboratorio, medicación, procedimientos y signos vitales.</t>
+          <t>El usuario decide qué registros recibe cada app y si los nuevos se comparten automáticamente (por defecto pide permiso cada vez); ej. importar recetas a Medisafe.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7585,7 +7585,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Conexión de historiales electrónicos y apps como Apple Health, MyFitnessPal, Peloton.</t>
+          <t>Vista central de alergias, condiciones, vacunas, laboratorio, medicación, procedimientos y signos vitales.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Acceso a historiales electrónicos de proveedores de EE.UU. vía b.well; solo EE.UU., sin plazo anunciado para Latinoamérica.</t>
+          <t>Conexión de historiales electrónicos y apps como Apple Health, MyFitnessPal, Peloton.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Además de b.well y Apple Health, vincula registros de One Medical y Function Health (solo EE.UU., Free/Go/Plus/Pro, web e iOS).</t>
+          <t>Acceso a historiales electrónicos de proveedores de EE.UU. vía b.well; solo EE.UU., sin plazo anunciado para Latinoamérica.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7666,7 +7666,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Acceso a resultados y registros de salud (beta, Pro/Max, EE.UU.).</t>
+          <t>Además de b.well y Apple Health, vincula registros de One Medical y Function Health (solo EE.UU., Free/Go/Plus/Pro, web e iOS).</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7693,7 +7693,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7708,19 +7708,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Datos desde profesionales/centros que usan Reservo (fichas clínicas, agenda, telemedicina).</t>
+          <t>Acceso a resultados y registros de salud (beta, Pro/Max, EE.UU.).</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7735,19 +7735,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tras autenticación simple, trae los últimos 3 años de historial de hospitales integrados (p. ej. Samsung Seoul, SNUH, Severance).</t>
+          <t>Datos desde profesionales/centros que usan Reservo (fichas clínicas, agenda, telemedicina).</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7762,19 +7762,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sincroniza resultados desde centros de salud y permite subir fotos o documentos de las solicitudes médicas.</t>
+          <t>Tras autenticación simple, trae los últimos 3 años de historial de hospitales integrados (p. ej. Samsung Seoul, SNUH, Severance).</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Reúne registros de hospitales, resultados de laboratorio y datos genómicos.</t>
+          <t>Sincroniza resultados desde centros de salud y permite subir fotos o documentos de las solicitudes médicas.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Analítica poblacional B2B</t>
+          <t>Agregación de registros de múltiples instituciones</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Analítica poblacional on-chain; integrada con Epic, Cerner, Meditech y Allscripts (B2B).</t>
+          <t>Reúne registros de hospitales, resultados de laboratorio y datos genómicos.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7828,7 +7828,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7838,24 +7838,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+          <t>Analítica poblacional B2B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Android, iOS y escritorio; médicos acceden a historias digitalizadas, envían estudios e indicaciones y organizan agenda.</t>
+          <t>Analítica poblacional on-chain; integrada con Epic, Cerner, Meditech y Allscripts (B2B).</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7870,19 +7870,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Disponible en App Store y Google Play. Reservo opera en Chile, México y Argentina y está certificada por FONASA y CENS.</t>
+          <t>Android, iOS y escritorio; médicos acceden a historias digitalizadas, envían estudios e indicaciones y organizan agenda.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Healfies</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7897,19 +7897,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Disponible en web, iOS y Android.</t>
+          <t>Disponible en App Store y Google Play. Reservo opera en Chile, México y Argentina y está certificada por FONASA y CENS.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Healfies</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7919,24 +7919,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Versión digital de los registros con acceso por móvil o web.</t>
+          <t>Disponible en web, iOS y Android.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7946,24 +7946,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Importación y exportación de datos</t>
+          <t>Historial médico centralizado</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Importar/exportar datos para compartir de forma segura con familias o cuidadores. Es MediPlanner Pro, de otro desarrollador (App Store MX, $39 MXN).</t>
+          <t>Versión digital de los registros con acceso por móvil o web.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7973,24 +7973,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Integración con EHR de proveedores</t>
+          <t>Importación y exportación de datos</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Según una AMA sin fecha, integraba dos sistemas de GP que cubren ~80% del mercado UK; no confirmado como ejecutado.</t>
+          <t>Importar/exportar datos para compartir de forma segura con familias o cuidadores. Es MediPlanner Pro, de otro desarrollador (App Store MX, $39 MXN).</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Integración con EHR de proveedores</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Integración beta en apps iOS/Android.</t>
+          <t>Según una AMA sin fecha, integraba dos sistemas de GP que cubren ~80% del mercado UK; no confirmado como ejecutado.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Integración beta con Health Connect en la app móvil; conectores de registros (HealthEx, Function) solo para Pro/Max en EE.UU.</t>
+          <t>Integración beta en apps iOS/Android.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8044,7 +8044,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
+          <t>Integración beta con Health Connect en la app móvil; conectores de registros (HealthEx, Function) solo para Pro/Max en EE.UU.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8071,22 +8071,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Gestión de lista de medicamentos</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Listas de medicamentos, vitaminas y suplementos con horarios; escaneo de etiqueta del frasco solo en EE.UU.</t>
+          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8098,7 +8098,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8108,24 +8108,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Importación automática de tratamientos desde receta digital</t>
+          <t>Gestión de lista de medicamentos</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Según la ficha de la App Store MX, los tratamientos llegan automáticamente desde la receta digital del médico (autodeclarado, sin verificar).</t>
+          <t>Listas de medicamentos, vitaminas y suplementos con horarios; escaneo de etiqueta del frasco solo en EE.UU.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8135,24 +8135,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
+          <t>Importación automática de tratamientos desde receta digital</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Recordatorios desde el app.</t>
+          <t>Según la ficha de la App Store MX, los tratamientos llegan automáticamente desde la receta digital del médico (autodeclarado, sin verificar).</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8167,19 +8167,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Recordatorios de citas/medicación.</t>
+          <t>Recordatorios desde el app.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8189,51 +8189,51 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Registro de tomas y adherencia al tratamiento</t>
+          <t>Recordatorios de medicación y citas</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Registro de cada toma y control de adherencia; gestiona medicamentos propios y de familiares.</t>
+          <t>Recordatorios de citas/medicación.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Comunidad de pacientes</t>
+          <t>Registro de tomas y adherencia al tratamiento</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Los usuarios con condiciones similares pueden preguntar, recibir recomendaciones y compartir experiencias.</t>
+          <t>Registro de cada toma y control de adherencia; gestiona medicamentos propios y de familiares.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8243,24 +8243,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Contenido educativo sobre salud</t>
+          <t>Comunidad de pacientes</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Busca que el paciente aprenda sobre sus enfermedades y sea más autónomo.</t>
+          <t>Los usuarios con condiciones similares pueden preguntar, recibir recomendaciones y compartir experiencias.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8270,24 +8270,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores</t>
+          <t>Contenido educativo sobre salud</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores de salud.</t>
+          <t>Busca que el paciente aprenda sobre sus enfermedades y sea más autónomo.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8297,24 +8297,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Datos de pasos, sueño, peso junto a registros.</t>
+          <t>Gráficas de evolución de indicadores de salud.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Panel de seguimiento de salud y bienestar</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>El relanzamiento de Medipass (mar-2023) agregó un panel para gestionar la información de salud del usuario.</t>
+          <t>Datos de pasos, sueño, peso junto a registros.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8341,7 +8341,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
+          <t>El relanzamiento de Medipass (mar-2023) agregó un panel para gestionar la información de salud del usuario.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8368,7 +8368,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Registro de nutrición</t>
+          <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Escaneo de etiquetas nutricionales con la cámara; según un análisis, no escribe en HealthKit.</t>
+          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seguimiento de salud femenina</t>
+          <t>Registro de nutrición</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Extiende el seguimiento de ciclo con perimenopausia y menopausia.</t>
+          <t>Escaneo de etiquetas nutricionales con la cámara; según un análisis, no escribe en HealthKit.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8422,7 +8422,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8432,51 +8432,51 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Valoración de profesionales</t>
+          <t>Seguimiento de salud femenina</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Calificación de la atención de profesionales con autorización previa, compartible con otros usuarios.</t>
+          <t>Extiende el seguimiento de ciclo con perimenopausia y menopausia.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Acceso mínimo por categorías de datos</t>
+          <t>Valoración de profesionales</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Claude solicita solo las categorías relevantes (p. ej. medicamentos o laboratorio) y no fichas completas; HealthEx agrega datos de más de 50.000 sistemas de salud de EE.UU.</t>
+          <t>Calificación de la atención de profesionales con autorización previa, compartible con otros usuarios.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8486,12 +8486,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Acceso mínimo por categorías de datos</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
+          <t>Claude solicita solo las categorías relevantes (p. ej. medicamentos o laboratorio) y no fichas completas; HealthEx agrega datos de más de 50.000 sistemas de salud de EE.UU.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Almacena huellas de datos médicos en un registro de solo escritura, sin guardar datos clínicos en cadena.</t>
+          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8530,7 +8530,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
+          <t>Almacena huellas de datos médicos en un registro de solo escritura, sin guardar datos clínicos en cadena.</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8557,7 +8557,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
+          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -8584,7 +8584,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso</t>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
+          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8611,7 +8611,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8626,19 +8626,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Almacenamiento seguro del historial con criterios de seguridad estrictos, comparable a apps bancarias.</t>
+          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cumplimiento regulatorio de salud y datos</t>
+          <t>Cifrado y control de acceso</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Reservo declara plataforma certificada por Fonasa y CENS, cumplimiento de estándares de telemedicina del Minsal y de la nueva ley chilena de datos personales (declaración de la empresa).</t>
+          <t>Almacenamiento seguro del historial con criterios de seguridad estrictos, comparable a apps bancarias.</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8665,7 +8665,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8675,24 +8675,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Gestión de consentimiento sobre uso de datos</t>
+          <t>Cumplimiento regulatorio de salud y datos</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Desde 14-sep-2026, las nuevas conexiones heredan la configuración global de plugins: ChatGPT puede usar datos de Health sin pedir permiso cada vez salvo acciones sensibles (web primero, móvil después).</t>
+          <t>Reservo declara plataforma certificada por Fonasa y CENS, cumplimiento de estándares de telemedicina del Minsal y de la nueva ley chilena de datos personales (declaración de la empresa).</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8702,12 +8702,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Identidad descentralizada (DID)</t>
+          <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Gestión de identificadores descentralizados en Panacea.</t>
+          <t>Desde 14-sep-2026, las nuevas conexiones heredan la configuración global de plugins: ChatGPT puede usar datos de Health sin pedir permiso cada vez salvo acciones sensibles (web primero, móvil después).</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8719,7 +8719,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
+          <t>Identidad descentralizada (DID)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
+          <t>Gestión de identificadores descentralizados en Panacea.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8746,7 +8746,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>El usuario activa y revoca permisos; los datos de salud compartidos se excluyen de la memoria de Claude y del entrenamiento.</t>
+          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8773,34 +8773,34 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Modelo freemium y suscripción</t>
+          <t>Privacidad reforzada para datos de salud</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Planes para personas y empresas.</t>
+          <t>El usuario activa y revoca permisos; los datos de salud compartidos se excluyen de la memoria de Claude y del entrenamiento.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8810,17 +8810,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Pagos con criptomoneda</t>
+          <t>Modelo freemium y suscripción</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Pago de consultas con token.</t>
+          <t>Planes para personas y empresas.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Piloto en New Malden (Londres): consultas por video pagables con tarjeta o con MedTokens.</t>
+          <t>Pago de consultas con token.</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8854,7 +8854,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8864,24 +8864,24 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Pagos dentro de la app</t>
+          <t>Pagos con criptomoneda</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Pagos dentro de la plataforma mediante la pasarela Flow (según resumen de entrevista de Pauta, oct-2024; esperada para mejorar la experiencia).</t>
+          <t>Piloto en New Malden (Londres): consultas por video pagables con tarjeta o con MedTokens.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8891,24 +8891,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
+          <t>Pagos dentro de la app</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
+          <t>Sección de notificaciones que avisa cuando hay una deuda disponible para pagar (fecha de la actualización desconocida).</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8918,17 +8918,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
+          <t>Pagos dentro de la app</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Reclamo de seguro médico (indemnización) desde la app, con verificación de autenticidad de los registros vía blockchain por la aseguradora.</t>
+          <t>Pagos dentro de la plataforma mediante la pasarela Flow (según resumen de entrevista de Pauta, oct-2024; esperada para mejorar la experiencia).</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -8940,17 +8940,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Telemedicina y atención remota</t>
+          <t>Seguros y pagos</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Mensajería paciente-institución</t>
+          <t>Reclamos y trámites con seguros</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Chat para consultas a hospitales, orientación simple de síntomas e información de tratamientos; comunicación bidireccional hospital-paciente (nov-2023).</t>
+          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8962,25 +8962,79 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Seguros y pagos</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Reclamo de seguro médico (indemnización) desde la app, con verificación de autenticidad de los registros vía blockchain por la aseguradora.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Telemedicina y atención remota</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Mensajería paciente-institución</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Chat para consultas a hospitales, orientación simple de síntomas e información de tratamientos; comunicación bidireccional hospital-paciente (nov-2023).</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
           <t>Medicalchain</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>Telemedicina y atención remota</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>Teleconsultas con GP.</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
@@ -8997,7 +9051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R68"/>
+  <dimension ref="A1:R69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9123,6 +9177,8 @@
           <t>Búsqueda de profesionales de salud</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9133,6 +9189,17 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2">
         <f>COUNTIF(C2:Q2,"✓")</f>
         <v/>
@@ -9154,11 +9221,24 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3">
         <f>COUNTIF(C3:Q3,"✓")</f>
         <v/>
@@ -9172,14 +9252,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Integración con calendario del dispositivo</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+          <t>Check-in de admisión digital</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4">
         <f>COUNTIF(C4:Q4,"✓")</f>
         <v/>
@@ -9193,14 +9287,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Localización de centros médicos y farmacias</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+          <t>Integración con calendario del dispositivo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5">
         <f>COUNTIF(C5:Q5,"✓")</f>
         <v/>
@@ -9214,24 +9322,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reserva de citas médicas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+          <t>Localización de centros médicos y farmacias</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6">
         <f>COUNTIF(C6:Q6,"✓")</f>
         <v/>
@@ -9240,19 +9352,41 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Compartición y consentimiento</t>
+          <t>Citas y agenda</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Acceso del profesional al historial del paciente</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>Reserva de citas médicas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7">
         <f>COUNTIF(C7:Q7,"✓")</f>
         <v/>
@@ -9266,14 +9400,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Compartir con personas sin cuenta mediante clave segura</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+          <t>Acceso del profesional al historial del paciente</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8">
         <f>COUNTIF(C8:Q8,"✓")</f>
         <v/>
@@ -9287,14 +9435,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Compartir datos con cuidador o persona de confianza</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+          <t>Compartir con personas sin cuenta mediante clave segura</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9">
         <f>COUNTIF(C9:Q9,"✓")</f>
         <v/>
@@ -9308,49 +9470,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Compartir información con profesionales (consentimiento del usuario)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+          <t>Compartir datos con cuidador o persona de confianza</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10">
         <f>COUNTIF(C10:Q10,"✓")</f>
         <v/>
@@ -9364,7 +9505,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gestión de consentimiento sobre uso de datos</t>
+          <t>Compartir información con profesionales (consentimiento del usuario)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -9372,6 +9535,26 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11">
         <f>COUNTIF(C11:Q11,"✓")</f>
         <v/>
@@ -9385,14 +9568,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ingreso de datos por profesional con consentimiento</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>Gestión de consentimiento sobre uso de datos</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12">
         <f>COUNTIF(C12:Q12,"✓")</f>
         <v/>
@@ -9406,14 +9603,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Red social con profesionales y familiares</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+          <t>Ingreso de datos por profesional con consentimiento</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13">
         <f>COUNTIF(C13:Q13,"✓")</f>
         <v/>
@@ -9422,29 +9633,33 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Emergencia</t>
+          <t>Compartición y consentimiento</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ficha de emergencia (alergias y medicación)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+          <t>Red social con profesionales y familiares</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14">
         <f>COUNTIF(C14:Q14,"✓")</f>
         <v/>
@@ -9453,39 +9668,41 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Familia y dependientes</t>
+          <t>Emergencia</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Perfiles familiares / dependientes</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+          <t>Ficha de emergencia (alergias y medicación)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15">
         <f>COUNTIF(C15:Q15,"✓")</f>
         <v/>
@@ -9494,15 +9711,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gestión documental</t>
+          <t>Familia y dependientes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Almacenamiento de documentos médicos</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+          <t>Perfiles familiares / dependientes</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -9512,21 +9731,29 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16">
         <f>COUNTIF(C16:Q16,"✓")</f>
         <v/>
@@ -9540,19 +9767,44 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Almacenamiento de recetas</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+          <t>Almacenamiento de documentos médicos</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17">
         <f>COUNTIF(C17:Q17,"✓")</f>
         <v/>
@@ -9566,14 +9818,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Búsqueda y filtros de documentos</t>
-        </is>
-      </c>
+          <t>Almacenamiento de recetas</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18">
         <f>COUNTIF(C18:Q18,"✓")</f>
         <v/>
@@ -9587,14 +9857,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Emisión de certificados médicos</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
+          <t>Búsqueda y filtros de documentos</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19">
         <f>COUNTIF(C19:Q19,"✓")</f>
         <v/>
@@ -9608,19 +9892,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Importación de órdenes/solicitudes médicas</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+          <t>Emisión de certificados médicos</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20">
         <f>COUNTIF(C20:Q20,"✓")</f>
         <v/>
@@ -9634,10 +9927,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Notificación y envío de resultados</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
+          <t>Importación de órdenes/solicitudes médicas</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -9655,14 +9966,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Recepción de documentos desde terceros</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+          <t>Notificación y envío de resultados</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22">
         <f>COUNTIF(C22:Q22,"✓")</f>
         <v/>
@@ -9671,24 +9996,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Historial y perfil clínico</t>
+          <t>Gestión documental</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Historial institucional (solo datos de la propia red)</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
+          <t>Recepción de documentos desde terceros</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23">
         <f>COUNTIF(C23:Q23,"✓")</f>
         <v/>
@@ -9702,34 +10036,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+          <t>Historial institucional (solo datos de la propia red)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24">
         <f>COUNTIF(C24:Q24,"✓")</f>
         <v/>
@@ -9743,10 +10075,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Línea de tiempo de salud</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -9764,14 +10126,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Registro de alergias y vacunas</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+          <t>Línea de tiempo de salud</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26">
         <f>COUNTIF(C26:Q26,"✓")</f>
         <v/>
@@ -9785,14 +10161,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Seguimiento de visitas, gastos y seguros</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
+          <t>Registro de alergias y vacunas</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27">
         <f>COUNTIF(C27:Q27,"✓")</f>
         <v/>
@@ -9801,29 +10191,33 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Incentivos y monetización de datos</t>
+          <t>Historial y perfil clínico</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Recompensas / monetización de datos del usuario</t>
-        </is>
-      </c>
+          <t>Seguimiento de visitas, gastos y seguros</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28">
         <f>COUNTIF(C28:Q28,"✓")</f>
         <v/>
@@ -9832,19 +10226,41 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Inteligencia artificial</t>
+          <t>Incentivos y monetización de datos</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Asistente de IA para profesionales de salud</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
+          <t>Recompensas / monetización de datos del usuario</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29">
         <f>COUNTIF(C29:Q29,"✓")</f>
         <v/>
@@ -9858,14 +10274,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Coaching de salud con IA</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
+          <t>Asistente de IA para profesionales de salud</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30">
         <f>COUNTIF(C30:Q30,"✓")</f>
         <v/>
@@ -9879,19 +10309,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Detección de patrones en métricas de salud con IA</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
+          <t>Coaching de salud con IA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31">
         <f>COUNTIF(C31:Q31,"✓")</f>
         <v/>
@@ -9905,9 +10344,18 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Interpretación de exámenes con IA</t>
-        </is>
-      </c>
+          <t>Detección de patrones en métricas de salud con IA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9918,11 +10366,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32">
         <f>COUNTIF(C32:Q32,"✓")</f>
         <v/>
@@ -9936,14 +10383,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Orientación médica con IA</t>
-        </is>
-      </c>
+          <t>Interpretación de exámenes con IA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9962,15 +10426,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Preparación de consultas médicas con IA</t>
-        </is>
-      </c>
+          <t>Orientación médica con IA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -9988,9 +10465,18 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Resumen de historial con IA</t>
-        </is>
-      </c>
+          <t>Preparación de consultas médicas con IA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10001,6 +10487,10 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35">
         <f>COUNTIF(C35:Q35,"✓")</f>
         <v/>
@@ -10009,19 +10499,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Interoperabilidad y fuentes de datos</t>
+          <t>Inteligencia artificial</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>API para apps de terceros</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
+          <t>Resumen de historial con IA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36">
         <f>COUNTIF(C36:Q36,"✓")</f>
         <v/>
@@ -10035,44 +10543,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Agregación de registros de múltiples instituciones</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
+          <t>API para apps de terceros</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37">
         <f>COUNTIF(C37:Q37,"✓")</f>
         <v/>
@@ -10086,14 +10578,52 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Analítica poblacional B2B</t>
-        </is>
-      </c>
+          <t>Agregación de registros de múltiples instituciones</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38">
         <f>COUNTIF(C38:Q38,"✓")</f>
         <v/>
@@ -10107,24 +10637,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
+          <t>Analítica poblacional B2B</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39">
         <f>COUNTIF(C39:Q39,"✓")</f>
         <v/>
@@ -10138,14 +10672,36 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Historial médico centralizado</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+          <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40">
         <f>COUNTIF(C40:Q40,"✓")</f>
         <v/>
@@ -10159,14 +10715,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Importación y exportación de datos</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
+          <t>Historial médico centralizado</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41">
         <f>COUNTIF(C41:Q41,"✓")</f>
         <v/>
@@ -10180,14 +10750,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Integración con EHR de proveedores</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+          <t>Importación y exportación de datos</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42">
         <f>COUNTIF(C42:Q42,"✓")</f>
         <v/>
@@ -10201,19 +10785,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
+          <t>Integración con EHR de proveedores</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43">
         <f>COUNTIF(C43:Q43,"✓")</f>
         <v/>
@@ -10222,19 +10815,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gestión de lista de medicamentos</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44">
         <f>COUNTIF(C44:Q44,"✓")</f>
         <v/>
@@ -10248,14 +10859,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Importación automática de tratamientos desde receta digital</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
+          <t>Gestión de lista de medicamentos</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45">
         <f>COUNTIF(C45:Q45,"✓")</f>
         <v/>
@@ -10269,19 +10894,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
+          <t>Importación automática de tratamientos desde receta digital</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46">
         <f>COUNTIF(C46:Q46,"✓")</f>
         <v/>
@@ -10295,14 +10929,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Registro de tomas y adherencia al tratamiento</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
+          <t>Recordatorios de medicación y citas</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47">
         <f>COUNTIF(C47:Q47,"✓")</f>
         <v/>
@@ -10311,19 +10963,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Comunidad de pacientes</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
+          <t>Registro de tomas y adherencia al tratamiento</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48">
         <f>COUNTIF(C48:Q48,"✓")</f>
         <v/>
@@ -10337,14 +11003,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Contenido educativo sobre salud</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+          <t>Comunidad de pacientes</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49">
         <f>COUNTIF(C49:Q49,"✓")</f>
         <v/>
@@ -10358,14 +11038,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
+          <t>Contenido educativo sobre salud</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50">
         <f>COUNTIF(C50:Q50,"✓")</f>
         <v/>
@@ -10379,14 +11073,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
+          <t>Gráficas de evolución de indicadores</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
       <c r="R51">
         <f>COUNTIF(C51:Q51,"✓")</f>
         <v/>
@@ -10400,19 +11108,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Panel de seguimiento de salud y bienestar</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
+          <t>Integración con wearables y apps de salud</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52">
         <f>COUNTIF(C52:Q52,"✓")</f>
         <v/>
@@ -10426,14 +11143,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Registro de nutrición</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
+          <t>Panel de seguimiento de salud y bienestar</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53">
         <f>COUNTIF(C53:Q53,"✓")</f>
         <v/>
@@ -10447,14 +11182,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Seguimiento de salud femenina</t>
-        </is>
-      </c>
+          <t>Registro de nutrición</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54">
         <f>COUNTIF(C54:Q54,"✓")</f>
         <v/>
@@ -10468,14 +11217,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Valoración de profesionales</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
+          <t>Seguimiento de salud femenina</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55">
         <f>COUNTIF(C55:Q55,"✓")</f>
         <v/>
@@ -10484,19 +11247,33 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Acceso mínimo por categorías de datos</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
+          <t>Valoración de profesionales</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56">
         <f>COUNTIF(C56:Q56,"✓")</f>
         <v/>
@@ -10510,24 +11287,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
+          <t>Acceso mínimo por categorías de datos</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57">
         <f>COUNTIF(C57:Q57,"✓")</f>
         <v/>
@@ -10541,19 +11322,36 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+          <t>Blockchain para integridad y trazabilidad de datos</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58">
         <f>COUNTIF(C58:Q58,"✓")</f>
         <v/>
@@ -10567,14 +11365,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cumplimiento regulatorio de salud y datos</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
+          <t>Cifrado y control de acceso</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
       <c r="R59">
         <f>COUNTIF(C59:Q59,"✓")</f>
         <v/>
@@ -10588,14 +11404,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gestión de consentimiento sobre uso de datos</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
+          <t>Cumplimiento regulatorio de salud y datos</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60">
         <f>COUNTIF(C60:Q60,"✓")</f>
         <v/>
@@ -10609,14 +11439,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Identidad descentralizada (DID)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
+          <t>Gestión de consentimiento sobre uso de datos</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61">
         <f>COUNTIF(C61:Q61,"✓")</f>
         <v/>
@@ -10630,19 +11474,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
+          <t>Identidad descentralizada (DID)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62">
         <f>COUNTIF(C62:Q62,"✓")</f>
         <v/>
@@ -10651,19 +11504,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Modelo freemium y suscripción</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
+          <t>Privacidad reforzada para datos de salud</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63">
         <f>COUNTIF(C63:Q63,"✓")</f>
         <v/>
@@ -10677,10 +11548,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pagos con criptomoneda</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+          <t>Modelo freemium y suscripción</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -10698,14 +11583,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pagos dentro de la app</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
+          <t>Pagos con criptomoneda</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
       <c r="R65">
         <f>COUNTIF(C65:Q65,"✓")</f>
         <v/>
@@ -10719,10 +11618,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
+          <t>Pagos dentro de la app</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -10735,19 +11652,33 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Telemedicina y atención remota</t>
+          <t>Seguros y pagos</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mensajería paciente-institución</t>
-        </is>
-      </c>
+          <t>Reclamos y trámites con seguros</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67">
         <f>COUNTIF(C67:Q67,"✓")</f>
         <v/>
@@ -10761,16 +11692,65 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Teleconsulta con profesionales</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+          <t>Mensajería paciente-institución</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68">
         <f>COUNTIF(C68:Q68,"✓")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Telemedicina y atención remota</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Teleconsulta con profesionales</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69">
+        <f>COUNTIF(C69:Q69,"✓")</f>
         <v/>
       </c>
     </row>
@@ -10785,7 +11765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -11050,6 +12030,13 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>VUELTA 8 COMPLETA (2026-10-24 12:15 UTC): Clinia, MiRedSalud y Mediko revisados sin búsqueda nueva (saturado). Contador de loops = 8 para todos, Revisado reiniciado a "No". func_norm (133 filas) y tabla_frecuencia (68 funcionalidades) regenerados. Vuelta 9 parte con Meedika, Infomed, MediPlanner, Clingot. Candidato a competidor sin agregar: HealthChain (Chile).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -513,12 +513,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar. [Vuelta 3] Sin novedades 2026 ni confirmación de la app Android en Google Play; usuarios actuales desconocidos. Nota de prensa no indica año de lanzamiento explícito. [Vuelta 4] Sin fuentes nuevas; portalinnova.cl no aparece en búsquedas. Sigue dependiendo de una sola nota de prensa. [Vuelta 5] Sin fuentes nuevas (ni entrevistas ni financiamiento); sigue dependiendo de una sola nota de prensa sin año explícito. [Vuelta 6] Sin ficha de Google Play ni fuentes nuevas; disponibilidad en Android sin confirmar. [Vuelta 7] Sin fuentes nuevas; no hay ficha oficial localizada. No confundir con apps de nombre parecido (Medika App, MEDDI, AI Medik). [Vuelta 8] Sin fuentes nuevas.</t>
+          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar. [Vuelta 3] Sin novedades 2026 ni confirmación de la app Android en Google Play; usuarios actuales desconocidos. Nota de prensa no indica año de lanzamiento explícito. [Vuelta 4] Sin fuentes nuevas; portalinnova.cl no aparece en búsquedas. Sigue dependiendo de una sola nota de prensa. [Vuelta 5] Sin fuentes nuevas (ni entrevistas ni financiamiento); sigue dependiendo de una sola nota de prensa sin año explícito. [Vuelta 6] Sin ficha de Google Play ni fuentes nuevas; disponibilidad en Android sin confirmar. [Vuelta 7] Sin fuentes nuevas; no hay ficha oficial localizada. No confundir con apps de nombre parecido (Medika App, MEDDI, AI Medik). [Vuelta 8] Sin fuentes nuevas. [Vuelta 9] Sin fuentes nuevas.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -526,7 +526,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -553,12 +553,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapa A] Fundada 2019 por Diego Ibarra, Andrés Fantuzzi y Gabriel Zamora. Lanzada mar-2021 en App Store y Play Store con 1.200 usuarios; planeaba nueva versión jul-2021 y ronda de US$500 mil. Objetivo: llevar el historial en el celular, acceso en emergencias, médico puede ingresar datos con consentimiento. Estado actual NO verificado (posible app inactiva). URL es la nota de prensa; sitio oficial por confirmar. [Vuelta 3] Sin evidencia posterior a 2021; relanzamiento previsto jul-2021 no confirmado. Probable app inactiva. [Vuelta 4] Sin cambios; sigue sin evidencia posterior a 2021. [Vuelta 5] Cofundador Andrés Fantuzzi es cardiólogo de la Clínica Santa María. Sin ronda de inversión ni relanzamiento confirmados; no confundir con Infomed de Cuba (portal del Minsap). [Vuelta 6] Sin búsqueda nueva (fuentes agotadas en vueltas 3-5); sin cambios. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin fuentes nuevas; relanzamiento de jul-2021 sigue sin confirmarse.</t>
+          <t>[DIRECTO · Chile · etapa A] Fundada 2019 por Diego Ibarra, Andrés Fantuzzi y Gabriel Zamora. Lanzada mar-2021 en App Store y Play Store con 1.200 usuarios; planeaba nueva versión jul-2021 y ronda de US$500 mil. Objetivo: llevar el historial en el celular, acceso en emergencias, médico puede ingresar datos con consentimiento. Estado actual NO verificado (posible app inactiva). URL es la nota de prensa; sitio oficial por confirmar. [Vuelta 3] Sin evidencia posterior a 2021; relanzamiento previsto jul-2021 no confirmado. Probable app inactiva. [Vuelta 4] Sin cambios; sigue sin evidencia posterior a 2021. [Vuelta 5] Cofundador Andrés Fantuzzi es cardiólogo de la Clínica Santa María. Sin ronda de inversión ni relanzamiento confirmados; no confundir con Infomed de Cuba (portal del Minsap). [Vuelta 6] Sin búsqueda nueva (fuentes agotadas en vueltas 3-5); sin cambios. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin fuentes nuevas; relanzamiento de jul-2021 sigue sin confirmarse. [Vuelta 9] Sin fuentes nuevas.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -593,12 +593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · México] Historial por perfil familiar, alergias, vacunas, recetas digitales, gráficas de evolución, agendamiento, compartir con profesionales. Gratis en App Store MX. Sin evidencia de uso en Chile. Cubre parte de la etapa C (familia). [Vuelta 3] Existen dos apps distintas: MediPlanner (gratis, Rym Solutions, MX, 3,7/5 con 3 calificaciones) y MediPlanner Pro (otro desarrollador, $39 MXN). Sin presencia verificada en Chile. [Vuelta 4] No pude confirmar el desarrollador de la versión gratuita (Rym Solutions no se repite en esta búsqueda). MediPlanner Pro (fichas BR/OM) guardaría datos solo en el dispositivo, sin nube; no confundir con MedPlanner/AskHEMI (otra empresa). [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Se reconfirma en la ficha de App Store MX que el desarrollador de la versión gratuita es Rym Solutions S. de R.L. de C.V. (3,7/5, 3 calificaciones); MediPlanner Pro no menciona a esa empresa, por lo que no se puede asegurar que sea el mismo desarrollador. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin búsqueda nueva (saturado).</t>
+          <t>[REGIONAL · México] Historial por perfil familiar, alergias, vacunas, recetas digitales, gráficas de evolución, agendamiento, compartir con profesionales. Gratis en App Store MX. Sin evidencia de uso en Chile. Cubre parte de la etapa C (familia). [Vuelta 3] Existen dos apps distintas: MediPlanner (gratis, Rym Solutions, MX, 3,7/5 con 3 calificaciones) y MediPlanner Pro (otro desarrollador, $39 MXN). Sin presencia verificada en Chile. [Vuelta 4] No pude confirmar el desarrollador de la versión gratuita (Rym Solutions no se repite en esta búsqueda). MediPlanner Pro (fichas BR/OM) guardaría datos solo en el dispositivo, sin nube; no confundir con MedPlanner/AskHEMI (otra empresa). [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Se reconfirma en la ficha de App Store MX que el desarrollador de la versión gratuita es Rym Solutions S. de R.L. de C.V. (3,7/5, 3 calificaciones); MediPlanner Pro no menciona a esa empresa, por lo que no se puede asegurar que sea el mismo desarrollador. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin búsqueda nueva (saturado). [Vuelta 9] Sin fuentes nuevas.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -606,7 +606,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · Argentina · débil] App para cargar antecedentes médicos propios. Única referencia: nota de opinión en grupoanimal.mx sin fecha verificada. Estado y sitio por confirmar. [Vuelta 3] Referencias de 2017 (apps4citizens, La Nación); sitio y precio no verificados; puede estar inactiva. [Vuelta 4] Sin fuentes nuevas. [Vuelta 5] Registro empresarial (indicadores.ar, datos a jul-2026) muestra CLINGOT S.A. activa en CABA, constituida el 4-abr-2016; no confirma que la app siga operando. Programa federal argentino de historias clínicas digitales como contexto regulatorio. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios. [Vuelta 7] Solo fuentes de 2017; sin evidencia nueva de operación más allá del registro societario. [Vuelta 8] Sin fuentes nuevas.</t>
+          <t>[REGIONAL · Argentina · débil] App para cargar antecedentes médicos propios. Única referencia: nota de opinión en grupoanimal.mx sin fecha verificada. Estado y sitio por confirmar. [Vuelta 3] Referencias de 2017 (apps4citizens, La Nación); sitio y precio no verificados; puede estar inactiva. [Vuelta 4] Sin fuentes nuevas. [Vuelta 5] Registro empresarial (indicadores.ar, datos a jul-2026) muestra CLINGOT S.A. activa en CABA, constituida el 4-abr-2016; no confirma que la app siga operando. Programa federal argentino de historias clínicas digitales como contexto regulatorio. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios. [Vuelta 7] Solo fuentes de 2017; sin evidencia nueva de operación más allá del registro societario. [Vuelta 8] Sin fuentes nuevas. [Vuelta 9] Sin fuentes nuevas.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9177,8 +9177,6 @@
           <t>Búsqueda de profesionales de salud</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9189,17 +9187,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2">
         <f>COUNTIF(C2:Q2,"✓")</f>
         <v/>
@@ -9221,24 +9208,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3">
         <f>COUNTIF(C3:Q3,"✓")</f>
         <v/>
@@ -9255,25 +9229,11 @@
           <t>Check-in de admisión digital</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4">
         <f>COUNTIF(C4:Q4,"✓")</f>
         <v/>
@@ -9290,25 +9250,11 @@
           <t>Integración con calendario del dispositivo</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5">
         <f>COUNTIF(C5:Q5,"✓")</f>
         <v/>
@@ -9325,25 +9271,11 @@
           <t>Localización de centros médicos y farmacias</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6">
         <f>COUNTIF(C6:Q6,"✓")</f>
         <v/>
@@ -9360,21 +9292,11 @@
           <t>Reserva de citas médicas</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9385,8 +9307,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7">
         <f>COUNTIF(C7:Q7,"✓")</f>
         <v/>
@@ -9403,25 +9323,11 @@
           <t>Acceso del profesional al historial del paciente</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8">
         <f>COUNTIF(C8:Q8,"✓")</f>
         <v/>
@@ -9438,25 +9344,11 @@
           <t>Compartir con personas sin cuenta mediante clave segura</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9">
         <f>COUNTIF(C9:Q9,"✓")</f>
         <v/>
@@ -9473,25 +9365,11 @@
           <t>Compartir datos con cuidador o persona de confianza</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10">
         <f>COUNTIF(C10:Q10,"✓")</f>
         <v/>
@@ -9513,13 +9391,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9545,16 +9421,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11">
         <f>COUNTIF(C11:Q11,"✓")</f>
         <v/>
@@ -9571,25 +9442,11 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12">
         <f>COUNTIF(C12:Q12,"✓")</f>
         <v/>
@@ -9606,25 +9463,11 @@
           <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13">
         <f>COUNTIF(C13:Q13,"✓")</f>
         <v/>
@@ -9641,25 +9484,11 @@
           <t>Red social con profesionales y familiares</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14">
         <f>COUNTIF(C14:Q14,"✓")</f>
         <v/>
@@ -9686,23 +9515,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15">
         <f>COUNTIF(C15:Q15,"✓")</f>
         <v/>
@@ -9719,8 +9536,6 @@
           <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9731,29 +9546,21 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16">
         <f>COUNTIF(C16:Q16,"✓")</f>
         <v/>
@@ -9775,8 +9582,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9792,19 +9597,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17">
         <f>COUNTIF(C17:Q17,"✓")</f>
         <v/>
@@ -9821,29 +9618,16 @@
           <t>Almacenamiento de recetas</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18">
         <f>COUNTIF(C18:Q18,"✓")</f>
         <v/>
@@ -9860,25 +9644,11 @@
           <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19">
         <f>COUNTIF(C19:Q19,"✓")</f>
         <v/>
@@ -9895,25 +9665,11 @@
           <t>Emisión de certificados médicos</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20">
         <f>COUNTIF(C20:Q20,"✓")</f>
         <v/>
@@ -9935,19 +9691,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9969,25 +9712,11 @@
           <t>Notificación y envío de resultados</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22">
         <f>COUNTIF(C22:Q22,"✓")</f>
         <v/>
@@ -10004,25 +9733,11 @@
           <t>Recepción de documentos desde terceros</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23">
         <f>COUNTIF(C23:Q23,"✓")</f>
         <v/>
@@ -10039,29 +9754,16 @@
           <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24">
         <f>COUNTIF(C24:Q24,"✓")</f>
         <v/>
@@ -10078,36 +9780,26 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10129,25 +9821,11 @@
           <t>Línea de tiempo de salud</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26">
         <f>COUNTIF(C26:Q26,"✓")</f>
         <v/>
@@ -10164,25 +9842,11 @@
           <t>Registro de alergias y vacunas</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27">
         <f>COUNTIF(C27:Q27,"✓")</f>
         <v/>
@@ -10199,25 +9863,11 @@
           <t>Seguimiento de visitas, gastos y seguros</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28">
         <f>COUNTIF(C28:Q28,"✓")</f>
         <v/>
@@ -10234,11 +9884,6 @@
           <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10254,13 +9899,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29">
         <f>COUNTIF(C29:Q29,"✓")</f>
         <v/>
@@ -10277,25 +9915,11 @@
           <t>Asistente de IA para profesionales de salud</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30">
         <f>COUNTIF(C30:Q30,"✓")</f>
         <v/>
@@ -10312,25 +9936,11 @@
           <t>Coaching de salud con IA</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31">
         <f>COUNTIF(C31:Q31,"✓")</f>
         <v/>
@@ -10347,15 +9957,6 @@
           <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10366,10 +9967,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32">
         <f>COUNTIF(C32:Q32,"✓")</f>
         <v/>
@@ -10386,15 +9983,6 @@
           <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10405,9 +9993,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10429,24 +10014,11 @@
           <t>Orientación médica con IA</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10468,15 +10040,6 @@
           <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10487,10 +10050,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35">
         <f>COUNTIF(C35:Q35,"✓")</f>
         <v/>
@@ -10507,15 +10066,6 @@
           <t>Resumen de historial con IA</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10526,10 +10076,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36">
         <f>COUNTIF(C36:Q36,"✓")</f>
         <v/>
@@ -10546,25 +10092,11 @@
           <t>API para apps de terceros</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37">
         <f>COUNTIF(C37:Q37,"✓")</f>
         <v/>
@@ -10586,10 +10118,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10600,7 +10128,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10616,14 +10143,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38">
         <f>COUNTIF(C38:Q38,"✓")</f>
         <v/>
@@ -10640,25 +10164,11 @@
           <t>Analítica poblacional B2B</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39">
         <f>COUNTIF(C39:Q39,"✓")</f>
         <v/>
@@ -10675,9 +10185,6 @@
           <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10688,20 +10195,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40">
         <f>COUNTIF(C40:Q40,"✓")</f>
         <v/>
@@ -10718,25 +10216,11 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41">
         <f>COUNTIF(C41:Q41,"✓")</f>
         <v/>
@@ -10753,25 +10237,11 @@
           <t>Importación y exportación de datos</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42">
         <f>COUNTIF(C42:Q42,"✓")</f>
         <v/>
@@ -10788,25 +10258,11 @@
           <t>Integración con EHR de proveedores</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43">
         <f>COUNTIF(C43:Q43,"✓")</f>
         <v/>
@@ -10823,29 +10279,16 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44">
         <f>COUNTIF(C44:Q44,"✓")</f>
         <v/>
@@ -10862,25 +10305,11 @@
           <t>Gestión de lista de medicamentos</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45">
         <f>COUNTIF(C45:Q45,"✓")</f>
         <v/>
@@ -10897,25 +10326,11 @@
           <t>Importación automática de tratamientos desde receta digital</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46">
         <f>COUNTIF(C46:Q46,"✓")</f>
         <v/>
@@ -10937,24 +10352,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47">
         <f>COUNTIF(C47:Q47,"✓")</f>
         <v/>
@@ -10971,25 +10373,11 @@
           <t>Registro de tomas y adherencia al tratamiento</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48">
         <f>COUNTIF(C48:Q48,"✓")</f>
         <v/>
@@ -11006,25 +10394,11 @@
           <t>Comunidad de pacientes</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49">
         <f>COUNTIF(C49:Q49,"✓")</f>
         <v/>
@@ -11041,25 +10415,11 @@
           <t>Contenido educativo sobre salud</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50">
         <f>COUNTIF(C50:Q50,"✓")</f>
         <v/>
@@ -11076,25 +10436,11 @@
           <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51">
         <f>COUNTIF(C51:Q51,"✓")</f>
         <v/>
@@ -11111,25 +10457,11 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52">
         <f>COUNTIF(C52:Q52,"✓")</f>
         <v/>
@@ -11146,11 +10478,6 @@
           <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11161,14 +10488,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
       <c r="R53">
         <f>COUNTIF(C53:Q53,"✓")</f>
         <v/>
@@ -11185,25 +10504,11 @@
           <t>Registro de nutrición</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54">
         <f>COUNTIF(C54:Q54,"✓")</f>
         <v/>
@@ -11220,25 +10525,11 @@
           <t>Seguimiento de salud femenina</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55">
         <f>COUNTIF(C55:Q55,"✓")</f>
         <v/>
@@ -11255,25 +10546,11 @@
           <t>Valoración de profesionales</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56">
         <f>COUNTIF(C56:Q56,"✓")</f>
         <v/>
@@ -11290,25 +10567,11 @@
           <t>Acceso mínimo por categorías de datos</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57">
         <f>COUNTIF(C57:Q57,"✓")</f>
         <v/>
@@ -11325,11 +10588,6 @@
           <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11345,13 +10603,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
       <c r="R58">
         <f>COUNTIF(C58:Q58,"✓")</f>
         <v/>
@@ -11368,29 +10619,16 @@
           <t>Cifrado y control de acceso</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
       <c r="R59">
         <f>COUNTIF(C59:Q59,"✓")</f>
         <v/>
@@ -11407,25 +10645,11 @@
           <t>Cumplimiento regulatorio de salud y datos</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
       <c r="R60">
         <f>COUNTIF(C60:Q60,"✓")</f>
         <v/>
@@ -11442,25 +10666,11 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
       <c r="R61">
         <f>COUNTIF(C61:Q61,"✓")</f>
         <v/>
@@ -11477,25 +10687,11 @@
           <t>Identidad descentralizada (DID)</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
       <c r="R62">
         <f>COUNTIF(C62:Q62,"✓")</f>
         <v/>
@@ -11512,15 +10708,6 @@
           <t>Privacidad reforzada para datos de salud</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11531,10 +10718,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
       <c r="R63">
         <f>COUNTIF(C63:Q63,"✓")</f>
         <v/>
@@ -11551,20 +10734,6 @@
           <t>Modelo freemium y suscripción</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11586,25 +10755,11 @@
           <t>Pagos con criptomoneda</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
       <c r="R65">
         <f>COUNTIF(C65:Q65,"✓")</f>
         <v/>
@@ -11621,24 +10776,11 @@
           <t>Pagos dentro de la app</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11660,25 +10802,11 @@
           <t>Reclamos y trámites con seguros</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
       <c r="R67">
         <f>COUNTIF(C67:Q67,"✓")</f>
         <v/>
@@ -11695,25 +10823,11 @@
           <t>Mensajería paciente-institución</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
       <c r="R68">
         <f>COUNTIF(C68:Q68,"✓")</f>
         <v/>
@@ -11730,25 +10844,11 @@
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
       <c r="R69">
         <f>COUNTIF(C69:Q69,"✓")</f>
         <v/>
@@ -11765,7 +10865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -12037,6 +11137,20 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Vuelta 9 (iter. 1, 2026-10-25 12:16 UTC): Meedika, Infomed, MediPlanner, Clingot verificados (+0 filas; saturado). Pendientes: Healfies, Patientory, MediBloc, Medicalchain, Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas, Clinia, MiRedSalud, Mediko.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CANDIDATO A COMPETIDOR (no agregado; decide el usuario): Medicyn (global). App de historial médico personal que guarda los datos solo en el dispositivo, sin cuentas ni rastreo; cubre condiciones, medicamentos, alergias y análisis; prueba gratuita de 7 días y pago único. Lanzada en Product Hunt el 12-jun-2026 (fuente: Product Hunt). Enfoque de privacidad local, relevante frente a la propuesta blockchain. Otros no agregados: DKV «Quiero cuidarme Más» v2.9 (España; historial médico compartido consultable por profesionales de cualquier centro; fecha sin confirmar).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B. [Vuelta 2] Lanzada simultáneamente en Brasil, Argentina y EE.UU.; permite compartir con no registrados vía clave por email. Sin novedades posteriores a 2016. [Vuelta 3] Sin evidencia de actividad reciente ni de cierre; Gust/Dealroom la listan en Florianópolis (10 empleados, healfies.com) sin fecha de actualización. Estado sin confirmar. [Vuelta 4] Sin Google Play localizado; no confundir con la app Healfy (otro producto). Sin novedades. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios. [Vuelta 7] Solo fuentes de 2015-2016; alianza con ClinCard (feb-2016). Sin evidencia de actividad reciente. [Vuelta 8] Sin fuentes nuevas.</t>
+          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B. [Vuelta 2] Lanzada simultáneamente en Brasil, Argentina y EE.UU.; permite compartir con no registrados vía clave por email. Sin novedades posteriores a 2016. [Vuelta 3] Sin evidencia de actividad reciente ni de cierre; Gust/Dealroom la listan en Florianópolis (10 empleados, healfies.com) sin fecha de actualización. Estado sin confirmar. [Vuelta 4] Sin Google Play localizado; no confundir con la app Healfy (otro producto). Sin novedades. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios. [Vuelta 7] Solo fuentes de 2015-2016; alianza con ClinCard (feb-2016). Sin evidencia de actividad reciente. [Vuelta 8] Sin fuentes nuevas. [Vuelta 9] Sin búsqueda nueva (saturado).</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain. [Vuelta 2] Sin noticias 2026 encontradas en búsqueda; sitio oficial bloqueado. [Vuelta 3] Búsqueda adicional solo devuelve hitos de 2017 (token sale US$7,2M) y 2019 (Serie A de US$5,3M, cierre no confirmado); sin datos 2025-26 propios. [Vuelta 4] App pública lanzada en la conferencia JP Morgan Healthcare (2019); red PTOYMatrix (blockchain HIPAA); socios reportados: StartUp Health y Kaiser Permanente (beta). Estado actual en App Store/Google Play sin confirmar. [Vuelta 5] Sin noticias 2026 del equipo. Token PTOY con capitalización de ~US$53K a fines de ago-2026 según Phantom (KuCoin discrepa en la circulación): señal de baja actividad, no prueba de cierre. Esto relativiza la actividad hasta abr-2026 mencionada en la ficha original. [Vuelta 6] Sin noticias posteriores a 2020 localizadas (hitos: token sale 2017, consorcio Hyperledger, alianza con Georgia State, Series A de US$5,3M vía R/GA Ventures, Neith con Prosper Healthtech en Birmingham). Estado actual desconocido. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin noticias 2025-26; en 2018 la oferta se dirigía a empresas de salud, con la versión individual planificada después.</t>
+          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain. [Vuelta 2] Sin noticias 2026 encontradas en búsqueda; sitio oficial bloqueado. [Vuelta 3] Búsqueda adicional solo devuelve hitos de 2017 (token sale US$7,2M) y 2019 (Serie A de US$5,3M, cierre no confirmado); sin datos 2025-26 propios. [Vuelta 4] App pública lanzada en la conferencia JP Morgan Healthcare (2019); red PTOYMatrix (blockchain HIPAA); socios reportados: StartUp Health y Kaiser Permanente (beta). Estado actual en App Store/Google Play sin confirmar. [Vuelta 5] Sin noticias 2026 del equipo. Token PTOY con capitalización de ~US$53K a fines de ago-2026 según Phantom (KuCoin discrepa en la circulación): señal de baja actividad, no prueba de cierre. Esto relativiza la actividad hasta abr-2026 mencionada en la ficha original. [Vuelta 6] Sin noticias posteriores a 2020 localizadas (hitos: token sale 2017, consorcio Hyperledger, alianza con Georgia State, Series A de US$5,3M vía R/GA Ventures, Neith con Prosper Healthtech en Birmingham). Estado actual desconocido. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin noticias 2025-26; en 2018 la oferta se dirigía a empresas de salud, con la versión individual planificada después. [Vuelta 9] Sin búsqueda nueva (saturado).</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain. [Vuelta 2] Panacea incluye DID, Append Only Log, IBC y PNFT; sin anuncios 2026 localizados. [Vuelta 3] Medipass: app en Corea con 20 hospitales/aseguradoras integrados (fecha de la lista desconocida) y plan 2022 de superapp con marketplace de datos; operación actual sin confirmar. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Medipass: ~400.000 usuarios acumulados (CEO, jun-2022); integración con aseguradoras Shinhan Life, Samsung Fire y Hyundai Marine (2020); renovación completa en mar-2023 (dashboard de salud, gestión familiar, certificados). Sin noticias 2026 encontradas. [Vuelta 6] Medipass 2023: comunicación bidireccional hospital-paciente y chat MediTalk; en 2019 fue seleccionada para el programa gubernamental de MyData médico con Samsung Fire y SNUH. Sin estrategia 2026 localizada. Meta declarada: usar Medipass como «identificación» de salud. [Vuelta 7] Una fuente sin fecha atribuye a Medipass más de 600.000 pacientes en 14 hospitales; MoU 2019 con Severance (plataforma de facturación de seguros y detección de falsificación de datos) y piloto con Massachusetts General Hospital. Sin datos 2025-26. [Vuelta 8] Sin noticias 2025-26.</t>
+          <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain. [Vuelta 2] Panacea incluye DID, Append Only Log, IBC y PNFT; sin anuncios 2026 localizados. [Vuelta 3] Medipass: app en Corea con 20 hospitales/aseguradoras integrados (fecha de la lista desconocida) y plan 2022 de superapp con marketplace de datos; operación actual sin confirmar. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Medipass: ~400.000 usuarios acumulados (CEO, jun-2022); integración con aseguradoras Shinhan Life, Samsung Fire y Hyundai Marine (2020); renovación completa en mar-2023 (dashboard de salud, gestión familiar, certificados). Sin noticias 2026 encontradas. [Vuelta 6] Medipass 2023: comunicación bidireccional hospital-paciente y chat MediTalk; en 2019 fue seleccionada para el programa gubernamental de MyData médico con Samsung Fire y SNUH. Sin estrategia 2026 localizada. Meta declarada: usar Medipass como «identificación» de salud. [Vuelta 7] Una fuente sin fecha atribuye a Medipass más de 600.000 pacientes en 14 hospitales; MoU 2019 con Severance (plataforma de facturación de seguros y detección de falsificación de datos) y piloto con Massachusetts General Hospital. Sin datos 2025-26. [Vuelta 8] Sin noticias 2025-26. [Vuelta 9] Sin búsqueda nueva (saturado).</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · Reino Unido · INACTIVO] Londres, 2017, Ethereum, con telemedicina. Piloto según registro de la UE (2020). Tracxn/PitchBook lo marcan fuera de operación (ago-2025). Solo caso de aprendizaje: no cuenta como competidor activo. [Vuelta 2] Token MTN deslistado de Bitfinex el 26-mar-2021; sin hallazgos de actividad posterior. [Vuelta 3] Seedtable la marca activa sin fuente; no hallé registro en Companies House. Sigue tratándose como caso de aprendizaje. [Vuelta 4] Pre-venta reportada de US$20M en MedTokens (un solo artículo secundario, sin verificar); modelo de token en revisión y exploración de security token según AMA; integraciones y servicios de 2019 sin confirmar. [Vuelta 5] Un agregador indica sitio medicalchain.com fuera de línea desde 15-feb-2025, último commit en GitHub hace ~3 años y proyecto en «fase de mantenimiento»; preventa de MedTokens reportada entre US$20M y US$24M (fuentes discrepan). Confirma tratarlo como inactivo. [Vuelta 6] Sin búsqueda nueva (revisada en vuelta 5; sitio fuera de línea desde feb-2025 según un agregador); sin cambios. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin fuentes nuevas; se mantiene como inactivo.</t>
+          <t>[BLOCKCHAIN · Reino Unido · INACTIVO] Londres, 2017, Ethereum, con telemedicina. Piloto según registro de la UE (2020). Tracxn/PitchBook lo marcan fuera de operación (ago-2025). Solo caso de aprendizaje: no cuenta como competidor activo. [Vuelta 2] Token MTN deslistado de Bitfinex el 26-mar-2021; sin hallazgos de actividad posterior. [Vuelta 3] Seedtable la marca activa sin fuente; no hallé registro en Companies House. Sigue tratándose como caso de aprendizaje. [Vuelta 4] Pre-venta reportada de US$20M en MedTokens (un solo artículo secundario, sin verificar); modelo de token en revisión y exploración de security token según AMA; integraciones y servicios de 2019 sin confirmar. [Vuelta 5] Un agregador indica sitio medicalchain.com fuera de línea desde 15-feb-2025, último commit en GitHub hace ~3 años y proyecto en «fase de mantenimiento»; preventa de MedTokens reportada entre US$20M y US$24M (fuentes discrepan). Confirma tratarlo como inactivo. [Vuelta 6] Sin búsqueda nueva (revisada en vuelta 5; sitio fuera de línea desde feb-2025 según un agregador); sin cambios. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin fuentes nuevas; se mantiene como inactivo. [Vuelta 9] Sin búsqueda nueva (saturado).</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -10865,7 +10865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -11151,6 +11151,20 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Vuelta 9 (iter. 2, 2026-10-26 12:21 UTC): Healfies, Patientory, MediBloc, Medicalchain verificados (+0 filas; saturado). Pendientes: Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas, Clinia, MiRedSalud, Mediko.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Ampliación ficha candidato Medicyn (iPhone; desarrollador Pranav Shirole): almacenamiento 100% local (SwiftData con protección de archivos), sin cuentas, nube ni rastreo; guarda condiciones, medicamentos, recetas, alergias, informes de laboratorio y cirugías; escaneo de documentos con IA, seguimiento de síntomas, recordatorios y hasta 6 familiares. Precio inconsistente entre fuentes (prueba de 7 días y pago único según Product Hunt; «gratis» según un directorio). Nota: la política de privacidad menciona suscripciones vía App Store, lo que contradice el «sin suscripciones».</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -833,12 +833,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Agrega registros clínicos vía FHIR; &gt;500 instituciones conectadas en EE.UU. (2018). Sin evidencia de disponibilidad en Chile. Incluida en el dispositivo. Amenaza si FHIR/IPS-CL se adopta en Chile. [Vuelta 2] Sin disponibilidad de registros clínicos en Chile (solo EE.UU., Reino Unido, Canadá). [Vuelta 3] iOS 27 (WWDC 8-jun-2026; publicado ~14-sep-2026): rediseño del app Health, menopausia, nutrición por cámara. El coach de salud con IA no se anunció. Sin ampliación de Health Records a Chile. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Sin ampliación de Health Records a Australia, Europa ni Latinoamérica (solo EE.UU., UK, Canadá). Funciones de dispositivo (apnea del sueño, prueba auditiva) sí se amplían a países latinoamericanos, pero no son registros clínicos. [Vuelta 6] Sin novedades de iOS 27.x localizadas. Health Records API permite compartir registros con apps de terceros con control por app; opción de enviar datos de uso a Apple. [Vuelta 7] Coach de salud con IA / Health+ de pago: solo rumores (Gurman), atrasado al menos a iOS 27; no confirmado ni anunciado. [Vuelta 8] Sin novedades.</t>
+          <t>[ADYACENTE · global] Agrega registros clínicos vía FHIR; &gt;500 instituciones conectadas en EE.UU. (2018). Sin evidencia de disponibilidad en Chile. Incluida en el dispositivo. Amenaza si FHIR/IPS-CL se adopta en Chile. [Vuelta 2] Sin disponibilidad de registros clínicos en Chile (solo EE.UU., Reino Unido, Canadá). [Vuelta 3] iOS 27 (WWDC 8-jun-2026; publicado ~14-sep-2026): rediseño del app Health, menopausia, nutrición por cámara. El coach de salud con IA no se anunció. Sin ampliación de Health Records a Chile. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Sin ampliación de Health Records a Australia, Europa ni Latinoamérica (solo EE.UU., UK, Canadá). Funciones de dispositivo (apnea del sueño, prueba auditiva) sí se amplían a países latinoamericanos, pero no son registros clínicos. [Vuelta 6] Sin novedades de iOS 27.x localizadas. Health Records API permite compartir registros con apps de terceros con control por app; opción de enviar datos de uso a Apple. [Vuelta 7] Coach de salud con IA / Health+ de pago: solo rumores (Gurman), atrasado al menos a iOS 27; no confirmado ni anunciado. [Vuelta 8] Sin novedades. [Vuelta 9] Sin novedades.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Lanzado 7-ene-2026. Conecta registros médicos; conectores solo en EE.UU. Dentro de suscripción del asistente. Fija la expectativa de consultar y resumir el historial. [Vuelta 2] Confirmado: registros solo EE.UU.; sin anuncios para Latinoamérica. Hay inconsistencia de fechas entre fuentes (7-ene-2026 lanzamiento vs. jul-2026 despliegue de registros). [Vuelta 3] Fechas aclaradas: presentación 7-ene-2026 (acceso limitado); despliegue de Health in ChatGPT con Apple Health y registros en EE.UU. el 23-jul-2026; mejora de salud jun-2026. Sin anuncios para Latinoamérica ni para sep-oct 2026. [Vuelta 4] Septiembre 2026: permisos por defecto para datos conectados (14-sep) y explicaciones por gráfico/métrica (28-sep); ChatGPT for Clinicians (abr-2026) para clínicos verificados de EE.UU. Más del 70% de usuarios de Health permite usar datos conectados sin pedir permiso (según OpenAI). Sigue solo EE.UU. [Vuelta 5] Nota de jul-2026: Health no está disponible en México, Android, modo de voz ni Codex; web e iOS en EE.UU., adultos con sesión iniciada. Sin anuncio para Chile ni Latinoamérica. [Vuelta 6] Última entrada de Health en las notas de OpenAI sigue siendo la del 23-jul-2026 (más cambios de sep); sin entradas de octubre localizadas. Health tab: laboratorios, medicamentos, actividad y sueño en una vista; solo EE.UU., web e iOS. [Vuelta 7] OpenAI afirma que más de 300 millones de personas usan ChatGPT cada semana para consultas de salud (dato de la empresa). No es una solución con cumplimiento HIPAA declarado. Sin novedades de oct-2026. [Vuelta 8] Sin novedades de fines de oct-2026.</t>
+          <t>[ADYACENTE · global] Lanzado 7-ene-2026. Conecta registros médicos; conectores solo en EE.UU. Dentro de suscripción del asistente. Fija la expectativa de consultar y resumir el historial. [Vuelta 2] Confirmado: registros solo EE.UU.; sin anuncios para Latinoamérica. Hay inconsistencia de fechas entre fuentes (7-ene-2026 lanzamiento vs. jul-2026 despliegue de registros). [Vuelta 3] Fechas aclaradas: presentación 7-ene-2026 (acceso limitado); despliegue de Health in ChatGPT con Apple Health y registros en EE.UU. el 23-jul-2026; mejora de salud jun-2026. Sin anuncios para Latinoamérica ni para sep-oct 2026. [Vuelta 4] Septiembre 2026: permisos por defecto para datos conectados (14-sep) y explicaciones por gráfico/métrica (28-sep); ChatGPT for Clinicians (abr-2026) para clínicos verificados de EE.UU. Más del 70% de usuarios de Health permite usar datos conectados sin pedir permiso (según OpenAI). Sigue solo EE.UU. [Vuelta 5] Nota de jul-2026: Health no está disponible en México, Android, modo de voz ni Codex; web e iOS en EE.UU., adultos con sesión iniciada. Sin anuncio para Chile ni Latinoamérica. [Vuelta 6] Última entrada de Health en las notas de OpenAI sigue siendo la del 23-jul-2026 (más cambios de sep); sin entradas de octubre localizadas. Health tab: laboratorios, medicamentos, actividad y sueño en una vista; solo EE.UU., web e iOS. [Vuelta 7] OpenAI afirma que más de 300 millones de personas usan ChatGPT cada semana para consultas de salud (dato de la empresa). No es una solución con cumplimiento HIPAA declarado. Sin novedades de oct-2026. [Vuelta 8] Sin novedades de fines de oct-2026. [Vuelta 9] Reporte de sep-2026: OpenAI conecta ChatGPT con Epic EHR para clínicos de EE.UU. (sin confirmar con fuente primaria). Sin novedades de oct-2026 para el consumidor.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -886,7 +886,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · global] Lanzado 11-ene-2026. Conectores solo en EE.UU., planes Pro/Max. Nota: producto de Anthropic, conflicto de interés al evaluarlo. [Vuelta 2] Sin cambios fuera de EE.UU. (HealthEx y Function para Pro/Max). [Vuelta 3] Sin anuncios posteriores a enero de 2026. Hoja de ruta de HealthEx (agendar, buscar prestadores, recetas) sin confirmar como lanzada. [Vuelta 4] Sin anuncios nuevos. Fuentes discrepan en el acceso (Pro/Max según Fortune y la mayoría; Pro/Team según Times of AI); sin evidencia de disponibilidad fuera de EE.UU. [Vuelta 5] Sin noticias de oct-2026; HealthEx agrega datos de &gt;50.000 sistemas de EE.UU. y Claude pide solo las categorías relevantes vía MCP. [Vuelta 6] Sin noticias posteriores a enero de 2026 localizadas. [Vuelta 7] Sin novedades posteriores a enero de 2026. [Vuelta 8] Sin novedades posteriores a enero de 2026.</t>
+          <t>[ADYACENTE · global] Lanzado 11-ene-2026. Conectores solo en EE.UU., planes Pro/Max. Nota: producto de Anthropic, conflicto de interés al evaluarlo. [Vuelta 2] Sin cambios fuera de EE.UU. (HealthEx y Function para Pro/Max). [Vuelta 3] Sin anuncios posteriores a enero de 2026. Hoja de ruta de HealthEx (agendar, buscar prestadores, recetas) sin confirmar como lanzada. [Vuelta 4] Sin anuncios nuevos. Fuentes discrepan en el acceso (Pro/Max según Fortune y la mayoría; Pro/Team según Times of AI); sin evidencia de disponibilidad fuera de EE.UU. [Vuelta 5] Sin noticias de oct-2026; HealthEx agrega datos de &gt;50.000 sistemas de EE.UU. y Claude pide solo las categorías relevantes vía MCP. [Vuelta 6] Sin noticias posteriores a enero de 2026 localizadas. [Vuelta 7] Sin novedades posteriores a enero de 2026. [Vuelta 8] Sin novedades posteriores a enero de 2026. [Vuelta 9] Sin novedades posteriores a enero de 2026.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -926,7 +926,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones. [Vuelta 2] App concreta: Mi Alemana Go (Clínica Alemana, Chile), con historial desde 2018, recetas, órdenes, familiar vinculado y resultados. [Vuelta 3] Búsqueda de otras clínicas (Las Condes, Santa María, UC Christus) sin ficha de app confirmada; solo canales digitales genéricos. [Vuelta 4] Mi Alemana Go: 3,1/5 con 137 calificaciones (App Store Chile), pantalla de inicio rediseñada para gestionar salud propia y familiar; sin evidencia de teleconsulta ni pagos en la app. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Sin búsqueda nueva; sin cambios. [Vuelta 7] Sin búsqueda nueva; sin cambios. [Vuelta 8] Mi Alemana Go: notificaciones de deuda pendiente, check-in de admisión y encuestas de salud; DF la describe como segundo paso de la estrategia digital de la clínica (registros de exámenes, indicaciones, historial y recetas). Otras apps de red: Mi Dávila (Red Dávila, gestión de citas en todos sus centros, según un directorio); Clínica Las Condes sin app confirmada.</t>
+          <t>[SUSTITUTO PARCIAL · Chile] Reservar hora, ver historial de esa institución, vincular familiar. Gratis; no consolida datos de otras instituciones. [Vuelta 2] App concreta: Mi Alemana Go (Clínica Alemana, Chile), con historial desde 2018, recetas, órdenes, familiar vinculado y resultados. [Vuelta 3] Búsqueda de otras clínicas (Las Condes, Santa María, UC Christus) sin ficha de app confirmada; solo canales digitales genéricos. [Vuelta 4] Mi Alemana Go: 3,1/5 con 137 calificaciones (App Store Chile), pantalla de inicio rediseñada para gestionar salud propia y familiar; sin evidencia de teleconsulta ni pagos en la app. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Sin búsqueda nueva; sin cambios. [Vuelta 7] Sin búsqueda nueva; sin cambios. [Vuelta 8] Mi Alemana Go: notificaciones de deuda pendiente, check-in de admisión y encuestas de salud; DF la describe como segundo paso de la estrategia digital de la clínica (registros de exámenes, indicaciones, historial y recetas). Otras apps de red: Mi Dávila (Red Dávila, gestión de citas en todos sus centros, según un directorio); Clínica Las Condes sin app confirmada. [Vuelta 9] Sin búsqueda nueva; sin cambios.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5398,6 +5398,38 @@
       <c r="F134" t="inlineStr">
         <is>
           <t>Ficha App Store Chile (Mi Alemana Go)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ChatGPT Health (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Interoperabilidad y fuentes de datos</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Conexión directa con Epic EHR para clínicos (reporte sep-2026)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Un reporte del 1-sep-2026 indica que OpenAI conecta ChatGPT directamente con los registros electrónicos Epic para clínicos de EE.UU.; lado profesional, no del paciente.</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Búsqueda web (Healthcare Brew, Becker's); sin confirmar con fuente primaria</t>
         </is>
       </c>
     </row>
@@ -10865,7 +10897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -11165,6 +11197,13 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Vuelta 9 (iter. 3, 2026-10-27 12:41 UTC): Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas verificados (+1 fila). Pendientes: Clinia, MiRedSalud, Mediko (cierran la vuelta 9 y regeneran func_norm/tabla_frecuencia).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -518,15 +518,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -558,15 +558,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -598,15 +598,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -638,15 +638,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -678,15 +678,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -718,15 +718,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -758,15 +758,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -798,15 +798,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -838,15 +838,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -878,15 +878,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -918,15 +918,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -958,15 +958,15 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar. [Vuelta 2] Confirmado por el CEO de Reservo (LinkedIn): app para pacientes en App Store y Google Play; guarda y comparte exámenes, recetas, órdenes y certificados. Fecha exacta de lanzamiento, precio y modelo de datos sin verificar. [Vuelta 3] Sin novedades de oct-2026. Reservo (Chile, México, Argentina) declara certificación Fonasa/CENS y cumplimiento de la nueva ley de datos personales; el Portal de Agendamiento de Reservo complementa a Clinia. Precio y modelo de datos sin verificar. [Vuelta 4] Una búsqueda adicional no encontró fuentes independientes sobre Clinia de Reservo (aparecen otras empresas llamadas Clinia); la evidencia sigue siendo la publicación del CEO en LinkedIn y notas de Reservo. Confianza media. [Vuelta 5] Sin fecha verificable del lanzamiento (publicación de LinkedIn del CEO sin fecha visible); existe otra empresa homónima en Brasil (Porto Alegre, IA para clínicas) que no es este producto. Sin funciones nuevas. [Vuelta 6] Sin novedades de oct-2026. Reservo declara &gt;36.500 profesionales y centros y ~14 millones de reservas al año (Chile, México, Argentina), sello CENS y certificación Fonasa (autodeclarado); la publicación del CEO pide ideas de nuevas funciones. Sigue sin fecha de lanzamiento verificable. [Vuelta 7] Sin novedades; sin datos verificables de descargas ni calificación. Reservo: fundada en 2015 según una fuente (otra indica 2017). No confundir con Clinia de Brasil. [Vuelta 8] Sin búsqueda nueva (saturado); sin cambios.</t>
+          <t>[DIRECTO · Chile · etapa A] App móvil anunciada en sep-2026 para centralizar recetas, diagnósticos y laboratorios en un solo lugar; respaldada por Reservo (tecnológica chilena desde 2015, software para profesionales y centros de salud). AMENAZA ALTA: Reservo ya tiene red de profesionales/centros que podrían alimentar el historial. Fuente: solo snippet de búsqueda (sitio bloqueado en este entorno); precio, funciones de compartir y sitio oficial por verificar. [Vuelta 2] Confirmado por el CEO de Reservo (LinkedIn): app para pacientes en App Store y Google Play; guarda y comparte exámenes, recetas, órdenes y certificados. Fecha exacta de lanzamiento, precio y modelo de datos sin verificar. [Vuelta 3] Sin novedades de oct-2026. Reservo (Chile, México, Argentina) declara certificación Fonasa/CENS y cumplimiento de la nueva ley de datos personales; el Portal de Agendamiento de Reservo complementa a Clinia. Precio y modelo de datos sin verificar. [Vuelta 4] Una búsqueda adicional no encontró fuentes independientes sobre Clinia de Reservo (aparecen otras empresas llamadas Clinia); la evidencia sigue siendo la publicación del CEO en LinkedIn y notas de Reservo. Confianza media. [Vuelta 5] Sin fecha verificable del lanzamiento (publicación de LinkedIn del CEO sin fecha visible); existe otra empresa homónima en Brasil (Porto Alegre, IA para clínicas) que no es este producto. Sin funciones nuevas. [Vuelta 6] Sin novedades de oct-2026. Reservo declara &gt;36.500 profesionales y centros y ~14 millones de reservas al año (Chile, México, Argentina), sello CENS y certificación Fonasa (autodeclarado); la publicación del CEO pide ideas de nuevas funciones. Sigue sin fecha de lanzamiento verificable. [Vuelta 7] Sin novedades; sin datos verificables de descargas ni calificación. Reservo: fundada en 2015 según una fuente (otra indica 2017). No confundir con Clinia de Brasil. [Vuelta 8] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 9] Sin búsqueda nueva (saturado); sin cambios.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1002,11 +1002,11 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis). [Vuelta 2] La búsqueda no encontró fuentes adicionales ni ficha de la app chilena (solo una app RedSalud de otro país); funciones sin confirmar. [Vuelta 3] Rankings de terceros la ubican como app médica gratuita nº 1 en App Store y Google Play Chile (fecha desconocida); sin descripción de funciones ni confirmación del desarrollador en Google Play. [Vuelta 4] Sin documentación oficial chilena localizada; las fichas con funciones (agendar, telemedicina, historial de hijos) corresponden a una app RedSalud de otro país. Quejas públicas 2020-21 sobre acceso en línea a resultados. Funciones de MiRedSalud sin confirmar. [Vuelta 5] Una búsqueda adicional no halló cobertura del lanzamiento de dic-2025 ni de la app chilena; solo apps de otras empresas Red Salud (Paraguay, Perú). Sigue sin confirmarse más allá de la nota de RedSalud. [Vuelta 6] Sin cobertura adicional; los resultados corresponden a la plataforma Red Salud de Paraguay (Interasistencia, ~350 especialistas, call center por WhatsApp), que no es la red chilena. Funciones de MiRedSalud sin confirmar. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin búsqueda nueva (saturado); sin cambios.</t>
+          <t>[SUSTITUTO PARCIAL · Chile] Nueva app móvil de la red RedSalud anunciada dic-2025: acceso a información clínica y servicios, guardar y administrar historial propio y familiar. Limitación: solo datos de la propia red; no consolida otras instituciones. Precio por verificar (probablemente gratis). [Vuelta 2] La búsqueda no encontró fuentes adicionales ni ficha de la app chilena (solo una app RedSalud de otro país); funciones sin confirmar. [Vuelta 3] Rankings de terceros la ubican como app médica gratuita nº 1 en App Store y Google Play Chile (fecha desconocida); sin descripción de funciones ni confirmación del desarrollador en Google Play. [Vuelta 4] Sin documentación oficial chilena localizada; las fichas con funciones (agendar, telemedicina, historial de hijos) corresponden a una app RedSalud de otro país. Quejas públicas 2020-21 sobre acceso en línea a resultados. Funciones de MiRedSalud sin confirmar. [Vuelta 5] Una búsqueda adicional no halló cobertura del lanzamiento de dic-2025 ni de la app chilena; solo apps de otras empresas Red Salud (Paraguay, Perú). Sigue sin confirmarse más allá de la nota de RedSalud. [Vuelta 6] Sin cobertura adicional; los resultados corresponden a la plataforma Red Salud de Paraguay (Interasistencia, ~350 especialistas, call center por WhatsApp), que no es la red chilena. Funciones de MiRedSalud sin confirmar. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 9] Sin búsqueda nueva (saturado); sin cambios.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc. [Vuelta 2] Sin precios ni planes vigentes localizados; sitio oficial bloqueado. [Vuelta 3] Pauta (oct-2024): su fundador, Tomás Riddell, dice que no reemplaza a médicos y apunta a lo ambulatorio y a la espera de derivación a especialidad en el sistema público. Financiamiento: fuentes discrepan (CLP 25M en dic-2023 según Bouncewatch; ~$40M según Descubre.vc). Precios vigentes sin verificar. [Vuelta 4] Entrevista oct-2024 menciona integración con la pasarela Flow. Sin novedades 2025-26 ni rondas verificadas; la cifra de US$40M de Bouncewatch es dudosa (perfil con 2 empleados). [Vuelta 5] CORRECCIÓN de financiamiento: Bouncewatch registra dos subvenciones (CLP 15M en ago-2022 y CLP 25M en dic-2023 = CLP 40M en total), no US$40M; 2 empleados; etapa Seed según Descubre.vc. No hay inversionistas de capital listados. [Vuelta 6] Sin noticias 2026 propias. Contexto: evento «IA y Salud en Chile 2026» (12-may) sobre regulación, datos personales e interoperabilidad de fichas clínicas; Doctoralia lanzó Noa Evidence (jul-2026, asistente de IA para profesionales); programa PRISMA IA 2.0 (dic-2025). [Vuelta 7] Sigue sin precios publicados de planes; un directorio la describe como gratuita y sin cuenta en su nivel básico (sin verificar). [Vuelta 8] Sin búsqueda nueva (saturado); sin cambios.</t>
+          <t>[ADYACENTE · Chile] Fundada 2022. Orientación médica inmediata, interpretación de exámenes y órdenes médicas digitales con IA; modelo freemium, suscripción y pago por servicio; menciona centralizar registros y monitoreo. Foco asistencial, no archivo personal; vigilar si añade historial. Grants por ~$40M según Descubre.vc. [Vuelta 2] Sin precios ni planes vigentes localizados; sitio oficial bloqueado. [Vuelta 3] Pauta (oct-2024): su fundador, Tomás Riddell, dice que no reemplaza a médicos y apunta a lo ambulatorio y a la espera de derivación a especialidad en el sistema público. Financiamiento: fuentes discrepan (CLP 25M en dic-2023 según Bouncewatch; ~$40M según Descubre.vc). Precios vigentes sin verificar. [Vuelta 4] Entrevista oct-2024 menciona integración con la pasarela Flow. Sin novedades 2025-26 ni rondas verificadas; la cifra de US$40M de Bouncewatch es dudosa (perfil con 2 empleados). [Vuelta 5] CORRECCIÓN de financiamiento: Bouncewatch registra dos subvenciones (CLP 15M en ago-2022 y CLP 25M en dic-2023 = CLP 40M en total), no US$40M; 2 empleados; etapa Seed según Descubre.vc. No hay inversionistas de capital listados. [Vuelta 6] Sin noticias 2026 propias. Contexto: evento «IA y Salud en Chile 2026» (12-may) sobre regulación, datos personales e interoperabilidad de fichas clínicas; Doctoralia lanzó Noa Evidence (jul-2026, asistente de IA para profesionales); programa PRISMA IA 2.0 (dic-2025). [Vuelta 7] Sigue sin precios publicados de planes; un directorio la describe como gratuita y sin cuenta en su nivel básico (sin verificar). [Vuelta 8] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 9] Sin búsqueda nueva (saturado); sin cambios.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1082,11 +1082,11 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8022,7 +8022,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Según una AMA sin fecha, integraba dos sistemas de GP que cubren ~80% del mercado UK; no confirmado como ejecutado.</t>
+          <t>Un reporte del 1-sep-2026 indica que OpenAI conecta ChatGPT directamente con los registros electrónicos Epic para clínicos de EE.UU.; lado profesional, no del paciente.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8049,7 +8049,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Integración con EHR de proveedores</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Integración beta en apps iOS/Android.</t>
+          <t>Según una AMA sin fecha, integraba dos sistemas de GP que cubren ~80% del mercado UK; no confirmado como ejecutado.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Integración beta con Health Connect en la app móvil; conectores de registros (HealthEx, Function) solo para Pro/Max en EE.UU.</t>
+          <t>Integración beta en apps iOS/Android.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8103,7 +8103,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
+          <t>Integración beta con Health Connect en la app móvil; conectores de registros (HealthEx, Function) solo para Pro/Max en EE.UU.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8130,22 +8130,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Medicación y recordatorios</t>
+          <t>Interoperabilidad y fuentes de datos</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Gestión de lista de medicamentos</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Listas de medicamentos, vitaminas y suplementos con horarios; escaneo de etiqueta del frasco solo en EE.UU.</t>
+          <t>Se integra con wearables y apps móviles populares y muestra vitales en un panel unificado.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8157,7 +8157,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8167,24 +8167,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Importación automática de tratamientos desde receta digital</t>
+          <t>Gestión de lista de medicamentos</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Según la ficha de la App Store MX, los tratamientos llegan automáticamente desde la receta digital del médico (autodeclarado, sin verificar).</t>
+          <t>Listas de medicamentos, vitaminas y suplementos con horarios; escaneo de etiqueta del frasco solo en EE.UU.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8194,24 +8194,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Recordatorios de medicación y citas</t>
+          <t>Importación automática de tratamientos desde receta digital</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Recordatorios desde el app.</t>
+          <t>Según la ficha de la App Store MX, los tratamientos llegan automáticamente desde la receta digital del médico (autodeclarado, sin verificar).</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Meedika</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8226,19 +8226,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Recordatorios de citas/medicación.</t>
+          <t>Recordatorios desde el app.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Meedika</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8248,51 +8248,51 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Registro de tomas y adherencia al tratamiento</t>
+          <t>Recordatorios de medicación y citas</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Registro de cada toma y control de adherencia; gestiona medicamentos propios y de familiares.</t>
+          <t>Recordatorios de citas/medicación.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Seguimiento y bienestar</t>
+          <t>Medicación y recordatorios</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Comunidad de pacientes</t>
+          <t>Registro de tomas y adherencia al tratamiento</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Los usuarios con condiciones similares pueden preguntar, recibir recomendaciones y compartir experiencias.</t>
+          <t>Registro de cada toma y control de adherencia; gestiona medicamentos propios y de familiares.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8302,24 +8302,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Contenido educativo sobre salud</t>
+          <t>Comunidad de pacientes</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Busca que el paciente aprenda sobre sus enfermedades y sea más autónomo.</t>
+          <t>Los usuarios con condiciones similares pueden preguntar, recibir recomendaciones y compartir experiencias.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MediPlanner</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8329,24 +8329,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores</t>
+          <t>Contenido educativo sobre salud</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Gráficas de evolución de indicadores de salud.</t>
+          <t>Busca que el paciente aprenda sobre sus enfermedades y sea más autónomo.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>MediPlanner</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8356,24 +8356,24 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Integración con wearables y apps de salud</t>
+          <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Datos de pasos, sueño, peso junto a registros.</t>
+          <t>Gráficas de evolución de indicadores de salud.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Panel de seguimiento de salud y bienestar</t>
+          <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>El relanzamiento de Medipass (mar-2023) agregó un panel para gestionar la información de salud del usuario.</t>
+          <t>Datos de pasos, sueño, peso junto a registros.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8400,7 +8400,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
+          <t>El relanzamiento de Medipass (mar-2023) agregó un panel para gestionar la información de salud del usuario.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8427,7 +8427,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Registro de nutrición</t>
+          <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Escaneo de etiquetas nutricionales con la cámara; según un análisis, no escribe en HealthKit.</t>
+          <t>Seguimiento de hábitos saludables y monitoreo de progreso.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seguimiento de salud femenina</t>
+          <t>Registro de nutrición</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Extiende el seguimiento de ciclo con perimenopausia y menopausia.</t>
+          <t>Escaneo de etiquetas nutricionales con la cámara; según un análisis, no escribe en HealthKit.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8481,7 +8481,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Clingot</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8491,51 +8491,51 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Valoración de profesionales</t>
+          <t>Seguimiento de salud femenina</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Calificación de la atención de profesionales con autorización previa, compartible con otros usuarios.</t>
+          <t>Extiende el seguimiento de ciclo con perimenopausia y menopausia.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Latam</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>Clingot</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Seguridad, privacidad y blockchain</t>
+          <t>Seguimiento y bienestar</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Acceso mínimo por categorías de datos</t>
+          <t>Valoración de profesionales</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Claude solicita solo las categorías relevantes (p. ej. medicamentos o laboratorio) y no fichas completas; HealthEx agrega datos de más de 50.000 sistemas de salud de EE.UU.</t>
+          <t>Calificación de la atención de profesionales con autorización previa, compartible con otros usuarios.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Latam</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Blockchain para integridad y trazabilidad de datos</t>
+          <t>Acceso mínimo por categorías de datos</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
+          <t>Claude solicita solo las categorías relevantes (p. ej. medicamentos o laboratorio) y no fichas completas; HealthEx agrega datos de más de 50.000 sistemas de salud de EE.UU.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Almacena huellas de datos médicos en un registro de solo escritura, sin guardar datos clínicos en cadena.</t>
+          <t>Blockchain propia (Cosmos SDK) para que el paciente almacene, use, actualice y transfiera sus registros; los datos no se guardan en la cadena, solo en el usuario, cifrados.</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8589,7 +8589,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
+          <t>Almacena huellas de datos médicos en un registro de solo escritura, sin guardar datos clínicos en cadena.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -8616,7 +8616,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Patientory</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
+          <t>Cada solicitud de acceso queda en un libro distribuido; acceso temporal por contratos inteligentes.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8643,7 +8643,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Apple Health (Health Records)</t>
+          <t>Patientory</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cifrado y control de acceso</t>
+          <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
+          <t>Registro respaldado en blockchain para seguridad y trazabilidad.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -8670,7 +8670,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Infomed</t>
+          <t>Apple Health (Health Records)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8685,19 +8685,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Almacenamiento seguro del historial con criterios de seguridad estrictos, comparable a apps bancarias.</t>
+          <t>Registros cifrados en el dispositivo, protegidos por Face ID/Touch ID/código.</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Clinia (Reservo)</t>
+          <t>Infomed</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cumplimiento regulatorio de salud y datos</t>
+          <t>Cifrado y control de acceso</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Reservo declara plataforma certificada por Fonasa y CENS, cumplimiento de estándares de telemedicina del Minsal y de la nueva ley chilena de datos personales (declaración de la empresa).</t>
+          <t>Almacenamiento seguro del historial con criterios de seguridad estrictos, comparable a apps bancarias.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8724,7 +8724,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>Clinia (Reservo)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8734,24 +8734,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Gestión de consentimiento sobre uso de datos</t>
+          <t>Cumplimiento regulatorio de salud y datos</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Desde 14-sep-2026, las nuevas conexiones heredan la configuración global de plugins: ChatGPT puede usar datos de Health sin pedir permiso cada vez salvo acciones sensibles (web primero, móvil después).</t>
+          <t>Reservo declara plataforma certificada por Fonasa y CENS, cumplimiento de estándares de telemedicina del Minsal y de la nueva ley chilena de datos personales (declaración de la empresa).</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Identidad descentralizada (DID)</t>
+          <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Gestión de identificadores descentralizados en Panacea.</t>
+          <t>Desde 14-sep-2026, las nuevas conexiones heredan la configuración global de plugins: ChatGPT puede usar datos de Health sin pedir permiso cada vez salvo acciones sensibles (web primero, móvil después).</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8778,7 +8778,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ChatGPT Health (OpenAI)</t>
+          <t>MediBloc</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Privacidad reforzada para datos de salud</t>
+          <t>Identidad descentralizada (DID)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
+          <t>Gestión de identificadores descentralizados en Panacea.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8805,7 +8805,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Claude for Healthcare (Anthropic)</t>
+          <t>ChatGPT Health (OpenAI)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>El usuario activa y revoca permisos; los datos de salud compartidos se excluyen de la memoria de Claude y del entrenamiento.</t>
+          <t>Chats y memoria de salud separados, no usados para entrenar modelos.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8832,34 +8832,34 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Claude for Healthcare (Anthropic)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Seguros y pagos</t>
+          <t>Seguridad, privacidad y blockchain</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Modelo freemium y suscripción</t>
+          <t>Privacidad reforzada para datos de salud</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Planes para personas y empresas.</t>
+          <t>El usuario activa y revoca permisos; los datos de salud compartidos se excluyen de la memoria de Claude y del entrenamiento.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Medicalchain</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8869,17 +8869,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Pagos con criptomoneda</t>
+          <t>Modelo freemium y suscripción</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Pago de consultas con token.</t>
+          <t>Planes para personas y empresas.</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -8901,7 +8901,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Piloto en New Malden (Londres): consultas por video pagables con tarjeta o con MedTokens.</t>
+          <t>Pago de consultas con token.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8913,7 +8913,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
+          <t>Medicalchain</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8923,24 +8923,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Pagos dentro de la app</t>
+          <t>Pagos con criptomoneda</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Sección de notificaciones que avisa cuando hay una deuda disponible para pagar (fecha de la actualización desconocida).</t>
+          <t>Piloto en New Malden (Londres): consultas por video pagables con tarjeta o con MedTokens.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Global</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Mediko</t>
+          <t>Apps de clínicas (ej. Clínica Alemana de Valdivia)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Pagos dentro de la plataforma mediante la pasarela Flow (según resumen de entrevista de Pauta, oct-2024; esperada para mejorar la experiencia).</t>
+          <t>Sección de notificaciones que avisa cuando hay una deuda disponible para pagar (fecha de la actualización desconocida).</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8967,7 +8967,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MediBloc</t>
+          <t>Mediko</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8977,17 +8977,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Reclamos y trámites con seguros</t>
+          <t>Pagos dentro de la app</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
+          <t>Pagos dentro de la plataforma mediante la pasarela Flow (según resumen de entrevista de Pauta, oct-2024; esperada para mejorar la experiencia).</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Chile</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Reclamo de seguro médico (indemnización) desde la app, con verificación de autenticidad de los registros vía blockchain por la aseguradora.</t>
+          <t>Simplifica el envío a aseguradoras sin gestionar papeles en hospitales.</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -9026,17 +9026,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Telemedicina y atención remota</t>
+          <t>Seguros y pagos</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Mensajería paciente-institución</t>
+          <t>Reclamos y trámites con seguros</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Chat para consultas a hospitales, orientación simple de síntomas e información de tratamientos; comunicación bidireccional hospital-paciente (nov-2023).</t>
+          <t>Reclamo de seguro médico (indemnización) desde la app, con verificación de autenticidad de los registros vía blockchain por la aseguradora.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -9048,25 +9048,52 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
+          <t>MediBloc</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Telemedicina y atención remota</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Mensajería paciente-institución</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Chat para consultas a hospitales, orientación simple de síntomas e información de tratamientos; comunicación bidireccional hospital-paciente (nov-2023).</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
           <t>Medicalchain</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>Telemedicina y atención remota</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>Teleconsultas con GP.</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
@@ -9209,6 +9236,8 @@
           <t>Búsqueda de profesionales de salud</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9219,6 +9248,17 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2">
         <f>COUNTIF(C2:Q2,"✓")</f>
         <v/>
@@ -9240,11 +9280,24 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3">
         <f>COUNTIF(C3:Q3,"✓")</f>
         <v/>
@@ -9261,11 +9314,25 @@
           <t>Check-in de admisión digital</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4">
         <f>COUNTIF(C4:Q4,"✓")</f>
         <v/>
@@ -9282,11 +9349,25 @@
           <t>Integración con calendario del dispositivo</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5">
         <f>COUNTIF(C5:Q5,"✓")</f>
         <v/>
@@ -9303,11 +9384,25 @@
           <t>Localización de centros médicos y farmacias</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6">
         <f>COUNTIF(C6:Q6,"✓")</f>
         <v/>
@@ -9324,11 +9419,21 @@
           <t>Reserva de citas médicas</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9339,6 +9444,8 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7">
         <f>COUNTIF(C7:Q7,"✓")</f>
         <v/>
@@ -9355,11 +9462,25 @@
           <t>Acceso del profesional al historial del paciente</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8">
         <f>COUNTIF(C8:Q8,"✓")</f>
         <v/>
@@ -9376,11 +9497,25 @@
           <t>Compartir con personas sin cuenta mediante clave segura</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9">
         <f>COUNTIF(C9:Q9,"✓")</f>
         <v/>
@@ -9397,11 +9532,25 @@
           <t>Compartir datos con cuidador o persona de confianza</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10">
         <f>COUNTIF(C10:Q10,"✓")</f>
         <v/>
@@ -9423,11 +9572,13 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9453,11 +9604,16 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11">
         <f>COUNTIF(C11:Q11,"✓")</f>
         <v/>
@@ -9474,11 +9630,25 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12">
         <f>COUNTIF(C12:Q12,"✓")</f>
         <v/>
@@ -9495,11 +9665,25 @@
           <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13">
         <f>COUNTIF(C13:Q13,"✓")</f>
         <v/>
@@ -9516,11 +9700,25 @@
           <t>Red social con profesionales y familiares</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14">
         <f>COUNTIF(C14:Q14,"✓")</f>
         <v/>
@@ -9547,11 +9745,23 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15">
         <f>COUNTIF(C15:Q15,"✓")</f>
         <v/>
@@ -9568,6 +9778,8 @@
           <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9578,21 +9790,29 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16">
         <f>COUNTIF(C16:Q16,"✓")</f>
         <v/>
@@ -9614,6 +9834,8 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9629,11 +9851,19 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17">
         <f>COUNTIF(C17:Q17,"✓")</f>
         <v/>
@@ -9650,16 +9880,29 @@
           <t>Almacenamiento de recetas</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18">
         <f>COUNTIF(C18:Q18,"✓")</f>
         <v/>
@@ -9676,11 +9919,25 @@
           <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19">
         <f>COUNTIF(C19:Q19,"✓")</f>
         <v/>
@@ -9697,11 +9954,25 @@
           <t>Emisión de certificados médicos</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20">
         <f>COUNTIF(C20:Q20,"✓")</f>
         <v/>
@@ -9723,6 +9994,19 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9744,11 +10028,25 @@
           <t>Notificación y envío de resultados</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22">
         <f>COUNTIF(C22:Q22,"✓")</f>
         <v/>
@@ -9765,11 +10063,25 @@
           <t>Recepción de documentos desde terceros</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23">
         <f>COUNTIF(C23:Q23,"✓")</f>
         <v/>
@@ -9786,16 +10098,29 @@
           <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24">
         <f>COUNTIF(C24:Q24,"✓")</f>
         <v/>
@@ -9812,26 +10137,36 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9853,11 +10188,25 @@
           <t>Línea de tiempo de salud</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26">
         <f>COUNTIF(C26:Q26,"✓")</f>
         <v/>
@@ -9874,11 +10223,25 @@
           <t>Registro de alergias y vacunas</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27">
         <f>COUNTIF(C27:Q27,"✓")</f>
         <v/>
@@ -9895,11 +10258,25 @@
           <t>Seguimiento de visitas, gastos y seguros</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28">
         <f>COUNTIF(C28:Q28,"✓")</f>
         <v/>
@@ -9916,6 +10293,11 @@
           <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9931,6 +10313,13 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29">
         <f>COUNTIF(C29:Q29,"✓")</f>
         <v/>
@@ -9947,11 +10336,25 @@
           <t>Asistente de IA para profesionales de salud</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30">
         <f>COUNTIF(C30:Q30,"✓")</f>
         <v/>
@@ -9968,11 +10371,25 @@
           <t>Coaching de salud con IA</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31">
         <f>COUNTIF(C31:Q31,"✓")</f>
         <v/>
@@ -9989,6 +10406,15 @@
           <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9999,6 +10425,10 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32">
         <f>COUNTIF(C32:Q32,"✓")</f>
         <v/>
@@ -10015,6 +10445,15 @@
           <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10025,6 +10464,9 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10046,11 +10488,24 @@
           <t>Orientación médica con IA</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10072,6 +10527,15 @@
           <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10082,6 +10546,10 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35">
         <f>COUNTIF(C35:Q35,"✓")</f>
         <v/>
@@ -10098,6 +10566,15 @@
           <t>Resumen de historial con IA</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10108,6 +10585,10 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36">
         <f>COUNTIF(C36:Q36,"✓")</f>
         <v/>
@@ -10124,11 +10605,25 @@
           <t>API para apps de terceros</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37">
         <f>COUNTIF(C37:Q37,"✓")</f>
         <v/>
@@ -10150,6 +10645,10 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10160,6 +10659,7 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10175,11 +10675,14 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38">
         <f>COUNTIF(C38:Q38,"✓")</f>
         <v/>
@@ -10196,11 +10699,25 @@
           <t>Analítica poblacional B2B</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39">
         <f>COUNTIF(C39:Q39,"✓")</f>
         <v/>
@@ -10217,6 +10734,9 @@
           <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10227,11 +10747,20 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40">
         <f>COUNTIF(C40:Q40,"✓")</f>
         <v/>
@@ -10248,11 +10777,25 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41">
         <f>COUNTIF(C41:Q41,"✓")</f>
         <v/>
@@ -10269,11 +10812,25 @@
           <t>Importación y exportación de datos</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42">
         <f>COUNTIF(C42:Q42,"✓")</f>
         <v/>
@@ -10290,11 +10847,29 @@
           <t>Integración con EHR de proveedores</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43">
         <f>COUNTIF(C43:Q43,"✓")</f>
         <v/>
@@ -10311,16 +10886,29 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44">
         <f>COUNTIF(C44:Q44,"✓")</f>
         <v/>
@@ -10337,11 +10925,25 @@
           <t>Gestión de lista de medicamentos</t>
         </is>
       </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45">
         <f>COUNTIF(C45:Q45,"✓")</f>
         <v/>
@@ -10358,11 +10960,25 @@
           <t>Importación automática de tratamientos desde receta digital</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46">
         <f>COUNTIF(C46:Q46,"✓")</f>
         <v/>
@@ -10384,11 +11000,24 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47">
         <f>COUNTIF(C47:Q47,"✓")</f>
         <v/>
@@ -10405,11 +11034,25 @@
           <t>Registro de tomas y adherencia al tratamiento</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48">
         <f>COUNTIF(C48:Q48,"✓")</f>
         <v/>
@@ -10426,11 +11069,25 @@
           <t>Comunidad de pacientes</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49">
         <f>COUNTIF(C49:Q49,"✓")</f>
         <v/>
@@ -10447,11 +11104,25 @@
           <t>Contenido educativo sobre salud</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50">
         <f>COUNTIF(C50:Q50,"✓")</f>
         <v/>
@@ -10468,11 +11139,25 @@
           <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
       <c r="R51">
         <f>COUNTIF(C51:Q51,"✓")</f>
         <v/>
@@ -10489,11 +11174,25 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52">
         <f>COUNTIF(C52:Q52,"✓")</f>
         <v/>
@@ -10510,6 +11209,11 @@
           <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10520,6 +11224,14 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53">
         <f>COUNTIF(C53:Q53,"✓")</f>
         <v/>
@@ -10536,11 +11248,25 @@
           <t>Registro de nutrición</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54">
         <f>COUNTIF(C54:Q54,"✓")</f>
         <v/>
@@ -10557,11 +11283,25 @@
           <t>Seguimiento de salud femenina</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55">
         <f>COUNTIF(C55:Q55,"✓")</f>
         <v/>
@@ -10578,11 +11318,25 @@
           <t>Valoración de profesionales</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56">
         <f>COUNTIF(C56:Q56,"✓")</f>
         <v/>
@@ -10599,11 +11353,25 @@
           <t>Acceso mínimo por categorías de datos</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57">
         <f>COUNTIF(C57:Q57,"✓")</f>
         <v/>
@@ -10620,6 +11388,11 @@
           <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10635,6 +11408,13 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58">
         <f>COUNTIF(C58:Q58,"✓")</f>
         <v/>
@@ -10651,16 +11431,29 @@
           <t>Cifrado y control de acceso</t>
         </is>
       </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
       <c r="R59">
         <f>COUNTIF(C59:Q59,"✓")</f>
         <v/>
@@ -10677,11 +11470,25 @@
           <t>Cumplimiento regulatorio de salud y datos</t>
         </is>
       </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60">
         <f>COUNTIF(C60:Q60,"✓")</f>
         <v/>
@@ -10698,11 +11505,25 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61">
         <f>COUNTIF(C61:Q61,"✓")</f>
         <v/>
@@ -10719,11 +11540,25 @@
           <t>Identidad descentralizada (DID)</t>
         </is>
       </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62">
         <f>COUNTIF(C62:Q62,"✓")</f>
         <v/>
@@ -10740,6 +11575,15 @@
           <t>Privacidad reforzada para datos de salud</t>
         </is>
       </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10750,6 +11594,10 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63">
         <f>COUNTIF(C63:Q63,"✓")</f>
         <v/>
@@ -10766,6 +11614,20 @@
           <t>Modelo freemium y suscripción</t>
         </is>
       </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10787,11 +11649,25 @@
           <t>Pagos con criptomoneda</t>
         </is>
       </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
       <c r="R65">
         <f>COUNTIF(C65:Q65,"✓")</f>
         <v/>
@@ -10808,11 +11684,24 @@
           <t>Pagos dentro de la app</t>
         </is>
       </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10834,11 +11723,25 @@
           <t>Reclamos y trámites con seguros</t>
         </is>
       </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67">
         <f>COUNTIF(C67:Q67,"✓")</f>
         <v/>
@@ -10855,11 +11758,25 @@
           <t>Mensajería paciente-institución</t>
         </is>
       </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68">
         <f>COUNTIF(C68:Q68,"✓")</f>
         <v/>
@@ -10876,11 +11793,25 @@
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
       <c r="R69">
         <f>COUNTIF(C69:Q69,"✓")</f>
         <v/>
@@ -10897,7 +11828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -11204,6 +12135,13 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>VUELTA 9 COMPLETA (2026-10-28 12:21 UTC): Clinia, MiRedSalud y Mediko revisados sin búsqueda nueva (saturado). Contador de loops = 9 para todos, Revisado reiniciado a "No". func_norm (134 filas) y tabla_frecuencia (68 funcionalidades) regenerados. Vuelta 10 parte con Meedika, Infomed, MediPlanner, Clingot. Candidatos sin agregar: HealthChain (Chile), Medicyn (global), DKV Quiero cuidarme Más (España).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -513,12 +513,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar. [Vuelta 3] Sin novedades 2026 ni confirmación de la app Android en Google Play; usuarios actuales desconocidos. Nota de prensa no indica año de lanzamiento explícito. [Vuelta 4] Sin fuentes nuevas; portalinnova.cl no aparece en búsquedas. Sigue dependiendo de una sola nota de prensa. [Vuelta 5] Sin fuentes nuevas (ni entrevistas ni financiamiento); sigue dependiendo de una sola nota de prensa sin año explícito. [Vuelta 6] Sin ficha de Google Play ni fuentes nuevas; disponibilidad en Android sin confirmar. [Vuelta 7] Sin fuentes nuevas; no hay ficha oficial localizada. No confundir con apps de nombre parecido (Medika App, MEDDI, AI Medik). [Vuelta 8] Sin fuentes nuevas. [Vuelta 9] Sin fuentes nuevas.</t>
+          <t>[DIRECTO · Chile · etapas A+B] Lanzada 25-sep-2024 en App Store (Android previsto la misma semana). &gt;1.500 usuarios en los primeros días; meta 32.000 (cofundador Francisco González). Funciones: gestión de documentos, importar solicitudes, SOS con alergias/medicación, calendario de citas, recordatorios, compartir con profesionales elegidos. Sin blockchain. Precio y estado actual NO verificados; única fuente es una nota de prensa. Sitio oficial por confirmar. [Iter. 2] Hay cobertura adicional en Portal Innova (portalinnova.cl); sitio bloqueado en este entorno, estado actual sigue sin verificar. [Vuelta 3] Sin novedades 2026 ni confirmación de la app Android en Google Play; usuarios actuales desconocidos. Nota de prensa no indica año de lanzamiento explícito. [Vuelta 4] Sin fuentes nuevas; portalinnova.cl no aparece en búsquedas. Sigue dependiendo de una sola nota de prensa. [Vuelta 5] Sin fuentes nuevas (ni entrevistas ni financiamiento); sigue dependiendo de una sola nota de prensa sin año explícito. [Vuelta 6] Sin ficha de Google Play ni fuentes nuevas; disponibilidad en Android sin confirmar. [Vuelta 7] Sin fuentes nuevas; no hay ficha oficial localizada. No confundir con apps de nombre parecido (Medika App, MEDDI, AI Medik). [Vuelta 8] Sin fuentes nuevas. [Vuelta 9] Sin fuentes nuevas. [Vuelta 10] Sin novedades.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -526,7 +526,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -553,12 +553,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>[DIRECTO · Chile · etapa A] Fundada 2019 por Diego Ibarra, Andrés Fantuzzi y Gabriel Zamora. Lanzada mar-2021 en App Store y Play Store con 1.200 usuarios; planeaba nueva versión jul-2021 y ronda de US$500 mil. Objetivo: llevar el historial en el celular, acceso en emergencias, médico puede ingresar datos con consentimiento. Estado actual NO verificado (posible app inactiva). URL es la nota de prensa; sitio oficial por confirmar. [Vuelta 3] Sin evidencia posterior a 2021; relanzamiento previsto jul-2021 no confirmado. Probable app inactiva. [Vuelta 4] Sin cambios; sigue sin evidencia posterior a 2021. [Vuelta 5] Cofundador Andrés Fantuzzi es cardiólogo de la Clínica Santa María. Sin ronda de inversión ni relanzamiento confirmados; no confundir con Infomed de Cuba (portal del Minsap). [Vuelta 6] Sin búsqueda nueva (fuentes agotadas en vueltas 3-5); sin cambios. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin fuentes nuevas; relanzamiento de jul-2021 sigue sin confirmarse. [Vuelta 9] Sin fuentes nuevas.</t>
+          <t>[DIRECTO · Chile · etapa A] Fundada 2019 por Diego Ibarra, Andrés Fantuzzi y Gabriel Zamora. Lanzada mar-2021 en App Store y Play Store con 1.200 usuarios; planeaba nueva versión jul-2021 y ronda de US$500 mil. Objetivo: llevar el historial en el celular, acceso en emergencias, médico puede ingresar datos con consentimiento. Estado actual NO verificado (posible app inactiva). URL es la nota de prensa; sitio oficial por confirmar. [Vuelta 3] Sin evidencia posterior a 2021; relanzamiento previsto jul-2021 no confirmado. Probable app inactiva. [Vuelta 4] Sin cambios; sigue sin evidencia posterior a 2021. [Vuelta 5] Cofundador Andrés Fantuzzi es cardiólogo de la Clínica Santa María. Sin ronda de inversión ni relanzamiento confirmados; no confundir con Infomed de Cuba (portal del Minsap). [Vuelta 6] Sin búsqueda nueva (fuentes agotadas en vueltas 3-5); sin cambios. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin fuentes nuevas; relanzamiento de jul-2021 sigue sin confirmarse. [Vuelta 9] Sin fuentes nuevas. [Vuelta 10] Sin novedades; relanzamiento de jul-2021 sigue sin confirmarse.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -593,12 +593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · México] Historial por perfil familiar, alergias, vacunas, recetas digitales, gráficas de evolución, agendamiento, compartir con profesionales. Gratis en App Store MX. Sin evidencia de uso en Chile. Cubre parte de la etapa C (familia). [Vuelta 3] Existen dos apps distintas: MediPlanner (gratis, Rym Solutions, MX, 3,7/5 con 3 calificaciones) y MediPlanner Pro (otro desarrollador, $39 MXN). Sin presencia verificada en Chile. [Vuelta 4] No pude confirmar el desarrollador de la versión gratuita (Rym Solutions no se repite en esta búsqueda). MediPlanner Pro (fichas BR/OM) guardaría datos solo en el dispositivo, sin nube; no confundir con MedPlanner/AskHEMI (otra empresa). [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Se reconfirma en la ficha de App Store MX que el desarrollador de la versión gratuita es Rym Solutions S. de R.L. de C.V. (3,7/5, 3 calificaciones); MediPlanner Pro no menciona a esa empresa, por lo que no se puede asegurar que sea el mismo desarrollador. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin búsqueda nueva (saturado). [Vuelta 9] Sin fuentes nuevas.</t>
+          <t>[REGIONAL · México] Historial por perfil familiar, alergias, vacunas, recetas digitales, gráficas de evolución, agendamiento, compartir con profesionales. Gratis en App Store MX. Sin evidencia de uso en Chile. Cubre parte de la etapa C (familia). [Vuelta 3] Existen dos apps distintas: MediPlanner (gratis, Rym Solutions, MX, 3,7/5 con 3 calificaciones) y MediPlanner Pro (otro desarrollador, $39 MXN). Sin presencia verificada en Chile. [Vuelta 4] No pude confirmar el desarrollador de la versión gratuita (Rym Solutions no se repite en esta búsqueda). MediPlanner Pro (fichas BR/OM) guardaría datos solo en el dispositivo, sin nube; no confundir con MedPlanner/AskHEMI (otra empresa). [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Se reconfirma en la ficha de App Store MX que el desarrollador de la versión gratuita es Rym Solutions S. de R.L. de C.V. (3,7/5, 3 calificaciones); MediPlanner Pro no menciona a esa empresa, por lo que no se puede asegurar que sea el mismo desarrollador. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin búsqueda nueva (saturado). [Vuelta 9] Sin fuentes nuevas. [Vuelta 10] Sin búsqueda nueva (saturado).</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -606,7 +606,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · Argentina · débil] App para cargar antecedentes médicos propios. Única referencia: nota de opinión en grupoanimal.mx sin fecha verificada. Estado y sitio por confirmar. [Vuelta 3] Referencias de 2017 (apps4citizens, La Nación); sitio y precio no verificados; puede estar inactiva. [Vuelta 4] Sin fuentes nuevas. [Vuelta 5] Registro empresarial (indicadores.ar, datos a jul-2026) muestra CLINGOT S.A. activa en CABA, constituida el 4-abr-2016; no confirma que la app siga operando. Programa federal argentino de historias clínicas digitales como contexto regulatorio. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios. [Vuelta 7] Solo fuentes de 2017; sin evidencia nueva de operación más allá del registro societario. [Vuelta 8] Sin fuentes nuevas. [Vuelta 9] Sin fuentes nuevas.</t>
+          <t>[REGIONAL · Argentina · débil] App para cargar antecedentes médicos propios. Única referencia: nota de opinión en grupoanimal.mx sin fecha verificada. Estado y sitio por confirmar. [Vuelta 3] Referencias de 2017 (apps4citizens, La Nación); sitio y precio no verificados; puede estar inactiva. [Vuelta 4] Sin fuentes nuevas. [Vuelta 5] Registro empresarial (indicadores.ar, datos a jul-2026) muestra CLINGOT S.A. activa en CABA, constituida el 4-abr-2016; no confirma que la app siga operando. Programa federal argentino de historias clínicas digitales como contexto regulatorio. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios. [Vuelta 7] Solo fuentes de 2017; sin evidencia nueva de operación más allá del registro societario. [Vuelta 8] Sin fuentes nuevas. [Vuelta 9] Sin fuentes nuevas. [Vuelta 10] Sin búsqueda nueva (saturado).</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -9236,8 +9236,6 @@
           <t>Búsqueda de profesionales de salud</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9248,17 +9246,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2">
         <f>COUNTIF(C2:Q2,"✓")</f>
         <v/>
@@ -9280,24 +9267,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3">
         <f>COUNTIF(C3:Q3,"✓")</f>
         <v/>
@@ -9314,25 +9288,11 @@
           <t>Check-in de admisión digital</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4">
         <f>COUNTIF(C4:Q4,"✓")</f>
         <v/>
@@ -9349,25 +9309,11 @@
           <t>Integración con calendario del dispositivo</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5">
         <f>COUNTIF(C5:Q5,"✓")</f>
         <v/>
@@ -9384,25 +9330,11 @@
           <t>Localización de centros médicos y farmacias</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6">
         <f>COUNTIF(C6:Q6,"✓")</f>
         <v/>
@@ -9419,21 +9351,11 @@
           <t>Reserva de citas médicas</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9444,8 +9366,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7">
         <f>COUNTIF(C7:Q7,"✓")</f>
         <v/>
@@ -9462,25 +9382,11 @@
           <t>Acceso del profesional al historial del paciente</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8">
         <f>COUNTIF(C8:Q8,"✓")</f>
         <v/>
@@ -9497,25 +9403,11 @@
           <t>Compartir con personas sin cuenta mediante clave segura</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9">
         <f>COUNTIF(C9:Q9,"✓")</f>
         <v/>
@@ -9532,25 +9424,11 @@
           <t>Compartir datos con cuidador o persona de confianza</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10">
         <f>COUNTIF(C10:Q10,"✓")</f>
         <v/>
@@ -9572,13 +9450,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9604,16 +9480,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11">
         <f>COUNTIF(C11:Q11,"✓")</f>
         <v/>
@@ -9630,25 +9501,11 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12">
         <f>COUNTIF(C12:Q12,"✓")</f>
         <v/>
@@ -9665,25 +9522,11 @@
           <t>Ingreso de datos por profesional con consentimiento</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13">
         <f>COUNTIF(C13:Q13,"✓")</f>
         <v/>
@@ -9700,25 +9543,11 @@
           <t>Red social con profesionales y familiares</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14">
         <f>COUNTIF(C14:Q14,"✓")</f>
         <v/>
@@ -9745,23 +9574,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15">
         <f>COUNTIF(C15:Q15,"✓")</f>
         <v/>
@@ -9778,8 +9595,6 @@
           <t>Perfiles familiares / dependientes</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9790,29 +9605,21 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16">
         <f>COUNTIF(C16:Q16,"✓")</f>
         <v/>
@@ -9834,8 +9641,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>✓</t>
@@ -9851,19 +9656,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17">
         <f>COUNTIF(C17:Q17,"✓")</f>
         <v/>
@@ -9880,29 +9677,16 @@
           <t>Almacenamiento de recetas</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18">
         <f>COUNTIF(C18:Q18,"✓")</f>
         <v/>
@@ -9919,25 +9703,11 @@
           <t>Búsqueda y filtros de documentos</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19">
         <f>COUNTIF(C19:Q19,"✓")</f>
         <v/>
@@ -9954,25 +9724,11 @@
           <t>Emisión de certificados médicos</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20">
         <f>COUNTIF(C20:Q20,"✓")</f>
         <v/>
@@ -9994,19 +9750,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10028,25 +9771,11 @@
           <t>Notificación y envío de resultados</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22">
         <f>COUNTIF(C22:Q22,"✓")</f>
         <v/>
@@ -10063,25 +9792,11 @@
           <t>Recepción de documentos desde terceros</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23">
         <f>COUNTIF(C23:Q23,"✓")</f>
         <v/>
@@ -10098,29 +9813,16 @@
           <t>Historial institucional (solo datos de la propia red)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24">
         <f>COUNTIF(C24:Q24,"✓")</f>
         <v/>
@@ -10137,36 +9839,26 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10188,25 +9880,11 @@
           <t>Línea de tiempo de salud</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26">
         <f>COUNTIF(C26:Q26,"✓")</f>
         <v/>
@@ -10223,25 +9901,11 @@
           <t>Registro de alergias y vacunas</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27">
         <f>COUNTIF(C27:Q27,"✓")</f>
         <v/>
@@ -10258,25 +9922,11 @@
           <t>Seguimiento de visitas, gastos y seguros</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28">
         <f>COUNTIF(C28:Q28,"✓")</f>
         <v/>
@@ -10293,11 +9943,6 @@
           <t>Recompensas / monetización de datos del usuario</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10313,13 +9958,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29">
         <f>COUNTIF(C29:Q29,"✓")</f>
         <v/>
@@ -10336,25 +9974,11 @@
           <t>Asistente de IA para profesionales de salud</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30">
         <f>COUNTIF(C30:Q30,"✓")</f>
         <v/>
@@ -10371,25 +9995,11 @@
           <t>Coaching de salud con IA</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31">
         <f>COUNTIF(C31:Q31,"✓")</f>
         <v/>
@@ -10406,15 +10016,6 @@
           <t>Detección de patrones en métricas de salud con IA</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10425,10 +10026,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32">
         <f>COUNTIF(C32:Q32,"✓")</f>
         <v/>
@@ -10445,15 +10042,6 @@
           <t>Interpretación de exámenes con IA</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10464,9 +10052,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10488,24 +10073,11 @@
           <t>Orientación médica con IA</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10527,15 +10099,6 @@
           <t>Preparación de consultas médicas con IA</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10546,10 +10109,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35">
         <f>COUNTIF(C35:Q35,"✓")</f>
         <v/>
@@ -10566,15 +10125,6 @@
           <t>Resumen de historial con IA</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10585,10 +10135,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36">
         <f>COUNTIF(C36:Q36,"✓")</f>
         <v/>
@@ -10605,25 +10151,11 @@
           <t>API para apps de terceros</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37">
         <f>COUNTIF(C37:Q37,"✓")</f>
         <v/>
@@ -10645,10 +10177,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10659,7 +10187,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10675,14 +10202,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38">
         <f>COUNTIF(C38:Q38,"✓")</f>
         <v/>
@@ -10699,25 +10223,11 @@
           <t>Analítica poblacional B2B</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39">
         <f>COUNTIF(C39:Q39,"✓")</f>
         <v/>
@@ -10734,9 +10244,6 @@
           <t>Disponibilidad multiplataforma (web/iOS/Android)</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>✓</t>
@@ -10747,20 +10254,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40">
         <f>COUNTIF(C40:Q40,"✓")</f>
         <v/>
@@ -10777,25 +10275,11 @@
           <t>Historial médico centralizado</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41">
         <f>COUNTIF(C41:Q41,"✓")</f>
         <v/>
@@ -10812,25 +10296,11 @@
           <t>Importación y exportación de datos</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42">
         <f>COUNTIF(C42:Q42,"✓")</f>
         <v/>
@@ -10847,29 +10317,16 @@
           <t>Integración con EHR de proveedores</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43">
         <f>COUNTIF(C43:Q43,"✓")</f>
         <v/>
@@ -10886,29 +10343,16 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44">
         <f>COUNTIF(C44:Q44,"✓")</f>
         <v/>
@@ -10925,25 +10369,11 @@
           <t>Gestión de lista de medicamentos</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45">
         <f>COUNTIF(C45:Q45,"✓")</f>
         <v/>
@@ -10960,25 +10390,11 @@
           <t>Importación automática de tratamientos desde receta digital</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46">
         <f>COUNTIF(C46:Q46,"✓")</f>
         <v/>
@@ -11000,24 +10416,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47">
         <f>COUNTIF(C47:Q47,"✓")</f>
         <v/>
@@ -11034,25 +10437,11 @@
           <t>Registro de tomas y adherencia al tratamiento</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48">
         <f>COUNTIF(C48:Q48,"✓")</f>
         <v/>
@@ -11069,25 +10458,11 @@
           <t>Comunidad de pacientes</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49">
         <f>COUNTIF(C49:Q49,"✓")</f>
         <v/>
@@ -11104,25 +10479,11 @@
           <t>Contenido educativo sobre salud</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50">
         <f>COUNTIF(C50:Q50,"✓")</f>
         <v/>
@@ -11139,25 +10500,11 @@
           <t>Gráficas de evolución de indicadores</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51">
         <f>COUNTIF(C51:Q51,"✓")</f>
         <v/>
@@ -11174,25 +10521,11 @@
           <t>Integración con wearables y apps de salud</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52">
         <f>COUNTIF(C52:Q52,"✓")</f>
         <v/>
@@ -11209,11 +10542,6 @@
           <t>Panel de seguimiento de salud y bienestar</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11224,14 +10552,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
       <c r="R53">
         <f>COUNTIF(C53:Q53,"✓")</f>
         <v/>
@@ -11248,25 +10568,11 @@
           <t>Registro de nutrición</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54">
         <f>COUNTIF(C54:Q54,"✓")</f>
         <v/>
@@ -11283,25 +10589,11 @@
           <t>Seguimiento de salud femenina</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55">
         <f>COUNTIF(C55:Q55,"✓")</f>
         <v/>
@@ -11318,25 +10610,11 @@
           <t>Valoración de profesionales</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56">
         <f>COUNTIF(C56:Q56,"✓")</f>
         <v/>
@@ -11353,25 +10631,11 @@
           <t>Acceso mínimo por categorías de datos</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57">
         <f>COUNTIF(C57:Q57,"✓")</f>
         <v/>
@@ -11388,11 +10652,6 @@
           <t>Blockchain para integridad y trazabilidad de datos</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11408,13 +10667,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
       <c r="R58">
         <f>COUNTIF(C58:Q58,"✓")</f>
         <v/>
@@ -11431,29 +10683,16 @@
           <t>Cifrado y control de acceso</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
       <c r="R59">
         <f>COUNTIF(C59:Q59,"✓")</f>
         <v/>
@@ -11470,25 +10709,11 @@
           <t>Cumplimiento regulatorio de salud y datos</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
       <c r="R60">
         <f>COUNTIF(C60:Q60,"✓")</f>
         <v/>
@@ -11505,25 +10730,11 @@
           <t>Gestión de consentimiento sobre uso de datos</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
       <c r="R61">
         <f>COUNTIF(C61:Q61,"✓")</f>
         <v/>
@@ -11540,25 +10751,11 @@
           <t>Identidad descentralizada (DID)</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
       <c r="R62">
         <f>COUNTIF(C62:Q62,"✓")</f>
         <v/>
@@ -11575,15 +10772,6 @@
           <t>Privacidad reforzada para datos de salud</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11594,10 +10782,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
       <c r="R63">
         <f>COUNTIF(C63:Q63,"✓")</f>
         <v/>
@@ -11614,20 +10798,6 @@
           <t>Modelo freemium y suscripción</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11649,25 +10819,11 @@
           <t>Pagos con criptomoneda</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
       <c r="R65">
         <f>COUNTIF(C65:Q65,"✓")</f>
         <v/>
@@ -11684,24 +10840,11 @@
           <t>Pagos dentro de la app</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
           <t>✓</t>
@@ -11723,25 +10866,11 @@
           <t>Reclamos y trámites con seguros</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
       <c r="R67">
         <f>COUNTIF(C67:Q67,"✓")</f>
         <v/>
@@ -11758,25 +10887,11 @@
           <t>Mensajería paciente-institución</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
       <c r="R68">
         <f>COUNTIF(C68:Q68,"✓")</f>
         <v/>
@@ -11793,25 +10908,11 @@
           <t>Teleconsulta con profesionales</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
       <c r="R69">
         <f>COUNTIF(C69:Q69,"✓")</f>
         <v/>
@@ -11828,7 +10929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:A45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -12142,6 +11243,13 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Vuelta 10 (iter. 1, 2026-10-29 12:25 UTC): Meedika, Infomed, MediPlanner, Clingot verificados (+0 filas; saturado). Pendientes: Healfies, Patientory, MediBloc, Medicalchain, Apple Health, ChatGPT Health, Claude for Healthcare, Apps de clínicas, Clinia, MiRedSalud, Mediko.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Outputs/Benchmark_Anamnesis.xlsx
+++ b/Outputs/Benchmark_Anamnesis.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B. [Vuelta 2] Lanzada simultáneamente en Brasil, Argentina y EE.UU.; permite compartir con no registrados vía clave por email. Sin novedades posteriores a 2016. [Vuelta 3] Sin evidencia de actividad reciente ni de cierre; Gust/Dealroom la listan en Florianópolis (10 empleados, healfies.com) sin fecha de actualización. Estado sin confirmar. [Vuelta 4] Sin Google Play localizado; no confundir con la app Healfy (otro producto). Sin novedades. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios. [Vuelta 7] Solo fuentes de 2015-2016; alianza con ClinCard (feb-2016). Sin evidencia de actividad reciente. [Vuelta 8] Sin fuentes nuevas. [Vuelta 9] Sin búsqueda nueva (saturado).</t>
+          <t>[REGIONAL · Brasil] Fundada ene-2015 en Florianópolis por Helyson Lewis Velasco. Centraliza registros de salud personales: carpetas, etiquetas, línea de tiempo (medicación, exámenes, citas, dieta), compartir con familia o profesionales. Gratis; web, iOS y Android. Estado actual NO verificado (fuentes de 2015-2016). Referencia funcional cercana a etapas A+B. [Vuelta 2] Lanzada simultáneamente en Brasil, Argentina y EE.UU.; permite compartir con no registrados vía clave por email. Sin novedades posteriores a 2016. [Vuelta 3] Sin evidencia de actividad reciente ni de cierre; Gust/Dealroom la listan en Florianópolis (10 empleados, healfies.com) sin fecha de actualización. Estado sin confirmar. [Vuelta 4] Sin Google Play localizado; no confundir con la app Healfy (otro producto). Sin novedades. [Vuelta 5] Sin búsqueda nueva (revisada en vuelta 4); sin cambios. [Vuelta 6] Sin búsqueda nueva (fuentes agotadas); sin cambios. [Vuelta 7] Solo fuentes de 2015-2016; alianza con ClinCard (feb-2016). Sin evidencia de actividad reciente. [Vuelta 8] Sin fuentes nuevas. [Vuelta 9] Sin búsqueda nueva (saturado). [Vuelta 10] Sin búsqueda nueva (saturado).</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain. [Vuelta 2] Sin noticias 2026 encontradas en búsqueda; sitio oficial bloqueado. [Vuelta 3] Búsqueda adicional solo devuelve hitos de 2017 (token sale US$7,2M) y 2019 (Serie A de US$5,3M, cierre no confirmado); sin datos 2025-26 propios. [Vuelta 4] App pública lanzada en la conferencia JP Morgan Healthcare (2019); red PTOYMatrix (blockchain HIPAA); socios reportados: StartUp Health y Kaiser Permanente (beta). Estado actual en App Store/Google Play sin confirmar. [Vuelta 5] Sin noticias 2026 del equipo. Token PTOY con capitalización de ~US$53K a fines de ago-2026 según Phantom (KuCoin discrepa en la circulación): señal de baja actividad, no prueba de cierre. Esto relativiza la actividad hasta abr-2026 mencionada en la ficha original. [Vuelta 6] Sin noticias posteriores a 2020 localizadas (hitos: token sale 2017, consorcio Hyperledger, alianza con Georgia State, Series A de US$5,3M vía R/GA Ventures, Neith con Prosper Healthtech en Birmingham). Estado actual desconocido. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin noticias 2025-26; en 2018 la oferta se dirigía a empresas de salud, con la versión individual planificada después. [Vuelta 9] Sin búsqueda nueva (saturado).</t>
+          <t>[BLOCKCHAIN · EE.UU.] Atlanta, fundada 2015, ~9 empleados. Levantó US$7,2M vía financiamiento cripto. App con registros de hospitales y wearables, coaching de salud con IA y recompensas en cripto; también dashboard empresarial Neith. PitchBook indica actividad y financiamiento hasta abr-2026: sigue operando. Sin presencia conocida en Chile. Referencia directa para la hipótesis blockchain. [Vuelta 2] Sin noticias 2026 encontradas en búsqueda; sitio oficial bloqueado. [Vuelta 3] Búsqueda adicional solo devuelve hitos de 2017 (token sale US$7,2M) y 2019 (Serie A de US$5,3M, cierre no confirmado); sin datos 2025-26 propios. [Vuelta 4] App pública lanzada en la conferencia JP Morgan Healthcare (2019); red PTOYMatrix (blockchain HIPAA); socios reportados: StartUp Health y Kaiser Permanente (beta). Estado actual en App Store/Google Play sin confirmar. [Vuelta 5] Sin noticias 2026 del equipo. Token PTOY con capitalización de ~US$53K a fines de ago-2026 según Phantom (KuCoin discrepa en la circulación): señal de baja actividad, no prueba de cierre. Esto relativiza la actividad hasta abr-2026 mencionada en la ficha original. [Vuelta 6] Sin noticias posteriores a 2020 localizadas (hitos: token sale 2017, consorcio Hyperledger, alianza con Georgia State, Series A de US$5,3M vía R/GA Ventures, Neith con Prosper Healthtech en Birmingham). Estado actual desconocido. [Vuelta 7] Sin búsqueda nueva (saturado); sin cambios. [Vuelta 8] Sin noticias 2025-26; en 2018 la oferta se dirigía a empresas de salud, con la versión individual planificada después. [Vuelta 9] Sin búsqueda nueva (saturado). [Vuelta 10] Sin búsqueda nueva (saturado).</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>[BLOCKCHAIN · Corea del Sur] Fundada 2017, Seúl. Blockchain propia Panacea (Cosmos SDK, mainnet 2019) para que el paciente gestione y transfiera sus registros; app Medipass para seguros. Serie A de ₩4.000 millones (Naver); alianzas con hospitales (Seoul National, Severance). Estado 2025-26 NO verificado. Referencia sobre seguros + blockchain. [Vuelta 2] Panacea incluye DID, Append Only Log, IBC y PNFT; sin anuncios 2026 localizados. [Vuelta 3] Medipass: app en Corea con 20 hospitales/aseguradoras integrados (fecha de la lista desconocida) y plan 2022 de superapp con marketplace de datos; operación actual sin confirmar. [Vuelta 4] Sin búsqueda nueva (revisada en vuelta 3); sin cambios. [Vuelta 5] Medipass: ~400.000 usuarios acumulados (CEO, jun-2022); integración con aseguradoras Shinhan Li